--- a/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
+++ b/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="00898781"/>
+    </font>
+    <font>
       <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00D03B3B"/>
-    </font>
-    <font>
-      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -84,21 +84,23 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,185 +559,209 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>2423100</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 56.13处中性区间未超买，现价0.77高于50日均线0.695约10.8%，技术面信号可靠性尚可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>5161</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>JCY</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.0424</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>1305600</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="K2" s="3" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>3490900</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>0.55</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号可靠度中等：RSI 59.26未超买，现价高于50日均线约11.8%，技术面偏强。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7192</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>-0.0068</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>15849400</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H3" t="n">
-        <v>81.18000000000001</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，现价0.605高于50日均线0.55，RSI 57.67处中性偏上，未超买，信号可靠性尚可。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E4" s="15" t="n">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>15125500</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H4" t="n">
-        <v>37.23</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" s="14" t="inlineStr"/>
+      <c r="F4" s="5" t="n">
+        <v>15912700</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>64.93000000000001</v>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 64.93接近超买区，现价高于50日均线约27%，技术面偏强。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DNEX</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>0.0227</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>3184900</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H5" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" s="14" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1718100</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>57.04</v>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>2.878</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>现价3.14高于50日均线2.878，SAR转多信号获趋势支撑；RSI 57.04处中性偏上区间，未超买，信号可靠性较高。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -745,42 +771,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MBN</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>3055100</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>1.04</v>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>99834700</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0.28</v>
       </c>
       <c r="H6" t="n">
-        <v>58.63</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>0.158</v>
+        <v>39.06</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0.235</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="14" t="inlineStr"/>
+      <c r="M6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,42 +816,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>2802100</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0.07000000000000001</v>
+          <t>MBN</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>0.06059999999999999</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>11004500</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>3.76</v>
       </c>
       <c r="H7" t="n">
-        <v>77.29000000000001</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>0.335</v>
+        <v>61.5</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.158</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="14" t="inlineStr"/>
+      <c r="M7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -835,42 +861,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.0104</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>950700</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.01</v>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>10515700</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.29</v>
       </c>
       <c r="H8" t="n">
-        <v>70.76000000000001</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>0.776</v>
+        <v>47.56</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>0.472</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="14" t="inlineStr"/>
+      <c r="M8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -880,42 +906,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UUE</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>661300</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.12</v>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>7169600</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>1.27</v>
       </c>
       <c r="H9" t="n">
-        <v>58.98</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>0.696</v>
+        <v>59.83</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>0.652</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="14" t="inlineStr"/>
+      <c r="M9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -925,45 +951,2108 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>7120</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AXTERIA</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>6927700</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H10" t="n">
+        <v>85.94</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>6716500</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H11" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0070</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MQTECH</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>5871400</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H12" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>5428000</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H13" t="n">
+        <v>51.28</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>8176</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WAVEFRNT</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>4728600</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="H14" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ICONIC</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>4061000</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H15" t="n">
+        <v>66.55</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>3874900</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>77.29000000000001</v>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="K16" s="11" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>3849200</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>63.98</v>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="K17" s="11" t="n">
+        <v>1.822</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>3660000</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>43.64</v>
+      </c>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>3585900</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H19" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>2754200</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H20" t="n">
+        <v>31.98</v>
+      </c>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>2720600</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H21" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>2695400</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H22" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>2554800</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>2444500</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>30.47</v>
+      </c>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="16" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>2225900</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H25" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="K25" s="11" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0382</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FOODIE</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>2168000</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H26" t="n">
+        <v>61.17</v>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>2142400</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="16" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>0.0293</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>1839400</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>2.099</v>
+      </c>
+      <c r="K28" s="11" t="n">
+        <v>2.226</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="16" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>1791300</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H29" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="16" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>1759600</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H30" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="K30" s="11" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="16" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>1296700</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="K31" s="11" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>1264500</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H32" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I32" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="K32" s="11" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="16" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>1039900</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H33" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="K33" s="11" t="n">
+        <v>2.566</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="16" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>1019800</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H34" t="n">
+        <v>40.07</v>
+      </c>
+      <c r="I34" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K34" s="11" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="16" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>993800</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H35" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="n">
+        <v>1.432</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>0318</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>ELRIDGE</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>-0.0053</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>503400</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H10" t="n">
-        <v>53.74</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="n">
+      <c r="D36" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>993100</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H36" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="K36" s="11" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="16" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>984700</v>
+      </c>
+      <c r="G37" s="14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="I37" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="K37" s="11" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>982100</v>
+      </c>
+      <c r="G38" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H38" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="n">
+        <v>4.884</v>
+      </c>
+      <c r="K38" s="11" t="n">
+        <v>4.783</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E39" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>955800</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H39" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="K39" s="11" t="n">
+        <v>2.641</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="16" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AEON</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>870500</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="n">
         <v>0.944</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K40" s="11" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="16" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>821600</v>
+      </c>
+      <c r="G41" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H41" t="n">
+        <v>41.33</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="n">
+        <v>5.348</v>
+      </c>
+      <c r="K41" s="11" t="n">
+        <v>5.521</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>805100</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H42" t="n">
+        <v>51.77</v>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="K42" s="11" t="n">
         <v>0.897</v>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" s="14" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>797300</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H43" t="n">
+        <v>65.89</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="K43" s="11" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>795500</v>
+      </c>
+      <c r="G44" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H44" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="K44" s="11" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>795500</v>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H45" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="K45" s="11" t="n">
+        <v>1.733</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="16" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E46" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>786600</v>
+      </c>
+      <c r="G46" s="14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H46" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="K46" s="11" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="16" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>762700</v>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="n"/>
+      <c r="K47" s="11" t="n"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="16" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>701000</v>
+      </c>
+      <c r="G48" s="14" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H48" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="16" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>648700</v>
+      </c>
+      <c r="G49" s="14" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H49" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="I49" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="K49" s="11" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="16" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>624600</v>
+      </c>
+      <c r="G50" s="14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H50" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="I50" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="16" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>620900</v>
+      </c>
+      <c r="G51" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="K51" s="11" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="16" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>586400</v>
+      </c>
+      <c r="G52" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="K52" s="11" t="n">
+        <v>1.837</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="16" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>578000</v>
+      </c>
+      <c r="G53" s="14" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H53" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="K53" s="11" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="16" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>564900</v>
+      </c>
+      <c r="G54" s="14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="11" t="n">
+        <v>3.847</v>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>3.338</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="16" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>557800</v>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H55" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="K55" s="11" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="16" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>511300</v>
+      </c>
+      <c r="G56" s="14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H56" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K56" s="11" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
+++ b/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00898781"/>
-    </font>
-    <font>
       <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00D03B3B"/>
+    </font>
+    <font>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="4">
@@ -74,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -84,23 +84,22 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -568,19 +567,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.77</v>
+        <v>0.775</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2423100</v>
+        <v>2765400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>56.13</v>
+        <v>56.88</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -591,7 +590,7 @@
         <v>0.747</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.695</v>
+        <v>0.696</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -600,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 56.13处中性区间未超买，现价0.77高于50日均线0.695约10.8%，技术面信号可靠性尚可。</t>
+          <t>现价0.775高于50日均线0.696，SAR转多信号获均线支撑；RSI 56.88处中性区间，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -623,14 +622,14 @@
       <c r="D3" s="3" t="n">
         <v>0.605</v>
       </c>
-      <c r="E3" s="9" t="n">
+      <c r="E3" s="4" t="n">
         <v>0.0254</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>3490900</v>
+        <v>4743600</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>57.67</v>
@@ -653,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.605高于50日均线0.55，RSI 57.67处中性偏上，未超买，信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 57.67未超买，现价高于50日均线约10%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -674,19 +673,19 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.345</v>
+        <v>0.35</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>15912700</v>
+        <v>18100800</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.93000000000001</v>
+        <v>66.31</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -694,7 +693,7 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.271</v>
@@ -706,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 64.93接近超买区，现价高于50日均线约27%，技术面偏强。</t>
+          <t>SAR转多信号，RSI 66.31偏高但未超买，现价0.35高于50日均线0.271约29%，技术面信号偏强。</t>
         </is>
       </c>
     </row>
@@ -727,19 +726,19 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-0.0095</v>
+        <v>3.11</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1718100</v>
+        <v>2483400</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.04</v>
+        <v>55.53</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -747,10 +746,10 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3.021</v>
+        <v>3.018</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>2.878</v>
+        <v>2.877</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -759,7 +758,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价3.14高于50日均线2.878，SAR转多信号获趋势支撑；RSI 57.04处中性偏上区间，未超买，信号可靠性较高。</t>
+          <t>现价3.11高于50日均线2.877，SAR转多信号获均线支撑；RSI 55.53处中性区间，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -779,34 +778,34 @@
           <t>ZETRIX</t>
         </is>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>0.09</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>0.0588</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <v>99834700</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>0.28</v>
+      <c r="F6" s="12" t="n">
+        <v>113915500</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>0.32</v>
       </c>
       <c r="H6" t="n">
         <v>39.06</v>
       </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="n">
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="n">
         <v>0.097</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="10" t="n">
         <v>0.235</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="16" t="inlineStr"/>
+      <c r="M6" s="15" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -824,34 +823,34 @@
           <t>MBN</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="10" t="n">
         <v>0.175</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>0.06059999999999999</v>
       </c>
-      <c r="F7" s="13" t="n">
-        <v>11004500</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>3.76</v>
+      <c r="F7" s="12" t="n">
+        <v>11957100</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>4.09</v>
       </c>
       <c r="H7" t="n">
         <v>61.5</v>
       </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="n">
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="n">
         <v>0.161</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="10" t="n">
         <v>0.158</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="16" t="inlineStr"/>
+      <c r="M7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -861,42 +860,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>0.0227</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>10515700</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>0.29</v>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>11107900</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.48</v>
       </c>
       <c r="H8" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="K8" s="11" t="n">
-        <v>0.472</v>
+        <v>75.84999999999999</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>0.575</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="16" t="inlineStr"/>
+      <c r="M8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -906,42 +905,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0.1479</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>7169600</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>1.27</v>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>10984900</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>0.3</v>
       </c>
       <c r="H9" t="n">
-        <v>59.83</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>0.837</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>0.652</v>
+        <v>46.03</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>0.472</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="16" t="inlineStr"/>
+      <c r="M9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -951,42 +950,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0227</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>6927700</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="H10" t="n">
-        <v>85.94</v>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>0.12</v>
-      </c>
+          <t>NWEBHD</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>10463200</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="16" t="inlineStr"/>
+      <c r="M10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -996,42 +988,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.0136</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>6716500</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>0.29</v>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>10055600</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>1.01</v>
       </c>
       <c r="H11" t="n">
-        <v>75.84999999999999</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>0.575</v>
+        <v>27.43</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>0.402</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="16" t="inlineStr"/>
+      <c r="M11" s="15" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1041,42 +1033,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MQTECH</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0.09089999999999999</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>5871400</v>
-      </c>
-      <c r="G12" s="14" t="n">
-        <v>3.29</v>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>9877700</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1.75</v>
       </c>
       <c r="H12" t="n">
-        <v>62.78</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>0.056</v>
+        <v>60.04</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>0.652</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="16" t="inlineStr"/>
+      <c r="M12" s="15" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1086,42 +1078,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JAKS</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>5428000</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>0.09</v>
+          <t>AXTERIA</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>8038400</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>1.14</v>
       </c>
       <c r="H13" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>0.149</v>
+        <v>82.61</v>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>0.12</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="16" t="inlineStr"/>
+      <c r="M13" s="15" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1131,42 +1123,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WAVEFRNT</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>0.0741</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>4728600</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>6.06</v>
+          <t>LANDMRK</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>7299500</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>3.38</v>
       </c>
       <c r="H14" t="n">
-        <v>56.78</v>
-      </c>
-      <c r="I14" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="K14" s="11" t="n">
-        <v>0.141</v>
+        <v>65.04000000000001</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>0.058</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="16" t="inlineStr"/>
+      <c r="M14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1176,42 +1168,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ICONIC</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>4061000</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <v>0.91</v>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>6795600</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0.12</v>
       </c>
       <c r="H15" t="n">
-        <v>66.55</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>0.08599999999999999</v>
+        <v>53.37</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>0.149</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="16" t="inlineStr"/>
+      <c r="M15" s="15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1221,42 +1213,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>3874900</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>0.1</v>
+          <t>MQTECH</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>6779600</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>3.8</v>
       </c>
       <c r="H16" t="n">
-        <v>77.29000000000001</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="K16" s="11" t="n">
-        <v>0.335</v>
+        <v>62.78</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>0.056</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="16" t="inlineStr"/>
+      <c r="M16" s="15" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1266,42 +1258,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NATGATE</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>0.009300000000000001</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>3849200</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>0.14</v>
+          <t>ICONIC</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>6461200</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>1.44</v>
       </c>
       <c r="H17" t="n">
-        <v>63.98</v>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>2.008</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>1.822</v>
+        <v>70.39</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>0.08599999999999999</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="16" t="inlineStr"/>
+      <c r="M17" s="15" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1311,42 +1303,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CEB</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>3660000</v>
-      </c>
-      <c r="G18" s="14" t="n">
-        <v>0.32</v>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>5872900</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0.4</v>
       </c>
       <c r="H18" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="K18" s="11" t="n">
-        <v>0.279</v>
+        <v>37.29</v>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>0.597</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="16" t="inlineStr"/>
+      <c r="M18" s="15" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1356,42 +1348,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>3585900</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>0.05</v>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>5783900</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.2</v>
       </c>
       <c r="H19" t="n">
-        <v>69.77</v>
-      </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>0.879</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>0.775</v>
+        <v>64.81999999999999</v>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>1.822</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="16" t="inlineStr"/>
+      <c r="M19" s="15" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1401,42 +1393,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AAGB</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>0.0233</v>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>2754200</v>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>0.19</v>
+          <t>WAVEFRNT</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>5315200</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>6.81</v>
       </c>
       <c r="H20" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="K20" s="11" t="n">
-        <v>0.596</v>
+        <v>53.08</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>0.141</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="16" t="inlineStr"/>
+      <c r="M20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1446,42 +1438,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NOTION</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>0.0517</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>2720600</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>0.3</v>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>5122300</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="K21" s="11" t="n">
-        <v>0.617</v>
+        <v>69.77</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>0.775</v>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="16" t="inlineStr"/>
+      <c r="M21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1499,17 +1491,17 @@
           <t>CAPITALA</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="10" t="n">
         <v>0.215</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="11" t="n">
         <v>0.0488</v>
       </c>
-      <c r="F22" s="13" t="n">
-        <v>2695400</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>0.28</v>
+      <c r="F22" s="12" t="n">
+        <v>4423400</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0.45</v>
       </c>
       <c r="H22" t="n">
         <v>39.8</v>
@@ -1519,14 +1511,14 @@
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="10" t="n">
         <v>0.221</v>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K22" s="10" t="n">
         <v>0.263</v>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="16" t="inlineStr"/>
+      <c r="M22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1536,42 +1528,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CTOS</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>0.4</v>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0.505</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>-0.0476</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>2554800</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>4330600</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.11</v>
       </c>
       <c r="H23" t="n">
-        <v>35.57</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="K23" s="11" t="n">
-        <v>0.573</v>
+        <v>76.67</v>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>0.335</v>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="16" t="inlineStr"/>
+      <c r="M23" s="15" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1581,42 +1573,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MATRIX</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>0.975</v>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0.27</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>2444500</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>1.1</v>
+        <v>0</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>3764000</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0.33</v>
       </c>
       <c r="H24" t="n">
-        <v>30.47</v>
+        <v>43.64</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J24" s="11" t="n">
-        <v>1.051</v>
-      </c>
-      <c r="K24" s="11" t="n">
-        <v>1.111</v>
+      <c r="J24" s="10" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>0.279</v>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="16" t="inlineStr"/>
+      <c r="M24" s="15" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1626,42 +1618,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>QES</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>2225900</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>0.53</v>
+          <t>OGX</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>3713200</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>1.51</v>
       </c>
       <c r="H25" t="n">
-        <v>62.04</v>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="K25" s="11" t="n">
-        <v>0.586</v>
+        <v>60.46</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>0.45</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="16" t="inlineStr"/>
+      <c r="M25" s="15" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1671,42 +1663,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FOODIE</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>0.0645</v>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>2168000</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>1.46</v>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>3672600</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0.4</v>
       </c>
       <c r="H26" t="n">
-        <v>61.17</v>
-      </c>
-      <c r="I26" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K26" s="11" t="n">
-        <v>0.325</v>
+        <v>48.86</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>0.617</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="16" t="inlineStr"/>
+      <c r="M26" s="15" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1716,42 +1708,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>2142400</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>0.14</v>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>3624900</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0.53</v>
       </c>
       <c r="H27" t="n">
-        <v>50.93</v>
-      </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K27" s="11" t="n">
-        <v>0.775</v>
+        <v>58.47</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>0.37</v>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="16" t="inlineStr"/>
+      <c r="M27" s="15" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1761,42 +1753,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YTL</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>0.0293</v>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>1839400</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>0.15</v>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>-0.0357</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>3529000</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0.28</v>
       </c>
       <c r="H28" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>2.099</v>
-      </c>
-      <c r="K28" s="11" t="n">
-        <v>2.226</v>
+        <v>36.15</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>0.573</v>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="16" t="inlineStr"/>
+      <c r="M28" s="15" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1806,42 +1798,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MBSB</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>1791300</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>0.49</v>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>3486500</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.45</v>
       </c>
       <c r="H29" t="n">
-        <v>37.91</v>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="K29" s="11" t="n">
-        <v>0.556</v>
+        <v>34.14</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>1.479</v>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="16" t="inlineStr"/>
+      <c r="M29" s="15" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1851,42 +1843,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>0.0556</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>1759600</v>
-      </c>
-      <c r="G30" s="14" t="n">
-        <v>0.35</v>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>3427500</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.82</v>
       </c>
       <c r="H30" t="n">
-        <v>71.14</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="n">
-        <v>1.129</v>
-      </c>
-      <c r="K30" s="11" t="n">
-        <v>0.988</v>
+        <v>63.39</v>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>0.587</v>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="16" t="inlineStr"/>
+      <c r="M30" s="15" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1896,42 +1888,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>0.007800000000000001</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>1296700</v>
-      </c>
-      <c r="G31" s="14" t="n">
+          <t>AQUAWALK</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>3422300</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H31" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="n">
         <v>0.13</v>
       </c>
-      <c r="H31" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="K31" s="11" t="n">
-        <v>0.619</v>
+      <c r="K31" s="10" t="n">
+        <v>0.14</v>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="16" t="inlineStr"/>
+      <c r="M31" s="15" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1941,42 +1933,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E32" s="19" t="n">
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E32" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="13" t="n">
-        <v>1264500</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <v>1.45</v>
+      <c r="F32" s="12" t="n">
+        <v>3416000</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.22</v>
       </c>
       <c r="H32" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="K32" s="11" t="n">
-        <v>0.268</v>
+        <v>54.27</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="K32" s="10" t="n">
+        <v>0.8149999999999999</v>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="16" t="inlineStr"/>
+      <c r="M32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1986,42 +1978,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INARI</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>0.007800000000000001</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>1039900</v>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>0.06</v>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>3300000</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.23</v>
       </c>
       <c r="H33" t="n">
-        <v>49.34</v>
-      </c>
-      <c r="I33" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="n">
-        <v>2.591</v>
-      </c>
-      <c r="K33" s="11" t="n">
-        <v>2.566</v>
+        <v>39.52</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K33" s="10" t="n">
+        <v>1.838</v>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="16" t="inlineStr"/>
+      <c r="M33" s="15" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2031,42 +2023,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CBHB</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>0.0054</v>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>1019800</v>
-      </c>
-      <c r="G34" s="14" t="n">
-        <v>0.09</v>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>3298500</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.17</v>
       </c>
       <c r="H34" t="n">
-        <v>40.07</v>
+        <v>54.46</v>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J34" s="11" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="K34" s="11" t="n">
-        <v>0.988</v>
-      </c>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="10" t="n"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="16" t="inlineStr"/>
+      <c r="M34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2076,42 +2064,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>1.39</v>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>0.535</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>993800</v>
-      </c>
-      <c r="G35" s="14" t="n">
-        <v>0.27</v>
+        <v>0</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>3202300</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0.77</v>
       </c>
       <c r="H35" t="n">
-        <v>36.45</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="n">
-        <v>1.432</v>
-      </c>
-      <c r="K35" s="11" t="n">
-        <v>1.454</v>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="K35" s="10" t="n">
+        <v>0.44</v>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="16" t="inlineStr"/>
+      <c r="M35" s="15" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2121,42 +2109,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>-0.0105</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>993100</v>
-      </c>
-      <c r="G36" s="14" t="n">
-        <v>0.23</v>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>3159400</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0.2</v>
       </c>
       <c r="H36" t="n">
-        <v>51.97</v>
-      </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J36" s="11" t="n">
-        <v>0.9429999999999999</v>
-      </c>
-      <c r="K36" s="11" t="n">
-        <v>0.897</v>
+        <v>50.93</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K36" s="10" t="n">
+        <v>0.775</v>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="16" t="inlineStr"/>
+      <c r="M36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2166,42 +2154,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GENM</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>0.0174</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>984700</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>0.13</v>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>2862400</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.24</v>
       </c>
       <c r="H37" t="n">
-        <v>29.12</v>
-      </c>
-      <c r="I37" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="n">
-        <v>1.277</v>
-      </c>
-      <c r="K37" s="11" t="n">
-        <v>1.478</v>
+        <v>50.85</v>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>2.101</v>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>2.226</v>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="16" t="inlineStr"/>
+      <c r="M37" s="15" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2211,42 +2199,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>0.004099999999999999</v>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>982100</v>
-      </c>
-      <c r="G38" s="14" t="n">
-        <v>0.04</v>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>2721000</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>1.23</v>
       </c>
       <c r="H38" t="n">
-        <v>54.41</v>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J38" s="11" t="n">
-        <v>4.884</v>
-      </c>
-      <c r="K38" s="11" t="n">
-        <v>4.783</v>
+        <v>31.1</v>
+      </c>
+      <c r="I38" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="K38" s="10" t="n">
+        <v>1.112</v>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="16" t="inlineStr"/>
+      <c r="M38" s="15" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2256,42 +2244,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E39" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>955800</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>0.3</v>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>2705200</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.54</v>
       </c>
       <c r="H39" t="n">
-        <v>89.59</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="n">
-        <v>3.119</v>
-      </c>
-      <c r="K39" s="11" t="n">
-        <v>2.641</v>
+        <v>70.65000000000001</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="K39" s="10" t="n">
+        <v>0.987</v>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="16" t="inlineStr"/>
+      <c r="M39" s="15" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2301,42 +2289,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AEON</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>0.005500000000000001</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>870500</v>
-      </c>
-      <c r="G40" s="14" t="n">
-        <v>1.1</v>
+          <t>FOODIE</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>0.0806</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>2644400</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>1.78</v>
       </c>
       <c r="H40" t="n">
-        <v>36.99</v>
-      </c>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J40" s="11" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="K40" s="11" t="n">
-        <v>0.968</v>
+        <v>62.67</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="K40" s="10" t="n">
+        <v>0.326</v>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="16" t="inlineStr"/>
+      <c r="M40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2346,42 +2334,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>0.0098</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>821600</v>
-      </c>
-      <c r="G41" s="14" t="n">
-        <v>0.05</v>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>2465000</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.24</v>
       </c>
       <c r="H41" t="n">
-        <v>41.33</v>
-      </c>
-      <c r="I41" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="n">
-        <v>5.348</v>
-      </c>
-      <c r="K41" s="11" t="n">
-        <v>5.521</v>
+        <v>63.72</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>0.619</v>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="16" t="inlineStr"/>
+      <c r="M41" s="15" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2391,42 +2379,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VLB</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>805100</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>0.42</v>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>2361700</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0.63</v>
       </c>
       <c r="H42" t="n">
-        <v>51.77</v>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="K42" s="11" t="n">
-        <v>0.897</v>
+        <v>34.63</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>1.432</v>
+      </c>
+      <c r="K42" s="10" t="n">
+        <v>1.453</v>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="16" t="inlineStr"/>
+      <c r="M42" s="15" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2436,42 +2424,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HARTA</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E43" s="19" t="n">
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E43" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="13" t="n">
-        <v>797300</v>
-      </c>
-      <c r="G43" s="14" t="n">
-        <v>0.08</v>
+      <c r="F43" s="12" t="n">
+        <v>2068700</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0.23</v>
       </c>
       <c r="H43" t="n">
-        <v>65.89</v>
-      </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="n">
-        <v>1.116</v>
-      </c>
-      <c r="K43" s="11" t="n">
-        <v>1.065</v>
+        <v>36.57</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>4.642</v>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="16" t="inlineStr"/>
+      <c r="M43" s="15" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2481,42 +2469,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E44" s="19" t="n">
+          <t>M&amp;G</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E44" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="13" t="n">
-        <v>795500</v>
-      </c>
-      <c r="G44" s="14" t="n">
-        <v>0.25</v>
+      <c r="F44" s="12" t="n">
+        <v>1960000</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>0.1</v>
       </c>
       <c r="H44" t="n">
-        <v>42.37</v>
-      </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="K44" s="11" t="n">
-        <v>0.731</v>
+        <v>47.46</v>
+      </c>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>0.303</v>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="16" t="inlineStr"/>
+      <c r="M44" s="15" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2526,42 +2514,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EG</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>795500</v>
-      </c>
-      <c r="G45" s="14" t="n">
-        <v>0.13</v>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>1852500</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0.18</v>
       </c>
       <c r="H45" t="n">
-        <v>40.79</v>
-      </c>
-      <c r="I45" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J45" s="11" t="n">
-        <v>1.643</v>
-      </c>
-      <c r="K45" s="11" t="n">
-        <v>1.733</v>
+        <v>49.08</v>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>2.106</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>2.113</v>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="16" t="inlineStr"/>
+      <c r="M45" s="15" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2571,42 +2559,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SDCG</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>786600</v>
-      </c>
-      <c r="G46" s="14" t="n">
-        <v>0.16</v>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>1852400</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.51</v>
       </c>
       <c r="H46" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="K46" s="11" t="n">
-        <v>0.782</v>
+        <v>34.49</v>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>0.556</v>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="16" t="inlineStr"/>
+      <c r="M46" s="15" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2616,35 +2604,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E47" s="12" t="n">
-        <v>0.0211</v>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>762700</v>
-      </c>
-      <c r="G47" s="14" t="n">
-        <v>0.03</v>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>1795200</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H47" t="n">
+        <v>40.07</v>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J47" s="11" t="n"/>
-      <c r="K47" s="11" t="n"/>
+      <c r="J47" s="10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>0.988</v>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" s="16" t="inlineStr"/>
+      <c r="M47" s="15" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2654,42 +2649,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="13" t="n">
-        <v>701000</v>
-      </c>
-      <c r="G48" s="14" t="n">
-        <v>0.34</v>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>1668100</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>0.16</v>
       </c>
       <c r="H48" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J48" s="11" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="K48" s="11" t="n">
-        <v>0.63</v>
+        <v>64.23999999999999</v>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="K48" s="10" t="n">
+        <v>1.065</v>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="16" t="inlineStr"/>
+      <c r="M48" s="15" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2699,42 +2694,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CORAZA</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E49" s="12" t="n">
-        <v>0.0074</v>
-      </c>
-      <c r="F49" s="13" t="n">
-        <v>648700</v>
-      </c>
-      <c r="G49" s="14" t="n">
-        <v>0.24</v>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>1662600</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.34</v>
       </c>
       <c r="H49" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="I49" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="n">
-        <v>1.284</v>
-      </c>
-      <c r="K49" s="11" t="n">
-        <v>1.193</v>
+        <v>72.53</v>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="K49" s="10" t="n">
+        <v>0.782</v>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="16" t="inlineStr"/>
+      <c r="M49" s="15" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2744,42 +2739,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E50" s="19" t="n">
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E50" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="13" t="n">
-        <v>624600</v>
-      </c>
-      <c r="G50" s="14" t="n">
-        <v>0.08</v>
+      <c r="F50" s="12" t="n">
+        <v>1390600</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>51.94</v>
+        <v>65.62</v>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J50" s="11" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="K50" s="11" t="n">
-        <v>0.771</v>
+      <c r="J50" s="10" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="K50" s="10" t="n">
+        <v>0.394</v>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="16" t="inlineStr"/>
+      <c r="M50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2789,42 +2784,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="13" t="n">
-        <v>620900</v>
-      </c>
-      <c r="G51" s="14" t="n">
-        <v>0.05</v>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>1367100</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0.08</v>
       </c>
       <c r="H51" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J51" s="11" t="n">
-        <v>9.994</v>
-      </c>
-      <c r="K51" s="11" t="n">
-        <v>10.1</v>
+        <v>42.14</v>
+      </c>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="K51" s="10" t="n">
+        <v>5.521</v>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" s="16" t="inlineStr"/>
+      <c r="M51" s="15" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2834,42 +2829,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GENTING</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>0.0138</v>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>586400</v>
-      </c>
-      <c r="G52" s="14" t="n">
-        <v>0.04</v>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>1355100</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>0.42</v>
       </c>
       <c r="H52" t="n">
-        <v>34.96</v>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J52" s="11" t="n">
-        <v>1.557</v>
-      </c>
-      <c r="K52" s="11" t="n">
-        <v>1.837</v>
+        <v>89.59</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>3.119</v>
+      </c>
+      <c r="K52" s="10" t="n">
+        <v>2.641</v>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" s="16" t="inlineStr"/>
+      <c r="M52" s="15" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2879,42 +2874,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>XL</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E53" s="19" t="n">
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E53" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="13" t="n">
-        <v>578000</v>
-      </c>
-      <c r="G53" s="14" t="n">
-        <v>0.04</v>
+      <c r="F53" s="12" t="n">
+        <v>1323400</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>0.11</v>
       </c>
       <c r="H53" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="K53" s="11" t="n">
-        <v>0.8149999999999999</v>
+        <v>48.07</v>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>9.994</v>
+      </c>
+      <c r="K53" s="10" t="n">
+        <v>10.1</v>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" s="16" t="inlineStr"/>
+      <c r="M53" s="15" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2924,42 +2919,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="n">
-        <v>4.05</v>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>2.56</v>
       </c>
       <c r="E54" s="18" t="n">
-        <v>-0.0146</v>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>564900</v>
-      </c>
-      <c r="G54" s="14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>1299700</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>0.08</v>
       </c>
       <c r="H54" t="n">
-        <v>60.99</v>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J54" s="11" t="n">
-        <v>3.847</v>
-      </c>
-      <c r="K54" s="11" t="n">
-        <v>3.338</v>
+        <v>47.97</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>2.589</v>
+      </c>
+      <c r="K54" s="10" t="n">
+        <v>2.566</v>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="16" t="inlineStr"/>
+      <c r="M54" s="15" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2969,42 +2964,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DAYANG</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E55" s="12" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>557800</v>
-      </c>
-      <c r="G55" s="14" t="n">
-        <v>0.22</v>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>1288000</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0.06</v>
       </c>
       <c r="H55" t="n">
-        <v>45.72</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J55" s="11" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="K55" s="11" t="n">
-        <v>1.431</v>
+        <v>46.13</v>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="K55" s="10" t="n">
+        <v>0.868</v>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="16" t="inlineStr"/>
+      <c r="M55" s="15" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3014,45 +3009,1613 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>1278700</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H56" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="K56" s="10" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="15" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>1264500</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H57" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="K57" s="10" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="15" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>0.005600000000000001</v>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>1213400</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H58" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="K58" s="10" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="15" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>1205000</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H59" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="K59" s="10" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="15" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>1181100</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H60" t="n">
+        <v>54.41</v>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>4.884</v>
+      </c>
+      <c r="K60" s="10" t="n">
+        <v>4.783</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="15" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>1154800</v>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H61" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="K61" s="10" t="n">
+        <v>1.733</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="15" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DXN</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E62" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>1118100</v>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H62" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="K62" s="10" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="15" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>1117400</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="15" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>1062000</v>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H64" t="n">
+        <v>45.16</v>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K64" s="10" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="15" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>1059700</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H65" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="K65" s="10" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="15" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>1051700</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H66" t="n">
+        <v>53.61</v>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K66" s="10" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="15" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>6599</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AEON</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>906000</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H67" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="K67" s="10" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="15" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>879600</v>
+      </c>
+      <c r="G68" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H68" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="K68" s="10" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="15" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>878300</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H69" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="K69" s="10" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="15" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>876800</v>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H70" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>3.848</v>
+      </c>
+      <c r="K70" s="10" t="n">
+        <v>3.338</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="15" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>0045</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>SSB8</t>
         </is>
       </c>
-      <c r="D56" s="11" t="n">
+      <c r="D71" s="10" t="n">
         <v>0.63</v>
       </c>
-      <c r="E56" s="18" t="n">
+      <c r="E71" s="16" t="n">
         <v>-0.007900000000000001</v>
       </c>
-      <c r="F56" s="13" t="n">
-        <v>511300</v>
-      </c>
-      <c r="G56" s="14" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H56" t="n">
+      <c r="F71" s="12" t="n">
+        <v>820500</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H71" t="n">
         <v>49.5</v>
       </c>
-      <c r="I56" s="17" t="inlineStr">
+      <c r="I71" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J56" s="11" t="n">
+      <c r="J71" s="10" t="n">
         <v>0.633</v>
       </c>
-      <c r="K56" s="11" t="n">
+      <c r="K71" s="10" t="n">
         <v>0.624</v>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" s="16" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="15" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>0.0444</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>777900</v>
+      </c>
+      <c r="G72" s="13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H72" t="n">
+        <v>59.57</v>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="K72" s="10" t="n">
+        <v>1.253</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="15" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>720300</v>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H73" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="K73" s="10" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="15" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>718200</v>
+      </c>
+      <c r="G74" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H74" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>6.402</v>
+      </c>
+      <c r="K74" s="10" t="n">
+        <v>6.046</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="15" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>709900</v>
+      </c>
+      <c r="G75" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H75" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="K75" s="10" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="15" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>701000</v>
+      </c>
+      <c r="G76" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H76" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K76" s="10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="15" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>683400</v>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H77" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="K77" s="10" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="15" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>663900</v>
+      </c>
+      <c r="G78" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="I78" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="K78" s="10" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="15" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>654700</v>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H79" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="I79" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K79" s="10" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="15" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>638200</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H80" t="n">
+        <v>44.69</v>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>2.633</v>
+      </c>
+      <c r="K80" s="10" t="n">
+        <v>2.817</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="15" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>622600</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H81" t="n">
+        <v>39.48</v>
+      </c>
+      <c r="I81" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="K81" s="10" t="n">
+        <v>1.278</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="15" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>622400</v>
+      </c>
+      <c r="G82" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H82" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K82" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="15" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>611500</v>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H83" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="I83" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="K83" s="10" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="15" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>597200</v>
+      </c>
+      <c r="G84" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H84" t="n">
+        <v>34.59</v>
+      </c>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="K84" s="10" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="15" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>583300</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H85" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="I85" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="K85" s="10" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="15" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>571200</v>
+      </c>
+      <c r="G86" s="13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H86" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="K86" s="10" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="15" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>565500</v>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H87" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="K87" s="10" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="15" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>560300</v>
+      </c>
+      <c r="G88" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H88" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>4.731</v>
+      </c>
+      <c r="K88" s="10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="15" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>554100</v>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H89" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="K89" s="10" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="15" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>537400</v>
+      </c>
+      <c r="G90" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H90" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>2.128</v>
+      </c>
+      <c r="K90" s="10" t="n">
+        <v>2.084</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="15" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>523000</v>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H91" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="I91" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="K91" s="10" t="n">
+        <v>2.221</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M56"/>
+  <autoFilter ref="A1:M91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
+++ b/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,8 +97,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.775</v>
+        <v>0.78</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2765400</v>
+        <v>3281400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>56.88</v>
+        <v>57.6</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.696</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.775高于50日均线0.696，SAR转多信号获均线支撑；RSI 56.88处中性区间，未超买，信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 57.6处中性偏上，未超买；现价0.78高于50日均线0.696约12%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0254</v>
+        <v>0.0169</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>4743600</v>
+        <v>4857600</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>57.67</v>
+        <v>56.83</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.574</v>
+        <v>0.573</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.55</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.67未超买，现价高于50日均线约10%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，现价0.6高于50日均线0.55，RSI 56.83处中性区间未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -664,28 +664,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0145</v>
+        <v>0.0313</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>18100800</v>
+        <v>1102700</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.31</v>
+        <v>57.68</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.322</v>
+        <v>0.317</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.271</v>
+        <v>0.329</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 66.31偏高但未超买，现价0.35高于50日均线0.271约29%，技术面信号偏强。</t>
+          <t>SAR转多信号，RSI 57.68处中性偏上，未超买；现价0.33略高于50日均线0.329，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -717,95 +717,103 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>20615300</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，现价0.355高于50日均线0.271约31%，RSI 67.58接近超买区，信号可靠性中等。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>7233</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>DUFU</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>3.11</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E6" s="9" t="n">
         <v>-0.0189</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>2483400</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H5" s="2" t="n">
+      <c r="F6" s="5" t="n">
+        <v>2951900</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>55.53</v>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>3.018</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>2.877</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>现价3.11高于50日均线2.877，SAR转多信号获均线支撑；RSI 55.53处中性区间，未超买，信号可靠性尚可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>113915500</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>39.06</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="15" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 55.53处中性区间，现价高于50日均线约8.1%，技术面信号较为可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -815,28 +823,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.175</v>
+        <v>0.09</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.0588</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>11957100</v>
+        <v>150349900</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>4.09</v>
+        <v>0.42</v>
       </c>
       <c r="H7" t="n">
-        <v>61.5</v>
+        <v>39.06</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -844,10 +852,10 @@
         </is>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0.161</v>
+        <v>0.097</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>0.158</v>
+        <v>0.235</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="15" t="inlineStr"/>
@@ -860,28 +868,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>LANDMRK</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0136</v>
+        <v>0.06</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0.5</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>11107900</v>
+        <v>16910500</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.48</v>
+        <v>7.83</v>
       </c>
       <c r="H8" t="n">
-        <v>75.84999999999999</v>
+        <v>60.21</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -889,10 +897,10 @@
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.673</v>
+        <v>0.044</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0.575</v>
+        <v>0.058</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
@@ -905,40 +913,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.445</v>
+        <v>0.195</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.0114</v>
+        <v>0.0541</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>10984900</v>
+        <v>15328000</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>46.03</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>0.472</v>
-      </c>
+        <v>0.58</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="15" t="inlineStr"/>
     </row>
@@ -950,33 +951,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.195</v>
+        <v>0.97</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.0541</v>
+        <v>0.0052</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>10463200</v>
+        <v>13196500</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
+        <v>0.17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>0.776</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="15" t="inlineStr"/>
     </row>
@@ -988,39 +996,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0132</v>
+        <v>0.725</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.0136</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>10055600</v>
+        <v>12695000</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1.01</v>
+        <v>0.54</v>
       </c>
       <c r="H11" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.84999999999999</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.387</v>
+        <v>0.673</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>0.402</v>
+        <v>0.575</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
@@ -1033,39 +1041,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>0.1538</v>
+        <v>0.375</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>9877700</v>
+        <v>12264200</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="H12" t="n">
-        <v>60.04</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
+        <v>27.43</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.837</v>
+        <v>0.387</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>0.652</v>
+        <v>0.402</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
@@ -1078,28 +1086,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0455</v>
+        <v>0.18</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>8038400</v>
+        <v>12047500</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1.14</v>
+        <v>4.12</v>
       </c>
       <c r="H13" t="n">
-        <v>82.61</v>
+        <v>63.99</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1107,10 +1115,10 @@
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.137</v>
+        <v>0.162</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>0.12</v>
+        <v>0.158</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="15" t="inlineStr"/>
@@ -1123,28 +1131,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LANDMRK</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>7299500</v>
+        <v>11704600</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>3.38</v>
+        <v>0.3</v>
       </c>
       <c r="H14" t="n">
-        <v>65.04000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1152,10 +1160,10 @@
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.045</v>
+        <v>0.435</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>0.058</v>
+        <v>0.335</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
@@ -1168,28 +1176,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.165</v>
+        <v>0.45</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.0313</v>
+        <v>0.0227</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>6795600</v>
+        <v>11535500</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="H15" t="n">
-        <v>53.37</v>
+        <v>47.56</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1197,10 +1205,10 @@
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.16</v>
+        <v>0.453</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>0.149</v>
+        <v>0.472</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
@@ -1213,39 +1221,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MQTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.06</v>
+        <v>0.985</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1657</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>6779600</v>
+        <v>10422900</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="H16" t="n">
-        <v>62.78</v>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.46</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.053</v>
+        <v>0.838</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.056</v>
+        <v>0.652</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1258,28 +1266,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>0.0455</v>
+        <v>0.21</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>6461200</v>
+        <v>9510500</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="H17" t="n">
-        <v>70.39</v>
+        <v>82.61</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
@@ -1287,10 +1295,10 @@
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.102</v>
+        <v>0.137</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="15" t="inlineStr"/>
@@ -1312,19 +1320,19 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.455</v>
+        <v>0.465</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.0581</v>
+        <v>0.0814</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>5872900</v>
+        <v>8702700</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="H18" t="n">
-        <v>37.29</v>
+        <v>40.39</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -1332,7 +1340,7 @@
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="K18" s="10" t="n">
         <v>0.597</v>
@@ -1348,39 +1356,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>2.2</v>
+        <v>0.165</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0185</v>
+        <v>0.0313</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>5783900</v>
+        <v>7840100</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H19" t="n">
-        <v>64.81999999999999</v>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.37</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>2.01</v>
+        <v>0.16</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>1.822</v>
+        <v>0.149</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="15" t="inlineStr"/>
@@ -1393,28 +1401,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WAVEFRNT</t>
+          <t>MQTECH</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>5315200</v>
+        <v>7708100</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>6.81</v>
+        <v>4.32</v>
       </c>
       <c r="H20" t="n">
-        <v>53.08</v>
+        <v>62.78</v>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
@@ -1422,10 +1430,10 @@
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.136</v>
+        <v>0.053</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.141</v>
+        <v>0.056</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
@@ -1438,39 +1446,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0.09759999999999999</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>5122300</v>
+        <v>7022400</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H21" t="n">
-        <v>69.77</v>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.67</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.879</v>
+        <v>0.222</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.775</v>
+        <v>0.263</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="15" t="inlineStr"/>
@@ -1483,39 +1491,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.215</v>
+        <v>2.18</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.0488</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>4423400</v>
+        <v>6728200</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.45</v>
+        <v>0.24</v>
       </c>
       <c r="H22" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
+        <v>63.98</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.221</v>
+        <v>2.008</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0.263</v>
+        <v>1.822</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
@@ -1528,28 +1536,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>WAVEFRNT</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>0</v>
+        <v>0.14</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>4330600</v>
+        <v>6668400</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.11</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>76.67</v>
+        <v>53.08</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -1557,10 +1565,10 @@
         </is>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.435</v>
+        <v>0.136</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0.335</v>
+        <v>0.141</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="15" t="inlineStr"/>
@@ -1573,39 +1581,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>0</v>
+        <v>0.115</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3764000</v>
+        <v>6461200</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.33</v>
+        <v>1.44</v>
       </c>
       <c r="H24" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.39</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.283</v>
+        <v>0.102</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.279</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1618,39 +1626,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>HBGLOB</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>0.0213</v>
+        <v>0.015</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>-0.5</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>3713200</v>
+        <v>5268000</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1.51</v>
+        <v>24.7</v>
       </c>
       <c r="H25" t="n">
-        <v>60.46</v>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>11.69</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.456</v>
+        <v>0.029</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0.45</v>
+        <v>0.031</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1663,39 +1671,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>0.0431</v>
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.0476</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>3672600</v>
+        <v>5025600</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H26" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.57</v>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.606</v>
+        <v>0.458</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.617</v>
+        <v>0.573</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1708,28 +1716,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>0.0133</v>
+        <v>0.82</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>3624900</v>
+        <v>5004100</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="H27" t="n">
-        <v>58.47</v>
+        <v>54.27</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
@@ -1737,10 +1745,10 @@
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.373</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0.37</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="15" t="inlineStr"/>
@@ -1753,39 +1761,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>-0.0357</v>
+        <v>0.27</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>3529000</v>
+        <v>4945700</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.28</v>
+        <v>0.44</v>
       </c>
       <c r="H28" t="n">
-        <v>36.15</v>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.64</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.458</v>
+        <v>0.283</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0.573</v>
+        <v>0.279</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="15" t="inlineStr"/>
@@ -1798,28 +1806,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>1.2</v>
+        <v>0.38</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0.0435</v>
+        <v>0.0133</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>3486500</v>
+        <v>4900400</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.45</v>
+        <v>0.72</v>
       </c>
       <c r="H29" t="n">
-        <v>34.14</v>
+        <v>58.47</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -1827,10 +1835,10 @@
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>1.279</v>
+        <v>0.373</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>1.479</v>
+        <v>0.37</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr"/>
@@ -1843,28 +1851,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.0469</v>
+        <v>0.0609</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>3427500</v>
+        <v>4843700</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="H30" t="n">
-        <v>63.39</v>
+        <v>37.11</v>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
@@ -1872,10 +1880,10 @@
         </is>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.604</v>
+        <v>1.281</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>0.587</v>
+        <v>1.479</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="15" t="inlineStr"/>
@@ -1888,39 +1896,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>3422300</v>
+        <v>4829500</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>1.52</v>
+        <v>0.31</v>
       </c>
       <c r="H31" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.93</v>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.13</v>
+        <v>0.774</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0.14</v>
+        <v>0.775</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="15" t="inlineStr"/>
@@ -1933,39 +1941,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.82</v>
+        <v>0.125</v>
       </c>
       <c r="E32" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>3416000</v>
+        <v>4539500</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.22</v>
+        <v>2.01</v>
       </c>
       <c r="H32" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.46</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="15" t="inlineStr"/>
@@ -1978,39 +1986,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>1.51</v>
+        <v>0.595</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0.0414</v>
+        <v>0.0259</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>3300000</v>
+        <v>4391100</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.23</v>
+        <v>0.48</v>
       </c>
       <c r="H33" t="n">
-        <v>39.52</v>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.11</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1.56</v>
+        <v>0.605</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>1.838</v>
+        <v>0.617</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2023,36 +2031,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>0.0222</v>
+        <v>0.305</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>3298500</v>
+        <v>4212000</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H34" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I34" s="17" t="inlineStr">
+        <v>47.46</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
+      <c r="J34" s="10" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K34" s="10" t="n">
+        <v>0.303</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="15" t="inlineStr"/>
     </row>
@@ -2064,28 +2076,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>0</v>
+        <v>1.51</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>0.0414</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>3202300</v>
+        <v>4096700</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.77</v>
+        <v>0.29</v>
       </c>
       <c r="H35" t="n">
-        <v>83.09999999999999</v>
+        <v>39.52</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2093,10 +2105,10 @@
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.466</v>
+        <v>1.56</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.44</v>
+        <v>1.838</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2109,28 +2121,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.775</v>
+        <v>0.48</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0213</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>3159400</v>
+        <v>4031100</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.2</v>
+        <v>1.64</v>
       </c>
       <c r="H36" t="n">
-        <v>50.93</v>
+        <v>60.46</v>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
@@ -2138,10 +2150,10 @@
         </is>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.774</v>
+        <v>0.456</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.775</v>
+        <v>0.45</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr"/>
@@ -2154,28 +2166,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>2.13</v>
+        <v>1.66</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.039</v>
+        <v>0.0641</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>2862400</v>
+        <v>3976300</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="H37" t="n">
-        <v>50.85</v>
+        <v>48.96</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2183,10 +2195,10 @@
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>2.101</v>
+        <v>1.65</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>2.226</v>
+        <v>1.734</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="15" t="inlineStr"/>
@@ -2199,39 +2211,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.98</v>
+        <v>0.865</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>2721000</v>
+        <v>3960300</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>1.23</v>
+        <v>0.19</v>
       </c>
       <c r="H38" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.051</v>
+        <v>0.867</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>1.112</v>
+        <v>0.868</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2244,28 +2256,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1.32</v>
+        <v>2.13</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.0476</v>
+        <v>0.039</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>2705200</v>
+        <v>3898500</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.54</v>
+        <v>0.32</v>
       </c>
       <c r="H39" t="n">
-        <v>70.65000000000001</v>
+        <v>50.85</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2273,10 +2285,10 @@
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.128</v>
+        <v>2.101</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>0.987</v>
+        <v>2.226</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2289,28 +2301,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.335</v>
+        <v>0.665</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0806</v>
+        <v>0.0391</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>2644400</v>
+        <v>3686100</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1.78</v>
+        <v>0.88</v>
       </c>
       <c r="H40" t="n">
-        <v>62.67</v>
+        <v>62.73</v>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
@@ -2318,10 +2330,10 @@
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.301</v>
+        <v>0.604</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.326</v>
+        <v>0.586</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2334,40 +2346,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>2465000</v>
+        <v>3561400</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="H41" t="n">
-        <v>63.72</v>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="K41" s="10" t="n">
-        <v>0.619</v>
-      </c>
+        <v>54.46</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
     </row>
@@ -2379,39 +2387,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>-0.035</v>
+        <v>0.535</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>2361700</v>
+        <v>3534600</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.63</v>
+        <v>0.85</v>
       </c>
       <c r="H42" t="n">
-        <v>34.63</v>
-      </c>
-      <c r="I42" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1.432</v>
+        <v>0.466</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>1.453</v>
+        <v>0.44</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
@@ -2424,39 +2432,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>4.45</v>
+        <v>0.64</v>
       </c>
       <c r="E43" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>2068700</v>
+        <v>3462700</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.23</v>
+        <v>0.34</v>
       </c>
       <c r="H43" t="n">
-        <v>36.57</v>
-      </c>
-      <c r="I43" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.72</v>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>4.54</v>
+        <v>0.627</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>4.642</v>
+        <v>0.619</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2469,39 +2477,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>0</v>
+        <v>0.985</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1960000</v>
+        <v>3378800</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.1</v>
+        <v>1.52</v>
       </c>
       <c r="H44" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="I44" s="17" t="inlineStr">
+        <v>32.49</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.307</v>
+        <v>1.052</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>0.303</v>
+        <v>1.112</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2514,28 +2522,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>-0.009399999999999999</v>
+        <v>1.32</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>1852500</v>
+        <v>3305600</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.18</v>
+        <v>0.66</v>
       </c>
       <c r="H45" t="n">
-        <v>49.08</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
@@ -2543,10 +2551,10 @@
         </is>
       </c>
       <c r="J45" s="10" t="n">
-        <v>2.106</v>
+        <v>1.128</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>2.113</v>
+        <v>0.987</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="15" t="inlineStr"/>
@@ -2559,39 +2567,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>0.0202</v>
+        <v>0.48</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>1852400</v>
+        <v>3204500</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.51</v>
+        <v>0.15</v>
       </c>
       <c r="H46" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I46" s="17" t="inlineStr">
+        <v>63.86</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.524</v>
+        <v>0.443</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>0.556</v>
+        <v>0.394</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2604,39 +2612,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>0.0054</v>
+        <v>1.36</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>-0.049</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>1795200</v>
+        <v>3061800</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.16</v>
+        <v>0.82</v>
       </c>
       <c r="H47" t="n">
-        <v>40.07</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
+        <v>31.47</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.99</v>
+        <v>1.43</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>0.988</v>
+        <v>1.453</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
@@ -2649,39 +2657,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.505</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>1668100</v>
+        <v>2989300</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.16</v>
+        <v>0.82</v>
       </c>
       <c r="H48" t="n">
-        <v>64.23999999999999</v>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>1.115</v>
+        <v>0.524</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>1.065</v>
+        <v>0.556</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2694,28 +2702,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>1662600</v>
+        <v>2779000</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H49" t="n">
-        <v>72.53</v>
+        <v>45.16</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
@@ -2723,10 +2731,10 @@
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.481</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0.782</v>
+        <v>0.533</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2739,39 +2747,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>0.0484</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1390600</v>
+        <v>2747900</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.85</v>
       </c>
       <c r="H50" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="I50" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.54</v>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.443</v>
+        <v>0.3</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0.394</v>
+        <v>0.325</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="15" t="inlineStr"/>
@@ -2784,39 +2792,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>5.17</v>
+        <v>1.23</v>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0.0137</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>1367100</v>
+        <v>2704700</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="H51" t="n">
-        <v>42.14</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.73999999999999</v>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>5.35</v>
+        <v>1.117</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>5.521</v>
+        <v>1.065</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2829,39 +2837,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>1355100</v>
+        <v>2483200</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.42</v>
+        <v>0.22</v>
       </c>
       <c r="H52" t="n">
-        <v>89.59</v>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.64</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>3.119</v>
+        <v>0.991</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>2.641</v>
+        <v>0.989</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2874,28 +2882,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>9.99</v>
+        <v>0.835</v>
       </c>
       <c r="E53" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>1323400</v>
+        <v>2241500</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
       <c r="H53" t="n">
-        <v>48.07</v>
+        <v>72.53</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -2903,10 +2911,10 @@
         </is>
       </c>
       <c r="J53" s="10" t="n">
-        <v>9.994</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>10.1</v>
+        <v>0.782</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="15" t="inlineStr"/>
@@ -2919,39 +2927,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>2.56</v>
+        <v>4.45</v>
       </c>
       <c r="E54" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>1299700</v>
+        <v>2100100</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="H54" t="n">
-        <v>47.97</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
+        <v>36.57</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J54" s="10" t="n">
-        <v>2.589</v>
+        <v>4.54</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>2.566</v>
+        <v>4.642</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="15" t="inlineStr"/>
@@ -2964,28 +2972,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.865</v>
+        <v>4.91</v>
       </c>
       <c r="E55" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>1288000</v>
+        <v>2035700</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="H55" t="n">
-        <v>46.13</v>
+        <v>53.19</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
@@ -2993,10 +3001,10 @@
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.867</v>
+        <v>4.882</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.868</v>
+        <v>4.783</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3009,39 +3017,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E56" s="11" t="n">
-        <v>0.0108</v>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1278700</v>
+        <v>2028200</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H56" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.74</v>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.488</v>
+        <v>9.992000000000001</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0.472</v>
+        <v>10.099</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3054,39 +3062,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>0</v>
+        <v>2.1</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>1264500</v>
+        <v>1931700</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>1.45</v>
+        <v>0.19</v>
       </c>
       <c r="H57" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.08</v>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.271</v>
+        <v>2.106</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>0.268</v>
+        <v>2.113</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3099,39 +3107,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0196</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>1213400</v>
+        <v>1847400</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.64</v>
+        <v>0.11</v>
       </c>
       <c r="H58" t="n">
-        <v>49.75</v>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.33</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.904</v>
+        <v>5.353</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>0.897</v>
+        <v>5.522</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3144,28 +3152,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>-0.0154</v>
+        <v>3.45</v>
+      </c>
+      <c r="E59" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>1205000</v>
+        <v>1796300</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>40.9</v>
+        <v>89.59</v>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
@@ -3173,10 +3181,10 @@
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.676</v>
+        <v>3.119</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>0.731</v>
+        <v>2.641</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3189,28 +3197,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E60" s="11" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.3</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>1181100</v>
+        <v>1740400</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="H60" t="n">
-        <v>54.41</v>
+        <v>38.94</v>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
@@ -3218,10 +3226,10 @@
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>4.884</v>
+        <v>0.312</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>4.783</v>
+        <v>0.355</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3234,39 +3242,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v>0.0385</v>
+        <v>0.775</v>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>1154800</v>
+        <v>1723700</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H61" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.94</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>1.646</v>
+        <v>0.769</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>1.733</v>
+        <v>0.771</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3279,39 +3287,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E62" s="18" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>1118100</v>
+        <v>1719500</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.51</v>
+        <v>0.15</v>
       </c>
       <c r="H62" t="n">
-        <v>54.59</v>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.4</v>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>0.462</v>
+        <v>0.402</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0.462</v>
+        <v>0.384</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3324,33 +3332,40 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E63" s="11" t="n">
-        <v>0.0282</v>
+        <v>2.65</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>1117400</v>
+        <v>1718200</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I63" s="17" t="inlineStr">
+        <v>0.17</v>
+      </c>
+      <c r="H63" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J63" s="10" t="n"/>
-      <c r="K63" s="10" t="n"/>
+      <c r="J63" s="10" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="K63" s="10" t="n">
+        <v>2.748</v>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
     </row>
@@ -3362,39 +3377,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E64" s="11" t="n">
-        <v>0.0213</v>
+        <v>2.56</v>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>1062000</v>
+        <v>1663200</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H64" t="n">
-        <v>45.16</v>
-      </c>
-      <c r="I64" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.97</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>0.481</v>
+        <v>2.589</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>0.533</v>
+        <v>2.566</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3407,39 +3422,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>-0.0105</v>
+        <v>0.47</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>1059700</v>
+        <v>1647500</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="H65" t="n">
-        <v>51.97</v>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.41</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.488</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>0.897</v>
+        <v>0.472</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3452,28 +3467,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>0.44</v>
+        <v>0.905</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.0233</v>
+        <v>0.0112</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>1051700</v>
+        <v>1620400</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="H66" t="n">
-        <v>53.61</v>
+        <v>48.48</v>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
@@ -3481,10 +3496,10 @@
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.43</v>
+        <v>0.898</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0.417</v>
+        <v>0.954</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3497,40 +3512,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E67" s="18" t="n">
-        <v>0</v>
+        <v>0.725</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>906000</v>
+        <v>1396700</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="H67" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="I67" s="17" t="inlineStr">
+        <v>0.05</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J67" s="10" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="K67" s="10" t="n">
-        <v>0.968</v>
-      </c>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
     </row>
@@ -3542,39 +3550,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E68" s="18" t="n">
-        <v>0</v>
+        <v>4.7</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>879600</v>
+        <v>1377200</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H68" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="I68" s="17" t="inlineStr">
+        <v>45.94</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>0.769</v>
+        <v>4.728</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>0.771</v>
+        <v>4.799</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3587,39 +3595,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>1.36</v>
+        <v>0.44</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0.0074</v>
+        <v>0.0233</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>878300</v>
+        <v>1374200</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="H69" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="I69" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.61</v>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>1.284</v>
+        <v>0.43</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>1.193</v>
+        <v>0.417</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3632,39 +3640,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>-0.0122</v>
+        <v>0.26</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>876800</v>
+        <v>1264500</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.12</v>
+        <v>1.45</v>
       </c>
       <c r="H70" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="I70" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.3</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>3.848</v>
+        <v>0.271</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>3.338</v>
+        <v>0.268</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3677,39 +3685,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>2.21</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>0.0327</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>820500</v>
+        <v>1257600</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.29</v>
+        <v>0.51</v>
       </c>
       <c r="H71" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="I71" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.12</v>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="10" t="n">
-        <v>0.633</v>
+        <v>2.128</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>0.624</v>
+        <v>2.084</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="15" t="inlineStr"/>
@@ -3722,39 +3730,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E72" s="11" t="n">
-        <v>0.0444</v>
+        <v>0.63</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>777900</v>
+        <v>1248500</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="H72" t="n">
-        <v>59.57</v>
-      </c>
-      <c r="I72" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.5</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>1.307</v>
+        <v>0.633</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>1.253</v>
+        <v>0.624</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3767,28 +3775,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.64</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>720300</v>
+        <v>1243700</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.14</v>
+        <v>0.39</v>
       </c>
       <c r="H73" t="n">
-        <v>59.29</v>
+        <v>40.9</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
@@ -3796,10 +3804,10 @@
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>0.531</v>
+        <v>0.731</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3812,28 +3820,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>6.86</v>
+        <v>1.66</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>0.0163</v>
+        <v>0.0184</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>718200</v>
+        <v>1238900</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H74" t="n">
-        <v>60.71</v>
+        <v>53.38</v>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
@@ -3841,10 +3849,10 @@
         </is>
       </c>
       <c r="J74" s="10" t="n">
-        <v>6.402</v>
+        <v>1.63</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>6.046</v>
+        <v>1.67</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="15" t="inlineStr"/>
@@ -3857,39 +3865,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>-0.0075</v>
+        <v>0.265</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>709900</v>
+        <v>1232400</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H75" t="n">
-        <v>42.92</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
+        <v>42.34</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>2.719</v>
+        <v>0.278</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>2.748</v>
+        <v>0.282</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3902,28 +3910,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.64</v>
+        <v>0.895</v>
       </c>
       <c r="E76" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>701000</v>
+        <v>1223200</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="H76" t="n">
-        <v>51.42</v>
+        <v>48.68</v>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
@@ -3931,10 +3939,10 @@
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>0.641</v>
+        <v>0.903</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0.63</v>
+        <v>0.897</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3947,28 +3955,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E77" s="11" t="n">
-        <v>0.0301</v>
+        <v>4.08</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>683400</v>
+        <v>1208200</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="H77" t="n">
-        <v>48.55</v>
+        <v>62.22</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
@@ -3976,10 +3984,10 @@
         </is>
       </c>
       <c r="J77" s="10" t="n">
-        <v>1.363</v>
+        <v>3.85</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>1.431</v>
+        <v>3.339</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
@@ -3992,39 +4000,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E78" s="11" t="n">
-        <v>0.045</v>
+        <v>0.945</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>663900</v>
+        <v>1165100</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H78" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="I78" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.74</v>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>1.105</v>
+        <v>0.944</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0.945</v>
+        <v>0.897</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4037,39 +4045,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E79" s="11" t="n">
-        <v>0.0167</v>
+        <v>0.465</v>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>654700</v>
+        <v>1140600</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="H79" t="n">
-        <v>41.55</v>
-      </c>
-      <c r="I79" s="17" t="inlineStr">
+        <v>54.59</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.64</v>
+        <v>0.462</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>0.679</v>
+        <v>0.462</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4082,28 +4090,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>2.56</v>
+        <v>1.41</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.0039</v>
+        <v>0.0444</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>638200</v>
+        <v>1088000</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.11</v>
+        <v>0.36</v>
       </c>
       <c r="H80" t="n">
-        <v>44.69</v>
+        <v>59.57</v>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
@@ -4111,10 +4119,10 @@
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>2.633</v>
+        <v>1.307</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>2.817</v>
+        <v>1.253</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4127,39 +4135,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>1.17</v>
+        <v>0.23</v>
       </c>
       <c r="E81" s="11" t="n">
-        <v>0.0174</v>
+        <v>0.0222</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>622600</v>
+        <v>1024700</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I81" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.85</v>
+      </c>
+      <c r="I81" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>1.196</v>
+        <v>0.23</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>1.278</v>
+        <v>0.237</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4172,28 +4180,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>1.66</v>
+        <v>0.355</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.0184</v>
+        <v>0.0441</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>622400</v>
+        <v>1015900</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.08</v>
+        <v>1.01</v>
       </c>
       <c r="H82" t="n">
-        <v>53.38</v>
+        <v>58.14</v>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
@@ -4201,10 +4209,10 @@
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>1.63</v>
+        <v>0.341</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>1.67</v>
+        <v>0.356</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4217,39 +4225,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>0.775</v>
+        <v>1.16</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.045</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>611500</v>
+        <v>1003400</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H83" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="I83" s="17" t="inlineStr">
+        <v>58.8</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.747</v>
+        <v>1.105</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>0.709</v>
+        <v>0.945</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4262,39 +4270,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0.83</v>
+        <v>1.36</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>0.0061</v>
+        <v>0.0074</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>597200</v>
+        <v>1002600</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.22</v>
+        <v>0.37</v>
       </c>
       <c r="H84" t="n">
-        <v>34.59</v>
-      </c>
-      <c r="I84" s="17" t="inlineStr">
+        <v>59.32</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J84" s="10" t="n">
-        <v>0.861</v>
+        <v>1.284</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>0.922</v>
+        <v>1.193</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="15" t="inlineStr"/>
@@ -4307,39 +4315,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>0.61</v>
+        <v>2.57</v>
       </c>
       <c r="E85" s="11" t="n">
-        <v>0.0167</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>583300</v>
+        <v>991300</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H85" t="n">
-        <v>57.27</v>
-      </c>
-      <c r="I85" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.16</v>
+      </c>
+      <c r="I85" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.582</v>
+        <v>2.633</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>0.493</v>
+        <v>2.818</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4352,28 +4360,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>1.44</v>
+        <v>6.89</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0207</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>571200</v>
+        <v>979000</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="H86" t="n">
-        <v>70.33</v>
+        <v>61.13</v>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
@@ -4381,10 +4389,10 @@
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>1.379</v>
+        <v>6.404</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>1.351</v>
+        <v>6.047</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4397,39 +4405,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.905</v>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>565500</v>
+        <v>926800</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>0.09</v>
+        <v>1.17</v>
       </c>
       <c r="H87" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="I87" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.99</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>1.192</v>
+        <v>0.944</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>1.156</v>
+        <v>0.968</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4442,39 +4450,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>-0.0042</v>
+        <v>0.835</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>560300</v>
+        <v>925200</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="H88" t="n">
-        <v>48.68</v>
-      </c>
-      <c r="I88" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.7</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>4.731</v>
+        <v>0.861</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>4.8</v>
+        <v>0.923</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4487,39 +4495,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E89" s="11" t="n">
-        <v>0.0071</v>
+        <v>1.25</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>554100</v>
+        <v>922000</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="H89" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I89" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.28</v>
+      </c>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.729</v>
+        <v>1.192</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>0.724</v>
+        <v>1.156</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4532,39 +4540,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>2.21</v>
+        <v>1.17</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>0.0327</v>
+        <v>0.0174</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>537400</v>
+        <v>857300</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
       <c r="H90" t="n">
-        <v>62.12</v>
-      </c>
-      <c r="I90" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>2.128</v>
+        <v>1.196</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>2.084</v>
+        <v>1.278</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4577,45 +4585,1215 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>-0.0248</v>
+        <v>0.615</v>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>0.025</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>523000</v>
+        <v>827400</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H91" t="n">
-        <v>56.47</v>
-      </c>
-      <c r="I91" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.89</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>2.302</v>
+        <v>0.582</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>2.221</v>
+        <v>0.493</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>814100</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H92" t="n">
+        <v>47.99</v>
+      </c>
+      <c r="I92" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="K92" s="10" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="15" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>812300</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H93" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="K93" s="10" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="15" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>799100</v>
+      </c>
+      <c r="G94" s="13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H94" t="n">
+        <v>66.87</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="K94" s="10" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="15" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>0.03759999999999999</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>794800</v>
+      </c>
+      <c r="G95" s="13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H95" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="K95" s="10" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="15" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.0165</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>788000</v>
+      </c>
+      <c r="G96" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H96" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>2.304</v>
+      </c>
+      <c r="K96" s="10" t="n">
+        <v>2.222</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="15" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>780800</v>
+      </c>
+      <c r="G97" s="13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H97" t="n">
+        <v>62.91</v>
+      </c>
+      <c r="I97" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="K97" s="10" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="15" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>0.004699999999999999</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>765500</v>
+      </c>
+      <c r="G98" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H98" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="K98" s="10" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="15" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>760900</v>
+      </c>
+      <c r="G99" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H99" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K99" s="10" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="15" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>753800</v>
+      </c>
+      <c r="G100" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H100" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="K100" s="10" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="15" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>735200</v>
+      </c>
+      <c r="G101" s="13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H101" t="n">
+        <v>45.83</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="K101" s="10" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="15" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>-0.0319</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>725500</v>
+      </c>
+      <c r="G102" s="13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H102" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="K102" s="10" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="15" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>701000</v>
+      </c>
+      <c r="G103" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H103" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="K103" s="10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="15" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>681800</v>
+      </c>
+      <c r="G104" s="13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H104" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>7.313</v>
+      </c>
+      <c r="K104" s="10" t="n">
+        <v>7.599</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="15" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>629700</v>
+      </c>
+      <c r="G105" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H105" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="K105" s="10" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="15" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>-0.0254</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>629400</v>
+      </c>
+      <c r="G106" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H106" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="I106" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>6.839</v>
+      </c>
+      <c r="K106" s="10" t="n">
+        <v>6.828</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="15" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>589100</v>
+      </c>
+      <c r="G107" s="13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H107" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="I107" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K107" s="10" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="15" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>578900</v>
+      </c>
+      <c r="G108" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H108" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="K108" s="10" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="15" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>561500</v>
+      </c>
+      <c r="G109" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H109" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="I109" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>4.466</v>
+      </c>
+      <c r="K109" s="10" t="n">
+        <v>4.446</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="15" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>554600</v>
+      </c>
+      <c r="G110" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H110" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="K110" s="10" t="n">
+        <v>3.519</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="15" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>543400</v>
+      </c>
+      <c r="G111" s="13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H111" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="I111" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>4.025</v>
+      </c>
+      <c r="K111" s="10" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="15" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>543400</v>
+      </c>
+      <c r="G112" s="13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H112" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K112" s="10" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="15" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>539200</v>
+      </c>
+      <c r="G113" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H113" t="n">
+        <v>63.52</v>
+      </c>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="K113" s="10" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="15" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>532600</v>
+      </c>
+      <c r="G114" s="13" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H114" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="10" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="K114" s="10" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="15" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>510800</v>
+      </c>
+      <c r="G115" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H115" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="I115" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="10" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="K115" s="10" t="n">
+        <v>3.768</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="15" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>506200</v>
+      </c>
+      <c r="G116" s="13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H116" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K116" s="10" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="15" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>503400</v>
+      </c>
+      <c r="G117" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H117" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="K117" s="10" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M91"/>
+  <autoFilter ref="A1:M117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
+++ b/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -573,10 +573,10 @@
         <v>0.013</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3281400</v>
+        <v>3792100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>57.6</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.6处中性偏上，未超买；现价0.78高于50日均线0.696约12%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 57.6处中性偏上未超买，现价高于50日均线约12%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.6</v>
+        <v>0.595</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0169</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>4857600</v>
+        <v>6208400</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>56.83</v>
+        <v>55.96</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.6高于50日均线0.55，RSI 56.83处中性区间未超买，信号可靠性尚可。</t>
+          <t>现价0.595高于50日均线0.55，RSI 55.96处中性区间，SAR转多信号技术面可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -679,10 +679,10 @@
         <v>0.0313</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1102700</v>
+        <v>1323100</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>57.68</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.68处中性偏上，未超买；现价0.33略高于50日均线0.329，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 57.68未超买，现价略高于50日均线，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -732,10 +732,10 @@
         <v>0.029</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>20615300</v>
+        <v>21449000</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>67.58</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.355高于50日均线0.271约31%，RSI 67.58接近超买区，信号可靠性中等。</t>
+          <t>SAR转多信号出现，但RSI 67.58已接近超买区，现价高于50日均线约31%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -779,19 +779,19 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>-0.0189</v>
+        <v>-0.0158</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2951900</v>
+        <v>3055900</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.53</v>
+        <v>56.03</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>3.018</v>
+        <v>3.019</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>2.877</v>
+        <v>2.878</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 55.53处中性区间，现价高于50日均线约8.1%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，现价高于50日均线约8.4%，RSI 56处中性区间，未超买，信号技术面可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -838,10 +838,10 @@
         <v>0.0588</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>150349900</v>
+        <v>186442400</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="H7" t="n">
         <v>39.06</v>
@@ -868,28 +868,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LANDMRK</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.06</v>
+        <v>0.97</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>0.5</v>
+        <v>0.0052</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>16910500</v>
+        <v>24737300</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>7.83</v>
+        <v>0.32</v>
       </c>
       <c r="H8" t="n">
-        <v>60.21</v>
+        <v>70.27</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.044</v>
+        <v>0.88</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0.058</v>
+        <v>0.776</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
@@ -913,33 +913,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>LANDMRK</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.195</v>
+        <v>0.06</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.0541</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>15328000</v>
+        <v>21304000</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
+        <v>9.859999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>0.058</v>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="15" t="inlineStr"/>
     </row>
@@ -951,40 +958,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.97</v>
+        <v>0.195</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.0052</v>
+        <v>0.0541</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>13196500</v>
+        <v>15551000</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H10" t="n">
-        <v>70.27</v>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>0.776</v>
-      </c>
+        <v>0.58</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="15" t="inlineStr"/>
     </row>
@@ -996,28 +996,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>-0.0136</v>
+        <v>0.45</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>12695000</v>
+        <v>13821500</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
       <c r="H11" t="n">
-        <v>75.84999999999999</v>
+        <v>47.56</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.673</v>
+        <v>0.453</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>0.575</v>
+        <v>0.472</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
@@ -1041,39 +1041,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.375</v>
+        <v>0.725</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>-0.0132</v>
+        <v>-0.0136</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>12264200</v>
+        <v>12783100</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1.23</v>
+        <v>0.55</v>
       </c>
       <c r="H12" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.84999999999999</v>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.387</v>
+        <v>0.673</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>0.402</v>
+        <v>0.575</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
@@ -1086,28 +1086,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.505</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>12047500</v>
+        <v>12638500</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>4.12</v>
+        <v>0.33</v>
       </c>
       <c r="H13" t="n">
-        <v>63.99</v>
+        <v>76.67</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.162</v>
+        <v>0.435</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>0.158</v>
+        <v>0.335</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="15" t="inlineStr"/>
@@ -1131,39 +1131,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.38</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>11704600</v>
+        <v>12334200</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.3</v>
+        <v>1.24</v>
       </c>
       <c r="H14" t="n">
-        <v>74.66</v>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.76</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.435</v>
+        <v>0.388</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>0.335</v>
+        <v>0.402</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
@@ -1176,28 +1176,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.45</v>
+        <v>0.18</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.0227</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>11535500</v>
+        <v>12097000</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.32</v>
+        <v>4.14</v>
       </c>
       <c r="H15" t="n">
-        <v>47.56</v>
+        <v>63.99</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.453</v>
+        <v>0.162</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>0.472</v>
+        <v>0.158</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
@@ -1221,39 +1221,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>0.1657</v>
+        <v>0.21</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>10422900</v>
+        <v>11970900</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
-        <v>60.46</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.61</v>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.838</v>
+        <v>0.137</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.652</v>
+        <v>0.12</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1266,39 +1266,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>-0.0455</v>
+        <v>0.98</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0.1598</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>9510500</v>
+        <v>10652100</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1.35</v>
+        <v>1.89</v>
       </c>
       <c r="H17" t="n">
-        <v>82.61</v>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.25</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.137</v>
+        <v>0.838</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.12</v>
+        <v>0.652</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="15" t="inlineStr"/>
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.465</v>
+        <v>0.46</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>0.0814</v>
+        <v>0.0698</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>8702700</v>
+        <v>9481000</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="H18" t="n">
-        <v>40.39</v>
+        <v>38.88</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -1356,28 +1356,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>MQTECH</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.165</v>
+        <v>0.06</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.0313</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>7840100</v>
+        <v>9015100</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.14</v>
+        <v>5.05</v>
       </c>
       <c r="H19" t="n">
-        <v>53.37</v>
+        <v>62.78</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.16</v>
+        <v>0.053</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0.149</v>
+        <v>0.056</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="15" t="inlineStr"/>
@@ -1401,39 +1401,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MQTECH</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0732</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>7708100</v>
+        <v>8492700</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>4.32</v>
+        <v>0.87</v>
       </c>
       <c r="H20" t="n">
-        <v>62.78</v>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.44</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.053</v>
+        <v>0.221</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.056</v>
+        <v>0.263</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
@@ -1446,39 +1446,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.225</v>
+        <v>0.165</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.09759999999999999</v>
+        <v>0.0313</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>7022400</v>
+        <v>8079400</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.72</v>
+        <v>0.14</v>
       </c>
       <c r="H21" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.37</v>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.222</v>
+        <v>0.16</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.263</v>
+        <v>0.149</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="15" t="inlineStr"/>
@@ -1491,39 +1491,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.065</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>6728200</v>
+        <v>7667400</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.24</v>
+        <v>4.08</v>
       </c>
       <c r="H22" t="n">
-        <v>63.98</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.52</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2.008</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>1.822</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         <v>0.03700000000000001</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>6668400</v>
+        <v>7021500</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>8.539999999999999</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
         <v>53.08</v>
@@ -1581,39 +1581,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.115</v>
+        <v>2.2</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.0455</v>
+        <v>0.0185</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>6461200</v>
+        <v>6962300</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>1.44</v>
+        <v>0.25</v>
       </c>
       <c r="H24" t="n">
-        <v>70.39</v>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.81999999999999</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.102</v>
+        <v>2.01</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.08599999999999999</v>
+        <v>1.822</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1626,39 +1626,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HBGLOB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>-0.5</v>
+        <v>0.82</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>5268000</v>
+        <v>6954100</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>24.7</v>
+        <v>0.44</v>
       </c>
       <c r="H25" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.029</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0.031</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1671,28 +1671,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>-0.0476</v>
+        <v>0.775</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>5025600</v>
+        <v>6820100</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="H26" t="n">
-        <v>35.57</v>
+        <v>50.93</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.458</v>
+        <v>0.774</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.573</v>
+        <v>0.775</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1716,28 +1716,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>0</v>
+        <v>0.115</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>5004100</v>
+        <v>6797800</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.32</v>
+        <v>1.52</v>
       </c>
       <c r="H27" t="n">
-        <v>54.27</v>
+        <v>70.39</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="15" t="inlineStr"/>
@@ -1761,39 +1761,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>0</v>
+        <v>1.69</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>4945700</v>
+        <v>6444200</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.44</v>
+        <v>1.03</v>
       </c>
       <c r="H28" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.81</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.283</v>
+        <v>1.653</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0.279</v>
+        <v>1.735</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="15" t="inlineStr"/>
@@ -1806,28 +1806,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>0.0133</v>
+        <v>0.395</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>-0.0595</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>4900400</v>
+        <v>6116200</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H29" t="n">
-        <v>58.47</v>
+        <v>35.01</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.373</v>
+        <v>0.457</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.37</v>
+        <v>0.573</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr"/>
@@ -1851,28 +1851,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>0.0609</v>
+        <v>0.0345</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>4843700</v>
+        <v>5970700</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="H30" t="n">
-        <v>37.11</v>
+        <v>38.44</v>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.281</v>
+        <v>1.559</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>1.479</v>
+        <v>1.837</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="15" t="inlineStr"/>
@@ -1896,28 +1896,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.775</v>
+        <v>2.13</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.039</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>4829500</v>
+        <v>5867900</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.31</v>
+        <v>0.48</v>
       </c>
       <c r="H31" t="n">
-        <v>50.93</v>
+        <v>50.85</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.774</v>
+        <v>2.101</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0.775</v>
+        <v>2.226</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="15" t="inlineStr"/>
@@ -1941,28 +1941,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>HBGLOB</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>0</v>
+        <v>0.015</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>-0.5</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>4539500</v>
+        <v>5837500</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>2.01</v>
+        <v>27.37</v>
       </c>
       <c r="H32" t="n">
-        <v>41.46</v>
+        <v>11.69</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.13</v>
+        <v>0.029</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0.14</v>
+        <v>0.031</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="15" t="inlineStr"/>
@@ -1986,39 +1986,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>0.0259</v>
+        <v>0.865</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>4391100</v>
+        <v>5821500</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.48</v>
+        <v>0.28</v>
       </c>
       <c r="H33" t="n">
-        <v>47.11</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.605</v>
+        <v>0.867</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0.617</v>
+        <v>0.868</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2031,39 +2031,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>4212000</v>
+        <v>5811300</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.22</v>
+        <v>0.85</v>
       </c>
       <c r="H34" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.47</v>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.307</v>
+        <v>0.373</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0.303</v>
+        <v>0.37</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="15" t="inlineStr"/>
@@ -2076,28 +2076,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>0.0414</v>
+        <v>0.53</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>4096700</v>
+        <v>5719300</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.29</v>
+        <v>1.38</v>
       </c>
       <c r="H35" t="n">
-        <v>39.52</v>
+        <v>79.91</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2105,10 +2105,10 @@
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1.56</v>
+        <v>0.465</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>1.838</v>
+        <v>0.44</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2121,39 +2121,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>0.0213</v>
+        <v>0.305</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>4031100</v>
+        <v>5420000</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1.64</v>
+        <v>0.28</v>
       </c>
       <c r="H36" t="n">
-        <v>60.46</v>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.46</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.456</v>
+        <v>0.307</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.45</v>
+        <v>0.303</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr"/>
@@ -2166,28 +2166,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0.0641</v>
+        <v>0.0435</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>3976300</v>
+        <v>5363900</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H37" t="n">
-        <v>48.96</v>
+        <v>34.14</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.65</v>
+        <v>1.279</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>1.734</v>
+        <v>1.479</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="15" t="inlineStr"/>
@@ -2211,39 +2211,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.865</v>
+        <v>0.27</v>
       </c>
       <c r="E38" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>3960300</v>
+        <v>5000700</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.19</v>
+        <v>0.44</v>
       </c>
       <c r="H38" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.64</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.867</v>
+        <v>0.283</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.868</v>
+        <v>0.279</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2256,39 +2256,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>2.13</v>
+        <v>0.6</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.039</v>
+        <v>0.0345</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>3898500</v>
+        <v>4726300</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="H39" t="n">
-        <v>50.85</v>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>2.101</v>
+        <v>0.605</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>2.226</v>
+        <v>0.617</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2301,39 +2301,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>0.0391</v>
+        <v>0.125</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>3686100</v>
+        <v>4539500</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.88</v>
+        <v>2.01</v>
       </c>
       <c r="H40" t="n">
-        <v>62.73</v>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.46</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.604</v>
+        <v>0.13</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.586</v>
+        <v>0.14</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2346,36 +2346,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>0.0222</v>
+        <v>0.64</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>3561400</v>
+        <v>4439500</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="H41" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
+        <v>63.72</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>0.619</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
     </row>
@@ -2387,28 +2391,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>3534600</v>
+        <v>4413400</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.85</v>
+        <v>1.79</v>
       </c>
       <c r="H42" t="n">
-        <v>83.09999999999999</v>
+        <v>60.46</v>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
@@ -2416,10 +2420,10 @@
         </is>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.466</v>
+        <v>0.456</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
@@ -2432,39 +2436,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.64</v>
+        <v>0.485</v>
       </c>
       <c r="E43" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>3462700</v>
+        <v>4271300</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H43" t="n">
-        <v>63.72</v>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.62</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.627</v>
+        <v>0.443</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.619</v>
+        <v>0.394</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2477,39 +2481,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.985</v>
+        <v>4.96</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.0051</v>
+        <v>0.0102</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>3378800</v>
+        <v>4057100</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>1.52</v>
+        <v>0.17</v>
       </c>
       <c r="H44" t="n">
-        <v>32.49</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.14</v>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1.052</v>
+        <v>4.887</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>1.112</v>
+        <v>4.784</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2522,28 +2526,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.0476</v>
+        <v>0.0164</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>3305600</v>
+        <v>3965800</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.66</v>
+        <v>0.39</v>
       </c>
       <c r="H45" t="n">
-        <v>70.65000000000001</v>
+        <v>67.55</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
@@ -2551,10 +2555,10 @@
         </is>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1.128</v>
+        <v>1.118</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>0.987</v>
+        <v>1.066</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="15" t="inlineStr"/>
@@ -2567,39 +2571,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.0103</v>
+        <v>0.665</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>0.0391</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3204500</v>
+        <v>3856100</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.15</v>
+        <v>0.92</v>
       </c>
       <c r="H46" t="n">
-        <v>63.86</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.73</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.443</v>
+        <v>0.604</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>0.394</v>
+        <v>0.586</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2612,40 +2616,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>-0.049</v>
+        <v>0.23</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3061800</v>
+        <v>3852200</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="H47" t="n">
-        <v>31.47</v>
+        <v>54.46</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J47" s="10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="K47" s="10" t="n">
-        <v>1.453</v>
-      </c>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="n"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
     </row>
@@ -2657,28 +2657,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.505</v>
+        <v>0.99</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.0202</v>
+        <v>0.0102</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2989300</v>
+        <v>3733000</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.82</v>
+        <v>1.68</v>
       </c>
       <c r="H48" t="n">
-        <v>34.49</v>
+        <v>33.83</v>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.524</v>
+        <v>1.052</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0.556</v>
+        <v>1.112</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>0.0213</v>
+        <v>4.45</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>2779000</v>
+        <v>3717700</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="H49" t="n">
-        <v>45.16</v>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.57</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.481</v>
+        <v>4.54</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0.533</v>
+        <v>4.642</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.325</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.0484</v>
+        <v>0.0217</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2747900</v>
+        <v>3606700</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>1.85</v>
+        <v>0.31</v>
       </c>
       <c r="H50" t="n">
-        <v>59.54</v>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.39</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.3</v>
+        <v>0.992</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0.325</v>
+        <v>0.989</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="15" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.11</v>
+      </c>
+      <c r="E51" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>2704700</v>
+        <v>3355600</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="H51" t="n">
-        <v>66.73999999999999</v>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.76</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>1.117</v>
+        <v>0.127</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>1.065</v>
+        <v>0.145</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.32</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>0.0163</v>
+        <v>0.0476</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>2483200</v>
+        <v>3354300</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="H52" t="n">
-        <v>41.64</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.65000000000001</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.991</v>
+        <v>1.128</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0.989</v>
+        <v>0.987</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>2241500</v>
+        <v>3199200</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>0.45</v>
       </c>
       <c r="H53" t="n">
-        <v>72.53</v>
+        <v>45.16</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.481</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>0.782</v>
+        <v>0.533</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="15" t="inlineStr"/>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E54" s="18" t="n">
-        <v>0</v>
+        <v>1.36</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>-0.049</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>2100100</v>
+        <v>3134500</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.23</v>
+        <v>0.84</v>
       </c>
       <c r="H54" t="n">
-        <v>36.57</v>
+        <v>31.47</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="J54" s="10" t="n">
-        <v>4.54</v>
+        <v>1.43</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>4.642</v>
+        <v>1.453</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="15" t="inlineStr"/>
@@ -2972,39 +2972,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>0</v>
+        <v>0.505</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>2035700</v>
+        <v>3078700</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="H55" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>4.882</v>
+        <v>0.524</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>4.783</v>
+        <v>0.556</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>-0.002</v>
+        <v>0.185</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>2028200</v>
+        <v>3046000</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H56" t="n">
-        <v>46.74</v>
+        <v>49.32</v>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>9.992000000000001</v>
+        <v>0.185</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>10.099</v>
+        <v>0.187</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>-0.009399999999999999</v>
+        <v>5.2</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>1931700</v>
+        <v>2922100</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H57" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.33</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>2.106</v>
+        <v>5.353</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>2.113</v>
+        <v>5.522</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3107,39 +3107,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>5.2</v>
+        <v>0.325</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>0.0196</v>
+        <v>0.0484</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>1847400</v>
+        <v>2751000</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>0.11</v>
+        <v>1.85</v>
       </c>
       <c r="H58" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.54</v>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>5.353</v>
+        <v>0.3</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>5.522</v>
+        <v>0.325</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>0</v>
+        <v>9.98</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>1796300</v>
+        <v>2423500</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H59" t="n">
-        <v>89.59</v>
+        <v>47.39</v>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>3.119</v>
+        <v>9.993</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>2.641</v>
+        <v>10.1</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.3</v>
+        <v>0.835</v>
       </c>
       <c r="E60" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>1740400</v>
+        <v>2383000</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="H60" t="n">
-        <v>38.94</v>
+        <v>72.53</v>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.312</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>0.355</v>
+        <v>0.782</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3242,39 +3242,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>0</v>
+        <v>3.43</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>1723700</v>
+        <v>2290100</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.23</v>
+        <v>0.71</v>
       </c>
       <c r="H61" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.70999999999999</v>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.769</v>
+        <v>3.117</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>0.771</v>
+        <v>2.641</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3287,39 +3287,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>-0.0122</v>
+        <v>0.78</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>1719500</v>
+        <v>2261100</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H62" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="I62" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.44</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>0.402</v>
+        <v>0.769</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0.384</v>
+        <v>0.771</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3341,19 +3341,19 @@
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>-0.0075</v>
+        <v>-0.0037</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>1718200</v>
+        <v>2198800</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H63" t="n">
-        <v>42.92</v>
+        <v>43.71</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>2.719</v>
+        <v>2.72</v>
       </c>
       <c r="K63" s="10" t="n">
         <v>2.748</v>
@@ -3377,39 +3377,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>2.56</v>
+        <v>0.225</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>1663200</v>
+        <v>2176700</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.1</v>
+        <v>1.46</v>
       </c>
       <c r="H64" t="n">
-        <v>47.97</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.99</v>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>2.589</v>
+        <v>0.229</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>2.566</v>
+        <v>0.237</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3422,39 +3422,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>0.47</v>
+        <v>2.21</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.0108</v>
+        <v>0.0327</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>1647500</v>
+        <v>2163800</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.19</v>
+        <v>0.88</v>
       </c>
       <c r="H65" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.12</v>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>0.488</v>
+        <v>2.128</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>0.472</v>
+        <v>2.084</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E66" s="11" t="n">
-        <v>0.0112</v>
+        <v>2.1</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>1620400</v>
+        <v>2102100</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="H66" t="n">
-        <v>48.48</v>
+        <v>49.08</v>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.898</v>
+        <v>2.106</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0.954</v>
+        <v>2.113</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3512,33 +3512,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v>0.0211</v>
+        <v>0.3</v>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>1396700</v>
+        <v>2025200</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="H67" t="n">
+        <v>38.94</v>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="K67" s="10" t="n">
+        <v>0.355</v>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
     </row>
@@ -3550,28 +3557,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>-0.0105</v>
+        <v>2.57</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>1377200</v>
+        <v>1975700</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H68" t="n">
-        <v>45.94</v>
+        <v>48.66</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3579,10 +3586,10 @@
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>4.728</v>
+        <v>2.59</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>4.799</v>
+        <v>2.566</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3595,28 +3602,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.44</v>
+        <v>0.905</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0.0233</v>
+        <v>0.0112</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>1374200</v>
+        <v>1946700</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.19</v>
+        <v>0.47</v>
       </c>
       <c r="H69" t="n">
-        <v>53.61</v>
+        <v>48.48</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -3624,10 +3631,10 @@
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>0.43</v>
+        <v>0.898</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0.417</v>
+        <v>0.954</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3640,39 +3647,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E70" s="18" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0122</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1264500</v>
+        <v>1876500</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>1.45</v>
+        <v>0.16</v>
       </c>
       <c r="H70" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.4</v>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>0.271</v>
+        <v>0.402</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>0.268</v>
+        <v>0.384</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3685,28 +3692,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E71" s="11" t="n">
-        <v>0.0327</v>
+        <v>4.04</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>1257600</v>
+        <v>1868100</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.51</v>
+        <v>0.25</v>
       </c>
       <c r="H71" t="n">
-        <v>62.12</v>
+        <v>60.59</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -3714,10 +3721,10 @@
         </is>
       </c>
       <c r="J71" s="10" t="n">
-        <v>2.128</v>
+        <v>3.846</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>2.084</v>
+        <v>3.338</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="15" t="inlineStr"/>
@@ -3730,39 +3737,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>1.66</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>1248500</v>
+        <v>1798200</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="H72" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.38</v>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>0.633</v>
+        <v>1.63</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>0.624</v>
+        <v>1.67</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3775,39 +3782,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>-0.0154</v>
+        <v>0.47</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>1243700</v>
+        <v>1797500</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.39</v>
+        <v>0.2</v>
       </c>
       <c r="H73" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="I73" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.41</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.676</v>
+        <v>0.488</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>0.731</v>
+        <v>0.472</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3820,39 +3827,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E74" s="11" t="n">
-        <v>0.0184</v>
+        <v>4.71</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>1238900</v>
+        <v>1755700</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H74" t="n">
-        <v>53.38</v>
-      </c>
-      <c r="I74" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.82</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="10" t="n">
-        <v>1.63</v>
+        <v>4.729</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="15" t="inlineStr"/>
@@ -3865,39 +3872,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v>0.0192</v>
+        <v>2.32</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>-0.0413</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>1232400</v>
+        <v>1739100</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="H75" t="n">
-        <v>42.34</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.29</v>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.278</v>
+        <v>2.299</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0.282</v>
+        <v>2.22</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3910,28 +3917,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1223200</v>
+        <v>1559900</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.64</v>
+        <v>0.22</v>
       </c>
       <c r="H76" t="n">
-        <v>48.68</v>
+        <v>53.61</v>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
@@ -3939,10 +3946,10 @@
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>0.903</v>
+        <v>0.43</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0.897</v>
+        <v>0.417</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3955,40 +3962,33 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>-0.0073</v>
+        <v>0.725</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>1208200</v>
+        <v>1542200</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H77" t="n">
-        <v>62.22</v>
-      </c>
-      <c r="I77" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K77" s="10" t="n">
-        <v>3.339</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
     </row>
@@ -4000,39 +4000,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>-0.0053</v>
+        <v>0.265</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>1165100</v>
+        <v>1507600</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H78" t="n">
-        <v>53.74</v>
-      </c>
-      <c r="I78" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.34</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.944</v>
+        <v>0.278</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0.897</v>
+        <v>0.282</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4045,39 +4045,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.465</v>
+        <v>1.26</v>
       </c>
       <c r="E79" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>1140600</v>
+        <v>1465700</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.52</v>
+        <v>0.22</v>
       </c>
       <c r="H79" t="n">
-        <v>54.59</v>
-      </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.05</v>
+      </c>
+      <c r="I79" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.462</v>
+        <v>1.193</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>0.462</v>
+        <v>1.156</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4090,39 +4090,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>1.41</v>
+        <v>0.245</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.0444</v>
+        <v>0.0426</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>1088000</v>
+        <v>1447500</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.36</v>
+        <v>1.32</v>
       </c>
       <c r="H80" t="n">
-        <v>59.57</v>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.9</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>1.307</v>
+        <v>0.246</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>1.253</v>
+        <v>0.25</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4135,28 +4135,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>0.0222</v>
+        <v>0.64</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1024700</v>
+        <v>1383800</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="H81" t="n">
-        <v>48.85</v>
+        <v>40.9</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>0.23</v>
+        <v>0.676</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>0.237</v>
+        <v>0.731</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4180,28 +4180,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0.355</v>
+        <v>2.57</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.0441</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1015900</v>
+        <v>1375100</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>1.01</v>
+        <v>0.23</v>
       </c>
       <c r="H82" t="n">
-        <v>58.14</v>
+        <v>45.16</v>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>0.341</v>
+        <v>2.633</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0.356</v>
+        <v>2.818</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4225,39 +4225,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>1.16</v>
+        <v>6.94</v>
       </c>
       <c r="E83" s="11" t="n">
-        <v>0.045</v>
+        <v>0.0281</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>1003400</v>
+        <v>1331300</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="H83" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.8</v>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>1.105</v>
+        <v>6.409</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>0.945</v>
+        <v>6.048</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4270,28 +4270,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E84" s="11" t="n">
-        <v>0.0074</v>
+        <v>0.63</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>1002600</v>
+        <v>1282400</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="H84" t="n">
-        <v>59.32</v>
+        <v>49.5</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="J84" s="10" t="n">
-        <v>1.284</v>
+        <v>0.633</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>1.193</v>
+        <v>0.624</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="15" t="inlineStr"/>
@@ -4315,28 +4315,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E85" s="11" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.945</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>991300</v>
+        <v>1281200</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="H85" t="n">
-        <v>45.16</v>
+        <v>53.74</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>2.633</v>
+        <v>0.944</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>2.818</v>
+        <v>0.897</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4360,39 +4360,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="E86" s="11" t="n">
-        <v>0.0207</v>
+        <v>0.26</v>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>979000</v>
+        <v>1264500</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.17</v>
+        <v>1.45</v>
       </c>
       <c r="H86" t="n">
-        <v>61.13</v>
-      </c>
-      <c r="I86" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.3</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>6.404</v>
+        <v>0.271</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>6.047</v>
+        <v>0.268</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4405,39 +4405,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>0</v>
+        <v>1.42</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>0.0519</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>926800</v>
+        <v>1252300</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>1.17</v>
+        <v>0.42</v>
       </c>
       <c r="H87" t="n">
-        <v>34.99</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.18</v>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.944</v>
+        <v>1.308</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>0.968</v>
+        <v>1.253</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4450,39 +4450,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E88" s="11" t="n">
-        <v>0.0121</v>
+        <v>0.89</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>925200</v>
+        <v>1250300</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="H88" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.67</v>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>0.861</v>
+        <v>0.903</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>0.923</v>
+        <v>0.897</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4495,39 +4495,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.485</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>922000</v>
+        <v>1220400</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H89" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="I89" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.42</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>1.192</v>
+        <v>0.492</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>1.156</v>
+        <v>0.512</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4540,28 +4540,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>1.17</v>
+        <v>0.915</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>0.0174</v>
+        <v>0.011</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>857300</v>
+        <v>1190400</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.09</v>
+        <v>1.5</v>
       </c>
       <c r="H90" t="n">
-        <v>39.48</v>
+        <v>38.87</v>
       </c>
       <c r="I90" s="16" t="inlineStr">
         <is>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>1.196</v>
+        <v>0.944</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>1.278</v>
+        <v>0.968</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4585,28 +4585,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>0.615</v>
+        <v>0.265</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>0.025</v>
+        <v>0.06</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>827400</v>
+        <v>1182800</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="H91" t="n">
-        <v>57.89</v>
+        <v>49.13</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>0.582</v>
+        <v>0.263</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>0.493</v>
+        <v>0.28</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4630,28 +4630,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.36</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>814100</v>
+        <v>1180100</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.12</v>
+        <v>1.17</v>
       </c>
       <c r="H92" t="n">
-        <v>47.99</v>
+        <v>60.77</v>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>1.275</v>
+        <v>0.341</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>1.319</v>
+        <v>0.356</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4675,28 +4675,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v>0.0267</v>
+        <v>0.46</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>812300</v>
+        <v>1168400</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="H93" t="n">
-        <v>56.26</v>
+        <v>47.63</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>0.746</v>
+        <v>0.462</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0.709</v>
+        <v>0.462</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4720,28 +4720,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.62</v>
+        <v>0.345</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>0.0248</v>
+        <v>0.0299</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>799100</v>
+        <v>1158300</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H94" t="n">
-        <v>66.87</v>
+        <v>49.8</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="J94" s="10" t="n">
-        <v>0.555</v>
+        <v>0.347</v>
       </c>
       <c r="K94" s="10" t="n">
-        <v>0.492</v>
+        <v>0.331</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="15" t="inlineStr"/>
@@ -4765,39 +4765,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>1.38</v>
+        <v>0.835</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0121</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>794800</v>
+        <v>1151000</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="H95" t="n">
-        <v>49.86</v>
-      </c>
-      <c r="I95" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.7</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>1.364</v>
+        <v>0.861</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>1.431</v>
+        <v>0.923</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4810,39 +4810,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0165</v>
+        <v>0.425</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>788000</v>
+        <v>1147300</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="H96" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="I96" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.01</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>2.304</v>
+        <v>0.403</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>2.222</v>
+        <v>0.368</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4855,39 +4855,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>-0.028</v>
+        <v>1.16</v>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>0.045</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>780800</v>
+        <v>1112300</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>1.41</v>
+        <v>0.33</v>
       </c>
       <c r="H97" t="n">
-        <v>62.91</v>
-      </c>
-      <c r="I97" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.8</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="10" t="n">
-        <v>0.655</v>
+        <v>1.105</v>
       </c>
       <c r="K97" s="10" t="n">
-        <v>0.618</v>
+        <v>0.945</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
@@ -4900,39 +4900,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>2.12</v>
+        <v>1.17</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0174</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>765500</v>
+        <v>1105700</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H98" t="n">
-        <v>68.81</v>
-      </c>
-      <c r="I98" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>1.995</v>
+        <v>1.196</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>1.969</v>
+        <v>1.278</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4945,28 +4945,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E99" s="11" t="n">
-        <v>0.025</v>
+        <v>0.7</v>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>760900</v>
+        <v>1097200</v>
       </c>
       <c r="G99" s="13" t="n">
         <v>0.1</v>
       </c>
       <c r="H99" t="n">
-        <v>42.74</v>
+        <v>44.94</v>
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.64</v>
+        <v>0.728</v>
       </c>
       <c r="K99" s="10" t="n">
-        <v>0.679</v>
+        <v>0.724</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -4990,28 +4990,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>0.6</v>
+        <v>2.12</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>0.0169</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>753800</v>
+        <v>1070200</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H100" t="n">
-        <v>60.09</v>
+        <v>68.81</v>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="J100" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.995</v>
       </c>
       <c r="K100" s="10" t="n">
-        <v>0.531</v>
+        <v>1.969</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
@@ -5035,28 +5035,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>0.735</v>
+        <v>1.36</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>0.028</v>
+        <v>0.0074</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>735200</v>
+        <v>1067800</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H101" t="n">
-        <v>45.83</v>
+        <v>59.32</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>0.751</v>
+        <v>1.284</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>0.765</v>
+        <v>1.193</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="15" t="inlineStr"/>
@@ -5080,39 +5080,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>-0.0319</v>
+        <v>0.615</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>0.025</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>725500</v>
+        <v>1029600</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="H102" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="I102" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.89</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>1.812</v>
+        <v>0.582</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>1.909</v>
+        <v>0.493</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5125,39 +5125,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D103" s="10" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>934500</v>
+      </c>
+      <c r="G103" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H103" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="10" t="n">
         <v>0.64</v>
       </c>
-      <c r="E103" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>701000</v>
-      </c>
-      <c r="G103" s="13" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H103" t="n">
-        <v>51.42</v>
-      </c>
-      <c r="I103" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>0.641</v>
-      </c>
       <c r="K103" s="10" t="n">
-        <v>0.63</v>
+        <v>0.679</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="15" t="inlineStr"/>
@@ -5170,39 +5170,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>7.1</v>
+        <v>0.68</v>
       </c>
       <c r="E104" s="17" t="n">
-        <v>-0.0014</v>
+        <v>-0.049</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>681800</v>
+        <v>929900</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.04</v>
+        <v>1.68</v>
       </c>
       <c r="H104" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="I104" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.54</v>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>7.313</v>
+        <v>0.654</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>7.599</v>
+        <v>0.618</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5215,28 +5215,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>1.44</v>
+        <v>0.595</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>629700</v>
+        <v>926200</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="H105" t="n">
-        <v>70.33</v>
+        <v>59.29</v>
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="J105" s="10" t="n">
-        <v>1.379</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K105" s="10" t="n">
-        <v>1.351</v>
+        <v>0.531</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="15" t="inlineStr"/>
@@ -5260,39 +5260,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>-0.0254</v>
+        <v>-0.0014</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>629400</v>
+        <v>896400</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="H106" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="I106" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.84</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="10" t="n">
-        <v>6.839</v>
+        <v>7.313</v>
       </c>
       <c r="K106" s="10" t="n">
-        <v>6.828</v>
+        <v>7.599</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="15" t="inlineStr"/>
@@ -5305,39 +5305,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E107" s="18" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>589100</v>
+        <v>889000</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="H107" t="n">
-        <v>60.23</v>
-      </c>
-      <c r="I107" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.55</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="10" t="n">
-        <v>1.24</v>
+        <v>0.554</v>
       </c>
       <c r="K107" s="10" t="n">
-        <v>1.212</v>
+        <v>0.492</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="15" t="inlineStr"/>
@@ -5350,39 +5350,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>0.705</v>
+        <v>0.88</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>0.0071</v>
+        <v>0.0292</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>578900</v>
+        <v>883500</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="H108" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.3</v>
+      </c>
+      <c r="I108" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.729</v>
+        <v>0.884</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>0.724</v>
+        <v>0.865</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="15" t="inlineStr"/>
@@ -5395,28 +5395,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>4.68</v>
+        <v>1.37</v>
       </c>
       <c r="E109" s="11" t="n">
-        <v>0.0108</v>
+        <v>0.0301</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>561500</v>
+        <v>882700</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H109" t="n">
-        <v>59.42</v>
+        <v>48.55</v>
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         </is>
       </c>
       <c r="J109" s="10" t="n">
-        <v>4.466</v>
+        <v>1.363</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>4.446</v>
+        <v>1.431</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="15" t="inlineStr"/>
@@ -5440,28 +5440,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E110" s="17" t="n">
-        <v>-0.0156</v>
+        <v>0.74</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>0.035</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>554600</v>
+        <v>876500</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.13</v>
+        <v>0.39</v>
       </c>
       <c r="H110" t="n">
-        <v>33.89</v>
+        <v>46.87</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="J110" s="10" t="n">
-        <v>3.287</v>
+        <v>0.752</v>
       </c>
       <c r="K110" s="10" t="n">
-        <v>3.519</v>
+        <v>0.765</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
@@ -5485,28 +5485,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E111" s="11" t="n">
-        <v>0.0144</v>
+        <v>1.26</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>543400</v>
+        <v>873500</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
       <c r="H111" t="n">
-        <v>60.35</v>
+        <v>46.55</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>4.025</v>
+        <v>1.274</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>3.685</v>
+        <v>1.319</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5530,28 +5530,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>1.34</v>
+        <v>0.775</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>0.0308</v>
+        <v>0.0333</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>543400</v>
+        <v>850400</v>
       </c>
       <c r="G112" s="13" t="n">
         <v>0.27</v>
       </c>
       <c r="H112" t="n">
-        <v>54.94</v>
+        <v>57.03</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5559,10 +5559,10 @@
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>1.3</v>
+        <v>0.747</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>1.309</v>
+        <v>0.709</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5575,28 +5575,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="E113" s="11" t="n">
-        <v>0.0243</v>
+        <v>6.9</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>-0.0254</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>539200</v>
+        <v>822900</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H113" t="n">
-        <v>63.52</v>
+        <v>53.89</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>2.762</v>
+        <v>6.839</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>2.405</v>
+        <v>6.828</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5620,39 +5620,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>0.028</v>
+        <v>0.0201</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>532600</v>
+        <v>792700</v>
       </c>
       <c r="G114" s="13" t="n">
         <v>0.17</v>
       </c>
       <c r="H114" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="I114" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.01</v>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="10" t="n">
-        <v>1.118</v>
+        <v>7.332</v>
       </c>
       <c r="K114" s="10" t="n">
-        <v>1.116</v>
+        <v>6.985</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
@@ -5665,28 +5665,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="E115" s="11" t="n">
-        <v>0.005</v>
+        <v>1.83</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>-0.0266</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>510800</v>
+        <v>783700</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H115" t="n">
-        <v>57.81</v>
+        <v>49.7</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>3.844</v>
+        <v>1.813</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>3.768</v>
+        <v>1.909</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5710,39 +5710,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>0.76</v>
+        <v>1.3</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>0.0133</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>506200</v>
+        <v>769600</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="H116" t="n">
-        <v>60.32</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.39</v>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>0.741</v>
+        <v>1.241</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>0.675</v>
+        <v>1.212</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5755,45 +5755,990 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>0.675</v>
+        <v>11.08</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>0.0227</v>
+        <v>0.024</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>503400</v>
+        <v>739700</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H117" t="n">
-        <v>45.04</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.81</v>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="10" t="n">
-        <v>0.707</v>
+        <v>10.56</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>0.6919999999999999</v>
+        <v>9.938000000000001</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="15" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>730000</v>
+      </c>
+      <c r="G118" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H118" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>4.024</v>
+      </c>
+      <c r="K118" s="10" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="15" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>726700</v>
+      </c>
+      <c r="G119" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H119" t="n">
+        <v>71.94</v>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="K119" s="10" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="15" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>701700</v>
+      </c>
+      <c r="G120" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H120" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="I120" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K120" s="10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="15" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>674800</v>
+      </c>
+      <c r="G121" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H121" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="10" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="K121" s="10" t="n">
+        <v>3.768</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="15" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SENTRAL</t>
+        </is>
+      </c>
+      <c r="D122" s="10" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>661000</v>
+      </c>
+      <c r="G122" s="13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H122" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="10" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="K122" s="10" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="15" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>629200</v>
+      </c>
+      <c r="G123" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H123" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>4.462</v>
+      </c>
+      <c r="K123" s="10" t="n">
+        <v>4.446</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="15" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>0.03240000000000001</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>623400</v>
+      </c>
+      <c r="G124" s="13" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H124" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>2.133</v>
+      </c>
+      <c r="K124" s="10" t="n">
+        <v>2.222</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="15" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>620300</v>
+      </c>
+      <c r="G125" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H125" t="n">
+        <v>63.87</v>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="K125" s="10" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="15" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>594800</v>
+      </c>
+      <c r="G126" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H126" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="K126" s="10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="15" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>582800</v>
+      </c>
+      <c r="G127" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H127" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="K127" s="10" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="15" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D128" s="10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>579600</v>
+      </c>
+      <c r="G128" s="13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H128" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K128" s="10" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0239</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ECOMATE</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>578000</v>
+      </c>
+      <c r="G129" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="K129" s="10" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="15" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D130" s="10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>565400</v>
+      </c>
+      <c r="G130" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H130" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="K130" s="10" t="n">
+        <v>3.519</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="15" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.004099999999999999</v>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>546600</v>
+      </c>
+      <c r="G131" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H131" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>2.467</v>
+      </c>
+      <c r="K131" s="10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="15" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>545400</v>
+      </c>
+      <c r="G132" s="13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H132" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="K132" s="10" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="15" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>541900</v>
+      </c>
+      <c r="G133" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H133" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="K133" s="10" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="15" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PESONA</t>
+        </is>
+      </c>
+      <c r="D134" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>541200</v>
+      </c>
+      <c r="G134" s="13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H134" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="I134" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="K134" s="10" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="15" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E135" s="11" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>521100</v>
+      </c>
+      <c r="G135" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H135" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="I135" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="K135" s="10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="15" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="E136" s="11" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>521100</v>
+      </c>
+      <c r="G136" s="13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H136" t="n">
+        <v>48.22</v>
+      </c>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="K136" s="10" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="15" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F137" s="12" t="n">
+        <v>506800</v>
+      </c>
+      <c r="G137" s="13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H137" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="K137" s="10" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="15" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>505700</v>
+      </c>
+      <c r="G138" s="13" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H138" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="I138" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>7.402</v>
+      </c>
+      <c r="K138" s="10" t="n">
+        <v>7.773</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M117"/>
+  <autoFilter ref="A1:M138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
+++ b/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,9 +97,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,28 +558,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.78</v>
+        <v>2.66</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.013</v>
+        <v>0.027</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3792100</v>
+        <v>1228100</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.71</v>
+        <v>0.23</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>57.6</v>
+        <v>55.55</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.748</v>
+        <v>2.603</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.696</v>
+        <v>2.601</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.6处中性偏上未超买，现价高于50日均线约12%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，现价2.66高于50日均线2.601，RSI 55.55处中性区间，未超买，信号技术面可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -611,28 +611,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.595</v>
+        <v>2.95</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0172</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>6208400</v>
+        <v>1125000</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>55.96</v>
+        <v>59.52</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.573</v>
+        <v>2.821</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.55</v>
+        <v>2.706</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.595高于50日均线0.55，RSI 55.96处中性区间，SAR转多信号技术面可靠性尚可。</t>
+          <t>SAR转多信号，RSI 59.52未超买，现价高于50日均线约9%，技术面信号可靠性较高。</t>
         </is>
       </c>
     </row>
@@ -664,28 +664,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.33</v>
+        <v>0.78</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.0313</v>
+        <v>0.013</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1323100</v>
+        <v>4046400</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.68</v>
+        <v>57.6</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.317</v>
+        <v>0.748</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.329</v>
+        <v>0.696</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.68未超买，现价略高于50日均线，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 57.6处中性偏上，未超买；现价0.78高于50日均线0.696约12%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -717,28 +717,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.355</v>
+        <v>0.6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.029</v>
+        <v>0.0169</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>21449000</v>
+        <v>6568800</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>67.58</v>
+        <v>56.83</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.322</v>
+        <v>0.573</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.271</v>
+        <v>0.55</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号出现，但RSI 67.58已接近超买区，现价高于50日均线约31%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+          <t>现价0.60高于50日均线0.55，SAR转多信号获均线支撑；RSI 56.83处中性区间，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -770,223 +770,262 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>-0.0254</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1041000</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>53.89</v>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>6.839</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>6.828</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t>现价6.9略高于50日均线6.828，RSI 53.89处中性区间，未超买，SAR转多信号技术面可靠性尚可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>5284</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>LCTITAN</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1403100</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 57.68处中性偏上，未超买；现价0.33略高于50日均线0.329，技术面信号可靠性尚可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>22667300</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>67.58</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>现价0.355高于50日均线0.271约31%，SAR转多信号获趋势支撑；RSI 67.58接近超买区，动能偏强但上行空间受限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1758500</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>1.191</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 58.61未超买，现价高于50日均线约7.3%，技术面信号可靠性尚可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>7233</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>DUFU</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>-0.0158</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>3055900</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.019</v>
-      </c>
-      <c r="K6" s="3" t="n">
+      <c r="D10" s="3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>3308200</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>3.022</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <v>2.878</v>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，现价高于50日均线约8.4%，RSI 56处中性区间，未超买，信号技术面可靠性尚可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>186442400</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="H7" t="n">
-        <v>39.06</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" s="15" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7113</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TOPGLOV</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>24737300</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H8" t="n">
-        <v>70.27</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" s="15" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1643</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LANDMRK</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>21304000</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="H9" t="n">
-        <v>60.21</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" s="15" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0478</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NWEBHD</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>0.0541</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>15551000</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" s="15" t="inlineStr"/>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>现价高于50日均线约9.4%，RSI 57.56处中性偏上区间，未超买，SAR转多信号技术面可靠性尚可。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -996,28 +1035,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.45</v>
+        <v>0.095</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.0227</v>
+        <v>0.1176</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>13821500</v>
+        <v>190110700</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="H11" t="n">
-        <v>47.56</v>
+        <v>40.78</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -1025,10 +1064,10 @@
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.453</v>
+        <v>0.097</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>0.472</v>
+        <v>0.235</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
@@ -1041,28 +1080,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>-0.0136</v>
+        <v>0.155</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>12783100</v>
+        <v>47428700</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.55</v>
+        <v>1.29</v>
       </c>
       <c r="H12" t="n">
-        <v>75.84999999999999</v>
+        <v>47.71</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -1070,10 +1109,10 @@
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.673</v>
+        <v>0.156</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>0.575</v>
+        <v>0.156</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
@@ -1086,28 +1125,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>0</v>
+        <v>0.96</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>12638500</v>
+        <v>27671500</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H13" t="n">
-        <v>76.67</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1115,10 +1154,10 @@
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.435</v>
+        <v>0.879</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>0.335</v>
+        <v>0.775</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="15" t="inlineStr"/>
@@ -1131,39 +1170,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>LANDMRK</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>0.375</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>12334200</v>
+        <v>22491200</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>1.24</v>
+        <v>10.41</v>
       </c>
       <c r="H14" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.25</v>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.388</v>
+        <v>0.043</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>0.402</v>
+        <v>0.058</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
@@ -1176,40 +1215,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.18</v>
+        <v>0.195</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0541</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>12097000</v>
+        <v>15797500</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="H15" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <v>0.158</v>
-      </c>
+        <v>0.59</v>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="10" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
     </row>
@@ -1221,28 +1253,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>-0.0455</v>
+        <v>0.45</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0.0227</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>11970900</v>
+        <v>14059800</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>1.7</v>
+        <v>0.39</v>
       </c>
       <c r="H16" t="n">
-        <v>82.61</v>
+        <v>47.56</v>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
@@ -1250,10 +1282,10 @@
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.137</v>
+        <v>0.453</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.12</v>
+        <v>0.472</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1266,39 +1298,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>0.1598</v>
+        <v>0.73</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>10652100</v>
+        <v>13808700</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1.89</v>
+        <v>0.59</v>
       </c>
       <c r="H17" t="n">
-        <v>60.25</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.43000000000001</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.838</v>
+        <v>0.673</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.652</v>
+        <v>0.575</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="15" t="inlineStr"/>
@@ -1311,28 +1343,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>0.0698</v>
+        <v>0.505</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>9481000</v>
+        <v>13421400</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.64</v>
+        <v>0.35</v>
       </c>
       <c r="H18" t="n">
-        <v>38.88</v>
+        <v>76.67</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -1340,10 +1372,10 @@
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.474</v>
+        <v>0.435</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.597</v>
+        <v>0.335</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="15" t="inlineStr"/>
@@ -1356,28 +1388,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MQTECH</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.21</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>9015100</v>
+        <v>12955600</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>5.05</v>
+        <v>1.84</v>
       </c>
       <c r="H19" t="n">
-        <v>62.78</v>
+        <v>82.61</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
@@ -1385,10 +1417,10 @@
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.053</v>
+        <v>0.137</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0.056</v>
+        <v>0.12</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="15" t="inlineStr"/>
@@ -1401,39 +1433,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>0.0732</v>
+        <v>0.38</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>8492700</v>
+        <v>12334200</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.87</v>
+        <v>1.24</v>
       </c>
       <c r="H20" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
+        <v>31.76</v>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.221</v>
+        <v>0.388</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.263</v>
+        <v>0.402</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
@@ -1446,28 +1478,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.165</v>
+        <v>0.18</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.0313</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>8079400</v>
+        <v>12122200</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.14</v>
+        <v>4.15</v>
       </c>
       <c r="H21" t="n">
-        <v>53.37</v>
+        <v>63.99</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
@@ -1475,10 +1507,10 @@
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.16</v>
+        <v>0.162</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.149</v>
+        <v>0.158</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="15" t="inlineStr"/>
@@ -1491,39 +1523,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.07139999999999999</v>
+        <v>0.97</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>0.1479</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>7667400</v>
+        <v>12018000</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>4.08</v>
+        <v>2.13</v>
       </c>
       <c r="H22" t="n">
-        <v>43.52</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.83</v>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.837</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.652</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
@@ -1536,28 +1568,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WAVEFRNT</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.14</v>
+        <v>0.455</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0581</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>7021500</v>
+        <v>9882200</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>9</v>
+        <v>0.67</v>
       </c>
       <c r="H23" t="n">
-        <v>53.08</v>
+        <v>37.29</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -1565,10 +1597,10 @@
         </is>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.136</v>
+        <v>0.473</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0.141</v>
+        <v>0.597</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="15" t="inlineStr"/>
@@ -1581,39 +1613,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>0.0185</v>
+        <v>0.16</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>6962300</v>
+        <v>9448600</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H24" t="n">
-        <v>64.81999999999999</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.28</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>2.01</v>
+        <v>0.159</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>1.822</v>
+        <v>0.149</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1635,19 +1667,19 @@
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>6954100</v>
+        <v>9333800</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="H25" t="n">
-        <v>54.27</v>
+        <v>48.71</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -1655,7 +1687,7 @@
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K25" s="10" t="n">
         <v>0.8149999999999999</v>
@@ -1671,28 +1703,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>MQTECH</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.775</v>
+        <v>0.06</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>6820100</v>
+        <v>9107600</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.44</v>
+        <v>5.1</v>
       </c>
       <c r="H26" t="n">
-        <v>50.93</v>
+        <v>62.78</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -1700,10 +1732,10 @@
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.774</v>
+        <v>0.053</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.775</v>
+        <v>0.056</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1716,39 +1748,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.115</v>
+        <v>2.21</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.0455</v>
+        <v>0.0231</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>6797800</v>
+        <v>9042400</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>1.52</v>
+        <v>0.32</v>
       </c>
       <c r="H27" t="n">
-        <v>70.39</v>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.22</v>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.102</v>
+        <v>2.011</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0.08599999999999999</v>
+        <v>1.822</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="15" t="inlineStr"/>
@@ -1761,39 +1793,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>1.69</v>
+        <v>0.22</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.0833</v>
+        <v>0.0732</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>6444200</v>
+        <v>8563800</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="H28" t="n">
-        <v>51.81</v>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.44</v>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="10" t="n">
-        <v>1.653</v>
+        <v>0.221</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>1.735</v>
+        <v>0.263</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="15" t="inlineStr"/>
@@ -1806,28 +1838,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7146</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>AEM</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>-0.0595</v>
+        <v>0.05</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.25</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>6116200</v>
+        <v>8219000</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.48</v>
+        <v>281.96</v>
       </c>
       <c r="H29" t="n">
-        <v>35.01</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -1835,10 +1867,10 @@
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.457</v>
+        <v>0.043</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.573</v>
+        <v>0.046</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr"/>
@@ -1851,28 +1883,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>0.0345</v>
+        <v>0.86</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>5970700</v>
+        <v>8145800</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="H30" t="n">
-        <v>38.44</v>
+        <v>40.85</v>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
@@ -1880,10 +1912,10 @@
         </is>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.559</v>
+        <v>0.867</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>1.837</v>
+        <v>0.868</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="15" t="inlineStr"/>
@@ -1896,28 +1928,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>0.039</v>
+        <v>0.065</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>5867900</v>
+        <v>7867400</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.48</v>
+        <v>4.19</v>
       </c>
       <c r="H31" t="n">
-        <v>50.85</v>
+        <v>43.52</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -1925,10 +1957,10 @@
         </is>
       </c>
       <c r="J31" s="10" t="n">
-        <v>2.101</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>2.226</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="15" t="inlineStr"/>
@@ -1941,39 +1973,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HBGLOB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>-0.5</v>
+        <v>0.775</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>5837500</v>
+        <v>7621100</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>27.37</v>
+        <v>0.49</v>
       </c>
       <c r="H32" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.93</v>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.029</v>
+        <v>0.774</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0.031</v>
+        <v>0.775</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="15" t="inlineStr"/>
@@ -1986,39 +2018,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>5821500</v>
+        <v>7308000</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="H33" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I33" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.867</v>
+        <v>0.306</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0.868</v>
+        <v>0.303</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2031,28 +2063,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>WAVEFRNT</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.38</v>
+        <v>0.14</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.0133</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>5811300</v>
+        <v>7024000</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>0.85</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>58.47</v>
+        <v>53.08</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
@@ -2060,10 +2092,10 @@
         </is>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.373</v>
+        <v>0.136</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0.37</v>
+        <v>0.141</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="15" t="inlineStr"/>
@@ -2076,28 +2108,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.11</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>5719300</v>
+        <v>6901400</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="H35" t="n">
-        <v>79.91</v>
+        <v>66.55</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2105,10 +2137,10 @@
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.465</v>
+        <v>0.101</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.44</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2121,39 +2153,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>0</v>
+        <v>1.68</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>5420000</v>
+        <v>6811800</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.28</v>
+        <v>1.09</v>
       </c>
       <c r="H36" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.9</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.307</v>
+        <v>1.652</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.303</v>
+        <v>1.734</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr"/>
@@ -2166,28 +2198,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>0.0435</v>
+        <v>0.395</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>-0.0595</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>5363900</v>
+        <v>6579800</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="H37" t="n">
-        <v>34.14</v>
+        <v>35.01</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2195,10 +2227,10 @@
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.279</v>
+        <v>0.457</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>1.479</v>
+        <v>0.573</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="15" t="inlineStr"/>
@@ -2211,39 +2243,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>0</v>
+        <v>0.065</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>5000700</v>
+        <v>6362900</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.44</v>
+        <v>5.72</v>
       </c>
       <c r="H38" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
+        <v>53.65</v>
+      </c>
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.283</v>
+        <v>0.063</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.279</v>
+        <v>0.065</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2256,39 +2288,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>0.0345</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>4726300</v>
+        <v>6290100</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="H39" t="n">
-        <v>48</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.44</v>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.605</v>
+        <v>1.559</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>0.617</v>
+        <v>1.837</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2301,39 +2333,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>0</v>
+        <v>1.21</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>0.0522</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>4539500</v>
+        <v>6248100</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>2.01</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.66</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.13</v>
+        <v>1.28</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.14</v>
+        <v>1.479</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2346,40 +2378,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>4439500</v>
+        <v>6085000</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="H41" t="n">
-        <v>63.72</v>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="K41" s="10" t="n">
-        <v>0.619</v>
-      </c>
+        <v>54.46</v>
+      </c>
+      <c r="I41" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
     </row>
@@ -2391,28 +2419,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.48</v>
+        <v>2.13</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.0213</v>
+        <v>0.039</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>4413400</v>
+        <v>6042200</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>1.79</v>
+        <v>0.5</v>
       </c>
       <c r="H42" t="n">
-        <v>60.46</v>
+        <v>50.85</v>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
@@ -2420,10 +2448,10 @@
         </is>
       </c>
       <c r="J42" s="10" t="n">
-        <v>0.456</v>
+        <v>2.101</v>
       </c>
       <c r="K42" s="10" t="n">
-        <v>0.45</v>
+        <v>2.226</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
@@ -2436,39 +2464,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E43" s="18" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E43" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>4271300</v>
+        <v>5994100</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.2</v>
+        <v>0.58</v>
       </c>
       <c r="H43" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.72</v>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.443</v>
+        <v>0.627</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.394</v>
+        <v>0.619</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2481,39 +2509,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>0.0102</v>
+        <v>0.48</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>4057100</v>
+        <v>5975000</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="H44" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.86</v>
+      </c>
+      <c r="I44" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>4.887</v>
+        <v>0.443</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>4.784</v>
+        <v>0.394</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2526,28 +2554,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>1.24</v>
+        <v>0.38</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0.0164</v>
+        <v>0.0133</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>3965800</v>
+        <v>5951500</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.39</v>
+        <v>0.88</v>
       </c>
       <c r="H45" t="n">
-        <v>67.55</v>
+        <v>58.47</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
@@ -2555,10 +2583,10 @@
         </is>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1.118</v>
+        <v>0.373</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>1.066</v>
+        <v>0.37</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="15" t="inlineStr"/>
@@ -2571,39 +2599,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>HBGLOB</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>0.0391</v>
+        <v>0.015</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>-0.5</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3856100</v>
+        <v>5893500</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>0.92</v>
+        <v>27.64</v>
       </c>
       <c r="H46" t="n">
-        <v>62.73</v>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>11.69</v>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.604</v>
+        <v>0.029</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>0.586</v>
+        <v>0.031</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2616,36 +2644,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>0.0222</v>
+        <v>0.535</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3852200</v>
+        <v>5724800</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.2</v>
+        <v>1.38</v>
       </c>
       <c r="H47" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="10" t="n"/>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="K47" s="10" t="n">
+        <v>0.44</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
     </row>
@@ -2657,39 +2689,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.99</v>
+        <v>4.94</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.0102</v>
+        <v>0.0061</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>3733000</v>
+        <v>5478500</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>1.68</v>
+        <v>0.23</v>
       </c>
       <c r="H48" t="n">
-        <v>33.83</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55</v>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>1.052</v>
+        <v>4.885</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>1.112</v>
+        <v>4.783</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2702,39 +2734,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E49" s="18" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>3717700</v>
+        <v>5202000</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="H49" t="n">
-        <v>36.57</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
+        <v>43.64</v>
+      </c>
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>4.54</v>
+        <v>0.283</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>4.642</v>
+        <v>0.279</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2756,27 +2788,27 @@
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.0217</v>
+        <v>0.0326</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>3606700</v>
+        <v>5037400</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="H50" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
+        <v>43.84</v>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.992</v>
+        <v>0.993</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>0.989</v>
@@ -2792,39 +2824,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>3355600</v>
+        <v>4991100</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.19</v>
+        <v>0.54</v>
       </c>
       <c r="H51" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
+        <v>48</v>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.127</v>
+        <v>0.605</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>0.145</v>
+        <v>0.617</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2837,39 +2869,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E52" s="11" t="n">
-        <v>0.0476</v>
+        <v>4.45</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>3354300</v>
+        <v>4962600</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="H52" t="n">
-        <v>70.65000000000001</v>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.57</v>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>1.128</v>
+        <v>4.54</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0.987</v>
+        <v>4.642</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2882,28 +2914,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>0.48</v>
+        <v>1.24</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.0213</v>
+        <v>0.0164</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>3199200</v>
+        <v>4698800</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H53" t="n">
-        <v>45.16</v>
+        <v>67.55</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -2911,10 +2943,10 @@
         </is>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.481</v>
+        <v>1.118</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>0.533</v>
+        <v>1.066</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="15" t="inlineStr"/>
@@ -2927,39 +2959,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>-0.049</v>
+        <v>0.475</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>3134500</v>
+        <v>4574300</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>0.84</v>
+        <v>1.86</v>
       </c>
       <c r="H54" t="n">
-        <v>31.47</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.94</v>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="10" t="n">
-        <v>1.43</v>
+        <v>0.456</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>1.453</v>
+        <v>0.45</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="15" t="inlineStr"/>
@@ -2972,39 +3004,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.505</v>
+        <v>0.67</v>
       </c>
       <c r="E55" s="11" t="n">
-        <v>0.0202</v>
+        <v>0.0469</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>3078700</v>
+        <v>4572300</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="H55" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.39</v>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.524</v>
+        <v>0.604</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.556</v>
+        <v>0.587</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3017,39 +3049,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E56" s="11" t="n">
-        <v>0.0278</v>
+        <v>0.125</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>3046000</v>
+        <v>4539500</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>0.16</v>
+        <v>2.01</v>
       </c>
       <c r="H56" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.46</v>
+      </c>
+      <c r="I56" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.185</v>
+        <v>0.13</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0.187</v>
+        <v>0.14</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3062,39 +3094,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0182</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>LKL</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v>0.0196</v>
+        <v>0.03</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>2922100</v>
+        <v>4316000</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.18</v>
+        <v>15.24</v>
       </c>
       <c r="H57" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
+        <v>47.17</v>
+      </c>
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>5.353</v>
+        <v>0.031</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>5.522</v>
+        <v>0.033</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3107,39 +3139,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>0.325</v>
+        <v>1.01</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>0.0484</v>
+        <v>0.0306</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>2751000</v>
+        <v>4245500</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="H58" t="n">
-        <v>59.54</v>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.69</v>
+      </c>
+      <c r="I58" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.3</v>
+        <v>1.054</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>0.325</v>
+        <v>1.112</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3152,39 +3184,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>9.98</v>
+        <v>1.34</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>-0.001</v>
+        <v>-0.0629</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>2423500</v>
+        <v>3739000</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="I59" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.84</v>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>9.993</v>
+        <v>1.428</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>10.1</v>
+        <v>1.453</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3197,28 +3229,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>0.0319</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>2383000</v>
+        <v>3603200</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="H60" t="n">
-        <v>72.53</v>
+        <v>47.24</v>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
@@ -3226,10 +3258,10 @@
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.482</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>0.782</v>
+        <v>0.533</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3242,39 +3274,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>-0.0058</v>
+        <v>2.61</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>2290100</v>
+        <v>3584900</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.71</v>
+        <v>0.21</v>
       </c>
       <c r="H61" t="n">
-        <v>86.70999999999999</v>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.27</v>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>3.117</v>
+        <v>2.594</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>2.641</v>
+        <v>2.567</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3287,39 +3319,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E62" s="11" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.11</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>2261100</v>
+        <v>3460400</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H62" t="n">
-        <v>53.44</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
+        <v>34.76</v>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>0.769</v>
+        <v>0.127</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0.771</v>
+        <v>0.145</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3332,39 +3364,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>-0.0037</v>
+        <v>1.32</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>2198800</v>
+        <v>3446600</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.22</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.65000000000001</v>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>2.72</v>
+        <v>1.128</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>2.748</v>
+        <v>0.987</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
@@ -3377,28 +3409,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E64" s="18" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>2176700</v>
+        <v>3396600</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>1.46</v>
+        <v>0.18</v>
       </c>
       <c r="H64" t="n">
-        <v>42.99</v>
+        <v>49.32</v>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
@@ -3406,10 +3438,10 @@
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>0.229</v>
+        <v>0.185</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>0.237</v>
+        <v>0.187</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3422,39 +3454,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>2.21</v>
+        <v>5.21</v>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0.0327</v>
+        <v>0.0216</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>2163800</v>
+        <v>3344300</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="H65" t="n">
-        <v>62.12</v>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.71</v>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>2.128</v>
+        <v>5.354</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>2.084</v>
+        <v>5.522</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3467,39 +3499,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>-0.009399999999999999</v>
+        <v>0.51</v>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>2102100</v>
+        <v>3167500</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.2</v>
+        <v>0.87</v>
       </c>
       <c r="H66" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="I66" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.91</v>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>2.106</v>
+        <v>0.524</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>2.113</v>
+        <v>0.556</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3512,39 +3544,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E67" s="18" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>2025200</v>
+        <v>2997800</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="H67" t="n">
-        <v>38.94</v>
-      </c>
-      <c r="I67" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.8</v>
+      </c>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="10" t="n">
-        <v>0.312</v>
+        <v>0.729</v>
       </c>
       <c r="K67" s="10" t="n">
-        <v>0.355</v>
+        <v>0.724</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
@@ -3557,39 +3589,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>2.57</v>
+        <v>0.05</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.0039</v>
+        <v>0.1111</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>1975700</v>
+        <v>2976300</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.12</v>
+        <v>0.27</v>
       </c>
       <c r="H68" t="n">
-        <v>48.66</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
+        <v>37.95</v>
+      </c>
+      <c r="I68" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>2.59</v>
+        <v>0.058</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>2.566</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3602,28 +3634,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.905</v>
+        <v>0.325</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0.0112</v>
+        <v>0.0484</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>1946700</v>
+        <v>2962300</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.47</v>
+        <v>1.99</v>
       </c>
       <c r="H69" t="n">
-        <v>48.48</v>
+        <v>59.54</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -3631,10 +3663,10 @@
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>0.898</v>
+        <v>0.3</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0.954</v>
+        <v>0.325</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3647,28 +3679,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0381</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>POLYMER</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>-0.0122</v>
+        <v>0.175</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1876500</v>
+        <v>2917900</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.16</v>
+        <v>1.37</v>
       </c>
       <c r="H70" t="n">
-        <v>52.4</v>
+        <v>42.17</v>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
@@ -3676,10 +3708,10 @@
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>0.402</v>
+        <v>0.182</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>0.384</v>
+        <v>0.191</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3692,28 +3724,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0039</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>GFM</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>-0.017</v>
+        <v>0.18</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>1868100</v>
+        <v>2902600</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.25</v>
+        <v>3.74</v>
       </c>
       <c r="H71" t="n">
-        <v>60.59</v>
+        <v>52.09</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -3721,10 +3753,10 @@
         </is>
       </c>
       <c r="J71" s="10" t="n">
-        <v>3.846</v>
+        <v>0.176</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>3.338</v>
+        <v>0.187</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="15" t="inlineStr"/>
@@ -3737,28 +3769,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E72" s="11" t="n">
-        <v>0.0184</v>
+        <v>9.98</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>1798200</v>
+        <v>2817700</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H72" t="n">
-        <v>53.38</v>
+        <v>47.39</v>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
@@ -3766,10 +3798,10 @@
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>1.63</v>
+        <v>9.993</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>1.67</v>
+        <v>10.1</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3782,39 +3814,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v>0.0108</v>
+        <v>0.4</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>1797500</v>
+        <v>2770800</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H73" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.64</v>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.488</v>
+        <v>0.402</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>0.472</v>
+        <v>0.384</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3827,39 +3859,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.835</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>1755700</v>
+        <v>2710300</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.08</v>
+        <v>0.55</v>
       </c>
       <c r="H74" t="n">
-        <v>46.82</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.53</v>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="10" t="n">
-        <v>4.729</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>4.8</v>
+        <v>0.782</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="15" t="inlineStr"/>
@@ -3872,28 +3904,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>-0.0413</v>
+        <v>1.66</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>1739100</v>
+        <v>2657900</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="H75" t="n">
-        <v>53.29</v>
+        <v>53.38</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
@@ -3901,10 +3933,10 @@
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>2.299</v>
+        <v>1.63</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3917,28 +3949,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E76" s="11" t="n">
-        <v>0.0233</v>
+        <v>4</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>-0.0268</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1559900</v>
+        <v>2649100</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.22</v>
+        <v>0.35</v>
       </c>
       <c r="H76" t="n">
-        <v>53.61</v>
+        <v>59.04</v>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
@@ -3946,10 +3978,10 @@
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>0.43</v>
+        <v>3.842</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0.417</v>
+        <v>3.337</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3962,33 +3994,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>PICORP</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.725</v>
+        <v>0.055</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>0.0211</v>
+        <v>0.2222</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>1542200</v>
+        <v>2616000</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
+        <v>7.66</v>
+      </c>
+      <c r="H77" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="K77" s="10" t="n">
+        <v>0.056</v>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
     </row>
@@ -4000,39 +4039,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E78" s="11" t="n">
-        <v>0.0192</v>
+        <v>2.65</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>1507600</v>
+        <v>2580300</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H78" t="n">
-        <v>42.34</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
+        <v>42.92</v>
+      </c>
+      <c r="I78" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.278</v>
+        <v>2.719</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>0.282</v>
+        <v>2.748</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4045,28 +4084,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>0</v>
+        <v>3.4</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>-0.0145</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>1465700</v>
+        <v>2534700</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.22</v>
+        <v>0.79</v>
       </c>
       <c r="H79" t="n">
-        <v>62.05</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
@@ -4074,10 +4113,10 @@
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>1.193</v>
+        <v>3.114</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>1.156</v>
+        <v>2.64</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4090,39 +4129,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>AMEREIT</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E80" s="11" t="n">
-        <v>0.0426</v>
+        <v>1.6</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>1447500</v>
+        <v>2450000</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>1.32</v>
+        <v>28.85</v>
       </c>
       <c r="H80" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
+        <v>56.91</v>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>0.246</v>
+        <v>1.56</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>0.25</v>
+        <v>1.543</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4135,28 +4174,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>-0.0154</v>
+        <v>2.59</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>0.0157</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>1383800</v>
+        <v>2365300</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="H81" t="n">
-        <v>40.9</v>
+        <v>46.07</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4164,10 +4203,10 @@
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>0.676</v>
+        <v>2.635</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>0.731</v>
+        <v>2.818</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4180,28 +4219,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E82" s="11" t="n">
-        <v>0.007800000000000001</v>
+        <v>2.11</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1375100</v>
+        <v>2346900</v>
       </c>
       <c r="G82" s="13" t="n">
         <v>0.23</v>
       </c>
       <c r="H82" t="n">
-        <v>45.16</v>
+        <v>51.01</v>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
@@ -4209,10 +4248,10 @@
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>2.633</v>
+        <v>2.107</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>2.818</v>
+        <v>2.114</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4225,28 +4264,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="E83" s="11" t="n">
-        <v>0.0281</v>
+        <v>0.13</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>1331300</v>
+        <v>2318100</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.23</v>
+        <v>1.46</v>
       </c>
       <c r="H83" t="n">
-        <v>61.8</v>
+        <v>50.66</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4254,10 +4293,10 @@
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>6.409</v>
+        <v>0.129</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>6.048</v>
+        <v>0.13</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4270,39 +4309,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>TALAMT</t>
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>1282400</v>
+        <v>2316800</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>0.46</v>
+        <v>1.39</v>
       </c>
       <c r="H84" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.25</v>
+      </c>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="10" t="n">
-        <v>0.633</v>
+        <v>0.078</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>0.624</v>
+        <v>0.08</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="15" t="inlineStr"/>
@@ -4315,39 +4354,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>-0.0053</v>
+        <v>0.775</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>1281200</v>
+        <v>2314200</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H85" t="n">
-        <v>53.74</v>
-      </c>
-      <c r="I85" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.94</v>
+      </c>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.944</v>
+        <v>0.769</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>0.897</v>
+        <v>0.771</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4360,39 +4399,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>0</v>
+        <v>0.915</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>0.0223</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>1264500</v>
+        <v>2296000</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>1.45</v>
+        <v>0.55</v>
       </c>
       <c r="H86" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.32</v>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.271</v>
+        <v>0.899</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>0.268</v>
+        <v>0.954</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4405,28 +4444,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v>0.0519</v>
+        <v>0.225</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>1252300</v>
+        <v>2273200</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>0.42</v>
+        <v>1.53</v>
       </c>
       <c r="H87" t="n">
-        <v>60.18</v>
+        <v>42.99</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
@@ -4434,10 +4473,10 @@
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>1.308</v>
+        <v>0.229</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>1.253</v>
+        <v>0.237</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4450,28 +4489,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.185</v>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>1250300</v>
+        <v>2253600</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="H88" t="n">
-        <v>47.67</v>
+        <v>42.99</v>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
@@ -4479,10 +4518,10 @@
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>0.903</v>
+        <v>0.189</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>0.897</v>
+        <v>0.204</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4495,39 +4534,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E89" s="11" t="n">
-        <v>0.0104</v>
+        <v>4.72</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>1220400</v>
+        <v>2218000</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="H89" t="n">
-        <v>45.42</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
+        <v>47.73</v>
+      </c>
+      <c r="I89" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.492</v>
+        <v>4.73</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>0.512</v>
+        <v>4.8</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4540,39 +4579,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E90" s="11" t="n">
-        <v>0.011</v>
+        <v>2.33</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>-0.0372</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>1190400</v>
+        <v>2214300</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>1.5</v>
+        <v>0.63</v>
       </c>
       <c r="H90" t="n">
-        <v>38.87</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.05</v>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>0.944</v>
+        <v>2.3</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>0.968</v>
+        <v>2.221</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4585,39 +4624,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>0.265</v>
+        <v>2.21</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>0.06</v>
+        <v>0.0327</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>1182800</v>
+        <v>2180700</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.21</v>
+        <v>0.89</v>
       </c>
       <c r="H91" t="n">
-        <v>49.13</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.12</v>
+      </c>
+      <c r="I91" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>0.263</v>
+        <v>2.128</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>0.28</v>
+        <v>2.084</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4630,28 +4669,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E92" s="11" t="n">
-        <v>0.0588</v>
+        <v>0.3</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>1180100</v>
+        <v>2141500</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>1.17</v>
+        <v>0.32</v>
       </c>
       <c r="H92" t="n">
-        <v>60.77</v>
+        <v>38.94</v>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
@@ -4659,10 +4698,10 @@
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>0.341</v>
+        <v>0.312</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4675,39 +4714,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>-0.0108</v>
+        <v>0.555</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>1168400</v>
+        <v>2080900</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.53</v>
+        <v>0.96</v>
       </c>
       <c r="H93" t="n">
-        <v>47.63</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
+        <v>46.19</v>
+      </c>
+      <c r="I93" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>0.462</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0.462</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4720,39 +4759,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.345</v>
+        <v>0.17</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>0.0299</v>
+        <v>0.0303</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>1158300</v>
+        <v>2052300</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
       <c r="H94" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.32</v>
+      </c>
+      <c r="I94" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="10" t="n">
-        <v>0.347</v>
+        <v>0.172</v>
       </c>
       <c r="K94" s="10" t="n">
-        <v>0.331</v>
+        <v>0.188</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="15" t="inlineStr"/>
@@ -4765,39 +4804,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>HUBLINE</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E95" s="11" t="n">
-        <v>0.0121</v>
+        <v>0.03</v>
+      </c>
+      <c r="E95" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>1151000</v>
+        <v>1958000</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="H95" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.24</v>
+      </c>
+      <c r="I95" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>0.861</v>
+        <v>0.03</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>0.923</v>
+        <v>0.031</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4810,39 +4849,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>0.425</v>
+        <v>0.265</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>0.0241</v>
+        <v>0.0192</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1147300</v>
+        <v>1886400</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="H96" t="n">
-        <v>57.01</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
+        <v>42.34</v>
+      </c>
+      <c r="I96" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>0.403</v>
+        <v>0.278</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>0.368</v>
+        <v>0.282</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4855,40 +4894,33 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>1.16</v>
+        <v>0.1</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>0.045</v>
+        <v>0.1111</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1112300</v>
+        <v>1859800</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H97" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
+        <v>0.09</v>
+      </c>
+      <c r="I97" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J97" s="10" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="K97" s="10" t="n">
-        <v>0.945</v>
-      </c>
+      <c r="J97" s="10" t="n"/>
+      <c r="K97" s="10" t="n"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
     </row>
@@ -4900,39 +4932,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>1.17</v>
+        <v>0.475</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>0.0174</v>
+        <v>0.0215</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1105700</v>
+        <v>1822800</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="H98" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
+        <v>47.4</v>
+      </c>
+      <c r="I98" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>1.196</v>
+        <v>0.489</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>1.278</v>
+        <v>0.472</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4945,39 +4977,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E99" s="18" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1097200</v>
+        <v>1801400</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="H99" t="n">
-        <v>44.94</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.61</v>
+      </c>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.728</v>
+        <v>0.43</v>
       </c>
       <c r="K99" s="10" t="n">
-        <v>0.724</v>
+        <v>0.417</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -4990,39 +5022,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E100" s="11" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.055</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1070200</v>
+        <v>1773300</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H100" t="n">
-        <v>68.81</v>
-      </c>
-      <c r="I100" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.53</v>
+      </c>
+      <c r="I100" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="10" t="n">
-        <v>1.995</v>
+        <v>0.051</v>
       </c>
       <c r="K100" s="10" t="n">
-        <v>1.969</v>
+        <v>0.047</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
@@ -5035,39 +5067,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SJC</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="E101" s="11" t="n">
-        <v>0.0074</v>
+        <v>0.475</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1067800</v>
+        <v>1731300</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.39</v>
+        <v>6.92</v>
       </c>
       <c r="H101" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
+        <v>48.39</v>
+      </c>
+      <c r="I101" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>1.284</v>
+        <v>0.475</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>1.193</v>
+        <v>0.482</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="15" t="inlineStr"/>
@@ -5080,39 +5112,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>0.615</v>
+        <v>6.98</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>0.025</v>
+        <v>0.0341</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1029600</v>
+        <v>1729700</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H102" t="n">
-        <v>57.89</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.32</v>
+      </c>
+      <c r="I102" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.582</v>
+        <v>6.413</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>0.493</v>
+        <v>6.049</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5125,39 +5157,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>0.615</v>
+        <v>0.485</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>0.025</v>
+        <v>0.0104</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>934500</v>
+        <v>1713300</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H103" t="n">
-        <v>42.74</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
+        <v>45.42</v>
+      </c>
+      <c r="I103" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J103" s="10" t="n">
-        <v>0.64</v>
+        <v>0.492</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>0.679</v>
+        <v>0.512</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="15" t="inlineStr"/>
@@ -5170,39 +5202,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>-0.049</v>
+        <v>0.005</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>929900</v>
+        <v>1667100</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>1.68</v>
+        <v>1.15</v>
       </c>
       <c r="H104" t="n">
-        <v>58.54</v>
-      </c>
-      <c r="I104" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I104" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>0.654</v>
+        <v>0.005</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>0.618</v>
+        <v>0.006</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5215,39 +5247,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>0.595</v>
+        <v>1.16</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>926200</v>
+        <v>1646300</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H105" t="n">
-        <v>59.29</v>
-      </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.74</v>
+      </c>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.195</v>
       </c>
       <c r="K105" s="10" t="n">
-        <v>0.531</v>
+        <v>1.278</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="15" t="inlineStr"/>
@@ -5269,27 +5301,27 @@
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>-0.0014</v>
+        <v>7.11</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>896400</v>
+        <v>1635300</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H106" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="I106" s="16" t="inlineStr">
+        <v>32.23</v>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J106" s="10" t="n">
-        <v>7.313</v>
+        <v>7.314</v>
       </c>
       <c r="K106" s="10" t="n">
         <v>7.599</v>
@@ -5305,40 +5337,33 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>0.61</v>
+        <v>0.725</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>0.0083</v>
+        <v>0.0211</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>889000</v>
+        <v>1617300</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H107" t="n">
-        <v>65.55</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
+        <v>0.05</v>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J107" s="10" t="n">
-        <v>0.554</v>
-      </c>
-      <c r="K107" s="10" t="n">
-        <v>0.492</v>
-      </c>
+      <c r="J107" s="10" t="n"/>
+      <c r="K107" s="10" t="n"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="15" t="inlineStr"/>
     </row>
@@ -5350,28 +5375,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E108" s="11" t="n">
-        <v>0.0292</v>
+        <v>0.025</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>-0.1667</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>883500</v>
+        <v>1603700</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.14</v>
+        <v>0.41</v>
       </c>
       <c r="H108" t="n">
-        <v>49.3</v>
+        <v>59.21</v>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
@@ -5379,10 +5404,10 @@
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.884</v>
+        <v>0.02</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>0.865</v>
+        <v>0.018</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="15" t="inlineStr"/>
@@ -5395,39 +5420,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E109" s="11" t="n">
-        <v>0.0301</v>
+        <v>0.865</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>882700</v>
+        <v>1592600</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.35</v>
+        <v>0.54</v>
       </c>
       <c r="H109" t="n">
-        <v>48.55</v>
-      </c>
-      <c r="I109" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.98</v>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="10" t="n">
-        <v>1.363</v>
+        <v>0.866</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>1.431</v>
+        <v>0.861</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="15" t="inlineStr"/>
@@ -5440,39 +5465,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>0.74</v>
+        <v>1.19</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>0.035</v>
+        <v>0.0721</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>876500</v>
+        <v>1592000</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="H110" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="I110" s="16" t="inlineStr">
+        <v>61.19</v>
+      </c>
+      <c r="I110" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J110" s="10" t="n">
-        <v>0.752</v>
+        <v>1.108</v>
       </c>
       <c r="K110" s="10" t="n">
-        <v>0.765</v>
+        <v>0.945</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
@@ -5485,39 +5510,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>-0.0156</v>
+        <v>0.245</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>0.0426</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>873500</v>
+        <v>1586200</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0.13</v>
+        <v>1.45</v>
       </c>
       <c r="H111" t="n">
-        <v>46.55</v>
-      </c>
-      <c r="I111" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.9</v>
+      </c>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>1.274</v>
+        <v>0.246</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>1.319</v>
+        <v>0.25</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5530,39 +5555,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>0.775</v>
+        <v>0.43</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.0361</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>850400</v>
+        <v>1559000</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="H112" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="I112" s="16" t="inlineStr">
+        <v>57.91</v>
+      </c>
+      <c r="I112" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.747</v>
+        <v>0.403</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>0.709</v>
+        <v>0.368</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5575,28 +5600,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>6.9</v>
+        <v>0.64</v>
       </c>
       <c r="E113" s="17" t="n">
-        <v>-0.0254</v>
+        <v>-0.0154</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>822900</v>
+        <v>1549800</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
       <c r="H113" t="n">
-        <v>53.89</v>
+        <v>40.9</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -5604,10 +5629,10 @@
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>6.839</v>
+        <v>0.676</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>6.828</v>
+        <v>0.731</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5620,28 +5645,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="E114" s="11" t="n">
-        <v>0.0201</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>792700</v>
+        <v>1485800</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.17</v>
+        <v>0.35</v>
       </c>
       <c r="H114" t="n">
-        <v>58.01</v>
+        <v>51.97</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
@@ -5649,10 +5674,10 @@
         </is>
       </c>
       <c r="J114" s="10" t="n">
-        <v>7.332</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K114" s="10" t="n">
-        <v>6.985</v>
+        <v>0.897</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
@@ -5665,39 +5690,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>TWL</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>-0.0266</v>
+        <v>0.025</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>783700</v>
+        <v>1478900</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H115" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="I115" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.81</v>
+      </c>
+      <c r="I115" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>1.813</v>
+        <v>0.024</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>1.909</v>
+        <v>0.024</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5710,28 +5735,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0593</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>769600</v>
+        <v>1456000</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.11</v>
+        <v>0.48</v>
       </c>
       <c r="H116" t="n">
-        <v>61.39</v>
+        <v>60.77</v>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
@@ -5739,10 +5764,10 @@
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>1.241</v>
+        <v>1.309</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>1.212</v>
+        <v>1.253</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5755,39 +5780,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0129</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SRIDGE</t>
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="E117" s="11" t="n">
-        <v>0.024</v>
+        <v>0.115</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>739700</v>
+        <v>1434100</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.2</v>
+        <v>1.28</v>
       </c>
       <c r="H117" t="n">
-        <v>62.81</v>
-      </c>
-      <c r="I117" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.86</v>
+      </c>
+      <c r="I117" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="10" t="n">
-        <v>10.56</v>
+        <v>0.119</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>9.938000000000001</v>
+        <v>0.131</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="15" t="inlineStr"/>
@@ -5800,28 +5825,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E118" s="11" t="n">
-        <v>0.012</v>
+        <v>2.11</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>730000</v>
+        <v>1422400</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="H118" t="n">
-        <v>60.06</v>
+        <v>68</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
@@ -5829,10 +5854,10 @@
         </is>
       </c>
       <c r="J118" s="10" t="n">
-        <v>4.024</v>
+        <v>1.994</v>
       </c>
       <c r="K118" s="10" t="n">
-        <v>3.685</v>
+        <v>1.968</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -5845,40 +5870,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D119" s="10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E119" s="11" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>726700</v>
-      </c>
-      <c r="G119" s="13" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H119" t="n">
-        <v>71.94</v>
-      </c>
-      <c r="I119" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="K119" s="10" t="n">
-        <v>1.352</v>
-      </c>
+        <v>1370300</v>
+      </c>
+      <c r="G119" s="13" t="n"/>
+      <c r="I119" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J119" s="10" t="n"/>
+      <c r="K119" s="10" t="n"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="15" t="inlineStr"/>
     </row>
@@ -5890,28 +5906,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.36</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>701700</v>
+        <v>1369900</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.34</v>
+        <v>1.36</v>
       </c>
       <c r="H120" t="n">
-        <v>48.28</v>
+        <v>60.77</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
@@ -5919,10 +5935,10 @@
         </is>
       </c>
       <c r="J120" s="10" t="n">
-        <v>0.64</v>
+        <v>0.341</v>
       </c>
       <c r="K120" s="10" t="n">
-        <v>0.63</v>
+        <v>0.356</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="15" t="inlineStr"/>
@@ -5935,28 +5951,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="E121" s="11" t="n">
-        <v>0.005</v>
+        <v>0.635</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>674800</v>
+        <v>1322300</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>0.18</v>
+        <v>0.64</v>
       </c>
       <c r="H121" t="n">
-        <v>57.81</v>
+        <v>48.28</v>
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
@@ -5964,10 +5980,10 @@
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>3.844</v>
+        <v>0.64</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>3.768</v>
+        <v>0.63</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="15" t="inlineStr"/>
@@ -5980,39 +5996,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>0007</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>PUC</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.035</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>661000</v>
+        <v>1307800</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>1.61</v>
+        <v>0.09</v>
       </c>
       <c r="H122" t="n">
-        <v>24.12</v>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
+        <v>48.23</v>
+      </c>
+      <c r="I122" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J122" s="10" t="n">
-        <v>0.629</v>
+        <v>0.037</v>
       </c>
       <c r="K122" s="10" t="n">
-        <v>0.652</v>
+        <v>0.034</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -6025,39 +6041,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="E123" s="11" t="n">
-        <v>0.0022</v>
+        <v>0.635</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>629200</v>
+        <v>1292600</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.12</v>
+        <v>0.46</v>
       </c>
       <c r="H123" t="n">
-        <v>58.11</v>
-      </c>
-      <c r="I123" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.46</v>
+      </c>
+      <c r="I123" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>4.462</v>
+        <v>0.634</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>4.446</v>
+        <v>0.624</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="15" t="inlineStr"/>
@@ -6070,39 +6086,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>2.23</v>
+        <v>0.26</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>623400</v>
+        <v>1270500</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.46</v>
+        <v>0.22</v>
       </c>
       <c r="H124" t="n">
-        <v>56.94</v>
-      </c>
-      <c r="I124" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.74</v>
+      </c>
+      <c r="I124" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="10" t="n">
-        <v>2.133</v>
+        <v>0.263</v>
       </c>
       <c r="K124" s="10" t="n">
-        <v>2.222</v>
+        <v>0.28</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -6115,39 +6131,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E125" s="11" t="n">
-        <v>0.0278</v>
+        <v>0.26</v>
+      </c>
+      <c r="E125" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>620300</v>
+        <v>1264500</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>0.22</v>
+        <v>1.45</v>
       </c>
       <c r="H125" t="n">
-        <v>63.87</v>
-      </c>
-      <c r="I125" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.3</v>
+      </c>
+      <c r="I125" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="10" t="n">
-        <v>2.763</v>
+        <v>0.271</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>2.405</v>
+        <v>0.268</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="15" t="inlineStr"/>
@@ -6160,39 +6176,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>2.64</v>
+        <v>0.14</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>0.0193</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>594800</v>
+        <v>1259300</v>
       </c>
       <c r="G126" s="13" t="n">
         <v>0.11</v>
       </c>
       <c r="H126" t="n">
-        <v>53.95</v>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
+        <v>60.95</v>
+      </c>
+      <c r="I126" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J126" s="10" t="n">
-        <v>2.601</v>
+        <v>0.128</v>
       </c>
       <c r="K126" s="10" t="n">
-        <v>2.6</v>
+        <v>0.107</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -6205,39 +6221,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E127" s="11" t="n">
-        <v>0.028</v>
+        <v>0.89</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>582800</v>
+        <v>1256800</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.18</v>
+        <v>0.66</v>
       </c>
       <c r="H127" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.67</v>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="10" t="n">
-        <v>1.118</v>
+        <v>0.903</v>
       </c>
       <c r="K127" s="10" t="n">
-        <v>1.116</v>
+        <v>0.897</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="15" t="inlineStr"/>
@@ -6250,39 +6266,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E128" s="11" t="n">
-        <v>0.0308</v>
+        <v>0.145</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>579600</v>
+        <v>1253100</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.28</v>
+        <v>0.08</v>
       </c>
       <c r="H128" t="n">
-        <v>54.94</v>
-      </c>
-      <c r="I128" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.24</v>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="10" t="n">
-        <v>1.3</v>
+        <v>0.152</v>
       </c>
       <c r="K128" s="10" t="n">
-        <v>1.309</v>
+        <v>0.174</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -6295,39 +6311,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E129" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.05</v>
+      </c>
+      <c r="E129" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>578000</v>
+        <v>1252500</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="H129" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
+        <v>41.03</v>
+      </c>
+      <c r="I129" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.866</v>
+        <v>0.054</v>
       </c>
       <c r="K129" s="10" t="n">
-        <v>0.861</v>
+        <v>0.057</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="15" t="inlineStr"/>
@@ -6340,39 +6356,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E130" s="17" t="n">
-        <v>-0.0156</v>
+        <v>0.835</v>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>565400</v>
+        <v>1234700</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="H130" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
+        <v>36.7</v>
+      </c>
+      <c r="I130" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J130" s="10" t="n">
-        <v>3.287</v>
+        <v>0.861</v>
       </c>
       <c r="K130" s="10" t="n">
-        <v>3.519</v>
+        <v>0.923</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -6385,39 +6401,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.91</v>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>546600</v>
+        <v>1222400</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>0.13</v>
+        <v>1.54</v>
       </c>
       <c r="H131" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="I131" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.99</v>
+      </c>
+      <c r="I131" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>2.467</v>
+        <v>0.944</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>2.62</v>
+        <v>0.968</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="15" t="inlineStr"/>
@@ -6430,39 +6446,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>0029</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>DIGISTA</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E132" s="11" t="n">
-        <v>0.0115</v>
+        <v>0.03</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>-0.1429</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>545400</v>
+        <v>1218300</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.27</v>
+        <v>30.95</v>
       </c>
       <c r="H132" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="I132" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.96</v>
+      </c>
+      <c r="I132" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="10" t="n">
-        <v>0.888</v>
+        <v>0.036</v>
       </c>
       <c r="K132" s="10" t="n">
-        <v>0.901</v>
+        <v>0.038</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -6475,40 +6491,38 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>EVOCOM</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E133" s="11" t="n">
-        <v>0.0303</v>
+        <v>0.09</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>541900</v>
+        <v>1202900</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="H133" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="I133" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="K133" s="10" t="n">
-        <v>0.6919999999999999</v>
-      </c>
+        <v>0.102</v>
+      </c>
+      <c r="K133" s="10" t="n"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="15" t="inlineStr"/>
     </row>
@@ -6520,39 +6534,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PESONA</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>0.52</v>
+        <v>0.615</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>0.0505</v>
+        <v>0.025</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>541200</v>
+        <v>1193500</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>2.02</v>
+        <v>0.18</v>
       </c>
       <c r="H134" t="n">
-        <v>74.34999999999999</v>
-      </c>
-      <c r="I134" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.89</v>
+      </c>
+      <c r="I134" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="10" t="n">
-        <v>0.475</v>
+        <v>0.582</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>0.474</v>
+        <v>0.493</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -6565,39 +6579,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E135" s="11" t="n">
-        <v>0.0156</v>
+        <v>0.465</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>521100</v>
+        <v>1177300</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="H135" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="I135" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.59</v>
+      </c>
+      <c r="I135" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
-        <v>1.257</v>
+        <v>0.462</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>1.13</v>
+        <v>0.462</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="15" t="inlineStr"/>
@@ -6610,39 +6624,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>0.555</v>
+        <v>0.35</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>0.0472</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>521100</v>
+        <v>1161200</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H136" t="n">
-        <v>48.22</v>
-      </c>
-      <c r="I136" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.74</v>
+      </c>
+      <c r="I136" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="10" t="n">
-        <v>0.553</v>
+        <v>0.347</v>
       </c>
       <c r="K136" s="10" t="n">
-        <v>0.588</v>
+        <v>0.331</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -6655,39 +6669,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>0.765</v>
+        <v>0.615</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>506800</v>
+        <v>1153700</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="H137" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
+        <v>42.74</v>
+      </c>
+      <c r="I137" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.742</v>
+        <v>0.64</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>0.675</v>
+        <v>0.679</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="15" t="inlineStr"/>
@@ -6700,45 +6714,2385 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="E138" s="18" t="n">
-        <v>0</v>
+        <v>2.76</v>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>0.0337</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>505700</v>
+        <v>1149300</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.04</v>
+        <v>0.32</v>
       </c>
       <c r="H138" t="n">
-        <v>42.72</v>
-      </c>
-      <c r="I138" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.71</v>
+      </c>
+      <c r="I138" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="10" t="n">
-        <v>7.402</v>
+        <v>2.812</v>
       </c>
       <c r="K138" s="10" t="n">
-        <v>7.773</v>
+        <v>2.95</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E139" s="11" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>1115500</v>
+      </c>
+      <c r="G139" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H139" t="n">
+        <v>57.03</v>
+      </c>
+      <c r="I139" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="K139" s="10" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="15" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D140" s="10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="F140" s="12" t="n">
+        <v>1114800</v>
+      </c>
+      <c r="G140" s="13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H140" t="n">
+        <v>60.04</v>
+      </c>
+      <c r="I140" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="10" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="K140" s="10" t="n">
+        <v>1.194</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="15" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>7235</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SUPERLN</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E141" s="11" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="F141" s="12" t="n">
+        <v>1102700</v>
+      </c>
+      <c r="G141" s="13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="H141" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I141" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="K141" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="15" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="F142" s="12" t="n">
+        <v>1101800</v>
+      </c>
+      <c r="G142" s="13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H142" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="K142" s="10" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="15" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5283</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>EWICAP</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="F143" s="12" t="n">
+        <v>1081300</v>
+      </c>
+      <c r="G143" s="13" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H143" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="I143" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="K143" s="10" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="15" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>HEXCARE</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>-0.07690000000000001</v>
+      </c>
+      <c r="F144" s="12" t="n">
+        <v>1060200</v>
+      </c>
+      <c r="G144" s="13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H144" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="I144" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K144" s="10" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="15" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2283</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>ZELAN</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="12" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="G145" s="13" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="H145" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="I145" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="10" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="K145" s="10" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="15" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="F146" s="12" t="n">
+        <v>1048600</v>
+      </c>
+      <c r="G146" s="13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H146" t="n">
+        <v>47.88</v>
+      </c>
+      <c r="I146" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="10" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="K146" s="10" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="F147" s="12" t="n">
+        <v>1040700</v>
+      </c>
+      <c r="G147" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H147" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="I147" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="10" t="n">
+        <v>4.025</v>
+      </c>
+      <c r="K147" s="10" t="n">
+        <v>3.685</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="15" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5073</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>NAIM</t>
+        </is>
+      </c>
+      <c r="D148" s="10" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E148" s="17" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="F148" s="12" t="n">
+        <v>1031500</v>
+      </c>
+      <c r="G148" s="13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H148" t="n">
+        <v>59.93</v>
+      </c>
+      <c r="I148" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="K148" s="10" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="15" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="F149" s="12" t="n">
+        <v>1023900</v>
+      </c>
+      <c r="G149" s="13" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H149" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="I149" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="10" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="K149" s="10" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="15" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>3395</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>BJCORP</t>
+        </is>
+      </c>
+      <c r="D150" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E150" s="11" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="F150" s="12" t="n">
+        <v>1016500</v>
+      </c>
+      <c r="G150" s="13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H150" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="I150" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="K150" s="10" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="15" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F151" s="12" t="n">
+        <v>996500</v>
+      </c>
+      <c r="G151" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H151" t="n">
+        <v>46.55</v>
+      </c>
+      <c r="I151" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="K151" s="10" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="15" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D152" s="10" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="E152" s="11" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F152" s="12" t="n">
+        <v>993000</v>
+      </c>
+      <c r="G152" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H152" t="n">
+        <v>58.56</v>
+      </c>
+      <c r="I152" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v>7.335</v>
+      </c>
+      <c r="K152" s="10" t="n">
+        <v>6.985</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="15" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E153" s="11" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F153" s="12" t="n">
+        <v>968900</v>
+      </c>
+      <c r="G153" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H153" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="I153" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="K153" s="10" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="15" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0336</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>WINSTAR</t>
+        </is>
+      </c>
+      <c r="D154" s="10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="12" t="n">
+        <v>930100</v>
+      </c>
+      <c r="G154" s="13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H154" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="I154" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K154" s="10" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="15" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="E155" s="11" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F155" s="12" t="n">
+        <v>903500</v>
+      </c>
+      <c r="G155" s="13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H155" t="n">
+        <v>62.81</v>
+      </c>
+      <c r="I155" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="10" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="K155" s="10" t="n">
+        <v>9.938000000000001</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="15" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E156" s="11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="F156" s="12" t="n">
+        <v>899500</v>
+      </c>
+      <c r="G156" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H156" t="n">
+        <v>66.22</v>
+      </c>
+      <c r="I156" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="10" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="K156" s="10" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="15" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>-0.0372</v>
+      </c>
+      <c r="F157" s="12" t="n">
+        <v>893500</v>
+      </c>
+      <c r="G157" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H157" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="I157" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>1.811</v>
+      </c>
+      <c r="K157" s="10" t="n">
+        <v>1.909</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="15" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="12" t="n">
+        <v>888900</v>
+      </c>
+      <c r="G158" s="13" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H158" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="I158" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K158" s="10" t="n">
+        <v>1.212</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="15" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E159" s="11" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F159" s="12" t="n">
+        <v>868500</v>
+      </c>
+      <c r="G159" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H159" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="I159" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>2.428</v>
+      </c>
+      <c r="K159" s="10" t="n">
+        <v>2.423</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="15" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D160" s="10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E160" s="11" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F160" s="12" t="n">
+        <v>837100</v>
+      </c>
+      <c r="G160" s="13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H160" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="I160" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="K160" s="10" t="n">
+        <v>1.351</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="15" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="E161" s="11" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F161" s="12" t="n">
+        <v>810500</v>
+      </c>
+      <c r="G161" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H161" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="I161" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="10" t="n">
+        <v>3.843</v>
+      </c>
+      <c r="K161" s="10" t="n">
+        <v>3.768</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="15" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E162" s="11" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F162" s="12" t="n">
+        <v>790500</v>
+      </c>
+      <c r="G162" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H162" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="I162" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>2.869</v>
+      </c>
+      <c r="K162" s="10" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="15" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E163" s="17" t="n">
+        <v>-0.004099999999999999</v>
+      </c>
+      <c r="F163" s="12" t="n">
+        <v>783400</v>
+      </c>
+      <c r="G163" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H163" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="I163" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="10" t="n">
+        <v>2.467</v>
+      </c>
+      <c r="K163" s="10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="15" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D164" s="10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E164" s="11" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="F164" s="12" t="n">
+        <v>757900</v>
+      </c>
+      <c r="G164" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H164" t="n">
+        <v>60.68</v>
+      </c>
+      <c r="I164" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J164" s="10" t="n">
+        <v>5.557</v>
+      </c>
+      <c r="K164" s="10" t="n">
+        <v>5.395</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="15" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E165" s="11" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="F165" s="12" t="n">
+        <v>744100</v>
+      </c>
+      <c r="G165" s="13" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H165" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="I165" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="K165" s="10" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="15" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SENTRAL</t>
+        </is>
+      </c>
+      <c r="D166" s="10" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="12" t="n">
+        <v>731500</v>
+      </c>
+      <c r="G166" s="13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H166" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I166" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K166" s="10" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="15" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E167" s="11" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F167" s="12" t="n">
+        <v>731000</v>
+      </c>
+      <c r="G167" s="13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H167" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="I167" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="10" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="K167" s="10" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="15" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E168" s="11" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="F168" s="12" t="n">
+        <v>712000</v>
+      </c>
+      <c r="G168" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H168" t="n">
+        <v>47.27</v>
+      </c>
+      <c r="I168" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>1.118</v>
+      </c>
+      <c r="K168" s="10" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="15" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="12" t="n">
+        <v>707800</v>
+      </c>
+      <c r="G169" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H169" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="I169" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>4.461</v>
+      </c>
+      <c r="K169" s="10" t="n">
+        <v>4.445</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="15" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E170" s="11" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="F170" s="12" t="n">
+        <v>706100</v>
+      </c>
+      <c r="G170" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H170" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="K170" s="10" t="n">
+        <v>2.406</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="15" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="F171" s="12" t="n">
+        <v>706000</v>
+      </c>
+      <c r="G171" s="13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H171" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="I171" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="K171" s="10" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="15" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E172" s="11" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F172" s="12" t="n">
+        <v>693200</v>
+      </c>
+      <c r="G172" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H172" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="I172" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="10" t="n">
+        <v>1.257</v>
+      </c>
+      <c r="K172" s="10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="15" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="12" t="n">
+        <v>684200</v>
+      </c>
+      <c r="G173" s="13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H173" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="I173" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>6.335</v>
+      </c>
+      <c r="K173" s="10" t="n">
+        <v>6.605</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="15" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="E174" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" s="12" t="n">
+        <v>673400</v>
+      </c>
+      <c r="G174" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H174" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="I174" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="K174" s="10" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="15" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E175" s="11" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F175" s="12" t="n">
+        <v>672200</v>
+      </c>
+      <c r="G175" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H175" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="I175" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>2.132</v>
+      </c>
+      <c r="K175" s="10" t="n">
+        <v>2.222</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="15" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E176" s="11" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="F176" s="12" t="n">
+        <v>620500</v>
+      </c>
+      <c r="G176" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H176" t="n">
+        <v>55.93</v>
+      </c>
+      <c r="I176" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="K176" s="10" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="15" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="F177" s="12" t="n">
+        <v>620400</v>
+      </c>
+      <c r="G177" s="13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H177" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="I177" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="K177" s="10" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="15" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2445</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>KLK</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="E178" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="12" t="n">
+        <v>599300</v>
+      </c>
+      <c r="G178" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H178" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="I178" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>20.767</v>
+      </c>
+      <c r="K178" s="10" t="n">
+        <v>21.619</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="15" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F179" s="12" t="n">
+        <v>595400</v>
+      </c>
+      <c r="G179" s="13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H179" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="I179" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>3.288</v>
+      </c>
+      <c r="K179" s="10" t="n">
+        <v>3.519</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="15" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E180" s="11" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F180" s="12" t="n">
+        <v>586100</v>
+      </c>
+      <c r="G180" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H180" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="I180" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="K180" s="10" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="15" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E181" s="11" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="F181" s="12" t="n">
+        <v>584400</v>
+      </c>
+      <c r="G181" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H181" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I181" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>6.992</v>
+      </c>
+      <c r="K181" s="10" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="15" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E182" s="11" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="F182" s="12" t="n">
+        <v>584300</v>
+      </c>
+      <c r="G182" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H182" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="I182" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="K182" s="10" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="15" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="F183" s="12" t="n">
+        <v>580200</v>
+      </c>
+      <c r="G183" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H183" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="I183" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>7.401</v>
+      </c>
+      <c r="K183" s="10" t="n">
+        <v>7.773</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="15" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="E184" s="11" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F184" s="12" t="n">
+        <v>551300</v>
+      </c>
+      <c r="G184" s="13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H184" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="I184" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="K184" s="10" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="15" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E185" s="11" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F185" s="12" t="n">
+        <v>546800</v>
+      </c>
+      <c r="G185" s="13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H185" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="I185" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="10" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K185" s="10" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="15" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>EMPIRE</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E186" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="12" t="n">
+        <v>544200</v>
+      </c>
+      <c r="G186" s="13" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H186" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="I186" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="K186" s="10" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="15" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>PESONA</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E187" s="11" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="F187" s="12" t="n">
+        <v>541200</v>
+      </c>
+      <c r="G187" s="13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H187" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="I187" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="10" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="K187" s="10" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="15" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>-0.0174</v>
+      </c>
+      <c r="F188" s="12" t="n">
+        <v>518100</v>
+      </c>
+      <c r="G188" s="13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H188" t="n">
+        <v>30.13</v>
+      </c>
+      <c r="I188" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="10" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K188" s="10" t="n">
+        <v>5.665</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="15" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" s="12" t="n">
+        <v>508100</v>
+      </c>
+      <c r="G189" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H189" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="I189" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="10" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="K189" s="10" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="15" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D190" s="10" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E190" s="17" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F190" s="12" t="n">
+        <v>504800</v>
+      </c>
+      <c r="G190" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H190" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="I190" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J190" s="10" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="K190" s="10" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M138"/>
+  <autoFilter ref="A1:M190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
+++ b/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M190"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,28 +558,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>2.66</v>
+        <v>0.785</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.027</v>
+        <v>0.0195</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1228100</v>
+        <v>4129400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.23</v>
+        <v>0.78</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>55.55</v>
+        <v>58.3</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>2.603</v>
+        <v>0.748</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>2.601</v>
+        <v>0.696</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价2.66高于50日均线2.601，RSI 55.55处中性区间，未超买，信号技术面可靠性尚可。</t>
+          <t>现价0.785高于50日均线0.696，SAR转多信号获均线支撑；RSI 58.3处中性偏上，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -611,28 +611,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2.95</v>
+        <v>0.605</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0172</v>
+        <v>0.0254</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1125000</v>
+        <v>7212900</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>59.52</v>
+        <v>57.67</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2.821</v>
+        <v>0.574</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2.706</v>
+        <v>0.55</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 59.52未超买，现价高于50日均线约9%，技术面信号可靠性较高。</t>
+          <t>现价0.605高于50日均线0.55，SAR转多信号获均线支撑；RSI 57.67处中性偏上区间，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -664,28 +664,28 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.78</v>
+        <v>0.335</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.013</v>
+        <v>0.0469</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4046400</v>
+        <v>1520600</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.76</v>
+        <v>1.12</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.6</v>
+        <v>60.32</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.748</v>
+        <v>0.318</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.696</v>
+        <v>0.329</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 57.6处中性偏上，未超买；现价0.78高于50日均线0.696约12%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 60.32未超买，现价0.335略高于50日均线0.329，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -717,28 +717,28 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.355</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.0169</v>
+        <v>0.029</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6568800</v>
+        <v>22944400</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.83</v>
+        <v>67.58</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.573</v>
+        <v>0.322</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.55</v>
+        <v>0.271</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.60高于50日均线0.55，SAR转多信号获均线支撑；RSI 56.83处中性区间，未超买，信号可靠性尚可。</t>
+          <t>SAR转多信号出现，但RSI 67.58已接近超买区，现价高于50日均线约31%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -770,28 +770,28 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6.9</v>
+        <v>3.12</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>-0.0254</v>
+        <v>-0.0158</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1041000</v>
+        <v>3545600</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.18</v>
+        <v>1.24</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>53.89</v>
+        <v>56.03</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>6.839</v>
+        <v>3.019</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.828</v>
+        <v>2.878</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -811,221 +811,189 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>现价6.9略高于50日均线6.828，RSI 53.89处中性区间，未超买，SAR转多信号技术面可靠性尚可。</t>
+          <t>SAR转多信号，RSI 56.03处中性区间未超买，现价高于50日均线约8.4%，技术面信号可靠性尚可。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>5284</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>LCTITAN</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>1403100</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>57.68</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>🎯 SAR 转多</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，RSI 57.68处中性偏上，未超买；现价0.33略高于50日均线0.329，技术面信号可靠性尚可。</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0138</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>193594000</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H7" t="n">
+        <v>40.78</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>6963</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>22667300</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>🎯 SAR 转多</t>
-        </is>
-      </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t>现价0.355高于50日均线0.271约31%，SAR转多信号获趋势支撑；RSI 67.58接近超买区，动能偏强但上行空间受限。</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>29296800</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H8" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>7153</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>KOSSAN</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>-0.0159</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>1758500</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>58.61</v>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>1.191</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>1.156</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>🎯 SAR 转多</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，RSI 58.61未超买，现价高于50日均线约7.3%，技术面信号可靠性尚可。</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>24714600</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H9" t="n">
+        <v>65.16</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>7233</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>DUFU</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>-0.0063</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>3308200</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>57.56</v>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>3.022</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>2.878</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>🎯 SAR 转多</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t>现价高于50日均线约9.4%，RSI 57.56处中性偏上区间，未超买，SAR转多信号技术面可靠性尚可。</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LANDMRK</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>22818900</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="H10" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1035,40 +1003,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.095</v>
+        <v>0.195</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.1176</v>
+        <v>0.0541</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>190110700</v>
+        <v>15913600</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H11" t="n">
-        <v>40.78</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>0.235</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
     </row>
@@ -1080,28 +1041,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0</v>
+        <v>2.26</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>0.0463</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>47428700</v>
+        <v>14850100</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1.29</v>
+        <v>0.52</v>
       </c>
       <c r="H12" t="n">
-        <v>47.71</v>
+        <v>67.11</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -1109,10 +1070,10 @@
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.156</v>
+        <v>2.016</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>0.156</v>
+        <v>1.823</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
@@ -1125,28 +1086,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>-0.0052</v>
+        <v>0.16</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>27671500</v>
+        <v>14424400</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="H13" t="n">
-        <v>68.59999999999999</v>
+        <v>51.28</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1154,10 +1115,10 @@
         </is>
       </c>
       <c r="J13" s="10" t="n">
-        <v>0.879</v>
+        <v>0.159</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>0.775</v>
+        <v>0.149</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="15" t="inlineStr"/>
@@ -1170,28 +1131,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LANDMRK</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.055</v>
+        <v>0.45</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.375</v>
+        <v>0.0227</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>22491200</v>
+        <v>14263800</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>10.41</v>
+        <v>0.39</v>
       </c>
       <c r="H14" t="n">
-        <v>57.25</v>
+        <v>47.56</v>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1199,10 +1160,10 @@
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.043</v>
+        <v>0.453</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>0.058</v>
+        <v>0.472</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
@@ -1215,33 +1176,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>0.0541</v>
+        <v>0.21</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>15797500</v>
+        <v>13723100</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="10" t="n"/>
+        <v>1.94</v>
+      </c>
+      <c r="H15" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>0.12</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
     </row>
@@ -1253,28 +1221,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>0.0227</v>
+        <v>0.5</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>14059800</v>
+        <v>13628900</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="H16" t="n">
-        <v>47.56</v>
+        <v>74.66</v>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
@@ -1282,10 +1250,10 @@
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.453</v>
+        <v>0.435</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.472</v>
+        <v>0.335</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1298,39 +1266,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>-0.0068</v>
+        <v>0.995</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0.1775</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>13808700</v>
+        <v>13389500</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.59</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
-        <v>78.43000000000001</v>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.87</v>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.673</v>
+        <v>0.839</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.575</v>
+        <v>0.652</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="15" t="inlineStr"/>
@@ -1343,28 +1311,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.505</v>
+        <v>0.155</v>
       </c>
       <c r="E18" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>13421400</v>
+        <v>12750000</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H18" t="n">
-        <v>76.67</v>
+        <v>47.71</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -1372,10 +1340,10 @@
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.435</v>
+        <v>0.156</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.335</v>
+        <v>0.156</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="15" t="inlineStr"/>
@@ -1388,39 +1356,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.0455</v>
+        <v>0.38</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>12955600</v>
+        <v>12334200</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1.84</v>
+        <v>1.24</v>
       </c>
       <c r="H19" t="n">
-        <v>82.61</v>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.76</v>
+      </c>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.137</v>
+        <v>0.388</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0.12</v>
+        <v>0.402</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="15" t="inlineStr"/>
@@ -1433,39 +1401,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>12334200</v>
+        <v>12237400</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>1.24</v>
+        <v>4.18</v>
       </c>
       <c r="H20" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.99</v>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.388</v>
+        <v>0.162</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.402</v>
+        <v>0.158</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
@@ -1478,28 +1446,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.865</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>12122200</v>
+        <v>11817500</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>4.15</v>
+        <v>0.57</v>
       </c>
       <c r="H21" t="n">
-        <v>63.99</v>
+        <v>46.13</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
@@ -1507,10 +1475,10 @@
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.162</v>
+        <v>0.867</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.158</v>
+        <v>0.868</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="15" t="inlineStr"/>
@@ -1523,39 +1491,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>0.1479</v>
+        <v>0.82</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>12018000</v>
+        <v>11535800</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>2.13</v>
+        <v>0.74</v>
       </c>
       <c r="H22" t="n">
-        <v>59.83</v>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.837</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0.652</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
@@ -1577,19 +1545,19 @@
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.455</v>
+        <v>0.46</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0.0581</v>
+        <v>0.0698</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>9882200</v>
+        <v>11282700</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="H23" t="n">
-        <v>37.29</v>
+        <v>38.88</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -1597,7 +1565,7 @@
         </is>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>0.597</v>
@@ -1613,39 +1581,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0</v>
+        <v>0.22</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>0.0732</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>9448600</v>
+        <v>10887900</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.16</v>
+        <v>1.12</v>
       </c>
       <c r="H24" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.44</v>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.159</v>
+        <v>0.221</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.149</v>
+        <v>0.263</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1658,39 +1626,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HBGLOB</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>-0.0061</v>
+        <v>-0.6667000000000001</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>9333800</v>
+        <v>10862900</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>0.6</v>
+        <v>50.94</v>
       </c>
       <c r="H25" t="n">
-        <v>48.71</v>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1703,12 +1671,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MQTECH</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
@@ -1718,24 +1686,24 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>9107600</v>
+        <v>9886300</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>5.1</v>
+        <v>0.82</v>
       </c>
       <c r="H26" t="n">
-        <v>62.78</v>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.9</v>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.056</v>
+        <v>0.047</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1748,39 +1716,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MQTECH</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>2.21</v>
+        <v>0.06</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.0231</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>9042400</v>
+        <v>9177600</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.32</v>
+        <v>5.14</v>
       </c>
       <c r="H27" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.78</v>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2.011</v>
+        <v>0.053</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>1.822</v>
+        <v>0.056</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="15" t="inlineStr"/>
@@ -1793,39 +1761,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.22</v>
+        <v>0.775</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.0732</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>8563800</v>
+        <v>8573100</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.88</v>
+        <v>0.55</v>
       </c>
       <c r="H28" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.93</v>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.221</v>
+        <v>0.774</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0.263</v>
+        <v>0.775</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="15" t="inlineStr"/>
@@ -1838,39 +1806,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AEM</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>0.25</v>
+        <v>0.305</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>8219000</v>
+        <v>8408000</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>281.96</v>
+        <v>0.43</v>
       </c>
       <c r="H29" t="n">
-        <v>64.65000000000001</v>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.46</v>
+      </c>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.043</v>
+        <v>0.307</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.046</v>
+        <v>0.303</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr"/>
@@ -1883,28 +1851,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>VELOCITY</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>0.86</v>
+        <v>0.065</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>-0.0058</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>8145800</v>
+        <v>7867400</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>0.39</v>
+        <v>4.19</v>
       </c>
       <c r="H30" t="n">
-        <v>40.85</v>
+        <v>43.52</v>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
@@ -1912,10 +1880,10 @@
         </is>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.867</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>0.868</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="15" t="inlineStr"/>
@@ -1928,28 +1896,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VELOCITY</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>-0.07139999999999999</v>
+        <v>2.13</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0.039</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>7867400</v>
+        <v>7628000</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>4.19</v>
+        <v>0.63</v>
       </c>
       <c r="H31" t="n">
-        <v>43.52</v>
+        <v>50.85</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -1957,10 +1925,10 @@
         </is>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.06900000000000001</v>
+        <v>2.101</v>
       </c>
       <c r="K31" s="10" t="n">
-        <v>0.06900000000000001</v>
+        <v>2.226</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="15" t="inlineStr"/>
@@ -1973,28 +1941,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>0.775</v>
+        <v>1.68</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>7621100</v>
+        <v>7623600</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
       <c r="H32" t="n">
-        <v>50.93</v>
+        <v>50.9</v>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
@@ -2002,10 +1970,10 @@
         </is>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.774</v>
+        <v>1.652</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>0.775</v>
+        <v>1.734</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="15" t="inlineStr"/>
@@ -2018,39 +1986,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>WAVEFRNT</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>-0.0164</v>
+        <v>0.14</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>7308000</v>
+        <v>7220400</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.37</v>
+        <v>9.25</v>
       </c>
       <c r="H33" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.08</v>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.306</v>
+        <v>0.136</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0.303</v>
+        <v>0.141</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2063,28 +2031,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WAVEFRNT</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.14</v>
+        <v>0.115</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0455</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>7024000</v>
+        <v>7191400</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="H34" t="n">
-        <v>53.08</v>
+        <v>70.39</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
@@ -2092,10 +2060,10 @@
         </is>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.136</v>
+        <v>0.102</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0.141</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="15" t="inlineStr"/>
@@ -2108,28 +2076,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="E35" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>6901400</v>
+        <v>7036200</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>1.54</v>
+        <v>0.68</v>
       </c>
       <c r="H35" t="n">
-        <v>66.55</v>
+        <v>63.72</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2137,10 +2105,10 @@
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.101</v>
+        <v>0.627</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2153,39 +2121,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.485</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>6811800</v>
+        <v>6913300</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>1.09</v>
+        <v>0.32</v>
       </c>
       <c r="H36" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.62</v>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1.652</v>
+        <v>0.443</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>1.734</v>
+        <v>0.394</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr"/>
@@ -2213,10 +2181,10 @@
         <v>-0.0595</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>6579800</v>
+        <v>6834100</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="H37" t="n">
         <v>35.01</v>
@@ -2243,39 +2211,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>0.065</v>
+        <v>1.22</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.0833</v>
+        <v>0.0609</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>6362900</v>
+        <v>6634800</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>5.72</v>
+        <v>0.86</v>
       </c>
       <c r="H38" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="I38" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.11</v>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.063</v>
+        <v>1.281</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>0.065</v>
+        <v>1.479</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2297,19 +2265,19 @@
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.0345</v>
+        <v>0.0414</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>6290100</v>
+        <v>6408000</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>0.45</v>
       </c>
       <c r="H39" t="n">
-        <v>38.44</v>
+        <v>39.52</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2317,10 +2285,10 @@
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.559</v>
+        <v>1.56</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1.837</v>
+        <v>1.838</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2333,39 +2301,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1.21</v>
+        <v>0.065</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0522</v>
+        <v>0.0833</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>6248100</v>
+        <v>6362900</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v>5.72</v>
       </c>
       <c r="H40" t="n">
-        <v>35.66</v>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I40" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1.28</v>
+        <v>0.063</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>1.479</v>
+        <v>0.065</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2378,36 +2346,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>0.23</v>
+        <v>4.94</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.0222</v>
+        <v>0.0061</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>6085000</v>
+        <v>6354000</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="H41" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I41" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
+        <v>55</v>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="K41" s="10" t="n">
+        <v>4.783</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
     </row>
@@ -2419,40 +2391,36 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>2.13</v>
+        <v>0.23</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.039</v>
+        <v>0.0222</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>6042200</v>
+        <v>6292900</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="H42" t="n">
-        <v>50.85</v>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>2.101</v>
-      </c>
-      <c r="K42" s="10" t="n">
-        <v>2.226</v>
-      </c>
+        <v>54.46</v>
+      </c>
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
     </row>
@@ -2464,28 +2432,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>5994100</v>
+        <v>6046500</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.58</v>
+        <v>0.89</v>
       </c>
       <c r="H43" t="n">
-        <v>63.72</v>
+        <v>58.47</v>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
@@ -2493,10 +2461,10 @@
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.627</v>
+        <v>0.373</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.619</v>
+        <v>0.37</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2509,28 +2477,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>-0.0103</v>
+        <v>0.275</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>5975000</v>
+        <v>5938000</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.28</v>
+        <v>0.53</v>
       </c>
       <c r="H44" t="n">
-        <v>63.86</v>
+        <v>46</v>
       </c>
       <c r="I44" s="18" t="inlineStr">
         <is>
@@ -2538,10 +2506,10 @@
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.443</v>
+        <v>0.283</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>0.394</v>
+        <v>0.279</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2554,39 +2522,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D45" s="10" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>0.0133</v>
+        <v>0.11</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>5951500</v>
+        <v>5891200</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.88</v>
+        <v>0.34</v>
       </c>
       <c r="H45" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.76</v>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="10" t="n">
-        <v>0.373</v>
+        <v>0.127</v>
       </c>
       <c r="K45" s="10" t="n">
-        <v>0.37</v>
+        <v>0.145</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="15" t="inlineStr"/>
@@ -2599,39 +2567,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HBGLOB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>-0.5</v>
+        <v>0.535</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>5893500</v>
+        <v>5754900</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>27.64</v>
+        <v>1.39</v>
       </c>
       <c r="H46" t="n">
-        <v>11.69</v>
-      </c>
-      <c r="I46" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.09999999999999</v>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.029</v>
+        <v>0.466</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>0.031</v>
+        <v>0.44</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2644,39 +2612,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0.0517</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>5724800</v>
+        <v>5576700</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>1.38</v>
+        <v>0.61</v>
       </c>
       <c r="H47" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.7</v>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.466</v>
+        <v>0.606</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>0.44</v>
+        <v>0.617</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
@@ -2689,39 +2657,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>4.94</v>
+        <v>0.945</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.0061</v>
+        <v>0.0272</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>5478500</v>
+        <v>5514500</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.23</v>
+        <v>0.48</v>
       </c>
       <c r="H48" t="n">
-        <v>55</v>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.13</v>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>4.885</v>
+        <v>0.992</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>4.783</v>
+        <v>0.989</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2734,39 +2702,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>5202000</v>
+        <v>5378000</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="H49" t="n">
-        <v>43.64</v>
-      </c>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.31999999999999</v>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>0.283</v>
+        <v>1.119</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>0.279</v>
+        <v>1.066</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2779,39 +2747,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.95</v>
+        <v>0.665</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.0326</v>
+        <v>0.0391</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>5037400</v>
+        <v>5012900</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>0.44</v>
+        <v>1.2</v>
       </c>
       <c r="H50" t="n">
-        <v>43.84</v>
-      </c>
-      <c r="I50" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.73</v>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.993</v>
+        <v>0.604</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0.989</v>
+        <v>0.586</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="15" t="inlineStr"/>
@@ -2824,28 +2792,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>0.0345</v>
+        <v>4.45</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>4991100</v>
+        <v>4997000</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H51" t="n">
-        <v>48</v>
+        <v>36.57</v>
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
@@ -2853,10 +2821,10 @@
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.605</v>
+        <v>4.54</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>0.617</v>
+        <v>4.642</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2869,39 +2837,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>4962600</v>
+        <v>4943300</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="H52" t="n">
-        <v>36.57</v>
-      </c>
-      <c r="I52" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.88</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>4.54</v>
+        <v>0.403</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>4.642</v>
+        <v>0.384</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2914,39 +2882,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D53" s="10" t="n">
-        <v>1.24</v>
+        <v>2.61</v>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0.0164</v>
+        <v>0.0195</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>4698800</v>
+        <v>4701100</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="H53" t="n">
-        <v>67.55</v>
-      </c>
-      <c r="I53" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.27</v>
+      </c>
+      <c r="I53" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="10" t="n">
-        <v>1.118</v>
+        <v>2.594</v>
       </c>
       <c r="K53" s="10" t="n">
-        <v>1.066</v>
+        <v>2.567</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="15" t="inlineStr"/>
@@ -2968,19 +2936,19 @@
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.475</v>
+        <v>0.48</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.0106</v>
+        <v>0.0213</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>4574300</v>
+        <v>4622000</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H54" t="n">
-        <v>58.94</v>
+        <v>60.46</v>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
@@ -3004,39 +2972,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E55" s="11" t="n">
-        <v>0.0469</v>
+        <v>0.125</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>4572300</v>
+        <v>4539500</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>1.09</v>
+        <v>2.01</v>
       </c>
       <c r="H55" t="n">
-        <v>63.39</v>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.46</v>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.604</v>
+        <v>0.13</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.587</v>
+        <v>0.14</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3049,28 +3017,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>4539500</v>
+        <v>4526900</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="H56" t="n">
-        <v>41.46</v>
+        <v>36.35</v>
       </c>
       <c r="I56" s="18" t="inlineStr">
         <is>
@@ -3078,10 +3046,10 @@
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.13</v>
+        <v>1.053</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0.14</v>
+        <v>1.112</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3094,39 +3062,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0182</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LKL</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>4316000</v>
+        <v>4194000</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>15.24</v>
+        <v>0.59</v>
       </c>
       <c r="H57" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="I57" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.16</v>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>0.033</v>
+        <v>0.533</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3139,28 +3107,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E58" s="11" t="n">
-        <v>0.0306</v>
+        <v>1.33</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.0699</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>4245500</v>
+        <v>4183600</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>1.91</v>
+        <v>1.12</v>
       </c>
       <c r="H58" t="n">
-        <v>38.69</v>
+        <v>27.68</v>
       </c>
       <c r="I58" s="18" t="inlineStr">
         <is>
@@ -3168,10 +3136,10 @@
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>1.054</v>
+        <v>1.427</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>1.112</v>
+        <v>1.452</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3184,28 +3152,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>-0.0629</v>
+        <v>5.23</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>3739000</v>
+        <v>3766500</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>1</v>
+        <v>0.23</v>
       </c>
       <c r="H59" t="n">
-        <v>28.84</v>
+        <v>44.46</v>
       </c>
       <c r="I59" s="18" t="inlineStr">
         <is>
@@ -3213,10 +3181,10 @@
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>1.428</v>
+        <v>5.356</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>1.453</v>
+        <v>5.522</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3229,28 +3197,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>0.485</v>
+        <v>1.3</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.0319</v>
+        <v>0.0317</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>3603200</v>
+        <v>3696000</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.5</v>
+        <v>0.74</v>
       </c>
       <c r="H60" t="n">
-        <v>47.24</v>
+        <v>69.62</v>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
@@ -3258,10 +3226,10 @@
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>0.482</v>
+        <v>1.126</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>0.533</v>
+        <v>0.987</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3274,39 +3242,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>2.61</v>
+        <v>0.185</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.0195</v>
+        <v>0.0278</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>3584900</v>
+        <v>3644000</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="H61" t="n">
-        <v>51.27</v>
-      </c>
-      <c r="I61" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.32</v>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>2.594</v>
+        <v>0.185</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>2.567</v>
+        <v>0.187</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3319,39 +3287,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0</v>
+        <v>3.98</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>-0.0316</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>3460400</v>
+        <v>3475200</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.2</v>
+        <v>0.46</v>
       </c>
       <c r="H62" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="I62" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.3</v>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>0.127</v>
+        <v>3.84</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0.145</v>
+        <v>3.337</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3364,39 +3332,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>1.32</v>
+        <v>0.705</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.0476</v>
+        <v>0.0071</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>3446600</v>
+        <v>3240500</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="H63" t="n">
-        <v>70.65000000000001</v>
-      </c>
-      <c r="I63" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.8</v>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>1.128</v>
+        <v>0.729</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0.987</v>
+        <v>0.724</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
@@ -3409,39 +3377,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.185</v>
+        <v>0.51</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>0.0278</v>
+        <v>0.0303</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>3396600</v>
+        <v>3185500</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.18</v>
+        <v>0.87</v>
       </c>
       <c r="H64" t="n">
-        <v>49.32</v>
-      </c>
-      <c r="I64" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.91</v>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>0.185</v>
+        <v>0.524</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>0.187</v>
+        <v>0.556</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3454,39 +3422,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v>0.0216</v>
+        <v>9.98</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>3344300</v>
+        <v>3173900</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H65" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="I65" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.39</v>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>5.354</v>
+        <v>9.993</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>5.522</v>
+        <v>10.1</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3499,39 +3467,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>0.51</v>
+        <v>0.325</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.0303</v>
+        <v>0.0484</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>3167500</v>
+        <v>2998300</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.87</v>
+        <v>2.02</v>
       </c>
       <c r="H66" t="n">
-        <v>37.91</v>
-      </c>
-      <c r="I66" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.54</v>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.524</v>
+        <v>0.3</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0.556</v>
+        <v>0.325</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3544,39 +3512,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>0.705</v>
+        <v>1.65</v>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0.0071</v>
+        <v>0.0123</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>2997800</v>
+        <v>2985300</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="H67" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I67" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.09</v>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="10" t="n">
-        <v>0.729</v>
+        <v>1.629</v>
       </c>
       <c r="K67" s="10" t="n">
-        <v>0.724</v>
+        <v>1.67</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
@@ -3589,39 +3557,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DATAPRP</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>0.05</v>
+        <v>2.59</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1111</v>
+        <v>0.0157</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>2976300</v>
+        <v>2848500</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="H68" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="I68" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.07</v>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>0.058</v>
+        <v>2.635</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>0.06900000000000001</v>
+        <v>2.818</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3634,28 +3602,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E69" s="11" t="n">
-        <v>0.0484</v>
+        <v>2.31</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>2962300</v>
+        <v>2816500</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>1.99</v>
+        <v>0.8</v>
       </c>
       <c r="H69" t="n">
-        <v>59.54</v>
+        <v>52.55</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -3663,10 +3631,10 @@
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>0.3</v>
+        <v>2.298</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>0.325</v>
+        <v>2.22</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3679,39 +3647,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0381</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>POLYMER</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>0</v>
+        <v>2.66</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>2917900</v>
+        <v>2795100</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>1.37</v>
+        <v>0.28</v>
       </c>
       <c r="H70" t="n">
-        <v>42.17</v>
-      </c>
-      <c r="I70" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.71</v>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>0.182</v>
+        <v>2.72</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>0.191</v>
+        <v>2.748</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3724,28 +3692,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0039</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GFM</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E71" s="11" t="n">
-        <v>0.0588</v>
+        <v>0.835</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>2902600</v>
+        <v>2711700</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>3.74</v>
+        <v>0.55</v>
       </c>
       <c r="H71" t="n">
-        <v>52.09</v>
+        <v>72.53</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -3753,10 +3721,10 @@
         </is>
       </c>
       <c r="J71" s="10" t="n">
-        <v>0.176</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K71" s="10" t="n">
-        <v>0.187</v>
+        <v>0.782</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="15" t="inlineStr"/>
@@ -3769,28 +3737,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>-0.001</v>
+        <v>3.45</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>2817700</v>
+        <v>2704600</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.23</v>
+        <v>0.84</v>
       </c>
       <c r="H72" t="n">
-        <v>47.39</v>
+        <v>89.59</v>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
@@ -3798,10 +3766,10 @@
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>9.993</v>
+        <v>3.119</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>10.1</v>
+        <v>2.641</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3814,28 +3782,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>-0.0244</v>
+        <v>7.02</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>0.04</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>2770800</v>
+        <v>2700000</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="H73" t="n">
-        <v>50.64</v>
+        <v>62.82</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
@@ -3843,10 +3811,10 @@
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.402</v>
+        <v>6.417</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>0.384</v>
+        <v>6.05</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3859,39 +3827,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>2710300</v>
+        <v>2639000</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
       <c r="H74" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="I74" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.98</v>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="10" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.641</v>
       </c>
       <c r="K74" s="10" t="n">
-        <v>0.782</v>
+        <v>0.679</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="15" t="inlineStr"/>
@@ -3904,39 +3872,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>1.66</v>
+        <v>0.555</v>
       </c>
       <c r="E75" s="11" t="n">
-        <v>0.0184</v>
+        <v>0.0091</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>2657900</v>
+        <v>2629700</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.32</v>
+        <v>1.22</v>
       </c>
       <c r="H75" t="n">
-        <v>53.38</v>
-      </c>
-      <c r="I75" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.19</v>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>1.63</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>1.67</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3949,28 +3917,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>-0.0268</v>
+        <v>0.3</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>2649100</v>
+        <v>2575600</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>59.04</v>
+        <v>38.94</v>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
@@ -3978,10 +3946,10 @@
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>3.842</v>
+        <v>0.312</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>3.337</v>
+        <v>0.355</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3994,40 +3962,33 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PICORP</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.055</v>
+        <v>0.735</v>
       </c>
       <c r="E77" s="11" t="n">
-        <v>0.2222</v>
+        <v>0.0352</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>2616000</v>
+        <v>2574900</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="H77" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="I77" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="K77" s="10" t="n">
-        <v>0.056</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
     </row>
@@ -4039,28 +4000,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>2.65</v>
+        <v>4.72</v>
       </c>
       <c r="E78" s="17" t="n">
-        <v>-0.0075</v>
+        <v>-0.0063</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2580300</v>
+        <v>2517000</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="H78" t="n">
-        <v>42.92</v>
+        <v>47.73</v>
       </c>
       <c r="I78" s="18" t="inlineStr">
         <is>
@@ -4068,10 +4029,10 @@
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>2.719</v>
+        <v>4.73</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>2.748</v>
+        <v>4.8</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4084,28 +4045,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>-0.0145</v>
+        <v>0.91</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>2534700</v>
+        <v>2375100</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="H79" t="n">
-        <v>82.70999999999999</v>
+        <v>49.94</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
@@ -4113,10 +4074,10 @@
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>3.114</v>
+        <v>0.898</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>2.64</v>
+        <v>0.954</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4129,39 +4090,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AMEREIT</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0</v>
+        <v>2.11</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>2450000</v>
+        <v>2356900</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>28.85</v>
+        <v>0.23</v>
       </c>
       <c r="H80" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="I80" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.01</v>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>1.56</v>
+        <v>2.107</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>1.543</v>
+        <v>2.114</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4174,28 +4135,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>0.0157</v>
+        <v>0.225</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>2365300</v>
+        <v>2335600</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>0.4</v>
+        <v>1.57</v>
       </c>
       <c r="H81" t="n">
-        <v>46.07</v>
+        <v>42.99</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4203,10 +4164,10 @@
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>2.635</v>
+        <v>0.229</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>2.818</v>
+        <v>0.237</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4219,39 +4180,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>-0.004699999999999999</v>
+        <v>0.775</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>2346900</v>
+        <v>2319700</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="H82" t="n">
-        <v>51.01</v>
-      </c>
-      <c r="I82" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.94</v>
+      </c>
+      <c r="I82" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>2.107</v>
+        <v>0.769</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>2.114</v>
+        <v>0.771</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4264,28 +4225,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0</v>
+        <v>2.21</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>0.0327</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>2318100</v>
+        <v>2271300</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="H83" t="n">
-        <v>50.66</v>
+        <v>62.12</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4293,10 +4254,10 @@
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.129</v>
+        <v>2.128</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>0.13</v>
+        <v>2.084</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4309,28 +4270,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TALAMT</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="E84" s="11" t="n">
-        <v>0.0625</v>
+        <v>8.26</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>2316800</v>
+        <v>2227300</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="H84" t="n">
-        <v>60.25</v>
+        <v>54.69</v>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
@@ -4338,10 +4299,10 @@
         </is>
       </c>
       <c r="J84" s="10" t="n">
-        <v>0.078</v>
+        <v>8.154</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>0.08</v>
+        <v>7.972</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="15" t="inlineStr"/>
@@ -4354,39 +4315,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>2314200</v>
+        <v>2203500</v>
       </c>
       <c r="G85" s="13" t="n">
         <v>0.31</v>
       </c>
       <c r="H85" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="I85" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.61</v>
+      </c>
+      <c r="I85" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.769</v>
+        <v>0.43</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>0.771</v>
+        <v>0.417</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4399,39 +4360,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.915</v>
+        <v>0.475</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>0.0223</v>
+        <v>0.0215</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>2296000</v>
+        <v>2104500</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.55</v>
+        <v>0.24</v>
       </c>
       <c r="H86" t="n">
-        <v>51.32</v>
-      </c>
-      <c r="I86" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.4</v>
+      </c>
+      <c r="I86" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.899</v>
+        <v>0.489</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>0.954</v>
+        <v>0.472</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4444,39 +4405,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E87" s="16" t="n">
-        <v>0</v>
+        <v>0.49</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>2273200</v>
+        <v>2102900</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>1.53</v>
+        <v>0.29</v>
       </c>
       <c r="H87" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="I87" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.32</v>
+      </c>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.229</v>
+        <v>0.492</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>0.237</v>
+        <v>0.512</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4489,39 +4450,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>2253600</v>
+        <v>1975200</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="H88" t="n">
-        <v>42.99</v>
-      </c>
-      <c r="I88" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.34</v>
+      </c>
+      <c r="I88" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>0.189</v>
+        <v>0.278</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>0.204</v>
+        <v>0.282</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4534,39 +4495,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>4.72</v>
+        <v>1.25</v>
       </c>
       <c r="E89" s="17" t="n">
-        <v>-0.0063</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>2218000</v>
+        <v>1939900</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="H89" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="I89" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.28</v>
+      </c>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>4.73</v>
+        <v>1.192</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>4.8</v>
+        <v>1.156</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4579,39 +4540,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>-0.0372</v>
+        <v>1.17</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>0.0174</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>2214300</v>
+        <v>1929500</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.63</v>
+        <v>0.2</v>
       </c>
       <c r="H90" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="I90" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>2.3</v>
+        <v>1.196</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>2.221</v>
+        <v>1.278</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4624,39 +4585,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E91" s="11" t="n">
-        <v>0.0327</v>
+        <v>7.11</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>2180700</v>
+        <v>1922600</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.89</v>
+        <v>0.12</v>
       </c>
       <c r="H91" t="n">
-        <v>62.12</v>
-      </c>
-      <c r="I91" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.23</v>
+      </c>
+      <c r="I91" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>2.128</v>
+        <v>7.314</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>2.084</v>
+        <v>7.599</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4669,39 +4630,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>0</v>
+        <v>1.18</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>0.06309999999999999</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>2141500</v>
+        <v>1819000</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.32</v>
+        <v>0.54</v>
       </c>
       <c r="H92" t="n">
-        <v>38.94</v>
-      </c>
-      <c r="I92" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.43</v>
+      </c>
+      <c r="I92" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>0.312</v>
+        <v>1.107</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>0.355</v>
+        <v>0.945</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4714,28 +4675,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.555</v>
+        <v>0.33</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>0.0091</v>
+        <v>0.0313</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>2080900</v>
+        <v>1807900</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.96</v>
+        <v>0.18</v>
       </c>
       <c r="H93" t="n">
-        <v>46.19</v>
+        <v>48.02</v>
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
@@ -4743,10 +4704,10 @@
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.336</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.338</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4759,39 +4720,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E94" s="11" t="n">
-        <v>0.0303</v>
+        <v>0.865</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>2052300</v>
+        <v>1783900</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.44</v>
+        <v>0.61</v>
       </c>
       <c r="H94" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="I94" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.98</v>
+      </c>
+      <c r="I94" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="10" t="n">
-        <v>0.172</v>
+        <v>0.866</v>
       </c>
       <c r="K94" s="10" t="n">
-        <v>0.188</v>
+        <v>0.861</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="15" t="inlineStr"/>
@@ -4804,28 +4765,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HUBLINE</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>0.0882</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>1958000</v>
+        <v>1766200</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>0.7</v>
+        <v>1.75</v>
       </c>
       <c r="H95" t="n">
-        <v>46.24</v>
+        <v>65.14</v>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
@@ -4833,10 +4794,10 @@
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>0.03</v>
+        <v>0.342</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>0.031</v>
+        <v>0.356</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4849,39 +4810,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E96" s="11" t="n">
-        <v>0.0192</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1886400</v>
+        <v>1755600</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="H96" t="n">
-        <v>42.34</v>
-      </c>
-      <c r="I96" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.31</v>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>0.278</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>0.282</v>
+        <v>0.897</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4894,33 +4855,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>0.1111</v>
+        <v>0.0361</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1859800</v>
+        <v>1696000</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
+      </c>
+      <c r="H97" t="n">
+        <v>57.91</v>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
+      <c r="J97" s="10" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="K97" s="10" t="n">
+        <v>0.368</v>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
     </row>
@@ -4932,28 +4900,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E98" s="11" t="n">
-        <v>0.0215</v>
+        <v>0.9</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1822800</v>
+        <v>1688800</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.21</v>
+        <v>2.13</v>
       </c>
       <c r="H98" t="n">
-        <v>47.4</v>
+        <v>33.91</v>
       </c>
       <c r="I98" s="18" t="inlineStr">
         <is>
@@ -4961,10 +4929,10 @@
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>0.489</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>0.472</v>
+        <v>0.968</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4977,39 +4945,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>0.0233</v>
+        <v>0.0638</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1801400</v>
+        <v>1665200</v>
       </c>
       <c r="G99" s="13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H99" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="I99" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K99" s="10" t="n">
         <v>0.25</v>
-      </c>
-      <c r="H99" t="n">
-        <v>53.61</v>
-      </c>
-      <c r="I99" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="K99" s="10" t="n">
-        <v>0.417</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -5022,39 +4990,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>0</v>
+        <v>1.43</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>0.0593</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1773300</v>
+        <v>1654900</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="H100" t="n">
-        <v>56.53</v>
-      </c>
-      <c r="I100" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.77</v>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="10" t="n">
-        <v>0.051</v>
+        <v>1.309</v>
       </c>
       <c r="K100" s="10" t="n">
-        <v>0.047</v>
+        <v>1.253</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
@@ -5067,39 +5035,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SJC</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>0.475</v>
+        <v>2.11</v>
       </c>
       <c r="E101" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1731300</v>
+        <v>1625700</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>6.92</v>
+        <v>0.25</v>
       </c>
       <c r="H101" t="n">
-        <v>48.39</v>
-      </c>
-      <c r="I101" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68</v>
+      </c>
+      <c r="I101" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>0.475</v>
+        <v>1.994</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>0.482</v>
+        <v>1.968</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="15" t="inlineStr"/>
@@ -5112,28 +5080,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>6.98</v>
-      </c>
-      <c r="E102" s="11" t="n">
-        <v>0.0341</v>
+        <v>0.64</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1729700</v>
+        <v>1592500</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H102" t="n">
-        <v>62.32</v>
+        <v>40.9</v>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
@@ -5141,10 +5109,10 @@
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>6.413</v>
+        <v>0.676</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>6.049</v>
+        <v>0.731</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5157,39 +5125,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E103" s="11" t="n">
-        <v>0.0104</v>
+        <v>0.89</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1713300</v>
+        <v>1586800</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>0.24</v>
+        <v>0.83</v>
       </c>
       <c r="H103" t="n">
-        <v>45.42</v>
-      </c>
-      <c r="I103" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.67</v>
+      </c>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="10" t="n">
-        <v>0.492</v>
+        <v>0.903</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>0.512</v>
+        <v>0.897</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="15" t="inlineStr"/>
@@ -5202,28 +5170,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>0.06</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1667100</v>
+        <v>1461400</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>1.15</v>
+        <v>0.25</v>
       </c>
       <c r="H104" t="n">
-        <v>47.02</v>
+        <v>49.13</v>
       </c>
       <c r="I104" s="18" t="inlineStr">
         <is>
@@ -5231,10 +5199,10 @@
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>0.005</v>
+        <v>0.263</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>0.006</v>
+        <v>0.28</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5247,39 +5215,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E105" s="11" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.25</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1646300</v>
+        <v>1423200</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H105" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="I105" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.19</v>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="10" t="n">
-        <v>1.195</v>
+        <v>1.273</v>
       </c>
       <c r="K105" s="10" t="n">
-        <v>1.278</v>
+        <v>1.319</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="15" t="inlineStr"/>
@@ -5292,28 +5260,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>0</v>
+        <v>2.77</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>0.0375</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1635300</v>
+        <v>1363200</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="H106" t="n">
-        <v>32.23</v>
+        <v>44.51</v>
       </c>
       <c r="I106" s="18" t="inlineStr">
         <is>
@@ -5321,10 +5289,10 @@
         </is>
       </c>
       <c r="J106" s="10" t="n">
-        <v>7.314</v>
+        <v>2.813</v>
       </c>
       <c r="K106" s="10" t="n">
-        <v>7.599</v>
+        <v>2.95</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="15" t="inlineStr"/>
@@ -5337,33 +5305,40 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>0.725</v>
+        <v>2.93</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>0.0211</v>
+        <v>0.0103</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>1617300</v>
+        <v>1325900</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I107" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J107" s="10" t="n"/>
-      <c r="K107" s="10" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>58.57</v>
+      </c>
+      <c r="I107" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>2.819</v>
+      </c>
+      <c r="K107" s="10" t="n">
+        <v>2.706</v>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="15" t="inlineStr"/>
     </row>
@@ -5375,28 +5350,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>0.025</v>
+        <v>0.635</v>
       </c>
       <c r="E108" s="17" t="n">
-        <v>-0.1667</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1603700</v>
+        <v>1322300</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.41</v>
+        <v>0.64</v>
       </c>
       <c r="H108" t="n">
-        <v>59.21</v>
+        <v>48.28</v>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
@@ -5404,10 +5379,10 @@
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.02</v>
+        <v>0.64</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>0.018</v>
+        <v>0.63</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="15" t="inlineStr"/>
@@ -5420,28 +5395,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.37</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>0.0148</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1592600</v>
+        <v>1321700</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H109" t="n">
-        <v>49.98</v>
+        <v>60.04</v>
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
@@ -5449,10 +5424,10 @@
         </is>
       </c>
       <c r="J109" s="10" t="n">
-        <v>0.866</v>
+        <v>1.285</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>0.861</v>
+        <v>1.194</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="15" t="inlineStr"/>
@@ -5465,39 +5440,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>1.19</v>
+        <v>2.66</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>0.0721</v>
+        <v>0.027</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1592000</v>
+        <v>1303700</v>
       </c>
       <c r="G110" s="13" t="n">
-        <v>0.47</v>
+        <v>0.25</v>
       </c>
       <c r="H110" t="n">
-        <v>61.19</v>
-      </c>
-      <c r="I110" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.55</v>
+      </c>
+      <c r="I110" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="10" t="n">
-        <v>1.108</v>
+        <v>2.603</v>
       </c>
       <c r="K110" s="10" t="n">
-        <v>0.945</v>
+        <v>2.601</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
@@ -5510,39 +5485,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E111" s="11" t="n">
-        <v>0.0426</v>
+        <v>6.9</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>-0.0254</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1586200</v>
+        <v>1296800</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>1.45</v>
+        <v>0.23</v>
       </c>
       <c r="H111" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="I111" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.89</v>
+      </c>
+      <c r="I111" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>0.246</v>
+        <v>6.839</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>0.25</v>
+        <v>6.828</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5555,28 +5530,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>0.43</v>
+        <v>0.285</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>0.0361</v>
+        <v>0.0179</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1559000</v>
+        <v>1293000</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="H112" t="n">
-        <v>57.91</v>
+        <v>43.56</v>
       </c>
       <c r="I112" s="18" t="inlineStr">
         <is>
@@ -5584,10 +5559,10 @@
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.403</v>
+        <v>0.294</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>0.368</v>
+        <v>0.318</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5600,39 +5575,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>-0.0154</v>
+        <v>0.635</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1549800</v>
+        <v>1292600</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H113" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="I113" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.46</v>
+      </c>
+      <c r="I113" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>0.676</v>
+        <v>0.634</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>0.731</v>
+        <v>0.624</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5645,39 +5620,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>-0.0105</v>
+        <v>0.615</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>0.025</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>1485800</v>
+        <v>1281400</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="H114" t="n">
-        <v>51.97</v>
-      </c>
-      <c r="I114" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.89</v>
+      </c>
+      <c r="I114" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="10" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.582</v>
       </c>
       <c r="K114" s="10" t="n">
-        <v>0.897</v>
+        <v>0.493</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
@@ -5690,28 +5665,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TWL</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>0.025</v>
+        <v>0.26</v>
       </c>
       <c r="E115" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>1478900</v>
+        <v>1264500</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.16</v>
+        <v>1.45</v>
       </c>
       <c r="H115" t="n">
-        <v>52.81</v>
+        <v>38.3</v>
       </c>
       <c r="I115" s="18" t="inlineStr">
         <is>
@@ -5719,10 +5694,10 @@
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>0.024</v>
+        <v>0.271</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>0.024</v>
+        <v>0.268</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5735,39 +5710,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>1.43</v>
+        <v>0.835</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>0.0593</v>
+        <v>0.0121</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1456000</v>
+        <v>1257500</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H116" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="I116" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.7</v>
+      </c>
+      <c r="I116" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>1.309</v>
+        <v>0.861</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>1.253</v>
+        <v>0.923</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5780,39 +5755,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0129</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SRIDGE</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>0</v>
+        <v>4.22</v>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>0.012</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>1434100</v>
+        <v>1255000</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>1.28</v>
+        <v>0.14</v>
       </c>
       <c r="H117" t="n">
-        <v>41.86</v>
-      </c>
-      <c r="I117" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.06</v>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="10" t="n">
-        <v>0.119</v>
+        <v>4.024</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>0.131</v>
+        <v>3.685</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="15" t="inlineStr"/>
@@ -5825,28 +5800,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E118" s="16" t="n">
-        <v>0</v>
+        <v>0.88</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>0.0292</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>1422400</v>
+        <v>1231200</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="H118" t="n">
-        <v>68</v>
+        <v>49.3</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
@@ -5854,10 +5829,10 @@
         </is>
       </c>
       <c r="J118" s="10" t="n">
-        <v>1.994</v>
+        <v>0.884</v>
       </c>
       <c r="K118" s="10" t="n">
-        <v>1.968</v>
+        <v>0.865</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -5870,31 +5845,40 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D119" s="10" t="n">
-        <v>0.005</v>
+        <v>0.63</v>
       </c>
       <c r="E119" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>1370300</v>
-      </c>
-      <c r="G119" s="13" t="n"/>
-      <c r="I119" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J119" s="10" t="n"/>
-      <c r="K119" s="10" t="n"/>
+        <v>1225600</v>
+      </c>
+      <c r="G119" s="13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H119" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="K119" s="10" t="n">
+        <v>0.612</v>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="15" t="inlineStr"/>
     </row>
@@ -5906,28 +5890,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>0.36</v>
+        <v>7.64</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>0.0588</v>
+        <v>0.0255</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>1369900</v>
+        <v>1224600</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>1.36</v>
+        <v>0.26</v>
       </c>
       <c r="H120" t="n">
-        <v>60.77</v>
+        <v>58.74</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
@@ -5935,10 +5919,10 @@
         </is>
       </c>
       <c r="J120" s="10" t="n">
-        <v>0.341</v>
+        <v>7.336</v>
       </c>
       <c r="K120" s="10" t="n">
-        <v>0.356</v>
+        <v>6.986</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="15" t="inlineStr"/>
@@ -5951,28 +5935,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>0.635</v>
+        <v>2.4</v>
       </c>
       <c r="E121" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>1322300</v>
+        <v>1205200</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>0.64</v>
+        <v>0.29</v>
       </c>
       <c r="H121" t="n">
-        <v>48.28</v>
+        <v>37.29</v>
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
@@ -5980,10 +5964,10 @@
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>0.64</v>
+        <v>2.467</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>0.63</v>
+        <v>2.62</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="15" t="inlineStr"/>
@@ -5996,39 +5980,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0007</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PUC</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="E122" s="16" t="n">
-        <v>0</v>
+        <v>1.36</v>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>0.0226</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>1307800</v>
+        <v>1200000</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.09</v>
+        <v>0.47</v>
       </c>
       <c r="H122" t="n">
-        <v>48.23</v>
-      </c>
-      <c r="I122" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.17</v>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="10" t="n">
-        <v>0.037</v>
+        <v>1.362</v>
       </c>
       <c r="K122" s="10" t="n">
-        <v>0.034</v>
+        <v>1.431</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -6041,28 +6025,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E123" s="16" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>1292600</v>
+        <v>1199900</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H123" t="n">
-        <v>51.46</v>
+        <v>57.03</v>
       </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
@@ -6070,10 +6054,10 @@
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>0.634</v>
+        <v>0.747</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>0.624</v>
+        <v>0.709</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="15" t="inlineStr"/>
@@ -6086,28 +6070,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>0.04</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1270500</v>
+        <v>1192900</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="H124" t="n">
-        <v>46.74</v>
+        <v>51.74</v>
       </c>
       <c r="I124" s="18" t="inlineStr">
         <is>
@@ -6115,10 +6099,10 @@
         </is>
       </c>
       <c r="J124" s="10" t="n">
-        <v>0.263</v>
+        <v>0.347</v>
       </c>
       <c r="K124" s="10" t="n">
-        <v>0.28</v>
+        <v>0.331</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -6131,39 +6115,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SUPERLN</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E125" s="16" t="n">
-        <v>0</v>
+        <v>0.955</v>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>0.0269</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>1264500</v>
+        <v>1192600</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="H125" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I125" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.31</v>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="10" t="n">
-        <v>0.271</v>
+        <v>0.897</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>0.268</v>
+        <v>0.86</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="15" t="inlineStr"/>
@@ -6176,28 +6160,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E126" s="11" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.465</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>1259300</v>
+        <v>1186600</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="H126" t="n">
-        <v>60.95</v>
+        <v>54.59</v>
       </c>
       <c r="I126" s="18" t="inlineStr">
         <is>
@@ -6205,10 +6189,10 @@
         </is>
       </c>
       <c r="J126" s="10" t="n">
-        <v>0.128</v>
+        <v>0.462</v>
       </c>
       <c r="K126" s="10" t="n">
-        <v>0.107</v>
+        <v>0.462</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -6221,28 +6205,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>1.29</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>1256800</v>
+        <v>1167000</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.66</v>
+        <v>0.17</v>
       </c>
       <c r="H127" t="n">
-        <v>47.67</v>
+        <v>60.23</v>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
@@ -6250,10 +6234,10 @@
         </is>
       </c>
       <c r="J127" s="10" t="n">
-        <v>0.903</v>
+        <v>1.24</v>
       </c>
       <c r="K127" s="10" t="n">
-        <v>0.897</v>
+        <v>1.212</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="15" t="inlineStr"/>
@@ -6266,28 +6250,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>0.145</v>
+        <v>0.67</v>
       </c>
       <c r="E128" s="17" t="n">
-        <v>-0.0333</v>
+        <v>-0.0629</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>1253100</v>
+        <v>1140000</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.08</v>
+        <v>2.05</v>
       </c>
       <c r="H128" t="n">
-        <v>33.24</v>
+        <v>55.96</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
@@ -6295,10 +6279,10 @@
         </is>
       </c>
       <c r="J128" s="10" t="n">
-        <v>0.152</v>
+        <v>0.653</v>
       </c>
       <c r="K128" s="10" t="n">
-        <v>0.174</v>
+        <v>0.618</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -6311,39 +6295,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ASTRO</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E129" s="16" t="n">
-        <v>0</v>
+        <v>5.74</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>1252500</v>
+        <v>1104300</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.28</v>
+        <v>0.14</v>
       </c>
       <c r="H129" t="n">
-        <v>41.03</v>
-      </c>
-      <c r="I129" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.4</v>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.054</v>
+        <v>5.811</v>
       </c>
       <c r="K129" s="10" t="n">
-        <v>0.057</v>
+        <v>6.057</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="15" t="inlineStr"/>
@@ -6356,28 +6340,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>0.835</v>
+        <v>3.11</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>0.0121</v>
+        <v>0.0197</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>1234700</v>
+        <v>1099700</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.46</v>
+        <v>0.29</v>
       </c>
       <c r="H130" t="n">
-        <v>36.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I130" s="18" t="inlineStr">
         <is>
@@ -6385,10 +6369,10 @@
         </is>
       </c>
       <c r="J130" s="10" t="n">
-        <v>0.861</v>
+        <v>2.871</v>
       </c>
       <c r="K130" s="10" t="n">
-        <v>0.923</v>
+        <v>2.407</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -6401,39 +6385,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E131" s="11" t="n">
-        <v>0.005500000000000001</v>
+        <v>7.35</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>1222400</v>
+        <v>1098500</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>1.54</v>
+        <v>0.1</v>
       </c>
       <c r="H131" t="n">
-        <v>36.99</v>
-      </c>
-      <c r="I131" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.2</v>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>0.944</v>
+        <v>7.401</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>0.968</v>
+        <v>7.773</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="15" t="inlineStr"/>
@@ -6446,39 +6430,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0029</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DIGISTA</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>-0.1429</v>
+        <v>11.08</v>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>0.024</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>1218300</v>
+        <v>1091600</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>30.95</v>
+        <v>0.29</v>
       </c>
       <c r="H132" t="n">
-        <v>36.96</v>
-      </c>
-      <c r="I132" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.81</v>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="10" t="n">
-        <v>0.036</v>
+        <v>10.56</v>
       </c>
       <c r="K132" s="10" t="n">
-        <v>0.038</v>
+        <v>9.938000000000001</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -6491,38 +6475,40 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>EVOCOM</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E133" s="16" t="n">
-        <v>0</v>
+        <v>0.6</v>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>1202900</v>
+        <v>1085800</v>
       </c>
       <c r="G133" s="13" t="n">
         <v>0.21</v>
       </c>
       <c r="H133" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="I133" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.09</v>
+      </c>
+      <c r="I133" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="K133" s="10" t="n"/>
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="K133" s="10" t="n">
+        <v>0.531</v>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="15" t="inlineStr"/>
     </row>
@@ -6534,28 +6520,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>0.615</v>
+        <v>0.74</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>1193500</v>
+        <v>1081000</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.18</v>
+        <v>0.49</v>
       </c>
       <c r="H134" t="n">
-        <v>57.89</v>
+        <v>46.87</v>
       </c>
       <c r="I134" s="18" t="inlineStr">
         <is>
@@ -6563,10 +6549,10 @@
         </is>
       </c>
       <c r="J134" s="10" t="n">
-        <v>0.582</v>
+        <v>0.752</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>0.493</v>
+        <v>0.765</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -6579,39 +6565,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E135" s="16" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>1177300</v>
+        <v>1076600</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H135" t="n">
-        <v>54.59</v>
-      </c>
-      <c r="I135" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.92</v>
+      </c>
+      <c r="I135" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.462</v>
+        <v>0.179</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>0.462</v>
+        <v>0.165</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="15" t="inlineStr"/>
@@ -6624,28 +6610,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>0.35</v>
+        <v>0.62</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1161200</v>
+        <v>1076500</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.15</v>
+        <v>2.62</v>
       </c>
       <c r="H136" t="n">
-        <v>51.74</v>
+        <v>34.14</v>
       </c>
       <c r="I136" s="18" t="inlineStr">
         <is>
@@ -6653,10 +6639,10 @@
         </is>
       </c>
       <c r="J136" s="10" t="n">
-        <v>0.347</v>
+        <v>0.63</v>
       </c>
       <c r="K136" s="10" t="n">
-        <v>0.331</v>
+        <v>0.652</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -6669,28 +6655,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>BJCORP</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>0.615</v>
+        <v>0.25</v>
       </c>
       <c r="E137" s="11" t="n">
-        <v>0.025</v>
+        <v>0.0204</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>1153700</v>
+        <v>1059200</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>0.15</v>
+        <v>0.46</v>
       </c>
       <c r="H137" t="n">
-        <v>42.74</v>
+        <v>56.77</v>
       </c>
       <c r="I137" s="18" t="inlineStr">
         <is>
@@ -6698,10 +6684,10 @@
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.64</v>
+        <v>0.248</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>0.679</v>
+        <v>0.249</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="15" t="inlineStr"/>
@@ -6714,39 +6700,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>2.76</v>
+        <v>4.64</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>0.0337</v>
+        <v>0.0022</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>1149300</v>
+        <v>1043400</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="H138" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="I138" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.11</v>
+      </c>
+      <c r="I138" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="10" t="n">
-        <v>2.812</v>
+        <v>4.462</v>
       </c>
       <c r="K138" s="10" t="n">
-        <v>2.95</v>
+        <v>4.446</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -6759,40 +6745,38 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E139" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.365</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>1115500</v>
+        <v>1022300</v>
       </c>
       <c r="G139" s="13" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="H139" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="I139" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.41</v>
+      </c>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="10" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="K139" s="10" t="n">
-        <v>0.709</v>
-      </c>
+        <v>0.342</v>
+      </c>
+      <c r="K139" s="10" t="n"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="15" t="inlineStr"/>
     </row>
@@ -6804,28 +6788,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>1.37</v>
+        <v>0.375</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>0.0148</v>
+        <v>0.0135</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>1114800</v>
+        <v>1016900</v>
       </c>
       <c r="G140" s="13" t="n">
         <v>0.41</v>
       </c>
       <c r="H140" t="n">
-        <v>60.04</v>
+        <v>45.96</v>
       </c>
       <c r="I140" s="18" t="inlineStr">
         <is>
@@ -6833,10 +6817,10 @@
         </is>
       </c>
       <c r="J140" s="10" t="n">
-        <v>1.285</v>
+        <v>0.381</v>
       </c>
       <c r="K140" s="10" t="n">
-        <v>1.194</v>
+        <v>0.386</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -6849,28 +6833,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SUPERLN</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>0.96</v>
+        <v>1.44</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>0.0323</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>1102700</v>
+        <v>997500</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>2.41</v>
+        <v>0.47</v>
       </c>
       <c r="H141" t="n">
-        <v>64.98999999999999</v>
+        <v>70.33</v>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
@@ -6878,10 +6862,10 @@
         </is>
       </c>
       <c r="J141" s="10" t="n">
-        <v>0.897</v>
+        <v>1.379</v>
       </c>
       <c r="K141" s="10" t="n">
-        <v>0.86</v>
+        <v>1.351</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="15" t="inlineStr"/>
@@ -6894,39 +6878,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>1.36</v>
+        <v>2.41</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>0.0226</v>
+        <v>0.0042</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>1101800</v>
+        <v>937300</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.43</v>
+        <v>0.09</v>
       </c>
       <c r="H142" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="I142" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.3</v>
+      </c>
+      <c r="I142" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="10" t="n">
-        <v>1.362</v>
+        <v>2.428</v>
       </c>
       <c r="K142" s="10" t="n">
-        <v>1.431</v>
+        <v>2.423</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -6939,28 +6923,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>EWICAP</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>0.125</v>
+        <v>0.61</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>0.0417</v>
+        <v>0.0083</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>1081300</v>
+        <v>915800</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>0.93</v>
+        <v>0.19</v>
       </c>
       <c r="H143" t="n">
-        <v>34.09</v>
+        <v>65.55</v>
       </c>
       <c r="I143" s="18" t="inlineStr">
         <is>
@@ -6968,10 +6952,10 @@
         </is>
       </c>
       <c r="J143" s="10" t="n">
-        <v>0.136</v>
+        <v>0.554</v>
       </c>
       <c r="K143" s="10" t="n">
-        <v>0.164</v>
+        <v>0.492</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="15" t="inlineStr"/>
@@ -6984,39 +6968,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>HEXCARE</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.515</v>
+      </c>
+      <c r="E144" s="11" t="n">
+        <v>0.0198</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1060200</v>
+        <v>913300</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>1.19</v>
+        <v>0.33</v>
       </c>
       <c r="H144" t="n">
-        <v>49.31</v>
-      </c>
-      <c r="I144" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.65</v>
+      </c>
+      <c r="I144" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J144" s="10" t="n">
-        <v>0.06</v>
+        <v>0.493</v>
       </c>
       <c r="K144" s="10" t="n">
-        <v>0.061</v>
+        <v>0.485</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -7029,39 +7013,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ZELAN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E145" s="16" t="n">
-        <v>0</v>
+        <v>6.81</v>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v>0.0134</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>1060000</v>
+        <v>907600</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>4.24</v>
+        <v>0.08</v>
       </c>
       <c r="H145" t="n">
-        <v>52.15</v>
-      </c>
-      <c r="I145" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.19</v>
+      </c>
+      <c r="I145" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="10" t="n">
-        <v>0.053</v>
+        <v>6.998</v>
       </c>
       <c r="K145" s="10" t="n">
-        <v>0.057</v>
+        <v>7.452</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="15" t="inlineStr"/>
@@ -7074,39 +7058,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E146" s="11" t="n">
-        <v>0.042</v>
+        <v>1.82</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>1048600</v>
+        <v>895700</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="H146" t="n">
-        <v>47.88</v>
-      </c>
-      <c r="I146" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I146" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="10" t="n">
-        <v>0.752</v>
+        <v>1.812</v>
       </c>
       <c r="K146" s="10" t="n">
-        <v>0.766</v>
+        <v>1.909</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -7119,39 +7103,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D147" s="10" t="n">
-        <v>4.23</v>
+        <v>5.89</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>0.0144</v>
+        <v>0.0261</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>1040700</v>
+        <v>875600</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="H147" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="I147" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.47</v>
+      </c>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="10" t="n">
-        <v>4.025</v>
+        <v>5.556</v>
       </c>
       <c r="K147" s="10" t="n">
-        <v>3.685</v>
+        <v>5.394</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="15" t="inlineStr"/>
@@ -7164,39 +7148,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E148" s="17" t="n">
-        <v>-0.042</v>
+        <v>6.3</v>
+      </c>
+      <c r="E148" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>1031500</v>
+        <v>867500</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>1.86</v>
+        <v>0.11</v>
       </c>
       <c r="H148" t="n">
-        <v>59.93</v>
-      </c>
-      <c r="I148" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.57</v>
+      </c>
+      <c r="I148" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="10" t="n">
-        <v>0.654</v>
+        <v>6.335</v>
       </c>
       <c r="K148" s="10" t="n">
-        <v>0.618</v>
+        <v>6.605</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -7209,39 +7193,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D149" s="10" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E149" s="11" t="n">
-        <v>0.0351</v>
+        <v>1.01</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>1023900</v>
+        <v>866100</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H149" t="n">
-        <v>49.95</v>
-      </c>
-      <c r="I149" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.04</v>
+      </c>
+      <c r="I149" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="10" t="n">
-        <v>0.884</v>
+        <v>1.023</v>
       </c>
       <c r="K149" s="10" t="n">
-        <v>0.865</v>
+        <v>0.985</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="15" t="inlineStr"/>
@@ -7254,39 +7238,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>BJCORP</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>0.25</v>
+        <v>3.98</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>0.0204</v>
+        <v>0.0025</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>1016500</v>
+        <v>860300</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.44</v>
+        <v>0.23</v>
       </c>
       <c r="H150" t="n">
-        <v>56.77</v>
-      </c>
-      <c r="I150" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.44</v>
+      </c>
+      <c r="I150" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="10" t="n">
-        <v>0.248</v>
+        <v>3.843</v>
       </c>
       <c r="K150" s="10" t="n">
-        <v>0.249</v>
+        <v>3.768</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -7299,39 +7283,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D151" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>-0.0156</v>
+        <v>1.1</v>
+      </c>
+      <c r="E151" s="11" t="n">
+        <v>0.028</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>996500</v>
+        <v>857800</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="H151" t="n">
-        <v>46.55</v>
-      </c>
-      <c r="I151" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.27</v>
+      </c>
+      <c r="I151" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="10" t="n">
-        <v>1.274</v>
+        <v>1.118</v>
       </c>
       <c r="K151" s="10" t="n">
-        <v>1.319</v>
+        <v>1.116</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="15" t="inlineStr"/>
@@ -7344,28 +7328,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D152" s="10" t="n">
-        <v>7.63</v>
+        <v>2.24</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>0.0242</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>993000</v>
+        <v>851400</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.21</v>
+        <v>0.63</v>
       </c>
       <c r="H152" t="n">
-        <v>58.56</v>
+        <v>57.61</v>
       </c>
       <c r="I152" s="14" t="inlineStr">
         <is>
@@ -7373,10 +7357,10 @@
         </is>
       </c>
       <c r="J152" s="10" t="n">
-        <v>7.335</v>
+        <v>2.134</v>
       </c>
       <c r="K152" s="10" t="n">
-        <v>6.985</v>
+        <v>2.222</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -7389,28 +7373,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>0.6</v>
+        <v>2.98</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>0.0169</v>
+        <v>0.0347</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>968900</v>
+        <v>819000</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H153" t="n">
-        <v>60.09</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="I153" s="14" t="inlineStr">
         <is>
@@ -7418,10 +7402,10 @@
         </is>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>2.764</v>
       </c>
       <c r="K153" s="10" t="n">
-        <v>0.531</v>
+        <v>2.406</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="15" t="inlineStr"/>
@@ -7434,28 +7418,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0336</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>WINSTAR</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E154" s="16" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E154" s="11" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>930100</v>
+        <v>749200</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>1.94</v>
+        <v>0.21</v>
       </c>
       <c r="H154" t="n">
-        <v>33.73</v>
+        <v>56.21</v>
       </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
@@ -7463,10 +7447,10 @@
         </is>
       </c>
       <c r="J154" s="10" t="n">
-        <v>0.637</v>
+        <v>1.257</v>
       </c>
       <c r="K154" s="10" t="n">
-        <v>0.644</v>
+        <v>1.13</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -7479,28 +7463,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D155" s="10" t="n">
-        <v>11.08</v>
+        <v>0.55</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>0.024</v>
+        <v>0.0377</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>903500</v>
+        <v>746000</v>
       </c>
       <c r="G155" s="13" t="n">
         <v>0.24</v>
       </c>
       <c r="H155" t="n">
-        <v>62.81</v>
+        <v>46.98</v>
       </c>
       <c r="I155" s="14" t="inlineStr">
         <is>
@@ -7508,10 +7492,10 @@
         </is>
       </c>
       <c r="J155" s="10" t="n">
-        <v>10.56</v>
+        <v>0.553</v>
       </c>
       <c r="K155" s="10" t="n">
-        <v>9.938000000000001</v>
+        <v>0.588</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="15" t="inlineStr"/>
@@ -7524,28 +7508,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D156" s="10" t="n">
-        <v>0.615</v>
+        <v>0.88</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>0.0165</v>
+        <v>0.0115</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>899500</v>
+        <v>721100</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H156" t="n">
-        <v>66.22</v>
+        <v>60.48</v>
       </c>
       <c r="I156" s="18" t="inlineStr">
         <is>
@@ -7553,10 +7537,10 @@
         </is>
       </c>
       <c r="J156" s="10" t="n">
-        <v>0.555</v>
+        <v>0.839</v>
       </c>
       <c r="K156" s="10" t="n">
-        <v>0.492</v>
+        <v>0.805</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -7569,28 +7553,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D157" s="10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="E157" s="17" t="n">
-        <v>-0.0372</v>
+        <v>5.19</v>
+      </c>
+      <c r="E157" s="11" t="n">
+        <v>0.0257</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>893500</v>
+        <v>661300</v>
       </c>
       <c r="G157" s="13" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="H157" t="n">
-        <v>47.61</v>
+        <v>56.42</v>
       </c>
       <c r="I157" s="14" t="inlineStr">
         <is>
@@ -7598,10 +7582,10 @@
         </is>
       </c>
       <c r="J157" s="10" t="n">
-        <v>1.811</v>
+        <v>5.072</v>
       </c>
       <c r="K157" s="10" t="n">
-        <v>1.909</v>
+        <v>5.034</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="15" t="inlineStr"/>
@@ -7614,28 +7598,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>KLK</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E158" s="16" t="n">
-        <v>0</v>
+        <v>20.5</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>888900</v>
+        <v>649300</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.13</v>
+        <v>0.98</v>
       </c>
       <c r="H158" t="n">
-        <v>60.23</v>
+        <v>43.23</v>
       </c>
       <c r="I158" s="14" t="inlineStr">
         <is>
@@ -7643,10 +7627,10 @@
         </is>
       </c>
       <c r="J158" s="10" t="n">
-        <v>1.24</v>
+        <v>20.765</v>
       </c>
       <c r="K158" s="10" t="n">
-        <v>1.212</v>
+        <v>21.619</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -7659,28 +7643,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D159" s="10" t="n">
-        <v>2.41</v>
+        <v>1.35</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>0.0042</v>
+        <v>0.0385</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>868500</v>
+        <v>645000</v>
       </c>
       <c r="G159" s="13" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="H159" t="n">
-        <v>47.3</v>
+        <v>55.93</v>
       </c>
       <c r="I159" s="18" t="inlineStr">
         <is>
@@ -7688,10 +7672,10 @@
         </is>
       </c>
       <c r="J159" s="10" t="n">
-        <v>2.428</v>
+        <v>1.301</v>
       </c>
       <c r="K159" s="10" t="n">
-        <v>2.423</v>
+        <v>1.309</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="15" t="inlineStr"/>
@@ -7704,28 +7688,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E160" s="11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.55</v>
+      </c>
+      <c r="E160" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>837100</v>
+        <v>643700</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.39</v>
+        <v>0.44</v>
       </c>
       <c r="H160" t="n">
-        <v>70.33</v>
+        <v>40.89</v>
       </c>
       <c r="I160" s="14" t="inlineStr">
         <is>
@@ -7733,10 +7717,10 @@
         </is>
       </c>
       <c r="J160" s="10" t="n">
-        <v>1.379</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K160" s="10" t="n">
-        <v>1.351</v>
+        <v>0.574</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -7749,39 +7733,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D161" s="10" t="n">
-        <v>3.98</v>
+        <v>0.68</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>0.0025</v>
+        <v>0.0303</v>
       </c>
       <c r="F161" s="12" t="n">
-        <v>810500</v>
+        <v>628200</v>
       </c>
       <c r="G161" s="13" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="H161" t="n">
-        <v>57.44</v>
-      </c>
-      <c r="I161" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.79</v>
+      </c>
+      <c r="I161" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="10" t="n">
-        <v>3.843</v>
+        <v>0.708</v>
       </c>
       <c r="K161" s="10" t="n">
-        <v>3.768</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="15" t="inlineStr"/>
@@ -7794,39 +7778,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D162" s="10" t="n">
-        <v>3.09</v>
+        <v>1.12</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>0.0131</v>
+        <v>0.0182</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>790500</v>
+        <v>622600</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.21</v>
+        <v>1.76</v>
       </c>
       <c r="H162" t="n">
-        <v>65.27</v>
-      </c>
-      <c r="I162" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.46</v>
+      </c>
+      <c r="I162" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="10" t="n">
-        <v>2.869</v>
+        <v>1.087</v>
       </c>
       <c r="K162" s="10" t="n">
-        <v>2.407</v>
+        <v>1.099</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -7839,39 +7823,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D163" s="10" t="n">
-        <v>2.4</v>
+        <v>0.68</v>
       </c>
       <c r="E163" s="17" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.0145</v>
       </c>
       <c r="F163" s="12" t="n">
-        <v>783400</v>
+        <v>620400</v>
       </c>
       <c r="G163" s="13" t="n">
-        <v>0.19</v>
+        <v>1.05</v>
       </c>
       <c r="H163" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="I163" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.91</v>
+      </c>
+      <c r="I163" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="10" t="n">
-        <v>2.467</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K163" s="10" t="n">
-        <v>2.62</v>
+        <v>0.665</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="15" t="inlineStr"/>
@@ -7884,28 +7868,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D164" s="10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E164" s="11" t="n">
-        <v>0.0279</v>
+        <v>3.16</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>757900</v>
+        <v>614500</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="H164" t="n">
-        <v>60.68</v>
+        <v>34.45</v>
       </c>
       <c r="I164" s="18" t="inlineStr">
         <is>
@@ -7913,10 +7897,10 @@
         </is>
       </c>
       <c r="J164" s="10" t="n">
-        <v>5.557</v>
+        <v>3.288</v>
       </c>
       <c r="K164" s="10" t="n">
-        <v>5.395</v>
+        <v>3.519</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -7929,28 +7913,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D165" s="10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E165" s="11" t="n">
-        <v>0.0069</v>
+        <v>5.09</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>-0.0174</v>
       </c>
       <c r="F165" s="12" t="n">
-        <v>744100</v>
+        <v>611200</v>
       </c>
       <c r="G165" s="13" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="H165" t="n">
-        <v>45.9</v>
+        <v>30.13</v>
       </c>
       <c r="I165" s="18" t="inlineStr">
         <is>
@@ -7958,10 +7942,10 @@
         </is>
       </c>
       <c r="J165" s="10" t="n">
-        <v>1.464</v>
+        <v>5.33</v>
       </c>
       <c r="K165" s="10" t="n">
-        <v>1.505</v>
+        <v>5.665</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="15" t="inlineStr"/>
@@ -7974,28 +7958,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D166" s="10" t="n">
-        <v>0.615</v>
+        <v>0.79</v>
       </c>
       <c r="E166" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>731500</v>
+        <v>602000</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>1.78</v>
+        <v>0.29</v>
       </c>
       <c r="H166" t="n">
-        <v>26.8</v>
+        <v>39.89</v>
       </c>
       <c r="I166" s="18" t="inlineStr">
         <is>
@@ -8003,10 +7987,10 @@
         </is>
       </c>
       <c r="J166" s="10" t="n">
-        <v>0.63</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K166" s="10" t="n">
-        <v>0.652</v>
+        <v>0.869</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -8019,28 +8003,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D167" s="10" t="n">
-        <v>0.515</v>
+        <v>1.56</v>
       </c>
       <c r="E167" s="11" t="n">
-        <v>0.0198</v>
+        <v>0.04</v>
       </c>
       <c r="F167" s="12" t="n">
-        <v>731000</v>
+        <v>569900</v>
       </c>
       <c r="G167" s="13" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H167" t="n">
-        <v>59.65</v>
+        <v>48.7</v>
       </c>
       <c r="I167" s="14" t="inlineStr">
         <is>
@@ -8048,10 +8032,10 @@
         </is>
       </c>
       <c r="J167" s="10" t="n">
-        <v>0.493</v>
+        <v>1.553</v>
       </c>
       <c r="K167" s="10" t="n">
-        <v>0.485</v>
+        <v>1.627</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="15" t="inlineStr"/>
@@ -8064,39 +8048,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D168" s="10" t="n">
-        <v>1.1</v>
+        <v>0.885</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>0.028</v>
+        <v>0.0172</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>712000</v>
+        <v>561400</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="H168" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="I168" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.48</v>
+      </c>
+      <c r="I168" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="10" t="n">
-        <v>1.118</v>
+        <v>0.889</v>
       </c>
       <c r="K168" s="10" t="n">
-        <v>1.116</v>
+        <v>0.901</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -8109,39 +8093,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D169" s="10" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="E169" s="16" t="n">
-        <v>0</v>
+        <v>0.755</v>
+      </c>
+      <c r="E169" s="11" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F169" s="12" t="n">
-        <v>707800</v>
+        <v>558800</v>
       </c>
       <c r="G169" s="13" t="n">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="H169" t="n">
-        <v>57.77</v>
-      </c>
-      <c r="I169" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.12</v>
+      </c>
+      <c r="I169" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J169" s="10" t="n">
-        <v>4.461</v>
+        <v>0.741</v>
       </c>
       <c r="K169" s="10" t="n">
-        <v>4.445</v>
+        <v>0.674</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="15" t="inlineStr"/>
@@ -8154,28 +8138,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>PESONA</t>
         </is>
       </c>
       <c r="D170" s="10" t="n">
-        <v>2.97</v>
+        <v>0.52</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>0.0313</v>
+        <v>0.0505</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>706100</v>
+        <v>541200</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>0.25</v>
+        <v>2.02</v>
       </c>
       <c r="H170" t="n">
-        <v>64.23</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I170" s="14" t="inlineStr">
         <is>
@@ -8183,10 +8167,10 @@
         </is>
       </c>
       <c r="J170" s="10" t="n">
-        <v>2.763</v>
+        <v>0.475</v>
       </c>
       <c r="K170" s="10" t="n">
-        <v>2.406</v>
+        <v>0.474</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -8199,39 +8183,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D171" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E171" s="11" t="n">
-        <v>0.0377</v>
+        <v>1.07</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="12" t="n">
-        <v>706000</v>
+        <v>531800</v>
       </c>
       <c r="G171" s="13" t="n">
         <v>0.22</v>
       </c>
       <c r="H171" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="I171" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.38</v>
+      </c>
+      <c r="I171" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="10" t="n">
-        <v>0.553</v>
+        <v>1.119</v>
       </c>
       <c r="K171" s="10" t="n">
-        <v>0.588</v>
+        <v>1.241</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="15" t="inlineStr"/>
@@ -8244,28 +8228,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E172" s="11" t="n">
-        <v>0.0156</v>
+        <v>0.78</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>693200</v>
+        <v>510800</v>
       </c>
       <c r="G172" s="13" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H172" t="n">
-        <v>56.21</v>
+        <v>22.49</v>
       </c>
       <c r="I172" s="14" t="inlineStr">
         <is>
@@ -8273,10 +8257,10 @@
         </is>
       </c>
       <c r="J172" s="10" t="n">
-        <v>1.257</v>
+        <v>0.864</v>
       </c>
       <c r="K172" s="10" t="n">
-        <v>1.13</v>
+        <v>1.025</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -8289,810 +8273,45 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D173" s="10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E173" s="16" t="n">
-        <v>0</v>
+        <v>0.95</v>
+      </c>
+      <c r="E173" s="11" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F173" s="12" t="n">
-        <v>684200</v>
+        <v>507200</v>
       </c>
       <c r="G173" s="13" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H173" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="I173" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.28</v>
+      </c>
+      <c r="I173" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="10" t="n">
-        <v>6.335</v>
+        <v>0.951</v>
       </c>
       <c r="K173" s="10" t="n">
-        <v>6.605</v>
+        <v>1.027</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="15" t="inlineStr"/>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>0296</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>HEGROUP</t>
-        </is>
-      </c>
-      <c r="D174" s="10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E174" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="12" t="n">
-        <v>673400</v>
-      </c>
-      <c r="G174" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H174" t="n">
-        <v>49.04</v>
-      </c>
-      <c r="I174" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="K174" s="10" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" s="15" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>6971</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>KOBAY</t>
-        </is>
-      </c>
-      <c r="D175" s="10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="E175" s="11" t="n">
-        <v>0.0278</v>
-      </c>
-      <c r="F175" s="12" t="n">
-        <v>672200</v>
-      </c>
-      <c r="G175" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H175" t="n">
-        <v>56.24</v>
-      </c>
-      <c r="I175" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v>2.132</v>
-      </c>
-      <c r="K175" s="10" t="n">
-        <v>2.222</v>
-      </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" s="15" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>0391</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>AMBEST</t>
-        </is>
-      </c>
-      <c r="D176" s="10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E176" s="11" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="F176" s="12" t="n">
-        <v>620500</v>
-      </c>
-      <c r="G176" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H176" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="I176" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J176" s="10" t="n">
-        <v>1.301</v>
-      </c>
-      <c r="K176" s="10" t="n">
-        <v>1.309</v>
-      </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" s="15" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>0326</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>SORENTO</t>
-        </is>
-      </c>
-      <c r="D177" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E177" s="17" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="F177" s="12" t="n">
-        <v>620400</v>
-      </c>
-      <c r="G177" s="13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H177" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I177" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="K177" s="10" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" s="15" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2445</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>KLK</t>
-        </is>
-      </c>
-      <c r="D178" s="10" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="E178" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" s="12" t="n">
-        <v>599300</v>
-      </c>
-      <c r="G178" s="13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H178" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="I178" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>20.767</v>
-      </c>
-      <c r="K178" s="10" t="n">
-        <v>21.619</v>
-      </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" s="15" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>5249</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>IOIPG</t>
-        </is>
-      </c>
-      <c r="D179" s="10" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="E179" s="17" t="n">
-        <v>-0.0125</v>
-      </c>
-      <c r="F179" s="12" t="n">
-        <v>595400</v>
-      </c>
-      <c r="G179" s="13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H179" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="I179" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>3.288</v>
-      </c>
-      <c r="K179" s="10" t="n">
-        <v>3.519</v>
-      </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" s="15" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>0390</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>ISF</t>
-        </is>
-      </c>
-      <c r="D180" s="10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E180" s="11" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="F180" s="12" t="n">
-        <v>586100</v>
-      </c>
-      <c r="G180" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H180" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="I180" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J180" s="10" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="K180" s="10" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" s="15" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>8869</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>PMETAL</t>
-        </is>
-      </c>
-      <c r="D181" s="10" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E181" s="11" t="n">
-        <v>0.004500000000000001</v>
-      </c>
-      <c r="F181" s="12" t="n">
-        <v>584400</v>
-      </c>
-      <c r="G181" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H181" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="I181" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>6.992</v>
-      </c>
-      <c r="K181" s="10" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" s="15" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>0459</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="D182" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E182" s="11" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="F182" s="12" t="n">
-        <v>584300</v>
-      </c>
-      <c r="G182" s="13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H182" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="I182" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="K182" s="10" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" s="15" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>RHBBANK</t>
-        </is>
-      </c>
-      <c r="D183" s="10" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="E183" s="17" t="n">
-        <v>-0.0014</v>
-      </c>
-      <c r="F183" s="12" t="n">
-        <v>580200</v>
-      </c>
-      <c r="G183" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H183" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="I183" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>7.401</v>
-      </c>
-      <c r="K183" s="10" t="n">
-        <v>7.773</v>
-      </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" s="15" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>5248</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>BAUTO</t>
-        </is>
-      </c>
-      <c r="D184" s="10" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E184" s="11" t="n">
-        <v>0.0172</v>
-      </c>
-      <c r="F184" s="12" t="n">
-        <v>551300</v>
-      </c>
-      <c r="G184" s="13" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H184" t="n">
-        <v>47.48</v>
-      </c>
-      <c r="I184" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="K184" s="10" t="n">
-        <v>0.901</v>
-      </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" s="15" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>0359</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>HKB</t>
-        </is>
-      </c>
-      <c r="D185" s="10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E185" s="11" t="n">
-        <v>0.0133</v>
-      </c>
-      <c r="F185" s="12" t="n">
-        <v>546800</v>
-      </c>
-      <c r="G185" s="13" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H185" t="n">
-        <v>60.32</v>
-      </c>
-      <c r="I185" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J185" s="10" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="K185" s="10" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" s="15" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>5351</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>EMPIRE</t>
-        </is>
-      </c>
-      <c r="D186" s="10" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E186" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" s="12" t="n">
-        <v>544200</v>
-      </c>
-      <c r="G186" s="13" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H186" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="I186" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="K186" s="10" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" s="15" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>8311</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>PESONA</t>
-        </is>
-      </c>
-      <c r="D187" s="10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E187" s="11" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="F187" s="12" t="n">
-        <v>541200</v>
-      </c>
-      <c r="G187" s="13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H187" t="n">
-        <v>74.34999999999999</v>
-      </c>
-      <c r="I187" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J187" s="10" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="K187" s="10" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" s="15" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>3794</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>MCEMENT</t>
-        </is>
-      </c>
-      <c r="D188" s="10" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="E188" s="17" t="n">
-        <v>-0.0174</v>
-      </c>
-      <c r="F188" s="12" t="n">
-        <v>518100</v>
-      </c>
-      <c r="G188" s="13" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H188" t="n">
-        <v>30.13</v>
-      </c>
-      <c r="I188" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J188" s="10" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="K188" s="10" t="n">
-        <v>5.665</v>
-      </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" s="15" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>0376</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>IAB</t>
-        </is>
-      </c>
-      <c r="D189" s="10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E189" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F189" s="12" t="n">
-        <v>508100</v>
-      </c>
-      <c r="G189" s="13" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H189" t="n">
-        <v>40.38</v>
-      </c>
-      <c r="I189" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J189" s="10" t="n">
-        <v>1.119</v>
-      </c>
-      <c r="K189" s="10" t="n">
-        <v>1.241</v>
-      </c>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" s="15" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>7081</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>PHARMA</t>
-        </is>
-      </c>
-      <c r="D190" s="10" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E190" s="17" t="n">
-        <v>-0.0063</v>
-      </c>
-      <c r="F190" s="12" t="n">
-        <v>504800</v>
-      </c>
-      <c r="G190" s="13" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H190" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="I190" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J190" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="K190" s="10" t="n">
-        <v>1.025</v>
-      </c>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" s="15" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M190"/>
+  <autoFilter ref="A1:M173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
+++ b/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,9 +97,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -573,10 +573,10 @@
         <v>0.0195</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4129400</v>
+        <v>4316400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>58.3</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.785高于50日均线0.696，SAR转多信号获均线支撑；RSI 58.3处中性偏上，未超买，信号可靠性尚可。</t>
+          <t>SAR转多信号，RSI 58.3未超买，现价高于50日均线约12.8%，技术面信号较为可靠。</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
         <v>0.0254</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>7212900</v>
+        <v>7261400</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>0.37</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>现价0.605高于50日均线0.55，SAR转多信号获均线支撑；RSI 57.67处中性偏上区间，未超买，信号可靠性尚可。</t>
+          <t>SAR转多信号，现价0.605高于50日均线0.55，RSI 57.67处中性偏上区间，未超买，信号技术面可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 60.32未超买，现价0.335略高于50日均线0.329，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，现价0.335略高于50日均线0.329，RSI 60.32处中性偏强区间，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -732,10 +732,10 @@
         <v>0.029</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>22944400</v>
+        <v>23352700</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>67.58</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号出现，但RSI 67.58已接近超买区，现价高于50日均线约31%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+          <t>现价0.355高于50日均线0.271约31%，SAR转多信号获趋势支撑；RSI 67.58接近超买区，可靠性中等偏强。</t>
         </is>
       </c>
     </row>
@@ -785,10 +785,10 @@
         <v>-0.0158</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3545600</v>
+        <v>3699300</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>56.03</v>
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0.1176</v>
+        <v>0.0588</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>193594000</v>
+        <v>224471400</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="H7" t="n">
-        <v>40.78</v>
+        <v>39.06</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -877,19 +877,19 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
+        <v>0.97</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>29296800</v>
+        <v>30041100</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H8" t="n">
-        <v>69.77</v>
+        <v>70.27</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.879</v>
+        <v>0.88</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
@@ -922,27 +922,27 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>-0.0476</v>
+        <v>0.71</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-0.034</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>24714600</v>
+        <v>26133700</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="H9" t="n">
-        <v>65.16</v>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
+        <v>69.05</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.67</v>
+        <v>0.671</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>0.575</v>
@@ -973,10 +973,10 @@
         <v>0.375</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>22818900</v>
+        <v>23104800</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>10.56</v>
+        <v>10.7</v>
       </c>
       <c r="H10" t="n">
         <v>57.25</v>
@@ -1003,33 +1003,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.195</v>
+        <v>2.26</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.0541</v>
+        <v>0.0463</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>15913600</v>
+        <v>16843700</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="10" t="n"/>
+        <v>0.59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>67.11</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>1.823</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="15" t="inlineStr"/>
     </row>
@@ -1041,28 +1048,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>0.0463</v>
+        <v>0.155</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>14850100</v>
+        <v>16232000</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="H12" t="n">
-        <v>67.11</v>
+        <v>47.71</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -1070,10 +1077,10 @@
         </is>
       </c>
       <c r="J12" s="10" t="n">
-        <v>2.016</v>
+        <v>0.156</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>1.823</v>
+        <v>0.156</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="15" t="inlineStr"/>
@@ -1086,40 +1093,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0</v>
+        <v>0.195</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0.0541</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>14424400</v>
+        <v>15978300</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H13" t="n">
-        <v>51.28</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>0.149</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="15" t="inlineStr"/>
     </row>
@@ -1131,28 +1131,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>0.0227</v>
+        <v>0.865</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>14263800</v>
+        <v>15252400</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
       <c r="H14" t="n">
-        <v>47.56</v>
+        <v>46.13</v>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.453</v>
+        <v>0.867</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>0.472</v>
+        <v>0.868</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
@@ -1176,28 +1176,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>-0.0455</v>
+        <v>0.16</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>13723100</v>
+        <v>15093800</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1.94</v>
+        <v>0.26</v>
       </c>
       <c r="H15" t="n">
-        <v>82.61</v>
+        <v>51.28</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.137</v>
+        <v>0.159</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>0.12</v>
+        <v>0.149</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
@@ -1221,39 +1221,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>-0.009899999999999999</v>
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0.1834</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>13628900</v>
+        <v>14536300</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.35</v>
+        <v>2.58</v>
       </c>
       <c r="H16" t="n">
-        <v>74.66</v>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.07</v>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.435</v>
+        <v>0.84</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>0.335</v>
+        <v>0.652</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="15" t="inlineStr"/>
@@ -1266,39 +1266,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.995</v>
+        <v>0.45</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0.1775</v>
+        <v>0.0227</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>13389500</v>
+        <v>14312400</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>2.38</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
-        <v>60.87</v>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.56</v>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="10" t="n">
-        <v>0.839</v>
+        <v>0.453</v>
       </c>
       <c r="K17" s="10" t="n">
-        <v>0.652</v>
+        <v>0.472</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="15" t="inlineStr"/>
@@ -1311,28 +1311,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.155</v>
+        <v>0.21</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>0</v>
+        <v>-0.0455</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>12750000</v>
+        <v>14121000</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.34</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>47.71</v>
+        <v>82.61</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.156</v>
+        <v>0.137</v>
       </c>
       <c r="K18" s="10" t="n">
-        <v>0.156</v>
+        <v>0.12</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="15" t="inlineStr"/>
@@ -1356,39 +1356,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>0</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>12334200</v>
+        <v>13662900</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>1.24</v>
+        <v>0.35</v>
       </c>
       <c r="H19" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.66</v>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.388</v>
+        <v>0.435</v>
       </c>
       <c r="K19" s="10" t="n">
-        <v>0.402</v>
+        <v>0.335</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="15" t="inlineStr"/>
@@ -1401,39 +1401,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.305</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>12237400</v>
+        <v>12787600</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>4.18</v>
+        <v>0.65</v>
       </c>
       <c r="H20" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.46</v>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.162</v>
+        <v>0.307</v>
       </c>
       <c r="K20" s="10" t="n">
-        <v>0.158</v>
+        <v>0.303</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="15" t="inlineStr"/>
@@ -1446,28 +1446,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D21" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>11817500</v>
+        <v>12762400</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>0.57</v>
+        <v>4.36</v>
       </c>
       <c r="H21" t="n">
-        <v>46.13</v>
+        <v>63.99</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.867</v>
+        <v>0.162</v>
       </c>
       <c r="K21" s="10" t="n">
-        <v>0.868</v>
+        <v>0.158</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="15" t="inlineStr"/>
@@ -1491,39 +1491,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.82</v>
+        <v>0.37</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>0</v>
+        <v>-0.0263</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>11535800</v>
+        <v>12741600</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.74</v>
+        <v>1.28</v>
       </c>
       <c r="H22" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.15</v>
+      </c>
+      <c r="I22" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.387</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.401</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
@@ -1536,28 +1536,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>0.0698</v>
+        <v>0.82</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>11282700</v>
+        <v>11843800</v>
       </c>
       <c r="G23" s="13" t="n">
         <v>0.76</v>
       </c>
       <c r="H23" t="n">
-        <v>38.88</v>
+        <v>54.27</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.474</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0.597</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="15" t="inlineStr"/>
@@ -1581,39 +1581,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>0.22</v>
+        <v>0.455</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>0.0732</v>
+        <v>0.0581</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>10887900</v>
+        <v>11746100</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>1.12</v>
+        <v>0.79</v>
       </c>
       <c r="H24" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="I24" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.29</v>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.221</v>
+        <v>0.473</v>
       </c>
       <c r="K24" s="10" t="n">
-        <v>0.263</v>
+        <v>0.597</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="15" t="inlineStr"/>
@@ -1626,39 +1626,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HBGLOB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>-0.6667000000000001</v>
+        <v>0.22</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0.0732</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>10862900</v>
+        <v>11451600</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>50.94</v>
+        <v>1.18</v>
       </c>
       <c r="H25" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
+        <v>43.44</v>
+      </c>
+      <c r="I25" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.028</v>
+        <v>0.221</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0.031</v>
+        <v>0.263</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1671,39 +1671,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>HBGLOB</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>-0.6667000000000001</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>9886300</v>
+        <v>11355800</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.82</v>
+        <v>53.25</v>
       </c>
       <c r="H26" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.051</v>
+        <v>0.028</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.047</v>
+        <v>0.031</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1716,28 +1716,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MQTECH</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>0.06</v>
+        <v>0.775</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>9177600</v>
+        <v>10117700</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>5.14</v>
+        <v>0.65</v>
       </c>
       <c r="H27" t="n">
-        <v>62.78</v>
+        <v>50.93</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.053</v>
+        <v>0.774</v>
       </c>
       <c r="K27" s="10" t="n">
-        <v>0.056</v>
+        <v>0.775</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="15" t="inlineStr"/>
@@ -1761,39 +1761,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.775</v>
+        <v>0.06</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>8573100</v>
+        <v>9892300</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="H28" t="n">
-        <v>50.93</v>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.9</v>
+      </c>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="10" t="n">
-        <v>0.774</v>
+        <v>0.051</v>
       </c>
       <c r="K28" s="10" t="n">
-        <v>0.775</v>
+        <v>0.047</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="15" t="inlineStr"/>
@@ -1806,39 +1806,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>MQTECH</t>
         </is>
       </c>
       <c r="D29" s="10" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>0</v>
+        <v>0.06</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>8408000</v>
+        <v>9191400</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>0.43</v>
+        <v>5.15</v>
       </c>
       <c r="H29" t="n">
-        <v>47.46</v>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.78</v>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.307</v>
+        <v>0.053</v>
       </c>
       <c r="K29" s="10" t="n">
-        <v>0.303</v>
+        <v>0.056</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="15" t="inlineStr"/>
@@ -1862,14 +1862,14 @@
       <c r="D30" s="10" t="n">
         <v>0.065</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="16" t="n">
         <v>-0.07139999999999999</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>7867400</v>
+        <v>7967400</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>4.19</v>
+        <v>4.24</v>
       </c>
       <c r="H30" t="n">
         <v>43.52</v>
@@ -1905,19 +1905,19 @@
         </is>
       </c>
       <c r="D31" s="10" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0.039</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>7628000</v>
+        <v>7829300</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="H31" t="n">
-        <v>50.85</v>
+        <v>51.69</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="J31" s="10" t="n">
-        <v>2.101</v>
+        <v>2.102</v>
       </c>
       <c r="K31" s="10" t="n">
         <v>2.226</v>
@@ -1956,10 +1956,10 @@
         <v>0.07690000000000001</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>7623600</v>
+        <v>7760800</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="H32" t="n">
         <v>50.9</v>
@@ -1986,28 +1986,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WAVEFRNT</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>7220400</v>
+        <v>7727400</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>9.25</v>
+        <v>0.6</v>
       </c>
       <c r="H33" t="n">
-        <v>53.08</v>
+        <v>34.46</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.136</v>
+        <v>0.457</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0.141</v>
+        <v>0.573</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2031,28 +2031,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>0.0455</v>
+        <v>0.64</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>7191400</v>
+        <v>7715400</v>
       </c>
       <c r="G34" s="13" t="n">
-        <v>1.6</v>
+        <v>0.75</v>
       </c>
       <c r="H34" t="n">
-        <v>70.39</v>
+        <v>63.72</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
@@ -2060,10 +2060,10 @@
         </is>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.102</v>
+        <v>0.627</v>
       </c>
       <c r="K34" s="10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.619</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="15" t="inlineStr"/>
@@ -2076,39 +2076,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E35" s="16" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="E35" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>7036200</v>
+        <v>7653500</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="H35" t="n">
-        <v>63.72</v>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.62</v>
+      </c>
+      <c r="I35" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="10" t="n">
-        <v>0.627</v>
+        <v>0.443</v>
       </c>
       <c r="K35" s="10" t="n">
-        <v>0.619</v>
+        <v>0.394</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="15" t="inlineStr"/>
@@ -2121,39 +2121,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>WAVEFRNT</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E36" s="16" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="E36" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>6913300</v>
+        <v>7247200</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>0.32</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.69</v>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="10" t="n">
-        <v>0.443</v>
+        <v>0.135</v>
       </c>
       <c r="K36" s="10" t="n">
-        <v>0.394</v>
+        <v>0.141</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="15" t="inlineStr"/>
@@ -2166,28 +2166,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D37" s="10" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>-0.0595</v>
+        <v>0.115</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>6834100</v>
+        <v>7191400</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>0.53</v>
+        <v>1.6</v>
       </c>
       <c r="H37" t="n">
-        <v>35.01</v>
+        <v>70.39</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="J37" s="10" t="n">
-        <v>0.457</v>
+        <v>0.102</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>0.573</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="15" t="inlineStr"/>
@@ -2220,19 +2220,19 @@
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.0609</v>
+        <v>0.0696</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>6634800</v>
+        <v>6854300</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="H38" t="n">
-        <v>37.11</v>
+        <v>38.49</v>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.281</v>
+        <v>1.282</v>
       </c>
       <c r="K38" s="10" t="n">
         <v>1.479</v>
@@ -2256,28 +2256,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>1.51</v>
+        <v>4.94</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.0414</v>
+        <v>0.0061</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>6408000</v>
+        <v>6846600</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.45</v>
+        <v>0.29</v>
       </c>
       <c r="H39" t="n">
-        <v>39.52</v>
+        <v>55</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1.56</v>
+        <v>4.885</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>1.838</v>
+        <v>4.783</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2301,39 +2301,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ASB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>0.065</v>
+        <v>1.5</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0833</v>
+        <v>0.0345</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>6362900</v>
+        <v>6721100</v>
       </c>
       <c r="G40" s="13" t="n">
-        <v>5.72</v>
+        <v>0.48</v>
       </c>
       <c r="H40" t="n">
-        <v>53.65</v>
-      </c>
-      <c r="I40" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.44</v>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.063</v>
+        <v>1.559</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>0.065</v>
+        <v>1.837</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2346,40 +2346,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D41" s="10" t="n">
-        <v>4.94</v>
+        <v>0.23</v>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0.0061</v>
+        <v>0.0222</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>6354000</v>
+        <v>6432300</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="H41" t="n">
-        <v>55</v>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>4.885</v>
-      </c>
-      <c r="K41" s="10" t="n">
-        <v>4.783</v>
-      </c>
+        <v>54.46</v>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="15" t="inlineStr"/>
     </row>
@@ -2391,36 +2387,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>0.0222</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>6292900</v>
+        <v>6374100</v>
       </c>
       <c r="G42" s="13" t="n">
-        <v>0.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>54.46</v>
-      </c>
-      <c r="I42" s="18" t="inlineStr">
+        <v>48.17</v>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J42" s="10" t="n"/>
-      <c r="K42" s="10" t="n"/>
+      <c r="J42" s="10" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="K42" s="10" t="n">
+        <v>0.279</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="15" t="inlineStr"/>
     </row>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ASB</t>
         </is>
       </c>
       <c r="D43" s="10" t="n">
-        <v>0.38</v>
+        <v>0.065</v>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0.0133</v>
+        <v>0.0833</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>6046500</v>
+        <v>6372900</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>0.89</v>
+        <v>5.73</v>
       </c>
       <c r="H43" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.65</v>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.373</v>
+        <v>0.063</v>
       </c>
       <c r="K43" s="10" t="n">
-        <v>0.37</v>
+        <v>0.065</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="15" t="inlineStr"/>
@@ -2477,39 +2477,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>0.275</v>
+        <v>0.38</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>0.0185</v>
+        <v>0.0133</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>5938000</v>
+        <v>6266500</v>
       </c>
       <c r="G44" s="13" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="H44" t="n">
-        <v>46</v>
-      </c>
-      <c r="I44" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.47</v>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.283</v>
+        <v>0.373</v>
       </c>
       <c r="K44" s="10" t="n">
-        <v>0.279</v>
+        <v>0.37</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="15" t="inlineStr"/>
@@ -2533,19 +2533,19 @@
       <c r="D45" s="10" t="n">
         <v>0.11</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>5891200</v>
+        <v>5992600</v>
       </c>
       <c r="G45" s="13" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="H45" t="n">
         <v>34.76</v>
       </c>
-      <c r="I45" s="18" t="inlineStr">
+      <c r="I45" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2567,28 +2567,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E46" s="16" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>5754900</v>
+        <v>5980800</v>
       </c>
       <c r="G46" s="13" t="n">
-        <v>1.39</v>
+        <v>0.51</v>
       </c>
       <c r="H46" t="n">
-        <v>83.09999999999999</v>
+        <v>55.88</v>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="J46" s="10" t="n">
-        <v>0.466</v>
+        <v>0.403</v>
       </c>
       <c r="K46" s="10" t="n">
-        <v>0.44</v>
+        <v>0.384</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="15" t="inlineStr"/>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.0517</v>
+        <v>0.0431</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>5576700</v>
+        <v>5932300</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H47" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="I47" s="18" t="inlineStr">
+        <v>48.86</v>
+      </c>
+      <c r="I47" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2672,15 +2672,15 @@
         <v>0.0272</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>5514500</v>
+        <v>5926300</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H48" t="n">
         <v>43.13</v>
       </c>
-      <c r="I48" s="18" t="inlineStr">
+      <c r="I48" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2702,28 +2702,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D49" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>0.0246</v>
+        <v>0.535</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>5378000</v>
+        <v>5780000</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>0.52</v>
+        <v>1.39</v>
       </c>
       <c r="H49" t="n">
-        <v>68.31999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="J49" s="10" t="n">
-        <v>1.119</v>
+        <v>0.466</v>
       </c>
       <c r="K49" s="10" t="n">
-        <v>1.066</v>
+        <v>0.44</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="15" t="inlineStr"/>
@@ -2747,28 +2747,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>0.665</v>
+        <v>1.25</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.0391</v>
+        <v>0.0246</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>5012900</v>
+        <v>5717200</v>
       </c>
       <c r="G50" s="13" t="n">
-        <v>1.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>62.73</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.604</v>
+        <v>1.119</v>
       </c>
       <c r="K50" s="10" t="n">
-        <v>0.586</v>
+        <v>1.066</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="15" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>0</v>
+        <v>0.67</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>0.0469</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>4997000</v>
+        <v>5247400</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>0.55</v>
+        <v>1.25</v>
       </c>
       <c r="H51" t="n">
-        <v>36.57</v>
-      </c>
-      <c r="I51" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.39</v>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>4.54</v>
+        <v>0.604</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>4.642</v>
+        <v>0.587</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E52" s="11" t="n">
-        <v>0.0122</v>
+        <v>4.44</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>4943300</v>
+        <v>5243600</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.42</v>
+        <v>0.58</v>
       </c>
       <c r="H52" t="n">
-        <v>55.88</v>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.77</v>
+      </c>
+      <c r="I52" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.403</v>
+        <v>4.539</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>0.384</v>
+        <v>4.642</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2897,15 +2897,15 @@
         <v>0.0195</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>4701100</v>
+        <v>5149600</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="H53" t="n">
         <v>51.27</v>
       </c>
-      <c r="I53" s="18" t="inlineStr">
+      <c r="I53" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2927,39 +2927,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>0.0213</v>
+        <v>0.0204</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>4622000</v>
+        <v>4806100</v>
       </c>
       <c r="G54" s="13" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="H54" t="n">
-        <v>60.46</v>
-      </c>
-      <c r="I54" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.35</v>
+      </c>
+      <c r="I54" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="10" t="n">
-        <v>0.456</v>
+        <v>1.053</v>
       </c>
       <c r="K54" s="10" t="n">
-        <v>0.45</v>
+        <v>1.112</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="15" t="inlineStr"/>
@@ -2972,39 +2972,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>4539500</v>
+        <v>4685300</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="H55" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="I55" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.46</v>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.13</v>
+        <v>0.456</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.14</v>
+        <v>0.45</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3017,39 +3017,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="11" t="n">
-        <v>0.0204</v>
+        <v>0.125</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>4526900</v>
+        <v>4669500</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="H56" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="I56" s="18" t="inlineStr">
+        <v>41.46</v>
+      </c>
+      <c r="I56" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>1.053</v>
+        <v>0.13</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>1.112</v>
+        <v>0.14</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v>0.0213</v>
+        <v>1.33</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>-0.0699</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>4194000</v>
+        <v>4435600</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>0.59</v>
+        <v>1.19</v>
       </c>
       <c r="H57" t="n">
-        <v>45.16</v>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.68</v>
+      </c>
+      <c r="I57" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>0.481</v>
+        <v>1.427</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>0.533</v>
+        <v>1.452</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3107,39 +3107,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>-0.0699</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>4183600</v>
+        <v>4335300</v>
       </c>
       <c r="G58" s="13" t="n">
-        <v>1.12</v>
+        <v>2.27</v>
       </c>
       <c r="H58" t="n">
-        <v>27.68</v>
-      </c>
-      <c r="I58" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.93</v>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>1.427</v>
+        <v>8.157</v>
       </c>
       <c r="K58" s="10" t="n">
-        <v>1.452</v>
+        <v>7.972</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="15" t="inlineStr"/>
@@ -3152,39 +3152,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>5.23</v>
+        <v>1.65</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.0255</v>
+        <v>0.0123</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>3766500</v>
+        <v>4234600</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.23</v>
+        <v>0.51</v>
       </c>
       <c r="H59" t="n">
-        <v>44.46</v>
-      </c>
-      <c r="I59" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.09</v>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>5.356</v>
+        <v>1.629</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>5.522</v>
+        <v>1.67</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3197,39 +3197,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>1.3</v>
+        <v>5.23</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.0317</v>
+        <v>0.0255</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>3696000</v>
+        <v>4228000</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.74</v>
+        <v>0.26</v>
       </c>
       <c r="H60" t="n">
-        <v>69.62</v>
-      </c>
-      <c r="I60" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.46</v>
+      </c>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>1.126</v>
+        <v>5.356</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>0.987</v>
+        <v>5.522</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3242,28 +3242,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.185</v>
+        <v>0.475</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.0278</v>
+        <v>0.0106</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>3644000</v>
+        <v>4204100</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>0.19</v>
+        <v>0.59</v>
       </c>
       <c r="H61" t="n">
-        <v>49.32</v>
+        <v>42.9</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="J61" s="10" t="n">
-        <v>0.185</v>
+        <v>0.481</v>
       </c>
       <c r="K61" s="10" t="n">
-        <v>0.187</v>
+        <v>0.533</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="15" t="inlineStr"/>
@@ -3287,39 +3287,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="E62" s="17" t="n">
-        <v>-0.0316</v>
+        <v>0.5</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>0.0101</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>3475200</v>
+        <v>3894700</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>0.46</v>
+        <v>1.06</v>
       </c>
       <c r="H62" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="I62" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.68</v>
+      </c>
+      <c r="I62" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>3.84</v>
+        <v>0.523</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>3.337</v>
+        <v>0.556</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3332,39 +3332,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>0.705</v>
+        <v>1.3</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.0071</v>
+        <v>0.0317</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>3240500</v>
+        <v>3891100</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.3</v>
+        <v>0.78</v>
       </c>
       <c r="H63" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I63" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.62</v>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>0.729</v>
+        <v>1.126</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0.724</v>
+        <v>0.987</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
@@ -3377,39 +3377,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E64" s="11" t="n">
-        <v>0.0303</v>
+        <v>3.98</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>-0.0316</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>3185500</v>
+        <v>3782900</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>0.87</v>
+        <v>0.5</v>
       </c>
       <c r="H64" t="n">
-        <v>37.91</v>
-      </c>
-      <c r="I64" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.3</v>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>0.524</v>
+        <v>3.84</v>
       </c>
       <c r="K64" s="10" t="n">
-        <v>0.556</v>
+        <v>3.337</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="15" t="inlineStr"/>
@@ -3422,28 +3422,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D65" s="10" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>-0.001</v>
+        <v>0.185</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>3173900</v>
+        <v>3644000</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="H65" t="n">
-        <v>47.39</v>
+        <v>49.32</v>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="J65" s="10" t="n">
-        <v>9.993</v>
+        <v>0.185</v>
       </c>
       <c r="K65" s="10" t="n">
-        <v>10.1</v>
+        <v>0.187</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="15" t="inlineStr"/>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>0.325</v>
+        <v>2.59</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>0.0484</v>
+        <v>0.0157</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>2998300</v>
+        <v>3426000</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>2.02</v>
+        <v>0.58</v>
       </c>
       <c r="H66" t="n">
-        <v>59.54</v>
+        <v>46.07</v>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.3</v>
+        <v>2.635</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>0.325</v>
+        <v>2.818</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v>0.0123</v>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>2985300</v>
+        <v>3406300</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="H67" t="n">
-        <v>52.09</v>
+        <v>46.74</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="J67" s="10" t="n">
-        <v>1.629</v>
+        <v>9.992000000000001</v>
       </c>
       <c r="K67" s="10" t="n">
-        <v>1.67</v>
+        <v>10.099</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
@@ -3557,39 +3557,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D68" s="10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E68" s="11" t="n">
-        <v>0.0157</v>
+        <v>0.7</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>2848500</v>
+        <v>3301100</v>
       </c>
       <c r="G68" s="13" t="n">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
       <c r="H68" t="n">
-        <v>46.07</v>
-      </c>
-      <c r="I68" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.94</v>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="10" t="n">
-        <v>2.635</v>
+        <v>0.728</v>
       </c>
       <c r="K68" s="10" t="n">
-        <v>2.818</v>
+        <v>0.724</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="15" t="inlineStr"/>
@@ -3602,39 +3602,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D69" s="10" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.0455</v>
+        <v>2.67</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>2816500</v>
+        <v>3261700</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="H69" t="n">
-        <v>52.55</v>
-      </c>
-      <c r="I69" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.52</v>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="10" t="n">
-        <v>2.298</v>
+        <v>2.721</v>
       </c>
       <c r="K69" s="10" t="n">
-        <v>2.22</v>
+        <v>2.748</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="15" t="inlineStr"/>
@@ -3647,39 +3647,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D70" s="10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>-0.0037</v>
+        <v>4.71</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>2795100</v>
+        <v>3191800</v>
       </c>
       <c r="G70" s="13" t="n">
-        <v>0.28</v>
+        <v>0.15</v>
       </c>
       <c r="H70" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="I70" s="18" t="inlineStr">
+        <v>46.82</v>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J70" s="10" t="n">
-        <v>2.72</v>
+        <v>4.729</v>
       </c>
       <c r="K70" s="10" t="n">
-        <v>2.748</v>
+        <v>4.8</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="15" t="inlineStr"/>
@@ -3692,40 +3692,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0</v>
+        <v>0.735</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>0.0352</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>2711700</v>
+        <v>3141400</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H71" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="I71" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="K71" s="10" t="n">
-        <v>0.782</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="10" t="n"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="15" t="inlineStr"/>
     </row>
@@ -3737,28 +3730,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>0.0484</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>2704600</v>
+        <v>3093300</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>0.84</v>
+        <v>2.08</v>
       </c>
       <c r="H72" t="n">
-        <v>89.59</v>
+        <v>59.54</v>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
@@ -3766,10 +3759,10 @@
         </is>
       </c>
       <c r="J72" s="10" t="n">
-        <v>3.119</v>
+        <v>0.3</v>
       </c>
       <c r="K72" s="10" t="n">
-        <v>2.641</v>
+        <v>0.325</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="15" t="inlineStr"/>
@@ -3782,28 +3775,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="E73" s="11" t="n">
-        <v>0.04</v>
+        <v>2.3</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>-0.0496</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>2700000</v>
+        <v>3059700</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.47</v>
+        <v>0.87</v>
       </c>
       <c r="H73" t="n">
-        <v>62.82</v>
+        <v>51.83</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
@@ -3811,10 +3804,10 @@
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>6.417</v>
+        <v>2.297</v>
       </c>
       <c r="K73" s="10" t="n">
-        <v>6.05</v>
+        <v>2.22</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="15" t="inlineStr"/>
@@ -3836,21 +3829,21 @@
         </is>
       </c>
       <c r="D74" s="10" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>0.0417</v>
+        <v>0.0333</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>2639000</v>
+        <v>3024400</v>
       </c>
       <c r="G74" s="13" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H74" t="n">
-        <v>44.98</v>
-      </c>
-      <c r="I74" s="18" t="inlineStr">
+        <v>43.88</v>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3872,39 +3865,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E75" s="11" t="n">
-        <v>0.0091</v>
+        <v>1.15</v>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>2629700</v>
+        <v>2979700</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>1.22</v>
+        <v>0.31</v>
       </c>
       <c r="H75" t="n">
-        <v>46.19</v>
-      </c>
-      <c r="I75" s="18" t="inlineStr">
+        <v>33.75</v>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.194</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.278</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3917,28 +3910,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>2575600</v>
+        <v>2858200</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="H76" t="n">
-        <v>38.94</v>
+        <v>62.57</v>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
@@ -3946,10 +3939,10 @@
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>0.312</v>
+        <v>6.415</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>0.355</v>
+        <v>6.049</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3962,33 +3955,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E77" s="11" t="n">
-        <v>0.0352</v>
+        <v>0.835</v>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>2574900</v>
+        <v>2713100</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I77" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
+        <v>0.55</v>
+      </c>
+      <c r="H77" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="I77" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="K77" s="10" t="n">
+        <v>0.782</v>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
     </row>
@@ -4000,39 +4000,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>-0.0063</v>
+        <v>3.45</v>
+      </c>
+      <c r="E78" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2517000</v>
+        <v>2711100</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.11</v>
+        <v>0.84</v>
       </c>
       <c r="H78" t="n">
-        <v>47.73</v>
-      </c>
-      <c r="I78" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>89.59</v>
+      </c>
+      <c r="I78" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>4.73</v>
+        <v>3.119</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>4.8</v>
+        <v>2.641</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4045,28 +4045,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.91</v>
+        <v>0.49</v>
       </c>
       <c r="E79" s="11" t="n">
-        <v>0.0168</v>
+        <v>0.0208</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>2375100</v>
+        <v>2710400</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="H79" t="n">
-        <v>49.94</v>
+        <v>47.32</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.898</v>
+        <v>0.492</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>0.954</v>
+        <v>0.512</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4090,39 +4090,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>-0.004699999999999999</v>
+        <v>0.78</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>2356900</v>
+        <v>2666200</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="H80" t="n">
-        <v>51.01</v>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.44</v>
+      </c>
+      <c r="I80" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>2.107</v>
+        <v>0.769</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>2.114</v>
+        <v>0.771</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4135,28 +4135,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E81" s="16" t="n">
-        <v>0</v>
+        <v>2.21</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>0.0327</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>2335600</v>
+        <v>2633400</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>1.57</v>
+        <v>1.07</v>
       </c>
       <c r="H81" t="n">
-        <v>42.99</v>
+        <v>62.12</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>0.229</v>
+        <v>2.128</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>0.237</v>
+        <v>2.084</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4180,39 +4180,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>2319700</v>
+        <v>2629700</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>0.31</v>
+        <v>1.22</v>
       </c>
       <c r="H82" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="I82" s="18" t="inlineStr">
+        <v>46.19</v>
+      </c>
+      <c r="I82" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>0.769</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0.771</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4225,28 +4225,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E83" s="11" t="n">
-        <v>0.0327</v>
+        <v>0.3</v>
+      </c>
+      <c r="E83" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>2271300</v>
+        <v>2616900</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.92</v>
+        <v>0.39</v>
       </c>
       <c r="H83" t="n">
-        <v>62.12</v>
+        <v>38.94</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>2.128</v>
+        <v>0.312</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>2.084</v>
+        <v>0.355</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4270,28 +4270,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D84" s="10" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.91</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>0.0168</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>2227300</v>
+        <v>2547900</v>
       </c>
       <c r="G84" s="13" t="n">
-        <v>1.16</v>
+        <v>0.61</v>
       </c>
       <c r="H84" t="n">
-        <v>54.69</v>
+        <v>49.94</v>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="J84" s="10" t="n">
-        <v>8.154</v>
+        <v>0.898</v>
       </c>
       <c r="K84" s="10" t="n">
-        <v>7.972</v>
+        <v>0.954</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="15" t="inlineStr"/>
@@ -4315,28 +4315,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D85" s="10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E85" s="11" t="n">
-        <v>0.0233</v>
+        <v>0.63</v>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>2203500</v>
+        <v>2520600</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>0.31</v>
+        <v>0.7</v>
       </c>
       <c r="H85" t="n">
-        <v>53.61</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.43</v>
+        <v>0.622</v>
       </c>
       <c r="K85" s="10" t="n">
-        <v>0.417</v>
+        <v>0.612</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="15" t="inlineStr"/>
@@ -4360,39 +4360,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E86" s="11" t="n">
-        <v>0.0215</v>
+        <v>2.11</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>2104500</v>
+        <v>2472800</v>
       </c>
       <c r="G86" s="13" t="n">
         <v>0.24</v>
       </c>
       <c r="H86" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I86" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.01</v>
+      </c>
+      <c r="I86" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.489</v>
+        <v>2.107</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>0.472</v>
+        <v>2.114</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4405,39 +4405,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v>0.0208</v>
+        <v>0.225</v>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>2102900</v>
+        <v>2350800</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>0.29</v>
+        <v>1.58</v>
       </c>
       <c r="H87" t="n">
-        <v>47.32</v>
-      </c>
-      <c r="I87" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.99</v>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.492</v>
+        <v>0.229</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>0.512</v>
+        <v>0.237</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4450,39 +4450,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D88" s="10" t="n">
-        <v>0.265</v>
+        <v>0.44</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>0.0192</v>
+        <v>0.0233</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>1975200</v>
+        <v>2322700</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="H88" t="n">
-        <v>42.34</v>
-      </c>
-      <c r="I88" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.61</v>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="10" t="n">
-        <v>0.278</v>
+        <v>0.43</v>
       </c>
       <c r="K88" s="10" t="n">
-        <v>0.282</v>
+        <v>0.417</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="15" t="inlineStr"/>
@@ -4495,28 +4495,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>2.4</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>1939900</v>
+        <v>2303200</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.29</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>60.28</v>
+        <v>37.29</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>1.192</v>
+        <v>2.467</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>1.156</v>
+        <v>2.62</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4540,39 +4540,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>1.17</v>
+        <v>0.37</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>0.0174</v>
+        <v>0.0882</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>1929500</v>
+        <v>2267400</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>0.2</v>
+        <v>2.24</v>
       </c>
       <c r="H90" t="n">
-        <v>39.48</v>
-      </c>
-      <c r="I90" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.14</v>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>1.196</v>
+        <v>0.342</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>1.278</v>
+        <v>0.356</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4585,39 +4585,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>1922600</v>
+        <v>2260100</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H91" t="n">
-        <v>32.23</v>
-      </c>
-      <c r="I91" s="18" t="inlineStr">
+        <v>46.41</v>
+      </c>
+      <c r="I91" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>7.314</v>
+        <v>0.488</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>7.599</v>
+        <v>0.472</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4630,39 +4630,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E92" s="11" t="n">
-        <v>0.06309999999999999</v>
+        <v>7.1</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>1819000</v>
+        <v>2230000</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.54</v>
+        <v>0.13</v>
       </c>
       <c r="H92" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="I92" s="18" t="inlineStr">
+        <v>31.84</v>
+      </c>
+      <c r="I92" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>1.107</v>
+        <v>7.313</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>0.945</v>
+        <v>7.599</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4675,39 +4675,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v>0.0313</v>
+        <v>0.75</v>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>1807900</v>
+        <v>2219800</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I93" s="18" t="inlineStr">
+        <v>52.84</v>
+      </c>
+      <c r="I93" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>0.336</v>
+        <v>0.744</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0.338</v>
+        <v>0.709</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4720,39 +4720,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D94" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.265</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>1783900</v>
+        <v>2218200</v>
       </c>
       <c r="G94" s="13" t="n">
-        <v>0.61</v>
+        <v>0.34</v>
       </c>
       <c r="H94" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="I94" s="18" t="inlineStr">
+        <v>42.34</v>
+      </c>
+      <c r="I94" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J94" s="10" t="n">
-        <v>0.866</v>
+        <v>0.278</v>
       </c>
       <c r="K94" s="10" t="n">
-        <v>0.861</v>
+        <v>0.282</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="15" t="inlineStr"/>
@@ -4765,28 +4765,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E95" s="11" t="n">
-        <v>0.0882</v>
+        <v>1.26</v>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>1766200</v>
+        <v>2071000</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>1.75</v>
+        <v>0.31</v>
       </c>
       <c r="H95" t="n">
-        <v>65.14</v>
+        <v>62.05</v>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>0.342</v>
+        <v>1.193</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>0.356</v>
+        <v>1.156</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4810,28 +4810,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0158</v>
+        <v>5.76</v>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1755600</v>
+        <v>1951600</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.41</v>
+        <v>0.24</v>
       </c>
       <c r="H96" t="n">
-        <v>50.31</v>
+        <v>42.51</v>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>0.9429999999999999</v>
+        <v>5.812</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>0.897</v>
+        <v>6.057</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4855,39 +4855,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>0.43</v>
+        <v>1.43</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>0.0361</v>
+        <v>0.0593</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1696000</v>
+        <v>1934800</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.26</v>
+        <v>0.64</v>
       </c>
       <c r="H97" t="n">
-        <v>57.91</v>
-      </c>
-      <c r="I97" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.77</v>
+      </c>
+      <c r="I97" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="10" t="n">
-        <v>0.403</v>
+        <v>1.309</v>
       </c>
       <c r="K97" s="10" t="n">
-        <v>0.368</v>
+        <v>1.253</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
@@ -4900,39 +4900,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AEON</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.33</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1688800</v>
+        <v>1921900</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>2.13</v>
+        <v>0.19</v>
       </c>
       <c r="H98" t="n">
-        <v>33.91</v>
-      </c>
-      <c r="I98" s="18" t="inlineStr">
+        <v>48.02</v>
+      </c>
+      <c r="I98" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.336</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>0.968</v>
+        <v>0.338</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4945,39 +4945,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>0.25</v>
+        <v>1.18</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>0.0638</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1665200</v>
+        <v>1903400</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>1.52</v>
+        <v>0.57</v>
       </c>
       <c r="H99" t="n">
-        <v>51.83</v>
-      </c>
-      <c r="I99" s="18" t="inlineStr">
+        <v>60.43</v>
+      </c>
+      <c r="I99" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.247</v>
+        <v>1.107</v>
       </c>
       <c r="K99" s="10" t="n">
-        <v>0.25</v>
+        <v>0.945</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -4990,28 +4990,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E100" s="11" t="n">
-        <v>0.0593</v>
+        <v>0.635</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>-0.0231</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1654900</v>
+        <v>1872500</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="H100" t="n">
-        <v>60.77</v>
+        <v>40.2</v>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="J100" s="10" t="n">
-        <v>1.309</v>
+        <v>0.675</v>
       </c>
       <c r="K100" s="10" t="n">
-        <v>1.253</v>
+        <v>0.73</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
@@ -5035,28 +5035,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>2.11</v>
+        <v>0.89</v>
       </c>
       <c r="E101" s="16" t="n">
-        <v>0</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1625700</v>
+        <v>1839100</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.25</v>
+        <v>0.96</v>
       </c>
       <c r="H101" t="n">
-        <v>68</v>
+        <v>47.67</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>1.994</v>
+        <v>0.903</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>1.968</v>
+        <v>0.897</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="15" t="inlineStr"/>
@@ -5080,28 +5080,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>-0.0154</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>-0.0158</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1592500</v>
+        <v>1838600</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="H102" t="n">
-        <v>40.9</v>
+        <v>50.31</v>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.676</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>0.731</v>
+        <v>0.897</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5125,28 +5125,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>-0.005600000000000001</v>
+        <v>2.11</v>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1586800</v>
+        <v>1820200</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>0.83</v>
+        <v>0.28</v>
       </c>
       <c r="H103" t="n">
-        <v>47.67</v>
+        <v>68</v>
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="J103" s="10" t="n">
-        <v>0.903</v>
+        <v>1.994</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>0.897</v>
+        <v>1.968</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="15" t="inlineStr"/>
@@ -5170,39 +5170,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E104" s="11" t="n">
-        <v>0.06</v>
+        <v>0.865</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1461400</v>
+        <v>1783900</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="H104" t="n">
-        <v>49.13</v>
-      </c>
-      <c r="I104" s="18" t="inlineStr">
+        <v>49.98</v>
+      </c>
+      <c r="I104" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>0.263</v>
+        <v>0.866</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>0.28</v>
+        <v>0.861</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5215,39 +5215,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D105" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>-0.0234</v>
+        <v>0.43</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>0.0361</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1423200</v>
+        <v>1774900</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H105" t="n">
-        <v>45.19</v>
-      </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.91</v>
+      </c>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="10" t="n">
-        <v>1.273</v>
+        <v>0.403</v>
       </c>
       <c r="K105" s="10" t="n">
-        <v>1.319</v>
+        <v>0.368</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="15" t="inlineStr"/>
@@ -5260,39 +5260,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>2.77</v>
+        <v>0.265</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>0.0375</v>
+        <v>0.06</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1363200</v>
+        <v>1725300</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H106" t="n">
-        <v>44.51</v>
-      </c>
-      <c r="I106" s="18" t="inlineStr">
+        <v>49.13</v>
+      </c>
+      <c r="I106" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J106" s="10" t="n">
-        <v>2.813</v>
+        <v>0.263</v>
       </c>
       <c r="K106" s="10" t="n">
-        <v>2.95</v>
+        <v>0.28</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="15" t="inlineStr"/>
@@ -5305,28 +5305,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E107" s="11" t="n">
-        <v>0.0103</v>
+        <v>6.89</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>-0.0268</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>1325900</v>
+        <v>1718100</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H107" t="n">
-        <v>58.57</v>
+        <v>53.39</v>
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
@@ -5334,10 +5334,10 @@
         </is>
       </c>
       <c r="J107" s="10" t="n">
-        <v>2.819</v>
+        <v>6.838</v>
       </c>
       <c r="K107" s="10" t="n">
-        <v>2.706</v>
+        <v>6.828</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="15" t="inlineStr"/>
@@ -5350,39 +5350,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>0.0638</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1322300</v>
+        <v>1712200</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>0.64</v>
+        <v>1.57</v>
       </c>
       <c r="H108" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="I108" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.83</v>
+      </c>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.64</v>
+        <v>0.247</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="15" t="inlineStr"/>
@@ -5395,39 +5395,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>AEON</t>
         </is>
       </c>
       <c r="D109" s="10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E109" s="11" t="n">
-        <v>0.0148</v>
+        <v>0.905</v>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1321700</v>
+        <v>1702100</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>0.48</v>
+        <v>2.15</v>
       </c>
       <c r="H109" t="n">
-        <v>60.04</v>
-      </c>
-      <c r="I109" s="18" t="inlineStr">
+        <v>34.99</v>
+      </c>
+      <c r="I109" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J109" s="10" t="n">
-        <v>1.285</v>
+        <v>0.944</v>
       </c>
       <c r="K109" s="10" t="n">
-        <v>1.194</v>
+        <v>0.968</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="15" t="inlineStr"/>
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>2.66</v>
+        <v>0.615</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1303700</v>
+        <v>1631500</v>
       </c>
       <c r="G110" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="H110" t="n">
-        <v>55.55</v>
-      </c>
-      <c r="I110" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.89</v>
+      </c>
+      <c r="I110" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="10" t="n">
-        <v>2.603</v>
+        <v>0.582</v>
       </c>
       <c r="K110" s="10" t="n">
-        <v>2.601</v>
+        <v>0.493</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
@@ -5485,39 +5485,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>-0.0254</v>
+        <v>2.77</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>0.0375</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1296800</v>
+        <v>1588300</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0.23</v>
+        <v>0.44</v>
       </c>
       <c r="H111" t="n">
-        <v>53.89</v>
-      </c>
-      <c r="I111" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.51</v>
+      </c>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>6.839</v>
+        <v>2.813</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>6.828</v>
+        <v>2.95</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5530,39 +5530,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E112" s="11" t="n">
-        <v>0.0179</v>
+        <v>1.25</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1293000</v>
+        <v>1532700</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H112" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="I112" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.19</v>
+      </c>
+      <c r="I112" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>0.294</v>
+        <v>1.273</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>0.318</v>
+        <v>1.319</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5575,39 +5575,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E113" s="16" t="n">
-        <v>0</v>
+        <v>4.22</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>0.012</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1292600</v>
+        <v>1475900</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
       <c r="H113" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I113" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.06</v>
+      </c>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>0.634</v>
+        <v>4.024</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>0.624</v>
+        <v>3.685</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5620,39 +5620,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>0.615</v>
+        <v>7.63</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>0.025</v>
+        <v>0.0242</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>1281400</v>
+        <v>1472000</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="H114" t="n">
-        <v>57.89</v>
-      </c>
-      <c r="I114" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.56</v>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="10" t="n">
-        <v>0.582</v>
+        <v>7.335</v>
       </c>
       <c r="K114" s="10" t="n">
-        <v>0.493</v>
+        <v>6.985</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
@@ -5665,39 +5665,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E115" s="16" t="n">
-        <v>0</v>
+        <v>0.835</v>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>0.0121</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>1264500</v>
+        <v>1443200</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>1.45</v>
+        <v>0.54</v>
       </c>
       <c r="H115" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I115" s="18" t="inlineStr">
+        <v>36.7</v>
+      </c>
+      <c r="I115" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>0.271</v>
+        <v>0.861</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>0.268</v>
+        <v>0.923</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5710,39 +5710,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>0.835</v>
+        <v>1.37</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>0.0121</v>
+        <v>0.0148</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1257500</v>
+        <v>1436400</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="H116" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="I116" s="18" t="inlineStr">
+        <v>60.04</v>
+      </c>
+      <c r="I116" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>0.861</v>
+        <v>1.285</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>0.923</v>
+        <v>1.194</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5755,28 +5755,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>4.22</v>
+        <v>0.885</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>0.012</v>
+        <v>0.0351</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>1255000</v>
+        <v>1428400</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H117" t="n">
-        <v>60.06</v>
+        <v>49.95</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="J117" s="10" t="n">
-        <v>4.024</v>
+        <v>0.884</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>3.685</v>
+        <v>0.865</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="15" t="inlineStr"/>
@@ -5800,28 +5800,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>0.88</v>
+        <v>1.35</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>0.0292</v>
+        <v>0.015</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>1231200</v>
+        <v>1395000</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.2</v>
+        <v>0.55</v>
       </c>
       <c r="H118" t="n">
-        <v>49.3</v>
+        <v>45.72</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="J118" s="10" t="n">
-        <v>0.884</v>
+        <v>1.361</v>
       </c>
       <c r="K118" s="10" t="n">
-        <v>0.865</v>
+        <v>1.431</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -5845,28 +5845,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D119" s="10" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E119" s="16" t="n">
-        <v>0</v>
+        <v>2.94</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>0.0138</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>1225600</v>
+        <v>1367400</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="H119" t="n">
-        <v>69.51000000000001</v>
+        <v>59.05</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="J119" s="10" t="n">
-        <v>0.622</v>
+        <v>2.82</v>
       </c>
       <c r="K119" s="10" t="n">
-        <v>0.612</v>
+        <v>2.706</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="15" t="inlineStr"/>
@@ -5890,28 +5890,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D120" s="10" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="E120" s="11" t="n">
-        <v>0.0255</v>
+        <v>7.35</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>1224600</v>
+        <v>1365800</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="H120" t="n">
-        <v>58.74</v>
+        <v>42.2</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
@@ -5919,10 +5919,10 @@
         </is>
       </c>
       <c r="J120" s="10" t="n">
-        <v>7.336</v>
+        <v>7.401</v>
       </c>
       <c r="K120" s="10" t="n">
-        <v>6.986</v>
+        <v>7.773</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="15" t="inlineStr"/>
@@ -5935,39 +5935,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>-0.004099999999999999</v>
+        <v>3.12</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>0.023</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>1205200</v>
+        <v>1364600</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="H121" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="I121" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.20999999999999</v>
+      </c>
+      <c r="I121" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>2.467</v>
+        <v>2.872</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>2.62</v>
+        <v>2.407</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="15" t="inlineStr"/>
@@ -5980,39 +5980,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>1.36</v>
+        <v>0.8</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>0.0226</v>
+        <v>0.0667</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>1200000</v>
+        <v>1352100</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.47</v>
+        <v>0.65</v>
       </c>
       <c r="H122" t="n">
-        <v>47.17</v>
-      </c>
-      <c r="I122" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.89</v>
+      </c>
+      <c r="I122" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="10" t="n">
-        <v>1.362</v>
+        <v>0.745</v>
       </c>
       <c r="K122" s="10" t="n">
-        <v>1.431</v>
+        <v>0.675</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -6025,39 +6025,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>0.775</v>
+        <v>2.67</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.0309</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>1199900</v>
+        <v>1342200</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H123" t="n">
-        <v>57.03</v>
-      </c>
-      <c r="I123" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.31</v>
+      </c>
+      <c r="I123" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>0.747</v>
+        <v>2.604</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>0.709</v>
+        <v>2.601</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="15" t="inlineStr"/>
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E124" s="11" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.635</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1192900</v>
+        <v>1332300</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="H124" t="n">
-        <v>51.74</v>
-      </c>
-      <c r="I124" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.28</v>
+      </c>
+      <c r="I124" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="10" t="n">
-        <v>0.347</v>
+        <v>0.64</v>
       </c>
       <c r="K124" s="10" t="n">
-        <v>0.331</v>
+        <v>0.63</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -6115,39 +6115,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SUPERLN</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>0.955</v>
+        <v>0.285</v>
       </c>
       <c r="E125" s="11" t="n">
-        <v>0.0269</v>
+        <v>0.0179</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>1192600</v>
+        <v>1332100</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
       </c>
       <c r="H125" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="I125" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.56</v>
+      </c>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="10" t="n">
-        <v>0.897</v>
+        <v>0.294</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>0.86</v>
+        <v>0.318</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="15" t="inlineStr"/>
@@ -6160,39 +6160,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>1186600</v>
+        <v>1319000</v>
       </c>
       <c r="G126" s="13" t="n">
-        <v>0.54</v>
+        <v>0.2</v>
       </c>
       <c r="H126" t="n">
-        <v>54.59</v>
-      </c>
-      <c r="I126" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.39</v>
+      </c>
+      <c r="I126" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="10" t="n">
-        <v>0.462</v>
+        <v>1.241</v>
       </c>
       <c r="K126" s="10" t="n">
-        <v>0.462</v>
+        <v>1.212</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -6205,39 +6205,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E127" s="16" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E127" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>1167000</v>
+        <v>1293600</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H127" t="n">
-        <v>60.23</v>
-      </c>
-      <c r="I127" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.46</v>
+      </c>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="10" t="n">
-        <v>1.24</v>
+        <v>0.634</v>
       </c>
       <c r="K127" s="10" t="n">
-        <v>1.212</v>
+        <v>0.624</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="15" t="inlineStr"/>
@@ -6250,39 +6250,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>-0.0629</v>
+        <v>0.35</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>0.04480000000000001</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>1140000</v>
+        <v>1282000</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>2.05</v>
+        <v>0.16</v>
       </c>
       <c r="H128" t="n">
-        <v>55.96</v>
-      </c>
-      <c r="I128" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.74</v>
+      </c>
+      <c r="I128" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="10" t="n">
-        <v>0.653</v>
+        <v>0.347</v>
       </c>
       <c r="K128" s="10" t="n">
-        <v>0.618</v>
+        <v>0.331</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -6295,39 +6295,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="E129" s="17" t="n">
-        <v>-0.0035</v>
+        <v>0.26</v>
+      </c>
+      <c r="E129" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>1104300</v>
+        <v>1264500</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>0.14</v>
+        <v>1.45</v>
       </c>
       <c r="H129" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I129" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.3</v>
+      </c>
+      <c r="I129" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>5.811</v>
+        <v>0.271</v>
       </c>
       <c r="K129" s="10" t="n">
-        <v>6.057</v>
+        <v>0.268</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="15" t="inlineStr"/>
@@ -6340,39 +6340,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>3.11</v>
+        <v>11.08</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>0.0197</v>
+        <v>0.024</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>1099700</v>
+        <v>1249000</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="H130" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="I130" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.81</v>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="10" t="n">
-        <v>2.871</v>
+        <v>10.56</v>
       </c>
       <c r="K130" s="10" t="n">
-        <v>2.407</v>
+        <v>9.938000000000001</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -6385,39 +6385,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>-0.0014</v>
+        <v>0.465</v>
+      </c>
+      <c r="E131" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>1098500</v>
+        <v>1243700</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>0.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="I131" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.59</v>
+      </c>
+      <c r="I131" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>7.401</v>
+        <v>0.462</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>7.773</v>
+        <v>0.462</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="15" t="inlineStr"/>
@@ -6430,28 +6430,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SUPERLN</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>11.08</v>
+        <v>0.955</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>0.024</v>
+        <v>0.0269</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>1091600</v>
+        <v>1213600</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>0.29</v>
+        <v>2.65</v>
       </c>
       <c r="H132" t="n">
-        <v>62.81</v>
+        <v>64.31</v>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="J132" s="10" t="n">
-        <v>10.56</v>
+        <v>0.897</v>
       </c>
       <c r="K132" s="10" t="n">
-        <v>9.938000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -6475,28 +6475,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E133" s="11" t="n">
-        <v>0.0169</v>
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E133" s="16" t="n">
+        <v>-0.042</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>1085800</v>
+        <v>1192800</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>0.21</v>
+        <v>2.15</v>
       </c>
       <c r="H133" t="n">
-        <v>60.09</v>
+        <v>59.93</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.654</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>0.531</v>
+        <v>0.618</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="15" t="inlineStr"/>
@@ -6535,15 +6535,15 @@
         <v>0.035</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>1081000</v>
+        <v>1186800</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="H134" t="n">
         <v>46.87</v>
       </c>
-      <c r="I134" s="18" t="inlineStr">
+      <c r="I134" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -6565,39 +6565,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>BJCORP</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>-0.0238</v>
+        <v>0.25</v>
+      </c>
+      <c r="E135" s="11" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>1076600</v>
+        <v>1139200</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H135" t="n">
-        <v>67.92</v>
-      </c>
-      <c r="I135" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.77</v>
+      </c>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.179</v>
+        <v>0.248</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>0.165</v>
+        <v>0.249</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="15" t="inlineStr"/>
@@ -6610,39 +6610,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0169</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1076500</v>
+        <v>1126000</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>2.62</v>
+        <v>0.22</v>
       </c>
       <c r="H136" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="I136" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.09</v>
+      </c>
+      <c r="I136" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="10" t="n">
-        <v>0.63</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K136" s="10" t="n">
-        <v>0.652</v>
+        <v>0.531</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -6655,39 +6655,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BJCORP</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E137" s="11" t="n">
-        <v>0.0204</v>
+        <v>1.01</v>
+      </c>
+      <c r="E137" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>1059200</v>
+        <v>1122600</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="H137" t="n">
-        <v>56.77</v>
-      </c>
-      <c r="I137" s="18" t="inlineStr">
+        <v>49.04</v>
+      </c>
+      <c r="I137" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.248</v>
+        <v>1.023</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>0.249</v>
+        <v>0.985</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="15" t="inlineStr"/>
@@ -6700,28 +6700,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="E138" s="11" t="n">
-        <v>0.0022</v>
+        <v>0.365</v>
+      </c>
+      <c r="E138" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>1043400</v>
+        <v>1118000</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H138" t="n">
-        <v>58.11</v>
+        <v>59.41</v>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
@@ -6729,11 +6729,9 @@
         </is>
       </c>
       <c r="J138" s="10" t="n">
-        <v>4.462</v>
-      </c>
-      <c r="K138" s="10" t="n">
-        <v>4.446</v>
-      </c>
+        <v>0.342</v>
+      </c>
+      <c r="K138" s="10" t="n"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
     </row>
@@ -6745,38 +6743,40 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E139" s="16" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E139" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>1022300</v>
+        <v>1109700</v>
       </c>
       <c r="G139" s="13" t="n">
-        <v>0.17</v>
+        <v>0.7</v>
       </c>
       <c r="H139" t="n">
-        <v>59.41</v>
-      </c>
-      <c r="I139" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.36</v>
+      </c>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="10" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="K139" s="10" t="n"/>
+        <v>0.748</v>
+      </c>
+      <c r="K139" s="10" t="n">
+        <v>0.725</v>
+      </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="15" t="inlineStr"/>
     </row>
@@ -6788,39 +6788,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E140" s="11" t="n">
-        <v>0.0135</v>
+        <v>0.615</v>
+      </c>
+      <c r="E140" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>1016900</v>
+        <v>1106200</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>0.41</v>
+        <v>2.69</v>
       </c>
       <c r="H140" t="n">
-        <v>45.96</v>
-      </c>
-      <c r="I140" s="18" t="inlineStr">
+        <v>26.8</v>
+      </c>
+      <c r="I140" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J140" s="10" t="n">
-        <v>0.381</v>
+        <v>0.63</v>
       </c>
       <c r="K140" s="10" t="n">
-        <v>0.386</v>
+        <v>0.652</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -6833,28 +6833,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>1.44</v>
+        <v>4.65</v>
       </c>
       <c r="E141" s="11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>997500</v>
+        <v>1099700</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>0.47</v>
+        <v>0.21</v>
       </c>
       <c r="H141" t="n">
-        <v>70.33</v>
+        <v>58.44</v>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="J141" s="10" t="n">
-        <v>1.379</v>
+        <v>4.463</v>
       </c>
       <c r="K141" s="10" t="n">
-        <v>1.351</v>
+        <v>4.446</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="15" t="inlineStr"/>
@@ -6878,39 +6878,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>2.41</v>
+        <v>3.98</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>0.0042</v>
+        <v>0.0025</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>937300</v>
+        <v>1091000</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="H142" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="I142" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.44</v>
+      </c>
+      <c r="I142" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="10" t="n">
-        <v>2.428</v>
+        <v>3.843</v>
       </c>
       <c r="K142" s="10" t="n">
-        <v>2.423</v>
+        <v>3.768</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -6923,39 +6923,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>0.61</v>
+        <v>6.31</v>
       </c>
       <c r="E143" s="11" t="n">
-        <v>0.0083</v>
+        <v>0.0016</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>915800</v>
+        <v>1089400</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="H143" t="n">
-        <v>65.55</v>
-      </c>
-      <c r="I143" s="18" t="inlineStr">
+        <v>45.25</v>
+      </c>
+      <c r="I143" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J143" s="10" t="n">
-        <v>0.554</v>
+        <v>6.336</v>
       </c>
       <c r="K143" s="10" t="n">
-        <v>0.492</v>
+        <v>6.605</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="15" t="inlineStr"/>
@@ -6968,28 +6968,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E144" s="11" t="n">
-        <v>0.0198</v>
+        <v>0.205</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>913300</v>
+        <v>1081100</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="H144" t="n">
-        <v>59.65</v>
+        <v>67.92</v>
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
@@ -6997,10 +6997,10 @@
         </is>
       </c>
       <c r="J144" s="10" t="n">
-        <v>0.493</v>
+        <v>0.179</v>
       </c>
       <c r="K144" s="10" t="n">
-        <v>0.485</v>
+        <v>0.165</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -7013,39 +7013,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>6.81</v>
+        <v>1.44</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>0.0134</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>907600</v>
+        <v>1071700</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="H145" t="n">
-        <v>39.19</v>
-      </c>
-      <c r="I145" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.33</v>
+      </c>
+      <c r="I145" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="10" t="n">
-        <v>6.998</v>
+        <v>1.379</v>
       </c>
       <c r="K145" s="10" t="n">
-        <v>7.452</v>
+        <v>1.351</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="15" t="inlineStr"/>
@@ -7058,39 +7058,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>-0.0319</v>
+        <v>5.9</v>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>0.0279</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>895700</v>
+        <v>1066400</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H146" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="I146" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.68</v>
+      </c>
+      <c r="I146" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="10" t="n">
-        <v>1.812</v>
+        <v>5.557</v>
       </c>
       <c r="K146" s="10" t="n">
-        <v>1.909</v>
+        <v>5.395</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -7103,39 +7103,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D147" s="10" t="n">
-        <v>5.89</v>
+        <v>2.26</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>0.0261</v>
+        <v>0.0463</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>875600</v>
+        <v>1057100</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>0.2</v>
+        <v>0.79</v>
       </c>
       <c r="H147" t="n">
-        <v>60.47</v>
-      </c>
-      <c r="I147" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.91</v>
+      </c>
+      <c r="I147" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J147" s="10" t="n">
-        <v>5.556</v>
+        <v>2.136</v>
       </c>
       <c r="K147" s="10" t="n">
-        <v>5.394</v>
+        <v>2.222</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="15" t="inlineStr"/>
@@ -7148,39 +7148,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E148" s="16" t="n">
-        <v>0</v>
+        <v>5.19</v>
+      </c>
+      <c r="E148" s="11" t="n">
+        <v>0.0257</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>867500</v>
+        <v>1055400</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H148" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="I148" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.42</v>
+      </c>
+      <c r="I148" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J148" s="10" t="n">
-        <v>6.335</v>
+        <v>5.072</v>
       </c>
       <c r="K148" s="10" t="n">
-        <v>6.605</v>
+        <v>5.034</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -7193,39 +7193,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D149" s="10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E149" s="16" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>866100</v>
+        <v>1030500</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>0.26</v>
+        <v>0.12</v>
       </c>
       <c r="H149" t="n">
-        <v>49.04</v>
-      </c>
-      <c r="I149" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.29</v>
+      </c>
+      <c r="I149" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="10" t="n">
-        <v>1.023</v>
+        <v>0.268</v>
       </c>
       <c r="K149" s="10" t="n">
-        <v>0.985</v>
+        <v>0.29</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="15" t="inlineStr"/>
@@ -7238,39 +7238,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>3.98</v>
+        <v>0.375</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>0.0025</v>
+        <v>0.0135</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>860300</v>
+        <v>1021900</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H150" t="n">
-        <v>57.44</v>
-      </c>
-      <c r="I150" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.96</v>
+      </c>
+      <c r="I150" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="10" t="n">
-        <v>3.843</v>
+        <v>0.381</v>
       </c>
       <c r="K150" s="10" t="n">
-        <v>3.768</v>
+        <v>0.386</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -7283,39 +7283,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D151" s="10" t="n">
-        <v>1.1</v>
+        <v>2.41</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>0.028</v>
+        <v>0.0042</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>857800</v>
+        <v>1011100</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="H151" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="I151" s="18" t="inlineStr">
+        <v>47.3</v>
+      </c>
+      <c r="I151" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J151" s="10" t="n">
-        <v>1.118</v>
+        <v>2.428</v>
       </c>
       <c r="K151" s="10" t="n">
-        <v>1.116</v>
+        <v>2.423</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="15" t="inlineStr"/>
@@ -7328,39 +7328,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D152" s="10" t="n">
-        <v>2.24</v>
+        <v>6.78</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0089</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>851400</v>
+        <v>960500</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.63</v>
+        <v>0.09</v>
       </c>
       <c r="H152" t="n">
-        <v>57.61</v>
-      </c>
-      <c r="I152" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.87</v>
+      </c>
+      <c r="I152" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="10" t="n">
-        <v>2.134</v>
+        <v>6.995</v>
       </c>
       <c r="K152" s="10" t="n">
-        <v>2.222</v>
+        <v>7.451</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -7373,39 +7373,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>2.98</v>
+        <v>0.615</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>0.0347</v>
+        <v>0.0165</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>819000</v>
+        <v>949600</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H153" t="n">
-        <v>64.56999999999999</v>
-      </c>
-      <c r="I153" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.22</v>
+      </c>
+      <c r="I153" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="10" t="n">
-        <v>2.764</v>
+        <v>0.555</v>
       </c>
       <c r="K153" s="10" t="n">
-        <v>2.406</v>
+        <v>0.492</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="15" t="inlineStr"/>
@@ -7418,28 +7418,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E154" s="11" t="n">
-        <v>0.0156</v>
+        <v>1.82</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>749200</v>
+        <v>925100</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="H154" t="n">
-        <v>56.21</v>
+        <v>48.63</v>
       </c>
       <c r="I154" s="14" t="inlineStr">
         <is>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="J154" s="10" t="n">
-        <v>1.257</v>
+        <v>1.812</v>
       </c>
       <c r="K154" s="10" t="n">
-        <v>1.13</v>
+        <v>1.909</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -7463,28 +7463,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D155" s="10" t="n">
-        <v>0.55</v>
+        <v>0.515</v>
       </c>
       <c r="E155" s="11" t="n">
-        <v>0.0377</v>
+        <v>0.0198</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>746000</v>
+        <v>913300</v>
       </c>
       <c r="G155" s="13" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="H155" t="n">
-        <v>46.98</v>
+        <v>59.65</v>
       </c>
       <c r="I155" s="14" t="inlineStr">
         <is>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="J155" s="10" t="n">
-        <v>0.553</v>
+        <v>0.493</v>
       </c>
       <c r="K155" s="10" t="n">
-        <v>0.588</v>
+        <v>0.485</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="15" t="inlineStr"/>
@@ -7508,39 +7508,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D156" s="10" t="n">
-        <v>0.88</v>
+        <v>2.97</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>0.0115</v>
+        <v>0.0313</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>721100</v>
+        <v>906300</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="H156" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="I156" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.23</v>
+      </c>
+      <c r="I156" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="10" t="n">
-        <v>0.839</v>
+        <v>2.763</v>
       </c>
       <c r="K156" s="10" t="n">
-        <v>0.805</v>
+        <v>2.406</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -7553,39 +7553,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D157" s="10" t="n">
-        <v>5.19</v>
+        <v>1.1</v>
       </c>
       <c r="E157" s="11" t="n">
-        <v>0.0257</v>
+        <v>0.028</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>661300</v>
+        <v>899900</v>
       </c>
       <c r="G157" s="13" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="H157" t="n">
-        <v>56.42</v>
-      </c>
-      <c r="I157" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.27</v>
+      </c>
+      <c r="I157" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="10" t="n">
-        <v>5.072</v>
+        <v>1.118</v>
       </c>
       <c r="K157" s="10" t="n">
-        <v>5.034</v>
+        <v>1.116</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="15" t="inlineStr"/>
@@ -7598,28 +7598,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>KLK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="E158" s="17" t="n">
-        <v>-0.001</v>
+        <v>1.29</v>
+      </c>
+      <c r="E158" s="11" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>649300</v>
+        <v>873600</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.98</v>
+        <v>0.24</v>
       </c>
       <c r="H158" t="n">
-        <v>43.23</v>
+        <v>55.45</v>
       </c>
       <c r="I158" s="14" t="inlineStr">
         <is>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="J158" s="10" t="n">
-        <v>20.765</v>
+        <v>1.256</v>
       </c>
       <c r="K158" s="10" t="n">
-        <v>21.619</v>
+        <v>1.13</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -7643,39 +7643,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D159" s="10" t="n">
-        <v>1.35</v>
+        <v>0.68</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>0.0385</v>
+        <v>0.0303</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>645000</v>
+        <v>795800</v>
       </c>
       <c r="G159" s="13" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="H159" t="n">
-        <v>55.93</v>
-      </c>
-      <c r="I159" s="18" t="inlineStr">
+        <v>45.79</v>
+      </c>
+      <c r="I159" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J159" s="10" t="n">
-        <v>1.301</v>
+        <v>0.708</v>
       </c>
       <c r="K159" s="10" t="n">
-        <v>1.309</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="15" t="inlineStr"/>
@@ -7688,39 +7688,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>0.55</v>
+        <v>3.15</v>
       </c>
       <c r="E160" s="16" t="n">
-        <v>0</v>
+        <v>-0.0156</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>643700</v>
+        <v>793600</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.44</v>
+        <v>0.18</v>
       </c>
       <c r="H160" t="n">
-        <v>40.89</v>
-      </c>
-      <c r="I160" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.89</v>
+      </c>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J160" s="10" t="n">
-        <v>0.5570000000000001</v>
+        <v>3.287</v>
       </c>
       <c r="K160" s="10" t="n">
-        <v>0.574</v>
+        <v>3.519</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -7733,39 +7733,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D161" s="10" t="n">
-        <v>0.68</v>
+        <v>0.545</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>0.0303</v>
+        <v>0.0283</v>
       </c>
       <c r="F161" s="12" t="n">
-        <v>628200</v>
+        <v>786500</v>
       </c>
       <c r="G161" s="13" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H161" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="I161" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.68</v>
+      </c>
+      <c r="I161" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="10" t="n">
-        <v>0.708</v>
+        <v>0.552</v>
       </c>
       <c r="K161" s="10" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="15" t="inlineStr"/>
@@ -7778,28 +7778,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D162" s="10" t="n">
-        <v>1.12</v>
+        <v>4.38</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>0.0182</v>
+        <v>0.021</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>622600</v>
+        <v>772900</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>1.76</v>
+        <v>0.19</v>
       </c>
       <c r="H162" t="n">
-        <v>58.46</v>
+        <v>49.74</v>
       </c>
       <c r="I162" s="14" t="inlineStr">
         <is>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="J162" s="10" t="n">
-        <v>1.087</v>
+        <v>4.333</v>
       </c>
       <c r="K162" s="10" t="n">
-        <v>1.099</v>
+        <v>4.592</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -7823,39 +7823,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D163" s="10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E163" s="17" t="n">
-        <v>-0.0145</v>
+        <v>0.88</v>
+      </c>
+      <c r="E163" s="11" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F163" s="12" t="n">
-        <v>620400</v>
+        <v>735800</v>
       </c>
       <c r="G163" s="13" t="n">
-        <v>1.05</v>
+        <v>0.19</v>
       </c>
       <c r="H163" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I163" s="18" t="inlineStr">
+        <v>60.48</v>
+      </c>
+      <c r="I163" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J163" s="10" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.839</v>
       </c>
       <c r="K163" s="10" t="n">
-        <v>0.665</v>
+        <v>0.805</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="15" t="inlineStr"/>
@@ -7868,39 +7868,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D164" s="10" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="E164" s="17" t="n">
-        <v>-0.0125</v>
+        <v>5.1</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>614500</v>
+        <v>729000</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="H164" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="I164" s="18" t="inlineStr">
+        <v>30.49</v>
+      </c>
+      <c r="I164" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J164" s="10" t="n">
-        <v>3.288</v>
+        <v>5.331</v>
       </c>
       <c r="K164" s="10" t="n">
-        <v>3.519</v>
+        <v>5.666</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -7913,39 +7913,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D165" s="10" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="E165" s="17" t="n">
-        <v>-0.0174</v>
+        <v>1.13</v>
+      </c>
+      <c r="E165" s="11" t="n">
+        <v>0.0273</v>
       </c>
       <c r="F165" s="12" t="n">
-        <v>611200</v>
+        <v>688000</v>
       </c>
       <c r="G165" s="13" t="n">
-        <v>0.45</v>
+        <v>1.95</v>
       </c>
       <c r="H165" t="n">
-        <v>30.13</v>
-      </c>
-      <c r="I165" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.32</v>
+      </c>
+      <c r="I165" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="10" t="n">
-        <v>5.33</v>
+        <v>1.088</v>
       </c>
       <c r="K165" s="10" t="n">
-        <v>5.665</v>
+        <v>1.1</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="15" t="inlineStr"/>
@@ -7958,39 +7958,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>KLK</t>
         </is>
       </c>
       <c r="D166" s="10" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E166" s="16" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="E166" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>602000</v>
+        <v>687300</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>0.29</v>
+        <v>1.03</v>
       </c>
       <c r="H166" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="I166" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.48</v>
+      </c>
+      <c r="I166" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="10" t="n">
-        <v>0.8120000000000001</v>
+        <v>20.767</v>
       </c>
       <c r="K166" s="10" t="n">
-        <v>0.869</v>
+        <v>21.619</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -8003,39 +8003,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D167" s="10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="E167" s="11" t="n">
-        <v>0.04</v>
+        <v>0.79</v>
+      </c>
+      <c r="E167" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F167" s="12" t="n">
-        <v>569900</v>
+        <v>687100</v>
       </c>
       <c r="G167" s="13" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H167" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="I167" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.89</v>
+      </c>
+      <c r="I167" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="10" t="n">
-        <v>1.553</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K167" s="10" t="n">
-        <v>1.627</v>
+        <v>0.869</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="15" t="inlineStr"/>
@@ -8057,19 +8057,19 @@
         </is>
       </c>
       <c r="D168" s="10" t="n">
-        <v>0.885</v>
+        <v>0.88</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>0.0172</v>
+        <v>0.0115</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>561400</v>
+        <v>668000</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H168" t="n">
-        <v>47.48</v>
+        <v>45.68</v>
       </c>
       <c r="I168" s="14" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="J168" s="10" t="n">
-        <v>0.889</v>
+        <v>0.888</v>
       </c>
       <c r="K168" s="10" t="n">
         <v>0.901</v>
@@ -8093,39 +8093,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D169" s="10" t="n">
-        <v>0.755</v>
+        <v>1.34</v>
       </c>
       <c r="E169" s="11" t="n">
-        <v>0.0067</v>
+        <v>0.0308</v>
       </c>
       <c r="F169" s="12" t="n">
-        <v>558800</v>
+        <v>658900</v>
       </c>
       <c r="G169" s="13" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H169" t="n">
-        <v>59.12</v>
-      </c>
-      <c r="I169" s="18" t="inlineStr">
+        <v>54.94</v>
+      </c>
+      <c r="I169" s="17" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J169" s="10" t="n">
-        <v>0.741</v>
+        <v>1.3</v>
       </c>
       <c r="K169" s="10" t="n">
-        <v>0.674</v>
+        <v>1.309</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="15" t="inlineStr"/>
@@ -8138,39 +8138,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PESONA</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D170" s="10" t="n">
-        <v>0.52</v>
+        <v>0.655</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>0.0505</v>
+        <v>0.0077</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>541200</v>
+        <v>653200</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>2.02</v>
+        <v>0.49</v>
       </c>
       <c r="H170" t="n">
-        <v>74.34999999999999</v>
-      </c>
-      <c r="I170" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>69.68000000000001</v>
+      </c>
+      <c r="I170" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="10" t="n">
-        <v>0.475</v>
+        <v>0.615</v>
       </c>
       <c r="K170" s="10" t="n">
-        <v>0.474</v>
+        <v>0.549</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -8183,39 +8183,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D171" s="10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E171" s="16" t="n">
-        <v>0</v>
+        <v>1.57</v>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F171" s="12" t="n">
-        <v>531800</v>
+        <v>648500</v>
       </c>
       <c r="G171" s="13" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
       <c r="H171" t="n">
-        <v>40.38</v>
-      </c>
-      <c r="I171" s="18" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.71</v>
+      </c>
+      <c r="I171" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="10" t="n">
-        <v>1.119</v>
+        <v>1.554</v>
       </c>
       <c r="K171" s="10" t="n">
-        <v>1.241</v>
+        <v>1.628</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="15" t="inlineStr"/>
@@ -8228,28 +8228,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D172" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E172" s="17" t="n">
-        <v>-0.0127</v>
+        <v>0.55</v>
+      </c>
+      <c r="E172" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>510800</v>
+        <v>645700</v>
       </c>
       <c r="G172" s="13" t="n">
-        <v>0.23</v>
+        <v>0.44</v>
       </c>
       <c r="H172" t="n">
-        <v>22.49</v>
+        <v>40.89</v>
       </c>
       <c r="I172" s="14" t="inlineStr">
         <is>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="J172" s="10" t="n">
-        <v>0.864</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K172" s="10" t="n">
-        <v>1.025</v>
+        <v>0.574</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -8273,45 +8273,585 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D173" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E173" s="11" t="n">
-        <v>0.0106</v>
+        <v>0.675</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F173" s="12" t="n">
-        <v>507200</v>
+        <v>622900</v>
       </c>
       <c r="G173" s="13" t="n">
-        <v>0.11</v>
+        <v>1.06</v>
       </c>
       <c r="H173" t="n">
-        <v>44.28</v>
-      </c>
-      <c r="I173" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.19</v>
+      </c>
+      <c r="I173" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="10" t="n">
-        <v>0.951</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K173" s="10" t="n">
-        <v>1.027</v>
+        <v>0.664</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="15" t="inlineStr"/>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F174" s="12" t="n">
+        <v>590200</v>
+      </c>
+      <c r="G174" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H174" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="I174" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="K174" s="10" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="15" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E175" s="11" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F175" s="12" t="n">
+        <v>582600</v>
+      </c>
+      <c r="G175" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="I175" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K175" s="10" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="15" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>6012</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>MAXIS</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F176" s="12" t="n">
+        <v>574100</v>
+      </c>
+      <c r="G176" s="13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H176" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="I176" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>3.551</v>
+      </c>
+      <c r="K176" s="10" t="n">
+        <v>3.576</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="15" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E177" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="12" t="n">
+        <v>542300</v>
+      </c>
+      <c r="G177" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H177" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="I177" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="K177" s="10" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="15" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>PESONA</t>
+        </is>
+      </c>
+      <c r="D178" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E178" s="11" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="F178" s="12" t="n">
+        <v>541200</v>
+      </c>
+      <c r="G178" s="13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H178" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="I178" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="K178" s="10" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="15" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E179" s="11" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F179" s="12" t="n">
+        <v>530500</v>
+      </c>
+      <c r="G179" s="13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H179" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="I179" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="K179" s="10" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="15" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AFFIN</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E180" s="16" t="n">
+        <v>-0.009899999999999999</v>
+      </c>
+      <c r="F180" s="12" t="n">
+        <v>530300</v>
+      </c>
+      <c r="G180" s="13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H180" t="n">
+        <v>54.51</v>
+      </c>
+      <c r="I180" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v>1.975</v>
+      </c>
+      <c r="K180" s="10" t="n">
+        <v>2.013</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="15" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>KGB</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E181" s="11" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="F181" s="12" t="n">
+        <v>518800</v>
+      </c>
+      <c r="G181" s="13" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H181" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="I181" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>8.563000000000001</v>
+      </c>
+      <c r="K181" s="10" t="n">
+        <v>8.664</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="15" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E182" s="16" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="F182" s="12" t="n">
+        <v>516800</v>
+      </c>
+      <c r="G182" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H182" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="I182" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>2.878</v>
+      </c>
+      <c r="K182" s="10" t="n">
+        <v>3.007</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="15" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F183" s="12" t="n">
+        <v>512900</v>
+      </c>
+      <c r="G183" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H183" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="I183" s="17" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="K183" s="10" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="15" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E184" s="11" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="F184" s="12" t="n">
+        <v>511500</v>
+      </c>
+      <c r="G184" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H184" t="n">
+        <v>56.74</v>
+      </c>
+      <c r="I184" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>2.092</v>
+      </c>
+      <c r="K184" s="10" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="15" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E185" s="16" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F185" s="12" t="n">
+        <v>510800</v>
+      </c>
+      <c r="G185" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H185" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="I185" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="10" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="K185" s="10" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M173"/>
+  <autoFilter ref="A1:M185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
+++ b/docs/downloads/2026-10-28/bursa-report-2026-10-28.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-28" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-28'!$A$1:$M$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,9 +97,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -573,10 +573,10 @@
         <v>0.0195</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4316400</v>
+        <v>4434600</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>58.3</v>
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 58.3未超买，现价高于50日均线约12.8%，技术面信号较为可靠。</t>
+          <t>SAR转多信号，RSI 58.3处中性偏上但未超买，现价高于50日均线约12.8%，技术面信号较为可靠。</t>
         </is>
       </c>
     </row>
@@ -620,19 +620,19 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.605</v>
+        <v>0.6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.0254</v>
+        <v>0.0169</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>7261400</v>
+        <v>7292000</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>0.37</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>57.67</v>
+        <v>56.83</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.574</v>
+        <v>0.573</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.55</v>
@@ -652,7 +652,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.605高于50日均线0.55，RSI 57.67处中性偏上区间，未超买，信号技术面可靠性尚可。</t>
+          <t>现价0.60高于50日均线0.55，SAR转多信号获均线支撑；RSI 56.83处中性区间，未超买，信号可靠性尚可。</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="M4" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，现价0.335略高于50日均线0.329，RSI 60.32处中性偏强区间，未超买，信号可靠性尚可。</t>
+          <t>SAR转多信号，现价0.335略高于50日均线0.329，RSI 60.32处中性偏强区间，未超买，信号技术面尚属可靠。</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
         <v>0.029</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>23352700</v>
+        <v>23485700</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>0.27</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>现价0.355高于50日均线0.271约31%，SAR转多信号获趋势支撑；RSI 67.58接近超买区，可靠性中等偏强。</t>
+          <t>SAR转多信号出现，但RSI 67.58已接近超买区，现价高于50日均线约31%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -785,10 +785,10 @@
         <v>-0.0158</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3699300</v>
+        <v>3714100</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>56.03</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 56.03处中性区间未超买，现价高于50日均线约8.4%，技术面信号可靠性尚可。</t>
+          <t>SAR转多信号，现价3.12高于50日均线2.878，RSI 56.03处中性区间，未超买，信号技术面较可靠。</t>
         </is>
       </c>
     </row>
@@ -838,10 +838,10 @@
         <v>0.0588</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>224471400</v>
+        <v>227588700</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H7" t="n">
         <v>39.06</v>
@@ -877,19 +877,19 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>0.0052</v>
+        <v>0.965</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>30041100</v>
+        <v>30100100</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>0.39</v>
       </c>
       <c r="H8" t="n">
-        <v>70.27</v>
+        <v>69.77</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
         </is>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0.88</v>
+        <v>0.879</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="15" t="inlineStr"/>
@@ -922,27 +922,27 @@
         </is>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.034</v>
+        <v>0.715</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.0272</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>26133700</v>
+        <v>26181500</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>1.12</v>
       </c>
       <c r="H9" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
+        <v>71.18000000000001</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J9" s="10" t="n">
-        <v>0.671</v>
+        <v>0.672</v>
       </c>
       <c r="K9" s="10" t="n">
         <v>0.575</v>
@@ -967,19 +967,19 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>23104800</v>
+        <v>23108600</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>10.7</v>
       </c>
       <c r="H10" t="n">
-        <v>57.25</v>
+        <v>60.21</v>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="K10" s="10" t="n">
         <v>0.058</v>
@@ -1012,19 +1012,19 @@
         </is>
       </c>
       <c r="D11" s="10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0.0463</v>
+        <v>0.0417</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>16843700</v>
+        <v>17250100</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H11" t="n">
-        <v>67.11</v>
+        <v>66.75</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="J11" s="10" t="n">
-        <v>2.016</v>
+        <v>2.015</v>
       </c>
       <c r="K11" s="10" t="n">
         <v>1.823</v>
@@ -1059,11 +1059,11 @@
       <c r="D12" s="10" t="n">
         <v>0.155</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>16232000</v>
+        <v>16282000</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>0.44</v>
@@ -1108,12 +1108,12 @@
         <v>0.0541</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>15978300</v>
+        <v>16018300</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1131,28 +1131,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E14" s="18" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>15252400</v>
+        <v>15856100</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.73</v>
+        <v>0.28</v>
       </c>
       <c r="H14" t="n">
-        <v>46.13</v>
+        <v>51.28</v>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.867</v>
+        <v>0.159</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>0.868</v>
+        <v>0.149</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="15" t="inlineStr"/>
@@ -1176,28 +1176,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>15093800</v>
+        <v>15706900</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.26</v>
+        <v>0.75</v>
       </c>
       <c r="H15" t="n">
-        <v>51.28</v>
+        <v>40.85</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="J15" s="10" t="n">
-        <v>0.159</v>
+        <v>0.867</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>0.149</v>
+        <v>0.868</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="15" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
         <v>0.1834</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>14536300</v>
+        <v>14551300</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>2.58</v>
@@ -1244,7 +1244,7 @@
       <c r="H16" t="n">
         <v>61.07</v>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1281,7 +1281,7 @@
         <v>0.0227</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>14312400</v>
+        <v>14337500</v>
       </c>
       <c r="G17" s="13" t="n">
         <v>0.4</v>
@@ -1322,14 +1322,14 @@
       <c r="D18" s="10" t="n">
         <v>0.21</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>-0.0455</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>14121000</v>
+        <v>14244000</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H18" t="n">
         <v>82.61</v>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.5</v>
+        <v>0.505</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>13662900</v>
+        <v>13719600</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H19" t="n">
-        <v>74.66</v>
+        <v>76.67</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
       <c r="D20" s="10" t="n">
         <v>0.305</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
@@ -1424,7 +1424,7 @@
       <c r="H20" t="n">
         <v>47.46</v>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1461,10 +1461,10 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>12762400</v>
+        <v>12783900</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="H21" t="n">
         <v>63.99</v>
@@ -1500,21 +1500,21 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>-0.0263</v>
+        <v>0.375</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>12741600</v>
+        <v>12767500</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H22" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
+        <v>27.43</v>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1523,7 +1523,7 @@
         <v>0.387</v>
       </c>
       <c r="K22" s="10" t="n">
-        <v>0.401</v>
+        <v>0.402</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="15" t="inlineStr"/>
@@ -1536,39 +1536,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>HBGLOB</t>
         </is>
       </c>
       <c r="D23" s="10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>-0.6667000000000001</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>11843800</v>
+        <v>12155800</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.76</v>
+        <v>57</v>
       </c>
       <c r="H23" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="K23" s="10" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="15" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         <v>0.0581</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>11746100</v>
+        <v>11924400</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>37.29</v>
@@ -1626,39 +1626,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>0.0732</v>
+        <v>0.82</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>11451600</v>
+        <v>11847400</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1.18</v>
+        <v>0.76</v>
       </c>
       <c r="H25" t="n">
-        <v>43.44</v>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.221</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K25" s="10" t="n">
-        <v>0.263</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="15" t="inlineStr"/>
@@ -1671,39 +1671,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HBGLOB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>-0.6667000000000001</v>
+        <v>0.22</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.0732</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>11355800</v>
+        <v>11465800</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>53.25</v>
+        <v>1.18</v>
       </c>
       <c r="H26" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
+        <v>43.44</v>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.028</v>
+        <v>0.221</v>
       </c>
       <c r="K26" s="10" t="n">
-        <v>0.031</v>
+        <v>0.263</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="15" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>10117700</v>
+        <v>10117800</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>0.65</v>
@@ -1784,7 +1784,7 @@
       <c r="H28" t="n">
         <v>60.9</v>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -1821,10 +1821,10 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>9191400</v>
+        <v>9221400</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
       <c r="H29" t="n">
         <v>62.78</v>
@@ -1862,7 +1862,7 @@
       <c r="D30" s="10" t="n">
         <v>0.065</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>-0.07139999999999999</v>
       </c>
       <c r="F30" s="12" t="n">
@@ -1911,10 +1911,10 @@
         <v>0.04389999999999999</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>7829300</v>
+        <v>7915700</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H31" t="n">
         <v>51.69</v>
@@ -1941,28 +1941,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>7760800</v>
+        <v>7860500</v>
       </c>
       <c r="G32" s="13" t="n">
-        <v>1.24</v>
+        <v>0.61</v>
       </c>
       <c r="H32" t="n">
-        <v>50.9</v>
+        <v>34.46</v>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1.652</v>
+        <v>0.457</v>
       </c>
       <c r="K32" s="10" t="n">
-        <v>1.734</v>
+        <v>0.573</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="15" t="inlineStr"/>
@@ -1986,28 +1986,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-0.07139999999999999</v>
+        <v>1.68</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0.07690000000000001</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>7727400</v>
+        <v>7763900</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.6</v>
+        <v>1.24</v>
       </c>
       <c r="H33" t="n">
-        <v>34.46</v>
+        <v>50.9</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.457</v>
+        <v>1.652</v>
       </c>
       <c r="K33" s="10" t="n">
-        <v>0.573</v>
+        <v>1.734</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="15" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       <c r="D34" s="10" t="n">
         <v>0.64</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="D35" s="10" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>7653500</v>
+        <v>7673500</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>0.36</v>
       </c>
       <c r="H35" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="I35" s="17" t="inlineStr">
+        <v>63.86</v>
+      </c>
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2132,14 +2132,14 @@
       <c r="D36" s="10" t="n">
         <v>0.135</v>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>7247200</v>
+        <v>7245100</v>
       </c>
       <c r="G36" s="13" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H36" t="n">
         <v>48.69</v>
@@ -2181,10 +2181,10 @@
         <v>0.0455</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>7191400</v>
+        <v>7212700</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H37" t="n">
         <v>70.39</v>
@@ -2211,28 +2211,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>1.23</v>
+        <v>4.94</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>0.0696</v>
+        <v>0.0061</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>6854300</v>
+        <v>6930500</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>0.89</v>
+        <v>0.3</v>
       </c>
       <c r="H38" t="n">
-        <v>38.49</v>
+        <v>55</v>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1.282</v>
+        <v>4.885</v>
       </c>
       <c r="K38" s="10" t="n">
-        <v>1.479</v>
+        <v>4.783</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="15" t="inlineStr"/>
@@ -2256,28 +2256,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D39" s="10" t="n">
-        <v>4.94</v>
+        <v>1.22</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0.0061</v>
+        <v>0.0609</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>6846600</v>
+        <v>6908000</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>0.29</v>
+        <v>0.9</v>
       </c>
       <c r="H39" t="n">
-        <v>55</v>
+        <v>37.11</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="J39" s="10" t="n">
-        <v>4.885</v>
+        <v>1.281</v>
       </c>
       <c r="K39" s="10" t="n">
-        <v>4.783</v>
+        <v>1.479</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="15" t="inlineStr"/>
@@ -2310,19 +2310,19 @@
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>0.0345</v>
+        <v>0.0414</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>6721100</v>
+        <v>6746100</v>
       </c>
       <c r="G40" s="13" t="n">
         <v>0.48</v>
       </c>
       <c r="H40" t="n">
-        <v>38.44</v>
+        <v>39.52</v>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1.559</v>
+        <v>1.56</v>
       </c>
       <c r="K40" s="10" t="n">
-        <v>1.837</v>
+        <v>1.838</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="15" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
         <v>0.0222</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>6432300</v>
+        <v>6434400</v>
       </c>
       <c r="G41" s="13" t="n">
         <v>0.33</v>
@@ -2369,7 +2369,7 @@
       <c r="H41" t="n">
         <v>54.46</v>
       </c>
-      <c r="I41" s="17" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2402,7 +2402,7 @@
         <v>0.03700000000000001</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>6374100</v>
+        <v>6376400</v>
       </c>
       <c r="G42" s="13" t="n">
         <v>0.5600000000000001</v>
@@ -2410,7 +2410,7 @@
       <c r="H42" t="n">
         <v>48.17</v>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2455,7 +2455,7 @@
       <c r="H43" t="n">
         <v>53.65</v>
       </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2533,11 +2533,11 @@
       <c r="D45" s="10" t="n">
         <v>0.11</v>
       </c>
-      <c r="E45" s="18" t="n">
+      <c r="E45" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>5992600</v>
+        <v>6092600</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>0.35</v>
@@ -2545,7 +2545,7 @@
       <c r="H45" t="n">
         <v>34.76</v>
       </c>
-      <c r="I45" s="17" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2582,7 +2582,7 @@
         <v>0.0122</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>5980800</v>
+        <v>6012900</v>
       </c>
       <c r="G46" s="13" t="n">
         <v>0.51</v>
@@ -2612,39 +2612,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D47" s="10" t="n">
-        <v>0.605</v>
+        <v>0.945</v>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0.0431</v>
+        <v>0.0272</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>5932300</v>
+        <v>5977400</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="H47" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="I47" s="17" t="inlineStr">
+        <v>43.13</v>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.606</v>
+        <v>0.992</v>
       </c>
       <c r="K47" s="10" t="n">
-        <v>0.617</v>
+        <v>0.989</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="15" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>0.945</v>
+        <v>0.605</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>0.0272</v>
+        <v>0.0431</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>5926300</v>
+        <v>5975800</v>
       </c>
       <c r="G48" s="13" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="H48" t="n">
-        <v>43.13</v>
-      </c>
-      <c r="I48" s="17" t="inlineStr">
+        <v>48.86</v>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J48" s="10" t="n">
-        <v>0.992</v>
+        <v>0.606</v>
       </c>
       <c r="K48" s="10" t="n">
-        <v>0.989</v>
+        <v>0.617</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="15" t="inlineStr"/>
@@ -2713,7 +2713,7 @@
       <c r="D49" s="10" t="n">
         <v>0.535</v>
       </c>
-      <c r="E49" s="18" t="n">
+      <c r="E49" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
@@ -2756,19 +2756,19 @@
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>0.0246</v>
+        <v>0.0164</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>5717200</v>
+        <v>5727500</v>
       </c>
       <c r="G50" s="13" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>68.31999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="J50" s="10" t="n">
-        <v>1.119</v>
+        <v>1.118</v>
       </c>
       <c r="K50" s="10" t="n">
         <v>1.066</v>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D51" s="10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>0.0469</v>
+        <v>4.44</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>5247400</v>
+        <v>5298300</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>1.25</v>
+        <v>0.59</v>
       </c>
       <c r="H51" t="n">
-        <v>63.39</v>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.77</v>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="10" t="n">
-        <v>0.604</v>
+        <v>4.539</v>
       </c>
       <c r="K51" s="10" t="n">
-        <v>0.587</v>
+        <v>4.642</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="15" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E52" s="16" t="n">
-        <v>-0.0022</v>
+        <v>0.665</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>0.0391</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>5243600</v>
+        <v>5270400</v>
       </c>
       <c r="G52" s="13" t="n">
-        <v>0.58</v>
+        <v>1.26</v>
       </c>
       <c r="H52" t="n">
-        <v>35.77</v>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.73</v>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="10" t="n">
-        <v>4.539</v>
+        <v>0.604</v>
       </c>
       <c r="K52" s="10" t="n">
-        <v>4.642</v>
+        <v>0.586</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="15" t="inlineStr"/>
@@ -2897,7 +2897,7 @@
         <v>0.0195</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>5149600</v>
+        <v>5170800</v>
       </c>
       <c r="G53" s="13" t="n">
         <v>0.3</v>
@@ -2905,7 +2905,7 @@
       <c r="H53" t="n">
         <v>51.27</v>
       </c>
-      <c r="I53" s="17" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2942,7 +2942,7 @@
         <v>0.0204</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>4806100</v>
+        <v>4821400</v>
       </c>
       <c r="G54" s="13" t="n">
         <v>2.17</v>
@@ -2950,7 +2950,7 @@
       <c r="H54" t="n">
         <v>36.35</v>
       </c>
-      <c r="I54" s="17" t="inlineStr">
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -2972,39 +2972,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D55" s="10" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E55" s="11" t="n">
-        <v>0.0213</v>
+        <v>1.32</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>4685300</v>
+        <v>4804900</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="H55" t="n">
-        <v>60.46</v>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.62</v>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.456</v>
+        <v>1.426</v>
       </c>
       <c r="K55" s="10" t="n">
-        <v>0.45</v>
+        <v>1.452</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="15" t="inlineStr"/>
@@ -3017,39 +3017,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0380</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AQUAWALK</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D56" s="10" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>0</v>
+        <v>0.48</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>4669500</v>
+        <v>4746600</v>
       </c>
       <c r="G56" s="13" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="H56" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.46</v>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.13</v>
+        <v>0.456</v>
       </c>
       <c r="K56" s="10" t="n">
-        <v>0.14</v>
+        <v>0.45</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="15" t="inlineStr"/>
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0380</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>AQUAWALK</t>
         </is>
       </c>
       <c r="D57" s="10" t="n">
-        <v>1.33</v>
+        <v>0.125</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>-0.0699</v>
+        <v>0</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>4435600</v>
+        <v>4669500</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>1.19</v>
+        <v>2.07</v>
       </c>
       <c r="H57" t="n">
-        <v>27.68</v>
-      </c>
-      <c r="I57" s="17" t="inlineStr">
+        <v>41.46</v>
+      </c>
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J57" s="10" t="n">
-        <v>1.427</v>
+        <v>0.13</v>
       </c>
       <c r="K57" s="10" t="n">
-        <v>1.452</v>
+        <v>0.14</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="15" t="inlineStr"/>
@@ -3116,19 +3116,19 @@
         </is>
       </c>
       <c r="D58" s="10" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>0</v>
+        <v>8.279999999999999</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.0024</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>4335300</v>
+        <v>4339800</v>
       </c>
       <c r="G58" s="13" t="n">
         <v>2.27</v>
       </c>
       <c r="H58" t="n">
-        <v>55.93</v>
+        <v>55.3</v>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="J58" s="10" t="n">
-        <v>8.157</v>
+        <v>8.154999999999999</v>
       </c>
       <c r="K58" s="10" t="n">
         <v>7.972</v>
@@ -3152,39 +3152,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D59" s="10" t="n">
-        <v>1.65</v>
+        <v>5.24</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0.0123</v>
+        <v>0.0275</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>4234600</v>
+        <v>4259500</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="H59" t="n">
-        <v>52.09</v>
-      </c>
-      <c r="I59" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.83</v>
+      </c>
+      <c r="I59" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="10" t="n">
-        <v>1.629</v>
+        <v>5.357</v>
       </c>
       <c r="K59" s="10" t="n">
-        <v>1.67</v>
+        <v>5.523</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="15" t="inlineStr"/>
@@ -3197,39 +3197,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D60" s="10" t="n">
-        <v>5.23</v>
+        <v>1.66</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>0.0255</v>
+        <v>0.0184</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>4228000</v>
+        <v>4237700</v>
       </c>
       <c r="G60" s="13" t="n">
-        <v>0.26</v>
+        <v>0.51</v>
       </c>
       <c r="H60" t="n">
-        <v>44.46</v>
-      </c>
-      <c r="I60" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.38</v>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="10" t="n">
-        <v>5.356</v>
+        <v>1.63</v>
       </c>
       <c r="K60" s="10" t="n">
-        <v>5.522</v>
+        <v>1.67</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="15" t="inlineStr"/>
@@ -3251,19 +3251,19 @@
         </is>
       </c>
       <c r="D61" s="10" t="n">
-        <v>0.475</v>
+        <v>0.48</v>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0.0106</v>
+        <v>0.0213</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>4204100</v>
+        <v>4204200</v>
       </c>
       <c r="G61" s="13" t="n">
         <v>0.59</v>
       </c>
       <c r="H61" t="n">
-        <v>42.9</v>
+        <v>45.16</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
@@ -3287,39 +3287,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D62" s="10" t="n">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>0.0101</v>
+        <v>0.0238</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>3894700</v>
+        <v>3964200</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>1.06</v>
+        <v>0.79</v>
       </c>
       <c r="H62" t="n">
-        <v>30.68</v>
-      </c>
-      <c r="I62" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.06999999999999</v>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="10" t="n">
-        <v>0.523</v>
+        <v>1.125</v>
       </c>
       <c r="K62" s="10" t="n">
-        <v>0.556</v>
+        <v>0.987</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="15" t="inlineStr"/>
@@ -3332,39 +3332,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D63" s="10" t="n">
-        <v>1.3</v>
+        <v>0.505</v>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0.0317</v>
+        <v>0.0202</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>3891100</v>
+        <v>3927200</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>0.78</v>
+        <v>1.07</v>
       </c>
       <c r="H63" t="n">
-        <v>69.62</v>
-      </c>
-      <c r="I63" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.49</v>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="10" t="n">
-        <v>1.126</v>
+        <v>0.524</v>
       </c>
       <c r="K63" s="10" t="n">
-        <v>0.987</v>
+        <v>0.556</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="15" t="inlineStr"/>
@@ -3386,19 +3386,19 @@
         </is>
       </c>
       <c r="D64" s="10" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>-0.0316</v>
+        <v>3.99</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.0292</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>3782900</v>
+        <v>3841900</v>
       </c>
       <c r="G64" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="H64" t="n">
-        <v>58.3</v>
+        <v>58.67</v>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="J64" s="10" t="n">
-        <v>3.84</v>
+        <v>3.841</v>
       </c>
       <c r="K64" s="10" t="n">
         <v>3.337</v>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D66" s="10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E66" s="11" t="n">
-        <v>0.0157</v>
+        <v>9.98</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>3426000</v>
+        <v>3540800</v>
       </c>
       <c r="G66" s="13" t="n">
-        <v>0.58</v>
+        <v>0.29</v>
       </c>
       <c r="H66" t="n">
-        <v>46.07</v>
+        <v>47.39</v>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="J66" s="10" t="n">
-        <v>2.635</v>
+        <v>9.993</v>
       </c>
       <c r="K66" s="10" t="n">
-        <v>2.818</v>
+        <v>10.1</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="15" t="inlineStr"/>
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D67" s="10" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>-0.002</v>
+        <v>2.58</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>3406300</v>
+        <v>3539700</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="H67" t="n">
-        <v>46.74</v>
+        <v>45.62</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="J67" s="10" t="n">
-        <v>9.992000000000001</v>
+        <v>2.634</v>
       </c>
       <c r="K67" s="10" t="n">
-        <v>10.099</v>
+        <v>2.818</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="15" t="inlineStr"/>
@@ -3568,11 +3568,11 @@
       <c r="D68" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="E68" s="18" t="n">
+      <c r="E68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>3301100</v>
+        <v>3310100</v>
       </c>
       <c r="G68" s="13" t="n">
         <v>0.31</v>
@@ -3580,7 +3580,7 @@
       <c r="H68" t="n">
         <v>44.94</v>
       </c>
-      <c r="I68" s="17" t="inlineStr">
+      <c r="I68" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3613,11 +3613,11 @@
       <c r="D69" s="10" t="n">
         <v>2.67</v>
       </c>
-      <c r="E69" s="18" t="n">
+      <c r="E69" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>3261700</v>
+        <v>3262000</v>
       </c>
       <c r="G69" s="13" t="n">
         <v>0.33</v>
@@ -3625,7 +3625,7 @@
       <c r="H69" t="n">
         <v>44.52</v>
       </c>
-      <c r="I69" s="17" t="inlineStr">
+      <c r="I69" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3658,11 +3658,11 @@
       <c r="D70" s="10" t="n">
         <v>4.71</v>
       </c>
-      <c r="E70" s="16" t="n">
+      <c r="E70" s="17" t="n">
         <v>-0.008399999999999999</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>3191800</v>
+        <v>3228500</v>
       </c>
       <c r="G70" s="13" t="n">
         <v>0.15</v>
@@ -3670,7 +3670,7 @@
       <c r="H70" t="n">
         <v>46.82</v>
       </c>
-      <c r="I70" s="17" t="inlineStr">
+      <c r="I70" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3701,18 +3701,18 @@
         </is>
       </c>
       <c r="D71" s="10" t="n">
-        <v>0.735</v>
+        <v>0.73</v>
       </c>
       <c r="E71" s="11" t="n">
-        <v>0.0352</v>
+        <v>0.0282</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>3141400</v>
+        <v>3143600</v>
       </c>
       <c r="G71" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="I71" s="17" t="inlineStr">
+      <c r="I71" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3739,19 +3739,19 @@
         </is>
       </c>
       <c r="D72" s="10" t="n">
-        <v>0.325</v>
+        <v>0.33</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>0.0484</v>
+        <v>0.0645</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>3093300</v>
+        <v>3113400</v>
       </c>
       <c r="G72" s="13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="H72" t="n">
-        <v>59.54</v>
+        <v>61.17</v>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
@@ -3784,19 +3784,19 @@
         </is>
       </c>
       <c r="D73" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>-0.0496</v>
+        <v>2.32</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.0413</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>3059700</v>
+        <v>3088700</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="H73" t="n">
-        <v>51.83</v>
+        <v>53.29</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="J73" s="10" t="n">
-        <v>2.297</v>
+        <v>2.299</v>
       </c>
       <c r="K73" s="10" t="n">
         <v>2.22</v>
@@ -3835,7 +3835,7 @@
         <v>0.0333</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>3024400</v>
+        <v>3031400</v>
       </c>
       <c r="G74" s="13" t="n">
         <v>0.39</v>
@@ -3843,7 +3843,7 @@
       <c r="H74" t="n">
         <v>43.88</v>
       </c>
-      <c r="I74" s="17" t="inlineStr">
+      <c r="I74" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -3865,39 +3865,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D75" s="10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>0</v>
+        <v>6.94</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>0.0281</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>2979700</v>
+        <v>3013400</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>0.31</v>
+        <v>0.52</v>
       </c>
       <c r="H75" t="n">
-        <v>33.75</v>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.8</v>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="10" t="n">
-        <v>1.194</v>
+        <v>6.409</v>
       </c>
       <c r="K75" s="10" t="n">
-        <v>1.278</v>
+        <v>6.048</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="15" t="inlineStr"/>
@@ -3910,39 +3910,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D76" s="10" t="n">
-        <v>7</v>
+        <v>1.16</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>2858200</v>
+        <v>3005500</v>
       </c>
       <c r="G76" s="13" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="H76" t="n">
-        <v>62.57</v>
-      </c>
-      <c r="I76" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.74</v>
+      </c>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="10" t="n">
-        <v>6.415</v>
+        <v>1.195</v>
       </c>
       <c r="K76" s="10" t="n">
-        <v>6.049</v>
+        <v>1.278</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="15" t="inlineStr"/>
@@ -3955,39 +3955,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D77" s="10" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>0.0129</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>2713100</v>
+        <v>2920700</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>0.55</v>
+        <v>0.39</v>
       </c>
       <c r="H77" t="n">
-        <v>72.53</v>
-      </c>
-      <c r="I77" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.85</v>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="10" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="K77" s="10" t="n">
-        <v>0.782</v>
+        <v>0.771</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="15" t="inlineStr"/>
@@ -4000,28 +4000,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D78" s="10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="E78" s="18" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E78" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2711100</v>
+        <v>2772200</v>
       </c>
       <c r="G78" s="13" t="n">
-        <v>0.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H78" t="n">
-        <v>89.59</v>
+        <v>72.53</v>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="J78" s="10" t="n">
-        <v>3.119</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K78" s="10" t="n">
-        <v>2.641</v>
+        <v>0.782</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="15" t="inlineStr"/>
@@ -4045,28 +4045,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D79" s="10" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E79" s="11" t="n">
-        <v>0.0208</v>
+        <v>3.45</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>2710400</v>
+        <v>2715300</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>0.38</v>
+        <v>0.84</v>
       </c>
       <c r="H79" t="n">
-        <v>47.32</v>
+        <v>89.59</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
@@ -4074,10 +4074,10 @@
         </is>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.492</v>
+        <v>3.119</v>
       </c>
       <c r="K79" s="10" t="n">
-        <v>0.512</v>
+        <v>2.641</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="15" t="inlineStr"/>
@@ -4090,39 +4090,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D80" s="10" t="n">
-        <v>0.78</v>
+        <v>0.495</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0313</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>2666200</v>
+        <v>2714600</v>
       </c>
       <c r="G80" s="13" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H80" t="n">
-        <v>53.44</v>
-      </c>
-      <c r="I80" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.1</v>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="10" t="n">
-        <v>0.769</v>
+        <v>0.493</v>
       </c>
       <c r="K80" s="10" t="n">
-        <v>0.771</v>
+        <v>0.512</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="15" t="inlineStr"/>
@@ -4135,28 +4135,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D81" s="10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E81" s="11" t="n">
-        <v>0.0327</v>
+        <v>0.295</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>2633400</v>
+        <v>2642900</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>1.07</v>
+        <v>0.39</v>
       </c>
       <c r="H81" t="n">
-        <v>62.12</v>
+        <v>37.17</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="J81" s="10" t="n">
-        <v>2.128</v>
+        <v>0.312</v>
       </c>
       <c r="K81" s="10" t="n">
-        <v>2.084</v>
+        <v>0.355</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="15" t="inlineStr"/>
@@ -4180,39 +4180,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D82" s="10" t="n">
-        <v>0.555</v>
+        <v>2.21</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>0.0091</v>
+        <v>0.0327</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>2629700</v>
+        <v>2641200</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="H82" t="n">
-        <v>46.19</v>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.12</v>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>2.128</v>
       </c>
       <c r="K82" s="10" t="n">
-        <v>0.5610000000000001</v>
+        <v>2.084</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="15" t="inlineStr"/>
@@ -4225,39 +4225,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D83" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>2616900</v>
+        <v>2629700</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>0.39</v>
+        <v>1.22</v>
       </c>
       <c r="H83" t="n">
-        <v>38.94</v>
-      </c>
-      <c r="I83" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.19</v>
+      </c>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.312</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K83" s="10" t="n">
-        <v>0.355</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="15" t="inlineStr"/>
@@ -4326,7 +4326,7 @@
       <c r="D85" s="10" t="n">
         <v>0.63</v>
       </c>
-      <c r="E85" s="18" t="n">
+      <c r="E85" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
@@ -4360,28 +4360,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>HEXTECH</t>
         </is>
       </c>
       <c r="D86" s="10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>-0.004699999999999999</v>
+        <v>1.12</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>2472800</v>
+        <v>2501000</v>
       </c>
       <c r="G86" s="13" t="n">
-        <v>0.24</v>
+        <v>13.47</v>
       </c>
       <c r="H86" t="n">
-        <v>51.01</v>
+        <v>41.79</v>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="J86" s="10" t="n">
-        <v>2.107</v>
+        <v>1.135</v>
       </c>
       <c r="K86" s="10" t="n">
-        <v>2.114</v>
+        <v>1.137</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="15" t="inlineStr"/>
@@ -4405,28 +4405,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D87" s="10" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>0</v>
+        <v>2.11</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>2350800</v>
+        <v>2482100</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>1.58</v>
+        <v>0.24</v>
       </c>
       <c r="H87" t="n">
-        <v>42.99</v>
+        <v>51.01</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="J87" s="10" t="n">
-        <v>0.229</v>
+        <v>2.107</v>
       </c>
       <c r="K87" s="10" t="n">
-        <v>0.237</v>
+        <v>2.114</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="15" t="inlineStr"/>
@@ -4465,10 +4465,10 @@
         <v>0.0233</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>2322700</v>
+        <v>2452900</v>
       </c>
       <c r="G88" s="13" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="H88" t="n">
         <v>53.61</v>
@@ -4495,28 +4495,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D89" s="10" t="n">
-        <v>2.4</v>
+        <v>0.225</v>
       </c>
       <c r="E89" s="16" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>2303200</v>
+        <v>2372100</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="H89" t="n">
-        <v>37.29</v>
+        <v>42.99</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
@@ -4524,10 +4524,10 @@
         </is>
       </c>
       <c r="J89" s="10" t="n">
-        <v>2.467</v>
+        <v>0.229</v>
       </c>
       <c r="K89" s="10" t="n">
-        <v>2.62</v>
+        <v>0.237</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="15" t="inlineStr"/>
@@ -4540,28 +4540,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0456</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MMCS</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D90" s="10" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E90" s="11" t="n">
-        <v>0.0882</v>
+        <v>2.4</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>2267400</v>
+        <v>2336600</v>
       </c>
       <c r="G90" s="13" t="n">
-        <v>2.24</v>
+        <v>0.57</v>
       </c>
       <c r="H90" t="n">
-        <v>65.14</v>
+        <v>37.29</v>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
@@ -4569,10 +4569,10 @@
         </is>
       </c>
       <c r="J90" s="10" t="n">
-        <v>0.342</v>
+        <v>2.467</v>
       </c>
       <c r="K90" s="10" t="n">
-        <v>0.356</v>
+        <v>2.62</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="15" t="inlineStr"/>
@@ -4585,39 +4585,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D91" s="10" t="n">
-        <v>0.47</v>
+        <v>7.12</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>0.0108</v>
+        <v>0.0014</v>
       </c>
       <c r="F91" s="12" t="n">
-        <v>2260100</v>
+        <v>2306400</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="H91" t="n">
-        <v>46.41</v>
-      </c>
-      <c r="I91" s="17" t="inlineStr">
+        <v>33.05</v>
+      </c>
+      <c r="I91" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J91" s="10" t="n">
-        <v>0.488</v>
+        <v>7.315</v>
       </c>
       <c r="K91" s="10" t="n">
-        <v>0.472</v>
+        <v>7.599</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="15" t="inlineStr"/>
@@ -4630,39 +4630,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D92" s="10" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v>-0.0014</v>
+        <v>0.47</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>2230000</v>
+        <v>2286300</v>
       </c>
       <c r="G92" s="13" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H92" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="I92" s="17" t="inlineStr">
+        <v>46.41</v>
+      </c>
+      <c r="I92" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J92" s="10" t="n">
-        <v>7.313</v>
+        <v>0.488</v>
       </c>
       <c r="K92" s="10" t="n">
-        <v>7.599</v>
+        <v>0.472</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="15" t="inlineStr"/>
@@ -4675,39 +4675,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0456</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MMCS</t>
         </is>
       </c>
       <c r="D93" s="10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>0.0882</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>2219800</v>
+        <v>2275400</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="H93" t="n">
-        <v>52.84</v>
-      </c>
-      <c r="I93" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.14</v>
+      </c>
+      <c r="I93" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="10" t="n">
-        <v>0.744</v>
+        <v>0.342</v>
       </c>
       <c r="K93" s="10" t="n">
-        <v>0.709</v>
+        <v>0.356</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="15" t="inlineStr"/>
@@ -4735,7 +4735,7 @@
         <v>0.0192</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>2218200</v>
+        <v>2260300</v>
       </c>
       <c r="G94" s="13" t="n">
         <v>0.34</v>
@@ -4743,7 +4743,7 @@
       <c r="H94" t="n">
         <v>42.34</v>
       </c>
-      <c r="I94" s="17" t="inlineStr">
+      <c r="I94" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -4765,39 +4765,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D95" s="10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E95" s="18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E95" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>2071000</v>
+        <v>2249400</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>0.31</v>
+        <v>0.7</v>
       </c>
       <c r="H95" t="n">
-        <v>62.05</v>
-      </c>
-      <c r="I95" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.84</v>
+      </c>
+      <c r="I95" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="10" t="n">
-        <v>1.193</v>
+        <v>0.744</v>
       </c>
       <c r="K95" s="10" t="n">
-        <v>1.156</v>
+        <v>0.709</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="15" t="inlineStr"/>
@@ -4810,28 +4810,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D96" s="10" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="E96" s="18" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>1951600</v>
+        <v>2076500</v>
       </c>
       <c r="G96" s="13" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="H96" t="n">
-        <v>42.51</v>
+        <v>60.28</v>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="J96" s="10" t="n">
-        <v>5.812</v>
+        <v>1.192</v>
       </c>
       <c r="K96" s="10" t="n">
-        <v>6.057</v>
+        <v>1.156</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="15" t="inlineStr"/>
@@ -4855,28 +4855,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D97" s="10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v>0.0593</v>
+        <v>5.74</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>1934800</v>
+        <v>2069800</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="H97" t="n">
-        <v>60.77</v>
+        <v>41.4</v>
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="J97" s="10" t="n">
-        <v>1.309</v>
+        <v>5.811</v>
       </c>
       <c r="K97" s="10" t="n">
-        <v>1.253</v>
+        <v>6.057</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="15" t="inlineStr"/>
@@ -4900,39 +4900,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D98" s="10" t="n">
-        <v>0.33</v>
+        <v>1.18</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>0.0313</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>1921900</v>
+        <v>1943900</v>
       </c>
       <c r="G98" s="13" t="n">
-        <v>0.19</v>
+        <v>0.58</v>
       </c>
       <c r="H98" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I98" s="17" t="inlineStr">
+        <v>60.43</v>
+      </c>
+      <c r="I98" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J98" s="10" t="n">
-        <v>0.336</v>
+        <v>1.107</v>
       </c>
       <c r="K98" s="10" t="n">
-        <v>0.338</v>
+        <v>0.945</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="15" t="inlineStr"/>
@@ -4945,39 +4945,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D99" s="10" t="n">
-        <v>1.18</v>
+        <v>0.33</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>0.06309999999999999</v>
+        <v>0.0313</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1903400</v>
+        <v>1938700</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="H99" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="I99" s="17" t="inlineStr">
+        <v>48.02</v>
+      </c>
+      <c r="I99" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J99" s="10" t="n">
-        <v>1.107</v>
+        <v>0.336</v>
       </c>
       <c r="K99" s="10" t="n">
-        <v>0.945</v>
+        <v>0.338</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="15" t="inlineStr"/>
@@ -4990,28 +4990,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D100" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>-0.0231</v>
+        <v>1.42</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>0.0519</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1872500</v>
+        <v>1936600</v>
       </c>
       <c r="G100" s="13" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="H100" t="n">
-        <v>40.2</v>
+        <v>60.18</v>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="J100" s="10" t="n">
-        <v>0.675</v>
+        <v>1.308</v>
       </c>
       <c r="K100" s="10" t="n">
-        <v>0.73</v>
+        <v>1.253</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="15" t="inlineStr"/>
@@ -5035,28 +5035,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D101" s="10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>-0.005600000000000001</v>
+        <v>2.1</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>1839100</v>
+        <v>1890800</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>0.96</v>
+        <v>0.29</v>
       </c>
       <c r="H101" t="n">
-        <v>47.67</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="J101" s="10" t="n">
-        <v>0.903</v>
+        <v>1.993</v>
       </c>
       <c r="K101" s="10" t="n">
-        <v>0.897</v>
+        <v>1.968</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="15" t="inlineStr"/>
@@ -5080,28 +5080,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D102" s="10" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>-0.0158</v>
+        <v>0.64</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>1838600</v>
+        <v>1882500</v>
       </c>
       <c r="G102" s="13" t="n">
-        <v>0.43</v>
+        <v>0.59</v>
       </c>
       <c r="H102" t="n">
-        <v>50.31</v>
+        <v>40.9</v>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.676</v>
       </c>
       <c r="K102" s="10" t="n">
-        <v>0.897</v>
+        <v>0.731</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="15" t="inlineStr"/>
@@ -5125,28 +5125,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D103" s="10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E103" s="18" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>1820200</v>
+        <v>1841600</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>0.28</v>
+        <v>0.43</v>
       </c>
       <c r="H103" t="n">
-        <v>68</v>
+        <v>51.97</v>
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
         </is>
       </c>
       <c r="J103" s="10" t="n">
-        <v>1.994</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="K103" s="10" t="n">
-        <v>1.968</v>
+        <v>0.897</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="15" t="inlineStr"/>
@@ -5170,39 +5170,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D104" s="10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E104" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.89</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1783900</v>
+        <v>1839100</v>
       </c>
       <c r="G104" s="13" t="n">
-        <v>0.61</v>
+        <v>0.96</v>
       </c>
       <c r="H104" t="n">
-        <v>49.98</v>
-      </c>
-      <c r="I104" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.67</v>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="10" t="n">
-        <v>0.866</v>
+        <v>0.903</v>
       </c>
       <c r="K104" s="10" t="n">
-        <v>0.861</v>
+        <v>0.897</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="15" t="inlineStr"/>
@@ -5230,15 +5230,15 @@
         <v>0.0361</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>1774900</v>
+        <v>1807000</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H105" t="n">
         <v>57.91</v>
       </c>
-      <c r="I105" s="17" t="inlineStr">
+      <c r="I105" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5260,39 +5260,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D106" s="10" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E106" s="11" t="n">
-        <v>0.06</v>
+        <v>0.865</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1725300</v>
+        <v>1783900</v>
       </c>
       <c r="G106" s="13" t="n">
-        <v>0.3</v>
+        <v>0.61</v>
       </c>
       <c r="H106" t="n">
-        <v>49.13</v>
-      </c>
-      <c r="I106" s="17" t="inlineStr">
+        <v>49.98</v>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J106" s="10" t="n">
-        <v>0.263</v>
+        <v>0.866</v>
       </c>
       <c r="K106" s="10" t="n">
-        <v>0.28</v>
+        <v>0.861</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="15" t="inlineStr"/>
@@ -5305,39 +5305,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D107" s="10" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>-0.0268</v>
+        <v>0.265</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>0.06</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>1718100</v>
+        <v>1755400</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H107" t="n">
-        <v>53.39</v>
-      </c>
-      <c r="I107" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.13</v>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="10" t="n">
-        <v>6.838</v>
+        <v>0.263</v>
       </c>
       <c r="K107" s="10" t="n">
-        <v>6.828</v>
+        <v>0.28</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="15" t="inlineStr"/>
@@ -5350,39 +5350,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>POS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D108" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E108" s="11" t="n">
-        <v>0.0638</v>
+        <v>6.9</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>-0.0254</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>1712200</v>
+        <v>1749200</v>
       </c>
       <c r="G108" s="13" t="n">
-        <v>1.57</v>
+        <v>0.3</v>
       </c>
       <c r="H108" t="n">
-        <v>51.83</v>
-      </c>
-      <c r="I108" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.89</v>
+      </c>
+      <c r="I108" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.247</v>
+        <v>6.839</v>
       </c>
       <c r="K108" s="10" t="n">
-        <v>0.25</v>
+        <v>6.828</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="15" t="inlineStr"/>
@@ -5406,19 +5406,19 @@
       <c r="D109" s="10" t="n">
         <v>0.905</v>
       </c>
-      <c r="E109" s="18" t="n">
+      <c r="E109" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>1702100</v>
+        <v>1719400</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="H109" t="n">
         <v>34.99</v>
       </c>
-      <c r="I109" s="17" t="inlineStr">
+      <c r="I109" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>POS</t>
         </is>
       </c>
       <c r="D110" s="10" t="n">
-        <v>0.615</v>
+        <v>0.25</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>0.025</v>
+        <v>0.0638</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1631500</v>
+        <v>1712200</v>
       </c>
       <c r="G110" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H110" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="I110" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="K110" s="10" t="n">
         <v>0.25</v>
-      </c>
-      <c r="H110" t="n">
-        <v>57.89</v>
-      </c>
-      <c r="I110" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="K110" s="10" t="n">
-        <v>0.493</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="15" t="inlineStr"/>
@@ -5485,39 +5485,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D111" s="10" t="n">
-        <v>2.77</v>
+        <v>0.615</v>
       </c>
       <c r="E111" s="11" t="n">
-        <v>0.0375</v>
+        <v>0.025</v>
       </c>
       <c r="F111" s="12" t="n">
-        <v>1588300</v>
+        <v>1633100</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="H111" t="n">
-        <v>44.51</v>
-      </c>
-      <c r="I111" s="17" t="inlineStr">
+        <v>57.89</v>
+      </c>
+      <c r="I111" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J111" s="10" t="n">
-        <v>2.813</v>
+        <v>0.582</v>
       </c>
       <c r="K111" s="10" t="n">
-        <v>2.95</v>
+        <v>0.493</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="15" t="inlineStr"/>
@@ -5530,39 +5530,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D112" s="10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E112" s="16" t="n">
-        <v>-0.0234</v>
+        <v>2.77</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>0.0375</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>1532700</v>
+        <v>1590700</v>
       </c>
       <c r="G112" s="13" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="H112" t="n">
-        <v>45.19</v>
-      </c>
-      <c r="I112" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.51</v>
+      </c>
+      <c r="I112" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="10" t="n">
-        <v>1.273</v>
+        <v>2.813</v>
       </c>
       <c r="K112" s="10" t="n">
-        <v>1.319</v>
+        <v>2.95</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -5575,28 +5575,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D113" s="10" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E113" s="11" t="n">
-        <v>0.012</v>
+        <v>1.25</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>1475900</v>
+        <v>1584900</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H113" t="n">
-        <v>60.06</v>
+        <v>45.19</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="J113" s="10" t="n">
-        <v>4.024</v>
+        <v>1.273</v>
       </c>
       <c r="K113" s="10" t="n">
-        <v>3.685</v>
+        <v>1.319</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="15" t="inlineStr"/>
@@ -5620,39 +5620,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D114" s="10" t="n">
-        <v>7.63</v>
+        <v>0.835</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>0.0242</v>
+        <v>0.0121</v>
       </c>
       <c r="F114" s="12" t="n">
-        <v>1472000</v>
+        <v>1561200</v>
       </c>
       <c r="G114" s="13" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="H114" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I114" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.7</v>
+      </c>
+      <c r="I114" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="10" t="n">
-        <v>7.335</v>
+        <v>0.861</v>
       </c>
       <c r="K114" s="10" t="n">
-        <v>6.985</v>
+        <v>0.923</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="15" t="inlineStr"/>
@@ -5665,39 +5665,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D115" s="10" t="n">
-        <v>0.835</v>
+        <v>7.61</v>
       </c>
       <c r="E115" s="11" t="n">
-        <v>0.0121</v>
+        <v>0.0215</v>
       </c>
       <c r="F115" s="12" t="n">
-        <v>1443200</v>
+        <v>1505300</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>0.54</v>
+        <v>0.33</v>
       </c>
       <c r="H115" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="I115" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.19</v>
+      </c>
+      <c r="I115" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="10" t="n">
-        <v>0.861</v>
+        <v>7.333</v>
       </c>
       <c r="K115" s="10" t="n">
-        <v>0.923</v>
+        <v>6.985</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="15" t="inlineStr"/>
@@ -5710,39 +5710,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D116" s="10" t="n">
-        <v>1.37</v>
+        <v>4.23</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>0.0148</v>
+        <v>0.0144</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>1436400</v>
+        <v>1482800</v>
       </c>
       <c r="G116" s="13" t="n">
-        <v>0.52</v>
+        <v>0.17</v>
       </c>
       <c r="H116" t="n">
-        <v>60.04</v>
-      </c>
-      <c r="I116" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.35</v>
+      </c>
+      <c r="I116" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="10" t="n">
-        <v>1.285</v>
+        <v>4.025</v>
       </c>
       <c r="K116" s="10" t="n">
-        <v>1.194</v>
+        <v>3.685</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -5755,39 +5755,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D117" s="10" t="n">
-        <v>0.885</v>
+        <v>1.37</v>
       </c>
       <c r="E117" s="11" t="n">
-        <v>0.0351</v>
+        <v>0.0148</v>
       </c>
       <c r="F117" s="12" t="n">
-        <v>1428400</v>
+        <v>1465300</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>0.23</v>
+        <v>0.53</v>
       </c>
       <c r="H117" t="n">
-        <v>49.95</v>
-      </c>
-      <c r="I117" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.04</v>
+      </c>
+      <c r="I117" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="10" t="n">
-        <v>0.884</v>
+        <v>1.285</v>
       </c>
       <c r="K117" s="10" t="n">
-        <v>0.865</v>
+        <v>1.194</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="15" t="inlineStr"/>
@@ -5800,28 +5800,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D118" s="10" t="n">
-        <v>1.35</v>
+        <v>0.885</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>0.015</v>
+        <v>0.0351</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>1395000</v>
+        <v>1446600</v>
       </c>
       <c r="G118" s="13" t="n">
-        <v>0.55</v>
+        <v>0.23</v>
       </c>
       <c r="H118" t="n">
-        <v>45.72</v>
+        <v>49.95</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="J118" s="10" t="n">
-        <v>1.361</v>
+        <v>0.884</v>
       </c>
       <c r="K118" s="10" t="n">
-        <v>1.431</v>
+        <v>0.865</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="15" t="inlineStr"/>
@@ -5845,39 +5845,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D119" s="10" t="n">
-        <v>2.94</v>
+        <v>0.795</v>
       </c>
       <c r="E119" s="11" t="n">
-        <v>0.0138</v>
+        <v>0.06</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>1367400</v>
+        <v>1442500</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>0.21</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>59.05</v>
-      </c>
-      <c r="I119" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.09999999999999</v>
+      </c>
+      <c r="I119" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="10" t="n">
-        <v>2.82</v>
+        <v>0.744</v>
       </c>
       <c r="K119" s="10" t="n">
-        <v>2.706</v>
+        <v>0.675</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="15" t="inlineStr"/>
@@ -5901,14 +5901,14 @@
       <c r="D120" s="10" t="n">
         <v>7.35</v>
       </c>
-      <c r="E120" s="16" t="n">
+      <c r="E120" s="17" t="n">
         <v>-0.0014</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>1365800</v>
+        <v>1418800</v>
       </c>
       <c r="G120" s="13" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H120" t="n">
         <v>42.2</v>
@@ -5935,39 +5935,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D121" s="10" t="n">
-        <v>3.12</v>
+        <v>1.36</v>
       </c>
       <c r="E121" s="11" t="n">
-        <v>0.023</v>
+        <v>0.0226</v>
       </c>
       <c r="F121" s="12" t="n">
-        <v>1364600</v>
+        <v>1414700</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>66.20999999999999</v>
-      </c>
-      <c r="I121" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.17</v>
+      </c>
+      <c r="I121" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="10" t="n">
-        <v>2.872</v>
+        <v>1.362</v>
       </c>
       <c r="K121" s="10" t="n">
-        <v>2.407</v>
+        <v>1.431</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="15" t="inlineStr"/>
@@ -5980,39 +5980,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D122" s="10" t="n">
-        <v>0.8</v>
+        <v>2.94</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>0.0667</v>
+        <v>0.0138</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>1352100</v>
+        <v>1382300</v>
       </c>
       <c r="G122" s="13" t="n">
-        <v>0.65</v>
+        <v>0.21</v>
       </c>
       <c r="H122" t="n">
-        <v>67.89</v>
-      </c>
-      <c r="I122" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.05</v>
+      </c>
+      <c r="I122" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="10" t="n">
-        <v>0.745</v>
+        <v>2.82</v>
       </c>
       <c r="K122" s="10" t="n">
-        <v>0.675</v>
+        <v>2.706</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="15" t="inlineStr"/>
@@ -6025,39 +6025,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D123" s="10" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="E123" s="11" t="n">
-        <v>0.0309</v>
+        <v>0.023</v>
       </c>
       <c r="F123" s="12" t="n">
-        <v>1342200</v>
+        <v>1369200</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="H123" t="n">
-        <v>56.31</v>
-      </c>
-      <c r="I123" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>66.20999999999999</v>
+      </c>
+      <c r="I123" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="10" t="n">
-        <v>2.604</v>
+        <v>2.872</v>
       </c>
       <c r="K123" s="10" t="n">
-        <v>2.601</v>
+        <v>2.407</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="15" t="inlineStr"/>
@@ -6070,28 +6070,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D124" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>2.67</v>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>0.0309</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1332300</v>
+        <v>1359400</v>
       </c>
       <c r="G124" s="13" t="n">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="H124" t="n">
-        <v>48.28</v>
+        <v>56.31</v>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="J124" s="10" t="n">
-        <v>0.64</v>
+        <v>2.604</v>
       </c>
       <c r="K124" s="10" t="n">
-        <v>0.63</v>
+        <v>2.601</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="15" t="inlineStr"/>
@@ -6115,39 +6115,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D125" s="10" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E125" s="11" t="n">
-        <v>0.0179</v>
+        <v>0.635</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F125" s="12" t="n">
-        <v>1332100</v>
+        <v>1332300</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>0.2</v>
+        <v>0.64</v>
       </c>
       <c r="H125" t="n">
-        <v>43.56</v>
-      </c>
-      <c r="I125" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.28</v>
+      </c>
+      <c r="I125" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="10" t="n">
-        <v>0.294</v>
+        <v>0.64</v>
       </c>
       <c r="K125" s="10" t="n">
-        <v>0.318</v>
+        <v>0.63</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="15" t="inlineStr"/>
@@ -6160,39 +6160,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D126" s="10" t="n">
-        <v>1.3</v>
+        <v>0.285</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>1319000</v>
+        <v>1332100</v>
       </c>
       <c r="G126" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="H126" t="n">
-        <v>61.39</v>
-      </c>
-      <c r="I126" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.56</v>
+      </c>
+      <c r="I126" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="10" t="n">
-        <v>1.241</v>
+        <v>0.294</v>
       </c>
       <c r="K126" s="10" t="n">
-        <v>1.212</v>
+        <v>0.318</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -6214,27 +6214,27 @@
         </is>
       </c>
       <c r="D127" s="10" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E127" s="18" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F127" s="12" t="n">
-        <v>1293600</v>
+        <v>1324700</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H127" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I127" s="17" t="inlineStr">
+        <v>49.5</v>
+      </c>
+      <c r="I127" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J127" s="10" t="n">
-        <v>0.634</v>
+        <v>0.633</v>
       </c>
       <c r="K127" s="10" t="n">
         <v>0.624</v>
@@ -6250,39 +6250,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D128" s="10" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E128" s="11" t="n">
-        <v>0.04480000000000001</v>
+        <v>1.29</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>1282000</v>
+        <v>1322000</v>
       </c>
       <c r="G128" s="13" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H128" t="n">
-        <v>51.74</v>
-      </c>
-      <c r="I128" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.23</v>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="10" t="n">
-        <v>0.347</v>
+        <v>1.24</v>
       </c>
       <c r="K128" s="10" t="n">
-        <v>0.331</v>
+        <v>1.212</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -6295,39 +6295,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D129" s="10" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E129" s="18" t="n">
-        <v>0</v>
+        <v>0.35</v>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>0.04480000000000001</v>
       </c>
       <c r="F129" s="12" t="n">
-        <v>1264500</v>
+        <v>1286000</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>1.45</v>
+        <v>0.16</v>
       </c>
       <c r="H129" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="I129" s="17" t="inlineStr">
+        <v>51.74</v>
+      </c>
+      <c r="I129" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.271</v>
+        <v>0.347</v>
       </c>
       <c r="K129" s="10" t="n">
-        <v>0.268</v>
+        <v>0.331</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="15" t="inlineStr"/>
@@ -6340,39 +6340,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D130" s="10" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="E130" s="11" t="n">
-        <v>0.024</v>
+        <v>0.26</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>1249000</v>
+        <v>1264500</v>
       </c>
       <c r="G130" s="13" t="n">
-        <v>0.33</v>
+        <v>1.45</v>
       </c>
       <c r="H130" t="n">
-        <v>62.81</v>
-      </c>
-      <c r="I130" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.3</v>
+      </c>
+      <c r="I130" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="10" t="n">
-        <v>10.56</v>
+        <v>0.271</v>
       </c>
       <c r="K130" s="10" t="n">
-        <v>9.938000000000001</v>
+        <v>0.268</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -6385,39 +6385,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D131" s="10" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E131" s="18" t="n">
-        <v>0</v>
+        <v>11.06</v>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F131" s="12" t="n">
-        <v>1243700</v>
+        <v>1253900</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="H131" t="n">
-        <v>54.59</v>
-      </c>
-      <c r="I131" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.54</v>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="10" t="n">
-        <v>0.462</v>
+        <v>10.558</v>
       </c>
       <c r="K131" s="10" t="n">
-        <v>0.462</v>
+        <v>9.938000000000001</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="15" t="inlineStr"/>
@@ -6430,39 +6430,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SUPERLN</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D132" s="10" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E132" s="11" t="n">
-        <v>0.0269</v>
+        <v>0.465</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>1213600</v>
+        <v>1243700</v>
       </c>
       <c r="G132" s="13" t="n">
-        <v>2.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="I132" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.59</v>
+      </c>
+      <c r="I132" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="10" t="n">
-        <v>0.897</v>
+        <v>0.462</v>
       </c>
       <c r="K132" s="10" t="n">
-        <v>0.86</v>
+        <v>0.462</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -6475,28 +6475,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NAIM</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D133" s="10" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E133" s="16" t="n">
-        <v>-0.042</v>
+        <v>4.67</v>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>1192800</v>
+        <v>1219300</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>2.15</v>
+        <v>0.24</v>
       </c>
       <c r="H133" t="n">
-        <v>59.93</v>
+        <v>59.1</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="J133" s="10" t="n">
-        <v>0.654</v>
+        <v>4.465</v>
       </c>
       <c r="K133" s="10" t="n">
-        <v>0.618</v>
+        <v>4.446</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="15" t="inlineStr"/>
@@ -6520,39 +6520,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>SUPERLN</t>
         </is>
       </c>
       <c r="D134" s="10" t="n">
-        <v>0.74</v>
+        <v>0.955</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>0.035</v>
+        <v>0.0269</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>1186800</v>
+        <v>1213600</v>
       </c>
       <c r="G134" s="13" t="n">
-        <v>0.53</v>
+        <v>2.65</v>
       </c>
       <c r="H134" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="I134" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.31</v>
+      </c>
+      <c r="I134" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="10" t="n">
-        <v>0.752</v>
+        <v>0.897</v>
       </c>
       <c r="K134" s="10" t="n">
-        <v>0.765</v>
+        <v>0.86</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="15" t="inlineStr"/>
@@ -6565,39 +6565,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BJCORP</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D135" s="10" t="n">
-        <v>0.25</v>
+        <v>0.74</v>
       </c>
       <c r="E135" s="11" t="n">
-        <v>0.0204</v>
+        <v>0.035</v>
       </c>
       <c r="F135" s="12" t="n">
-        <v>1139200</v>
+        <v>1200600</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="H135" t="n">
-        <v>56.77</v>
-      </c>
-      <c r="I135" s="17" t="inlineStr">
+        <v>46.87</v>
+      </c>
+      <c r="I135" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.248</v>
+        <v>0.752</v>
       </c>
       <c r="K135" s="10" t="n">
-        <v>0.249</v>
+        <v>0.765</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="15" t="inlineStr"/>
@@ -6610,28 +6610,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>NAIM</t>
         </is>
       </c>
       <c r="D136" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E136" s="11" t="n">
-        <v>0.0169</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>-0.035</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1126000</v>
+        <v>1195800</v>
       </c>
       <c r="G136" s="13" t="n">
-        <v>0.22</v>
+        <v>2.15</v>
       </c>
       <c r="H136" t="n">
-        <v>60.09</v>
+        <v>61.38</v>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
@@ -6639,10 +6639,10 @@
         </is>
       </c>
       <c r="J136" s="10" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="K136" s="10" t="n">
-        <v>0.531</v>
+        <v>0.618</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -6655,39 +6655,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>BJCORP</t>
         </is>
       </c>
       <c r="D137" s="10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E137" s="18" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>1122600</v>
+        <v>1149300</v>
       </c>
       <c r="G137" s="13" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H137" t="n">
-        <v>49.04</v>
-      </c>
-      <c r="I137" s="17" t="inlineStr">
+        <v>56.77</v>
+      </c>
+      <c r="I137" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J137" s="10" t="n">
-        <v>1.023</v>
+        <v>0.248</v>
       </c>
       <c r="K137" s="10" t="n">
-        <v>0.985</v>
+        <v>0.249</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="15" t="inlineStr"/>
@@ -6700,38 +6700,40 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SENTRAL</t>
         </is>
       </c>
       <c r="D138" s="10" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E138" s="18" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E138" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>1118000</v>
+        <v>1137700</v>
       </c>
       <c r="G138" s="13" t="n">
-        <v>0.19</v>
+        <v>2.77</v>
       </c>
       <c r="H138" t="n">
-        <v>59.41</v>
-      </c>
-      <c r="I138" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.8</v>
+      </c>
+      <c r="I138" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="10" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="K138" s="10" t="n"/>
+        <v>0.63</v>
+      </c>
+      <c r="K138" s="10" t="n">
+        <v>0.652</v>
+      </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
     </row>
@@ -6752,27 +6754,27 @@
         </is>
       </c>
       <c r="D139" s="10" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E139" s="18" t="n">
-        <v>0</v>
+        <v>0.735</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F139" s="12" t="n">
-        <v>1109700</v>
+        <v>1136400</v>
       </c>
       <c r="G139" s="13" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H139" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="I139" s="17" t="inlineStr">
+        <v>44.89</v>
+      </c>
+      <c r="I139" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J139" s="10" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="K139" s="10" t="n">
         <v>0.725</v>
@@ -6788,39 +6790,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D140" s="10" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E140" s="18" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F140" s="12" t="n">
-        <v>1106200</v>
+        <v>1126500</v>
       </c>
       <c r="G140" s="13" t="n">
-        <v>2.69</v>
+        <v>0.22</v>
       </c>
       <c r="H140" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="I140" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.29</v>
+      </c>
+      <c r="I140" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="10" t="n">
-        <v>0.63</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K140" s="10" t="n">
-        <v>0.652</v>
+        <v>0.531</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -6833,39 +6835,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D141" s="10" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E141" s="11" t="n">
-        <v>0.0043</v>
+        <v>1.01</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="12" t="n">
-        <v>1099700</v>
+        <v>1122600</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="H141" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="I141" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.04</v>
+      </c>
+      <c r="I141" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="10" t="n">
-        <v>4.463</v>
+        <v>1.023</v>
       </c>
       <c r="K141" s="10" t="n">
-        <v>4.446</v>
+        <v>0.985</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="15" t="inlineStr"/>
@@ -6878,28 +6880,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D142" s="10" t="n">
-        <v>3.98</v>
+        <v>1.44</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>0.0025</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>1091000</v>
+        <v>1121700</v>
       </c>
       <c r="G142" s="13" t="n">
-        <v>0.29</v>
+        <v>0.53</v>
       </c>
       <c r="H142" t="n">
-        <v>57.44</v>
+        <v>70.33</v>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
@@ -6907,10 +6909,10 @@
         </is>
       </c>
       <c r="J142" s="10" t="n">
-        <v>3.843</v>
+        <v>1.379</v>
       </c>
       <c r="K142" s="10" t="n">
-        <v>3.768</v>
+        <v>1.351</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -6923,40 +6925,38 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D143" s="10" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="E143" s="11" t="n">
-        <v>0.0016</v>
+        <v>0.365</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="12" t="n">
-        <v>1089400</v>
+        <v>1118000</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H143" t="n">
-        <v>45.25</v>
-      </c>
-      <c r="I143" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.41</v>
+      </c>
+      <c r="I143" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="10" t="n">
-        <v>6.336</v>
-      </c>
-      <c r="K143" s="10" t="n">
-        <v>6.605</v>
-      </c>
+        <v>0.342</v>
+      </c>
+      <c r="K143" s="10" t="n"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="15" t="inlineStr"/>
     </row>
@@ -6968,39 +6968,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>COMFORT</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D144" s="10" t="n">
-        <v>0.205</v>
+        <v>6.3</v>
       </c>
       <c r="E144" s="16" t="n">
-        <v>-0.0238</v>
+        <v>0</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1081100</v>
+        <v>1096900</v>
       </c>
       <c r="G144" s="13" t="n">
-        <v>0.55</v>
+        <v>0.14</v>
       </c>
       <c r="H144" t="n">
-        <v>67.92</v>
-      </c>
-      <c r="I144" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.57</v>
+      </c>
+      <c r="I144" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="10" t="n">
-        <v>0.179</v>
+        <v>6.335</v>
       </c>
       <c r="K144" s="10" t="n">
-        <v>0.165</v>
+        <v>6.605</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="15" t="inlineStr"/>
@@ -7013,28 +7013,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D145" s="10" t="n">
-        <v>1.44</v>
+        <v>3.98</v>
       </c>
       <c r="E145" s="11" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.0025</v>
       </c>
       <c r="F145" s="12" t="n">
-        <v>1071700</v>
+        <v>1092200</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="H145" t="n">
-        <v>70.33</v>
+        <v>57.44</v>
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
@@ -7042,10 +7042,10 @@
         </is>
       </c>
       <c r="J145" s="10" t="n">
-        <v>1.379</v>
+        <v>3.843</v>
       </c>
       <c r="K145" s="10" t="n">
-        <v>1.351</v>
+        <v>3.768</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="15" t="inlineStr"/>
@@ -7058,39 +7058,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>COMFORT</t>
         </is>
       </c>
       <c r="D146" s="10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E146" s="11" t="n">
-        <v>0.0279</v>
+        <v>0.205</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>1066400</v>
+        <v>1091100</v>
       </c>
       <c r="G146" s="13" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="H146" t="n">
-        <v>60.68</v>
-      </c>
-      <c r="I146" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.92</v>
+      </c>
+      <c r="I146" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="10" t="n">
-        <v>5.557</v>
+        <v>0.179</v>
       </c>
       <c r="K146" s="10" t="n">
-        <v>5.395</v>
+        <v>0.165</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -7103,39 +7103,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D147" s="10" t="n">
-        <v>2.26</v>
+        <v>5.89</v>
       </c>
       <c r="E147" s="11" t="n">
-        <v>0.0463</v>
+        <v>0.0261</v>
       </c>
       <c r="F147" s="12" t="n">
-        <v>1057100</v>
+        <v>1081400</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>0.79</v>
+        <v>0.25</v>
       </c>
       <c r="H147" t="n">
-        <v>58.91</v>
-      </c>
-      <c r="I147" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.47</v>
+      </c>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="10" t="n">
-        <v>2.136</v>
+        <v>5.556</v>
       </c>
       <c r="K147" s="10" t="n">
-        <v>2.222</v>
+        <v>5.394</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="15" t="inlineStr"/>
@@ -7148,39 +7148,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D148" s="10" t="n">
-        <v>5.19</v>
+        <v>2.42</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>0.0257</v>
+        <v>0.0083</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>1055400</v>
+        <v>1081100</v>
       </c>
       <c r="G148" s="13" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="H148" t="n">
-        <v>56.42</v>
-      </c>
-      <c r="I148" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.91</v>
+      </c>
+      <c r="I148" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="10" t="n">
-        <v>5.072</v>
+        <v>2.429</v>
       </c>
       <c r="K148" s="10" t="n">
-        <v>5.034</v>
+        <v>2.423</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -7193,39 +7193,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D149" s="10" t="n">
-        <v>0.265</v>
+        <v>0.2</v>
       </c>
       <c r="E149" s="11" t="n">
-        <v>0.0192</v>
+        <v>0.0256</v>
       </c>
       <c r="F149" s="12" t="n">
-        <v>1030500</v>
+        <v>1067900</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="H149" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="I149" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.79</v>
+      </c>
+      <c r="I149" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="10" t="n">
-        <v>0.268</v>
+        <v>0.207</v>
       </c>
       <c r="K149" s="10" t="n">
-        <v>0.29</v>
+        <v>0.226</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="15" t="inlineStr"/>
@@ -7238,39 +7238,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D150" s="10" t="n">
-        <v>0.375</v>
+        <v>2.28</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>0.0135</v>
+        <v>0.0556</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>1021900</v>
+        <v>1064100</v>
       </c>
       <c r="G150" s="13" t="n">
-        <v>0.41</v>
+        <v>0.79</v>
       </c>
       <c r="H150" t="n">
-        <v>45.96</v>
-      </c>
-      <c r="I150" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.12</v>
+      </c>
+      <c r="I150" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="10" t="n">
-        <v>0.381</v>
+        <v>2.138</v>
       </c>
       <c r="K150" s="10" t="n">
-        <v>0.386</v>
+        <v>2.223</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -7283,39 +7283,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D151" s="10" t="n">
-        <v>2.41</v>
+        <v>5.19</v>
       </c>
       <c r="E151" s="11" t="n">
-        <v>0.0042</v>
+        <v>0.0257</v>
       </c>
       <c r="F151" s="12" t="n">
-        <v>1011100</v>
+        <v>1056200</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H151" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="I151" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.42</v>
+      </c>
+      <c r="I151" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="10" t="n">
-        <v>2.428</v>
+        <v>5.072</v>
       </c>
       <c r="K151" s="10" t="n">
-        <v>2.423</v>
+        <v>5.034</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="15" t="inlineStr"/>
@@ -7328,39 +7328,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D152" s="10" t="n">
-        <v>6.78</v>
+        <v>0.265</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>0.0089</v>
+        <v>0.0192</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>960500</v>
+        <v>1050000</v>
       </c>
       <c r="G152" s="13" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="H152" t="n">
-        <v>37.87</v>
-      </c>
-      <c r="I152" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.29</v>
+      </c>
+      <c r="I152" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="10" t="n">
-        <v>6.995</v>
+        <v>0.268</v>
       </c>
       <c r="K152" s="10" t="n">
-        <v>7.451</v>
+        <v>0.29</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="15" t="inlineStr"/>
@@ -7373,39 +7373,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D153" s="10" t="n">
-        <v>0.615</v>
+        <v>0.38</v>
       </c>
       <c r="E153" s="11" t="n">
-        <v>0.0165</v>
+        <v>0.027</v>
       </c>
       <c r="F153" s="12" t="n">
-        <v>949600</v>
+        <v>1027900</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>0.2</v>
+        <v>0.41</v>
       </c>
       <c r="H153" t="n">
-        <v>66.22</v>
-      </c>
-      <c r="I153" s="17" t="inlineStr">
+        <v>48.5</v>
+      </c>
+      <c r="I153" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.555</v>
+        <v>0.382</v>
       </c>
       <c r="K153" s="10" t="n">
-        <v>0.492</v>
+        <v>0.386</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="15" t="inlineStr"/>
@@ -7418,39 +7418,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D154" s="10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E154" s="16" t="n">
-        <v>-0.0319</v>
+        <v>6.78</v>
+      </c>
+      <c r="E154" s="11" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>925100</v>
+        <v>974000</v>
       </c>
       <c r="G154" s="13" t="n">
-        <v>0.31</v>
+        <v>0.09</v>
       </c>
       <c r="H154" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="I154" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.87</v>
+      </c>
+      <c r="I154" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="10" t="n">
-        <v>1.812</v>
+        <v>6.995</v>
       </c>
       <c r="K154" s="10" t="n">
-        <v>1.909</v>
+        <v>7.451</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="15" t="inlineStr"/>
@@ -7463,28 +7463,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D155" s="10" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E155" s="11" t="n">
-        <v>0.0198</v>
+        <v>1.28</v>
+      </c>
+      <c r="E155" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="12" t="n">
-        <v>913300</v>
+        <v>971800</v>
       </c>
       <c r="G155" s="13" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="H155" t="n">
-        <v>59.65</v>
+        <v>54.67</v>
       </c>
       <c r="I155" s="14" t="inlineStr">
         <is>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="J155" s="10" t="n">
-        <v>0.493</v>
+        <v>1.255</v>
       </c>
       <c r="K155" s="10" t="n">
-        <v>0.485</v>
+        <v>1.13</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="15" t="inlineStr"/>
@@ -7508,39 +7508,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D156" s="10" t="n">
-        <v>2.97</v>
+        <v>0.61</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>0.0313</v>
+        <v>0.0083</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>906300</v>
+        <v>967600</v>
       </c>
       <c r="G156" s="13" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="H156" t="n">
-        <v>64.23</v>
-      </c>
-      <c r="I156" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.55</v>
+      </c>
+      <c r="I156" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="10" t="n">
-        <v>2.763</v>
+        <v>0.554</v>
       </c>
       <c r="K156" s="10" t="n">
-        <v>2.406</v>
+        <v>0.492</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="15" t="inlineStr"/>
@@ -7553,39 +7553,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D157" s="10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E157" s="11" t="n">
-        <v>0.028</v>
+        <v>1.82</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>-0.0319</v>
       </c>
       <c r="F157" s="12" t="n">
-        <v>899900</v>
+        <v>950400</v>
       </c>
       <c r="G157" s="13" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H157" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="I157" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.63</v>
+      </c>
+      <c r="I157" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="10" t="n">
-        <v>1.118</v>
+        <v>1.812</v>
       </c>
       <c r="K157" s="10" t="n">
-        <v>1.116</v>
+        <v>1.909</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="15" t="inlineStr"/>
@@ -7598,28 +7598,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0277</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CLOUDPT</t>
         </is>
       </c>
       <c r="D158" s="10" t="n">
-        <v>1.29</v>
+        <v>0.51</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>873600</v>
+        <v>943300</v>
       </c>
       <c r="G158" s="13" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="H158" t="n">
-        <v>55.45</v>
+        <v>58.08</v>
       </c>
       <c r="I158" s="14" t="inlineStr">
         <is>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="J158" s="10" t="n">
-        <v>1.256</v>
+        <v>0.493</v>
       </c>
       <c r="K158" s="10" t="n">
-        <v>1.13</v>
+        <v>0.485</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="15" t="inlineStr"/>
@@ -7643,39 +7643,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D159" s="10" t="n">
-        <v>0.68</v>
+        <v>2.96</v>
       </c>
       <c r="E159" s="11" t="n">
-        <v>0.0303</v>
+        <v>0.0278</v>
       </c>
       <c r="F159" s="12" t="n">
-        <v>795800</v>
+        <v>931500</v>
       </c>
       <c r="G159" s="13" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H159" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="I159" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.87</v>
+      </c>
+      <c r="I159" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="10" t="n">
-        <v>0.708</v>
+        <v>2.763</v>
       </c>
       <c r="K159" s="10" t="n">
-        <v>0.6919999999999999</v>
+        <v>2.405</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="15" t="inlineStr"/>
@@ -7688,39 +7688,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D160" s="10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E160" s="16" t="n">
-        <v>-0.0156</v>
+        <v>1.1</v>
+      </c>
+      <c r="E160" s="11" t="n">
+        <v>0.028</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>793600</v>
+        <v>906500</v>
       </c>
       <c r="G160" s="13" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="H160" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I160" s="17" t="inlineStr">
+        <v>47.27</v>
+      </c>
+      <c r="I160" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J160" s="10" t="n">
-        <v>3.287</v>
+        <v>1.118</v>
       </c>
       <c r="K160" s="10" t="n">
-        <v>3.519</v>
+        <v>1.116</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="15" t="inlineStr"/>
@@ -7733,28 +7733,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D161" s="10" t="n">
-        <v>0.545</v>
+        <v>1.58</v>
       </c>
       <c r="E161" s="11" t="n">
-        <v>0.0283</v>
+        <v>0.0064</v>
       </c>
       <c r="F161" s="12" t="n">
-        <v>786500</v>
+        <v>816500</v>
       </c>
       <c r="G161" s="13" t="n">
-        <v>0.25</v>
+        <v>1.02</v>
       </c>
       <c r="H161" t="n">
-        <v>45.68</v>
+        <v>33.15</v>
       </c>
       <c r="I161" s="14" t="inlineStr">
         <is>
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="J161" s="10" t="n">
-        <v>0.552</v>
+        <v>1.695</v>
       </c>
       <c r="K161" s="10" t="n">
-        <v>0.588</v>
+        <v>1.761</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="15" t="inlineStr"/>
@@ -7778,39 +7778,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D162" s="10" t="n">
-        <v>4.38</v>
+        <v>0.68</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>0.021</v>
+        <v>0.0303</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>772900</v>
+        <v>810800</v>
       </c>
       <c r="G162" s="13" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="H162" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="I162" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.79</v>
+      </c>
+      <c r="I162" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="10" t="n">
-        <v>4.333</v>
+        <v>0.708</v>
       </c>
       <c r="K162" s="10" t="n">
-        <v>4.592</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -7823,39 +7823,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D163" s="10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E163" s="11" t="n">
-        <v>0.0115</v>
+        <v>3.14</v>
+      </c>
+      <c r="E163" s="17" t="n">
+        <v>-0.0188</v>
       </c>
       <c r="F163" s="12" t="n">
-        <v>735800</v>
+        <v>793900</v>
       </c>
       <c r="G163" s="13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H163" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="I163" s="17" t="inlineStr">
+        <v>33.34</v>
+      </c>
+      <c r="I163" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J163" s="10" t="n">
-        <v>0.839</v>
+        <v>3.286</v>
       </c>
       <c r="K163" s="10" t="n">
-        <v>0.805</v>
+        <v>3.519</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="15" t="inlineStr"/>
@@ -7868,39 +7868,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D164" s="10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E164" s="16" t="n">
-        <v>-0.0154</v>
+        <v>0.545</v>
+      </c>
+      <c r="E164" s="11" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>729000</v>
+        <v>786500</v>
       </c>
       <c r="G164" s="13" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="H164" t="n">
-        <v>30.49</v>
-      </c>
-      <c r="I164" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.68</v>
+      </c>
+      <c r="I164" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="10" t="n">
-        <v>5.331</v>
+        <v>0.552</v>
       </c>
       <c r="K164" s="10" t="n">
-        <v>5.666</v>
+        <v>0.588</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -7913,28 +7913,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>9172</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>FPI</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D165" s="10" t="n">
-        <v>1.13</v>
+        <v>4.38</v>
       </c>
       <c r="E165" s="11" t="n">
-        <v>0.0273</v>
+        <v>0.021</v>
       </c>
       <c r="F165" s="12" t="n">
-        <v>688000</v>
+        <v>778000</v>
       </c>
       <c r="G165" s="13" t="n">
-        <v>1.95</v>
+        <v>0.19</v>
       </c>
       <c r="H165" t="n">
-        <v>60.32</v>
+        <v>49.74</v>
       </c>
       <c r="I165" s="14" t="inlineStr">
         <is>
@@ -7942,10 +7942,10 @@
         </is>
       </c>
       <c r="J165" s="10" t="n">
-        <v>1.088</v>
+        <v>4.333</v>
       </c>
       <c r="K165" s="10" t="n">
-        <v>1.1</v>
+        <v>4.592</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="15" t="inlineStr"/>
@@ -7958,28 +7958,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>KLK</t>
+          <t>FPI</t>
         </is>
       </c>
       <c r="D166" s="10" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="E166" s="18" t="n">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>0.0273</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>687300</v>
+        <v>770900</v>
       </c>
       <c r="G166" s="13" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="H166" t="n">
-        <v>43.48</v>
+        <v>60.32</v>
       </c>
       <c r="I166" s="14" t="inlineStr">
         <is>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="J166" s="10" t="n">
-        <v>20.767</v>
+        <v>1.088</v>
       </c>
       <c r="K166" s="10" t="n">
-        <v>21.619</v>
+        <v>1.1</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="15" t="inlineStr"/>
@@ -8003,39 +8003,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>EMPIRE</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D167" s="10" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E167" s="18" t="n">
-        <v>0</v>
+        <v>0.88</v>
+      </c>
+      <c r="E167" s="11" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F167" s="12" t="n">
-        <v>687100</v>
+        <v>745800</v>
       </c>
       <c r="G167" s="13" t="n">
-        <v>0.33</v>
+        <v>0.19</v>
       </c>
       <c r="H167" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="I167" s="17" t="inlineStr">
+        <v>60.48</v>
+      </c>
+      <c r="I167" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J167" s="10" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.839</v>
       </c>
       <c r="K167" s="10" t="n">
-        <v>0.869</v>
+        <v>0.805</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="15" t="inlineStr"/>
@@ -8048,39 +8048,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D168" s="10" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E168" s="11" t="n">
-        <v>0.0115</v>
+        <v>5.1</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>668000</v>
+        <v>729000</v>
       </c>
       <c r="G168" s="13" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="H168" t="n">
-        <v>45.68</v>
-      </c>
-      <c r="I168" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.49</v>
+      </c>
+      <c r="I168" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="10" t="n">
-        <v>0.888</v>
+        <v>5.331</v>
       </c>
       <c r="K168" s="10" t="n">
-        <v>0.901</v>
+        <v>5.666</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="15" t="inlineStr"/>
@@ -8093,39 +8093,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>EMPIRE</t>
         </is>
       </c>
       <c r="D169" s="10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E169" s="11" t="n">
-        <v>0.0308</v>
+        <v>0.79</v>
+      </c>
+      <c r="E169" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F169" s="12" t="n">
-        <v>658900</v>
+        <v>697600</v>
       </c>
       <c r="G169" s="13" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H169" t="n">
-        <v>54.94</v>
-      </c>
-      <c r="I169" s="17" t="inlineStr">
+        <v>39.89</v>
+      </c>
+      <c r="I169" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J169" s="10" t="n">
-        <v>1.3</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="K169" s="10" t="n">
-        <v>1.309</v>
+        <v>0.869</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="15" t="inlineStr"/>
@@ -8138,39 +8138,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>KLK</t>
         </is>
       </c>
       <c r="D170" s="10" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E170" s="11" t="n">
-        <v>0.0077</v>
+        <v>20.52</v>
+      </c>
+      <c r="E170" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>653200</v>
+        <v>687500</v>
       </c>
       <c r="G170" s="13" t="n">
-        <v>0.49</v>
+        <v>1.03</v>
       </c>
       <c r="H170" t="n">
-        <v>69.68000000000001</v>
-      </c>
-      <c r="I170" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.48</v>
+      </c>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="10" t="n">
-        <v>0.615</v>
+        <v>20.767</v>
       </c>
       <c r="K170" s="10" t="n">
-        <v>0.549</v>
+        <v>21.619</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -8183,39 +8183,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D171" s="10" t="n">
-        <v>1.57</v>
+        <v>0.655</v>
       </c>
       <c r="E171" s="11" t="n">
-        <v>0.0467</v>
+        <v>0.0077</v>
       </c>
       <c r="F171" s="12" t="n">
-        <v>648500</v>
+        <v>686200</v>
       </c>
       <c r="G171" s="13" t="n">
-        <v>0.39</v>
+        <v>0.51</v>
       </c>
       <c r="H171" t="n">
-        <v>49.71</v>
-      </c>
-      <c r="I171" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>69.68000000000001</v>
+      </c>
+      <c r="I171" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="10" t="n">
-        <v>1.554</v>
+        <v>0.615</v>
       </c>
       <c r="K171" s="10" t="n">
-        <v>1.628</v>
+        <v>0.549</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="15" t="inlineStr"/>
@@ -8228,28 +8228,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D172" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E172" s="18" t="n">
-        <v>0</v>
+        <v>0.885</v>
+      </c>
+      <c r="E172" s="11" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>645700</v>
+        <v>678000</v>
       </c>
       <c r="G172" s="13" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H172" t="n">
-        <v>40.89</v>
+        <v>47.48</v>
       </c>
       <c r="I172" s="14" t="inlineStr">
         <is>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="J172" s="10" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="K172" s="10" t="n">
-        <v>0.574</v>
+        <v>0.901</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -8273,39 +8273,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D173" s="10" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E173" s="16" t="n">
-        <v>-0.0217</v>
+        <v>1.34</v>
+      </c>
+      <c r="E173" s="11" t="n">
+        <v>0.0308</v>
       </c>
       <c r="F173" s="12" t="n">
-        <v>622900</v>
+        <v>662200</v>
       </c>
       <c r="G173" s="13" t="n">
-        <v>1.06</v>
+        <v>0.33</v>
       </c>
       <c r="H173" t="n">
-        <v>47.19</v>
-      </c>
-      <c r="I173" s="17" t="inlineStr">
+        <v>54.94</v>
+      </c>
+      <c r="I173" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J173" s="10" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="K173" s="10" t="n">
-        <v>0.664</v>
+        <v>1.309</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="15" t="inlineStr"/>
@@ -8318,39 +8318,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D174" s="10" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E174" s="11" t="n">
-        <v>0.0106</v>
+        <v>2.02</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>590200</v>
+        <v>656200</v>
       </c>
       <c r="G174" s="13" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="H174" t="n">
-        <v>44.28</v>
-      </c>
-      <c r="I174" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.43</v>
+      </c>
+      <c r="I174" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J174" s="10" t="n">
-        <v>0.951</v>
+        <v>2.036</v>
       </c>
       <c r="K174" s="10" t="n">
-        <v>1.027</v>
+        <v>2.06</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -8363,28 +8363,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D175" s="10" t="n">
-        <v>0.7</v>
+        <v>1.57</v>
       </c>
       <c r="E175" s="11" t="n">
-        <v>0.0072</v>
+        <v>0.0467</v>
       </c>
       <c r="F175" s="12" t="n">
-        <v>582600</v>
+        <v>649100</v>
       </c>
       <c r="G175" s="13" t="n">
-        <v>0.1</v>
+        <v>0.39</v>
       </c>
       <c r="H175" t="n">
-        <v>42.77</v>
+        <v>49.71</v>
       </c>
       <c r="I175" s="14" t="inlineStr">
         <is>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="J175" s="10" t="n">
-        <v>0.71</v>
+        <v>1.554</v>
       </c>
       <c r="K175" s="10" t="n">
-        <v>0.763</v>
+        <v>1.628</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="15" t="inlineStr"/>
@@ -8408,28 +8408,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D176" s="10" t="n">
-        <v>3.61</v>
+        <v>0.55</v>
       </c>
       <c r="E176" s="16" t="n">
-        <v>-0.011</v>
+        <v>0</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>574100</v>
+        <v>646900</v>
       </c>
       <c r="G176" s="13" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="H176" t="n">
-        <v>56.87</v>
+        <v>40.89</v>
       </c>
       <c r="I176" s="14" t="inlineStr">
         <is>
@@ -8437,10 +8437,10 @@
         </is>
       </c>
       <c r="J176" s="10" t="n">
-        <v>3.551</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K176" s="10" t="n">
-        <v>3.576</v>
+        <v>0.574</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="15" t="inlineStr"/>
@@ -8453,39 +8453,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D177" s="10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E177" s="18" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>-0.0217</v>
       </c>
       <c r="F177" s="12" t="n">
-        <v>542300</v>
+        <v>622900</v>
       </c>
       <c r="G177" s="13" t="n">
-        <v>0.23</v>
+        <v>1.06</v>
       </c>
       <c r="H177" t="n">
-        <v>40.38</v>
-      </c>
-      <c r="I177" s="17" t="inlineStr">
+        <v>47.19</v>
+      </c>
+      <c r="I177" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J177" s="10" t="n">
-        <v>1.119</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="K177" s="10" t="n">
-        <v>1.241</v>
+        <v>0.664</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="15" t="inlineStr"/>
@@ -8498,28 +8498,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PESONA</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D178" s="10" t="n">
-        <v>0.52</v>
+        <v>0.95</v>
       </c>
       <c r="E178" s="11" t="n">
-        <v>0.0505</v>
+        <v>0.0106</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>541200</v>
+        <v>607100</v>
       </c>
       <c r="G178" s="13" t="n">
-        <v>2.02</v>
+        <v>0.13</v>
       </c>
       <c r="H178" t="n">
-        <v>74.34999999999999</v>
+        <v>44.28</v>
       </c>
       <c r="I178" s="14" t="inlineStr">
         <is>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="J178" s="10" t="n">
-        <v>0.475</v>
+        <v>0.951</v>
       </c>
       <c r="K178" s="10" t="n">
-        <v>0.474</v>
+        <v>1.027</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="15" t="inlineStr"/>
@@ -8543,28 +8543,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D179" s="10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E179" s="11" t="n">
-        <v>0.0064</v>
+        <v>3.6</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F179" s="12" t="n">
-        <v>530500</v>
+        <v>582800</v>
       </c>
       <c r="G179" s="13" t="n">
-        <v>0.67</v>
+        <v>0.39</v>
       </c>
       <c r="H179" t="n">
-        <v>33.15</v>
+        <v>55.67</v>
       </c>
       <c r="I179" s="14" t="inlineStr">
         <is>
@@ -8572,10 +8572,10 @@
         </is>
       </c>
       <c r="J179" s="10" t="n">
-        <v>1.695</v>
+        <v>3.55</v>
       </c>
       <c r="K179" s="10" t="n">
-        <v>1.761</v>
+        <v>3.576</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="15" t="inlineStr"/>
@@ -8588,28 +8588,28 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AFFIN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D180" s="10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E180" s="16" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.7</v>
+      </c>
+      <c r="E180" s="11" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>530300</v>
+        <v>582600</v>
       </c>
       <c r="G180" s="13" t="n">
-        <v>0.72</v>
+        <v>0.1</v>
       </c>
       <c r="H180" t="n">
-        <v>54.51</v>
+        <v>42.77</v>
       </c>
       <c r="I180" s="14" t="inlineStr">
         <is>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="J180" s="10" t="n">
-        <v>1.975</v>
+        <v>0.71</v>
       </c>
       <c r="K180" s="10" t="n">
-        <v>2.013</v>
+        <v>0.763</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="15" t="inlineStr"/>
@@ -8633,39 +8633,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>KGB</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D181" s="10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="E181" s="11" t="n">
-        <v>0.0023</v>
+        <v>1.06</v>
+      </c>
+      <c r="E181" s="17" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F181" s="12" t="n">
-        <v>518800</v>
+        <v>562100</v>
       </c>
       <c r="G181" s="13" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H181" t="n">
-        <v>50.64</v>
-      </c>
-      <c r="I181" s="17" t="inlineStr">
+        <v>39.47</v>
+      </c>
+      <c r="I181" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J181" s="10" t="n">
-        <v>8.563000000000001</v>
+        <v>1.118</v>
       </c>
       <c r="K181" s="10" t="n">
-        <v>8.664</v>
+        <v>1.241</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="15" t="inlineStr"/>
@@ -8678,39 +8678,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>PESONA</t>
         </is>
       </c>
       <c r="D182" s="10" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E182" s="16" t="n">
-        <v>-0.0035</v>
+        <v>0.515</v>
+      </c>
+      <c r="E182" s="11" t="n">
+        <v>0.0404</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>516800</v>
+        <v>545700</v>
       </c>
       <c r="G182" s="13" t="n">
-        <v>0.4</v>
+        <v>2.04</v>
       </c>
       <c r="H182" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I182" s="17" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.05</v>
+      </c>
+      <c r="I182" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="10" t="n">
-        <v>2.878</v>
+        <v>0.475</v>
       </c>
       <c r="K182" s="10" t="n">
-        <v>3.007</v>
+        <v>0.474</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="15" t="inlineStr"/>
@@ -8723,39 +8723,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D183" s="10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E183" s="16" t="n">
-        <v>-0.008100000000000001</v>
+        <v>2.83</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F183" s="12" t="n">
-        <v>512900</v>
+        <v>545400</v>
       </c>
       <c r="G183" s="13" t="n">
-        <v>0.18</v>
+        <v>0.42</v>
       </c>
       <c r="H183" t="n">
-        <v>37.95</v>
-      </c>
-      <c r="I183" s="17" t="inlineStr">
+        <v>38.75</v>
+      </c>
+      <c r="I183" s="18" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J183" s="10" t="n">
-        <v>2.514</v>
+        <v>2.878</v>
       </c>
       <c r="K183" s="10" t="n">
-        <v>2.631</v>
+        <v>3.007</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="15" t="inlineStr"/>
@@ -8768,39 +8768,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>KGB</t>
         </is>
       </c>
       <c r="D184" s="10" t="n">
-        <v>2.19</v>
+        <v>8.6</v>
       </c>
       <c r="E184" s="11" t="n">
-        <v>0.0379</v>
+        <v>0.0023</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>511500</v>
+        <v>534800</v>
       </c>
       <c r="G184" s="13" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H184" t="n">
-        <v>56.74</v>
-      </c>
-      <c r="I184" s="14" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.64</v>
+      </c>
+      <c r="I184" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J184" s="10" t="n">
-        <v>2.092</v>
+        <v>8.563000000000001</v>
       </c>
       <c r="K184" s="10" t="n">
-        <v>2.008</v>
+        <v>8.664</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="15" t="inlineStr"/>
@@ -8813,28 +8813,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>AFFIN</t>
         </is>
       </c>
       <c r="D185" s="10" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E185" s="16" t="n">
-        <v>-0.0127</v>
+        <v>2</v>
+      </c>
+      <c r="E185" s="17" t="n">
+        <v>-0.0148</v>
       </c>
       <c r="F185" s="12" t="n">
-        <v>510800</v>
+        <v>533600</v>
       </c>
       <c r="G185" s="13" t="n">
-        <v>0.23</v>
+        <v>0.72</v>
       </c>
       <c r="H185" t="n">
-        <v>22.49</v>
+        <v>52.74</v>
       </c>
       <c r="I185" s="14" t="inlineStr">
         <is>
@@ -8842,16 +8842,196 @@
         </is>
       </c>
       <c r="J185" s="10" t="n">
-        <v>0.864</v>
+        <v>1.974</v>
       </c>
       <c r="K185" s="10" t="n">
-        <v>1.025</v>
+        <v>2.013</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="15" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D186" s="10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E186" s="17" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F186" s="12" t="n">
+        <v>514400</v>
+      </c>
+      <c r="G186" s="13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H186" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="I186" s="18" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="K186" s="10" t="n">
+        <v>2.631</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="15" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E187" s="11" t="n">
+        <v>0.04269999999999999</v>
+      </c>
+      <c r="F187" s="12" t="n">
+        <v>513700</v>
+      </c>
+      <c r="G187" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H187" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="I187" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="10" t="n">
+        <v>2.093</v>
+      </c>
+      <c r="K187" s="10" t="n">
+        <v>2.008</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="15" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D188" s="10" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="F188" s="12" t="n">
+        <v>512100</v>
+      </c>
+      <c r="G188" s="13" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H188" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="I188" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J188" s="10" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="K188" s="10" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="15" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F189" s="12" t="n">
+        <v>507000</v>
+      </c>
+      <c r="G189" s="13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H189" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="I189" s="14" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J189" s="10" t="n">
+        <v>13.113</v>
+      </c>
+      <c r="K189" s="10" t="n">
+        <v>13.277</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M185"/>
+  <autoFilter ref="A1:M189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>